--- a/全国交通事故データ.xlsx
+++ b/全国交通事故データ.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="253">
   <si>
     <t xml:space="preserve">このファイルについて</t>
   </si>
@@ -276,6 +276,33 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">マップを検索するリンクです。正確な事故地点ではありません</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・「緯度」「経度」は町名・交差点が分かるものはその付近、それ以外は市区町村の中心付近の概略値です（「位置の精度」列を参照）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Google </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">マイマップなどに読み込めます</t>
     </r>
   </si>
   <si>
@@ -406,6 +433,15 @@
     <t xml:space="preserve">備考</t>
   </si>
   <si>
+    <t xml:space="preserve">緯度</t>
+  </si>
+  <si>
+    <t xml:space="preserve">経度</t>
+  </si>
+  <si>
+    <t xml:space="preserve">位置の精度</t>
+  </si>
+  <si>
     <t xml:space="preserve">火</t>
   </si>
   <si>
@@ -528,6 +564,9 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">地点付近</t>
+  </si>
+  <si>
     <t xml:space="preserve">福岡県</t>
   </si>
   <si>
@@ -600,6 +639,9 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">市区町村の中心</t>
+  </si>
+  <si>
     <t xml:space="preserve">水</t>
   </si>
   <si>
@@ -751,6 +793,9 @@
     <t xml:space="preserve">NHK</t>
   </si>
   <si>
+    <t xml:space="preserve">町名付近</t>
+  </si>
+  <si>
     <t xml:space="preserve">木</t>
   </si>
   <si>
@@ -942,6 +987,9 @@
     <t xml:space="preserve">死者数・詳細は未確認</t>
   </si>
   <si>
+    <t xml:space="preserve">道路上（概略）</t>
+  </si>
+  <si>
     <t xml:space="preserve">神奈川県</t>
   </si>
   <si>
@@ -1224,6 +1272,9 @@
   </si>
   <si>
     <t xml:space="preserve">山口県警察（発表）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">市区町村内（概略）</t>
   </si>
   <si>
     <t xml:space="preserve">広島県</t>
@@ -3207,9 +3258,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="事故一覧" displayName="事故一覧" ref="A1:O28" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:O28"/>
-  <tableColumns count="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="事故一覧" displayName="事故一覧" ref="A1:R28" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:R28"/>
+  <tableColumns count="18">
     <tableColumn id="1" name="No"/>
     <tableColumn id="2" name="発生日"/>
     <tableColumn id="3" name="曜日"/>
@@ -3225,6 +3276,9 @@
     <tableColumn id="13" name="出典"/>
     <tableColumn id="14" name="出典URL"/>
     <tableColumn id="15" name="備考"/>
+    <tableColumn id="16" name="緯度"/>
+    <tableColumn id="17" name="経度"/>
+    <tableColumn id="18" name="位置の精度"/>
   </tableColumns>
 </table>
 </file>
@@ -3409,7 +3463,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="110"/>
@@ -3453,16 +3507,16 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2"/>
-    </row>
-    <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+    <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2"/>
+    </row>
+    <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3477,21 +3531,26 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2"/>
-    </row>
-    <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
+      <c r="A14" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2"/>
+    </row>
+    <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -3510,7 +3569,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:R31"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -3528,53 +3587,64 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="16" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3585,23 +3655,23 @@
         <v>46294</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G2" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%8D%83%E8%91%89%E7%9C%8C%E5%8D%83%E8%91%89%E5%B8%82%E4%B8%AD%E5%A4%AE%E5%8C%BA%20%E8%98%87%E6%88%91%20%E5%9B%BD%E9%81%93357%E5%8F%B7%E3%81%AE%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
         <v>地図</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I2" s="7" t="n">
         <v>3</v>
@@ -3610,19 +3680,28 @@
         <v>2</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L2" s="10" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="N2" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.jiji.com/jc/article?k=2026092900387&amp;g=soc","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O2" s="8"/>
+      <c r="P2" s="8" t="n">
+        <v>35.572</v>
+      </c>
+      <c r="Q2" s="8" t="n">
+        <v>140.128</v>
+      </c>
+      <c r="R2" s="8" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="n">
@@ -3632,42 +3711,51 @@
         <v>46294</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G3" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A6%8F%E5%B2%A1%E7%9C%8C%E7%B2%95%E5%B1%8B%E7%94%BA","地図")</f>
         <v>地図</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I3" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J3" s="7"/>
       <c r="K3" s="8" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="L3" s="10" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="N3" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.google.com/read/CBMif0FVX3lxTFBzdkhIY1I4QzRMN204dE5lRWV3aDBRellDMU92NjMtTWxhZ0xjLVhMbkZMR2tGdnBIZzhBOG1mT2lTQ1R6Rno0ZUxET0FkM3VKSk5VbzRTU0U3NDRPUXZQU3BwUXpIWGlhSmFMQXNzTUJGN2NVSk9SeXJTWEVEYVE","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O3" s="8"/>
+      <c r="P3" s="8" t="n">
+        <v>33.611</v>
+      </c>
+      <c r="Q3" s="8" t="n">
+        <v>130.481</v>
+      </c>
+      <c r="R3" s="8" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="n">
@@ -3677,42 +3765,51 @@
         <v>46295</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="G4" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%85%B5%E5%BA%AB%E7%9C%8C%E8%A5%BF%E5%AE%AE%E5%B8%82%20%E5%9B%BD%E9%81%932%E5%8F%B7","地図")</f>
         <v>地図</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="I4" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J4" s="7"/>
       <c r="K4" s="8" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="N4" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.kobe-np.co.jp/news/richa/koutsuujiko/202610/0020879803.shtml","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O4" s="8"/>
+      <c r="P4" s="8" t="n">
+        <v>34.737</v>
+      </c>
+      <c r="Q4" s="8" t="n">
+        <v>135.342</v>
+      </c>
+      <c r="R4" s="8" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="n">
@@ -3722,42 +3819,51 @@
         <v>46295</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G5" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E9%95%B7%E9%87%8E%E7%9C%8C%E4%B8%AD%E9%87%8E%E5%B8%82%20%E6%96%B0%E4%BA%95%20%E5%9B%BD%E9%81%93292%E5%8F%B7","地図")</f>
         <v>地図</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="I5" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J5" s="7"/>
       <c r="K5" s="8" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="L5" s="10" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="N5" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nb-1010039588","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O5" s="8"/>
+      <c r="P5" s="8" t="n">
+        <v>36.745</v>
+      </c>
+      <c r="Q5" s="8" t="n">
+        <v>138.395</v>
+      </c>
+      <c r="R5" s="8" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="n">
@@ -3767,23 +3873,23 @@
         <v>46296</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G6" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%85%B5%E5%BA%AB%E7%9C%8C%E7%A5%9E%E6%88%B8%E5%B8%82%E4%B8%AD%E5%A4%AE%E5%8C%BA%20%E4%B8%89%E5%AE%AE%20%E3%83%95%E3%83%A9%E3%83%AF%E3%83%BC%E3%83%AD%E3%83%BC%E3%83%89%E3%81%AE%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
         <v>地図</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="I6" s="7" t="n">
         <v>1</v>
@@ -3792,20 +3898,29 @@
         <v>3</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="L6" s="10" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="N6" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261001de53642","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>61</v>
+        <v>68</v>
+      </c>
+      <c r="P6" s="8" t="n">
+        <v>34.6935</v>
+      </c>
+      <c r="Q6" s="8" t="n">
+        <v>135.1955</v>
+      </c>
+      <c r="R6" s="8" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3816,41 +3931,50 @@
         <v>46296</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="G7" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%84%9B%E7%9F%A5%E7%9C%8C%E5%B2%A1%E5%B4%8E%E5%B8%82%20%E6%9D%B1%E5%90%8D%E9%AB%98%E9%80%9F%E9%81%93%E8%B7%AF%20%E4%B8%8B%E3%82%8A%E7%B7%9A","地図")</f>
         <v>地図</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
       <c r="K7" s="8" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="L7" s="12" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="N7" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.chunichi.co.jp/aichi_news","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O7" s="8" t="s">
-        <v>69</v>
+        <v>76</v>
+      </c>
+      <c r="P7" s="8" t="n">
+        <v>34.924</v>
+      </c>
+      <c r="Q7" s="8" t="n">
+        <v>137.204</v>
+      </c>
+      <c r="R7" s="8" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3861,23 +3985,23 @@
         <v>46296</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="G8" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A5%9E%E5%A5%88%E5%B7%9D%E7%9C%8C%E5%B7%9D%E5%B4%8E%E5%B8%82%E5%B7%9D%E5%B4%8E%E5%8C%BA%20%E6%9D%B1%E4%BA%AC%E6%B9%BE%E3%82%A2%E3%82%AF%E3%82%A2%E3%83%A9%E3%82%A4%E3%83%B3","地図")</f>
         <v>地図</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>2</v>
@@ -3886,19 +4010,28 @@
         <v>3</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="N8" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261001de53536","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O8" s="8"/>
+      <c r="P8" s="8" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="Q8" s="8" t="n">
+        <v>139.82</v>
+      </c>
+      <c r="R8" s="8" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="n">
@@ -3908,42 +4041,51 @@
         <v>46296</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G9" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E9%9D%92%E6%A3%AE%E7%9C%8C%E5%85%AB%E6%88%B8%E5%B8%82%20%E6%96%B0%E4%BA%95%E7%94%B0%20%E5%9B%BD%E9%81%9345%E5%8F%B7%E3%81%AE%E6%A8%AA%E6%96%AD%E6%AD%A9%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="I9" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J9" s="7"/>
       <c r="K9" s="8" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="N9" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nb-6080031283","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O9" s="8"/>
+      <c r="P9" s="8" t="n">
+        <v>40.487</v>
+      </c>
+      <c r="Q9" s="8" t="n">
+        <v>141.545</v>
+      </c>
+      <c r="R9" s="8" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="n">
@@ -3953,23 +4095,23 @@
         <v>46298</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="G10" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%8C%97%E6%B5%B7%E9%81%93%E5%AE%A4%E8%98%AD%E5%B8%82%20%E5%9B%BD%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="I10" s="7" t="n">
         <v>1</v>
@@ -3978,19 +4120,28 @@
         <v>2</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="L10" s="10" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="N10" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261004de54150","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O10" s="8"/>
+      <c r="P10" s="8" t="n">
+        <v>42.33</v>
+      </c>
+      <c r="Q10" s="8" t="n">
+        <v>140.98</v>
+      </c>
+      <c r="R10" s="8" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="n">
@@ -4000,43 +4151,52 @@
         <v>46298</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G11" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%A4%A7%E9%98%AA%E5%BA%9C%E5%A0%BA%E5%B8%82%E5%8C%97%E5%8C%BA%20%E5%8D%97%E8%8A%B1%E7%94%B0%E7%94%BA%E3%81%AE%E8%B7%AF%E4%B8%8A","地図")</f>
         <v>地図</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I11" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J11" s="7"/>
       <c r="K11" s="8" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="N11" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.police.pref.osaka.lg.jp/jiken/jiko/14349.html","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O11" s="8" t="s">
-        <v>92</v>
+        <v>100</v>
+      </c>
+      <c r="P11" s="8" t="n">
+        <v>34.567</v>
+      </c>
+      <c r="Q11" s="8" t="n">
+        <v>135.513</v>
+      </c>
+      <c r="R11" s="8" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4047,23 +4207,23 @@
         <v>46299</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="G12" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%B1%B1%E5%8F%A3%E7%9C%8C%E5%B1%B1%E5%8F%A3%E5%B8%82%20%E6%B1%9F%E5%B4%8E%E3%81%AE%E5%9B%BD%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="I12" s="7" t="n">
         <v>1</v>
@@ -4072,20 +4232,29 @@
         <v>3</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="L12" s="10" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="N12" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.pref.yamaguchi.lg.jp/site/police/151660.html","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O12" s="8" t="s">
-        <v>92</v>
+        <v>100</v>
+      </c>
+      <c r="P12" s="8" t="n">
+        <v>34.08</v>
+      </c>
+      <c r="Q12" s="8" t="n">
+        <v>131.4</v>
+      </c>
+      <c r="R12" s="8" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4096,43 +4265,52 @@
         <v>46299</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="G13" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%BA%83%E5%B3%B6%E7%9C%8C%E5%B0%BE%E9%81%93%E5%B8%82%20%E7%89%87%E5%81%B41%E8%BB%8A%E7%B7%9A%E3%81%AE%E7%9C%8C%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="I13" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J13" s="7"/>
       <c r="K13" s="8" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="N13" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.think-sp.com/2026/10/08/tw-jitensha-miotosi","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O13" s="8" t="s">
-        <v>107</v>
+        <v>116</v>
+      </c>
+      <c r="P13" s="8" t="n">
+        <v>34.409</v>
+      </c>
+      <c r="Q13" s="8" t="n">
+        <v>133.205</v>
+      </c>
+      <c r="R13" s="8" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4143,43 +4321,52 @@
         <v>46299</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="G14" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%BE%A4%E9%A6%AC%E7%9C%8C%E9%A4%A8%E6%9E%97%E5%B8%82%20%E7%9C%8C%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="I14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="11" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="L14" s="12" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="M14" s="8" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="N14" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.jomo-news.co.jp/subcategory/%E4%BA%8B%E4%BB%B6%E3%83%BB%E4%BA%8B%E6%95%85","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O14" s="8" t="s">
-        <v>113</v>
+        <v>122</v>
+      </c>
+      <c r="P14" s="8" t="n">
+        <v>36.245</v>
+      </c>
+      <c r="Q14" s="8" t="n">
+        <v>139.542</v>
+      </c>
+      <c r="R14" s="8" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4190,42 +4377,51 @@
         <v>46299</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="G15" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E8%8C%A8%E5%9F%8E%E7%9C%8C%E5%9C%9F%E6%B5%A6%E5%B8%82%20%E7%9C%8C%E9%81%93%E3%81%AE%E5%8D%81%E5%AD%97%E8%B7%AF","地図")</f>
         <v>地図</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="I15" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J15" s="7"/>
       <c r="K15" s="8" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M15" s="11" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="N15" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261005de54731","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O15" s="8"/>
+      <c r="P15" s="8" t="n">
+        <v>36.072</v>
+      </c>
+      <c r="Q15" s="8" t="n">
+        <v>140.198</v>
+      </c>
+      <c r="R15" s="8" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="n">
@@ -4235,42 +4431,51 @@
         <v>46299</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="G16" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E9%B3%A5%E5%8F%96%E7%9C%8C%E7%B1%B3%E5%AD%90%E5%B8%82%20%E5%9B%BD%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="I16" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J16" s="7"/>
       <c r="K16" s="11" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="L16" s="10" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M16" s="11" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="N16" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261004de54296","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O16" s="8"/>
+      <c r="P16" s="8" t="n">
+        <v>35.428</v>
+      </c>
+      <c r="Q16" s="8" t="n">
+        <v>133.331</v>
+      </c>
+      <c r="R16" s="8" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="n">
@@ -4280,23 +4485,23 @@
         <v>46300</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="G17" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%B1%B1%E5%BD%A2%E7%9C%8C%E9%B6%B4%E5%B2%A1%E5%B8%82%20%E7%9C%8C%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="I17" s="7" t="n">
         <v>1</v>
@@ -4305,19 +4510,28 @@
         <v>3</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M17" s="11" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="N17" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261006de54976","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O17" s="8"/>
+      <c r="P17" s="8" t="n">
+        <v>38.727</v>
+      </c>
+      <c r="Q17" s="8" t="n">
+        <v>139.827</v>
+      </c>
+      <c r="R17" s="8" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="n">
@@ -4327,23 +4541,23 @@
         <v>46300</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="G18" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%B2%96%E7%B8%84%E7%9C%8C%E9%82%A3%E8%A6%87%E5%B8%82%20%E9%A6%96%E9%87%8C%E6%9C%AB%E5%90%89%E7%94%BA%20%E7%9C%8C%E9%81%9382%E5%8F%B7%E3%81%AE%E4%BF%A1%E5%8F%B7%E3%81%AE%E3%81%82%E3%82%8B%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
         <v>地図</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="I18" s="7" t="n">
         <v>1</v>
@@ -4352,19 +4566,28 @@
         <v>1</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="L18" s="10" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M18" s="8" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="N18" s="9" t="str">
         <f aca="false">HYPERLINK("https://ryukyushimpo.jp/national/entry-5538964.html","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O18" s="8"/>
+      <c r="P18" s="8" t="n">
+        <v>26.226</v>
+      </c>
+      <c r="Q18" s="8" t="n">
+        <v>127.71</v>
+      </c>
+      <c r="R18" s="8" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="n">
@@ -4374,23 +4597,23 @@
         <v>46301</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="G19" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%B2%90%E9%98%9C%E7%9C%8C%E5%B2%90%E9%98%9C%E5%B8%82%20%E9%87%91%E8%8F%AF%E5%B1%B1%E3%83%89%E3%83%A9%E3%82%A4%E3%83%96%E3%82%A6%E3%82%A7%E3%82%A4%E3%81%AE%E3%83%98%E3%82%A2%E3%83%94%E3%83%B3%E3%82%AB%E3%83%BC%E3%83%96","地図")</f>
         <v>地図</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="I19" s="7" t="n">
         <v>1</v>
@@ -4399,19 +4622,28 @@
         <v>1</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="L19" s="10" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M19" s="11" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="N19" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/50988fd3cbfff6e6a97e45b98587bf9db84c27b3","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O19" s="8"/>
+      <c r="P19" s="8" t="n">
+        <v>35.433</v>
+      </c>
+      <c r="Q19" s="8" t="n">
+        <v>136.786</v>
+      </c>
+      <c r="R19" s="8" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="n">
@@ -4421,43 +4653,52 @@
         <v>46301</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="G20" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A5%9E%E5%A5%88%E5%B7%9D%E7%9C%8C%E9%8E%8C%E5%80%89%E5%B8%82","地図")</f>
         <v>地図</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="I20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="8" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="M20" s="8" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="N20" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.kanaloco.jp/news/social/case","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O20" s="8" t="s">
-        <v>142</v>
+        <v>151</v>
+      </c>
+      <c r="P20" s="8" t="n">
+        <v>35.319</v>
+      </c>
+      <c r="Q20" s="8" t="n">
+        <v>139.547</v>
+      </c>
+      <c r="R20" s="8" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4468,42 +4709,51 @@
         <v>46301</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="G21" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E9%9D%99%E5%B2%A1%E7%9C%8C%E5%BE%A1%E6%AE%BF%E5%A0%B4%E5%B8%82%20%E5%9B%BD%E9%81%93138%E5%8F%B7","地図")</f>
         <v>地図</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="I21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="8" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="L21" s="10" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="N21" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/3b0fd061a9e7f49b11a18228d212989cc0b2a40a","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O21" s="8"/>
+      <c r="P21" s="8" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="Q21" s="8" t="n">
+        <v>138.95</v>
+      </c>
+      <c r="R21" s="8" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="n">
@@ -4513,42 +4763,51 @@
         <v>46302</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="G22" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%85%B5%E5%BA%AB%E7%9C%8C%E4%BC%8A%E4%B8%B9%E5%B8%82%20%E5%8D%97%E6%9C%AC%E7%94%BA4%E4%B8%81%E7%9B%AE%20%E7%9C%8C%E9%81%93%E3%81%AE%E4%BF%A1%E5%8F%B7%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
         <v>地図</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="I22" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="8" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="L22" s="10" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M22" s="8" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="N22" s="9" t="str">
         <f aca="false">HYPERLINK("https://kobe-np.co.jp/news/richa/koutsuujiko/202610/0020905694.shtml","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O22" s="8"/>
+      <c r="P22" s="8" t="n">
+        <v>34.774</v>
+      </c>
+      <c r="Q22" s="8" t="n">
+        <v>135.405</v>
+      </c>
+      <c r="R22" s="8" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="n">
@@ -4558,42 +4817,51 @@
         <v>46302</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="G23" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%85%B5%E5%BA%AB%E7%9C%8C%E9%AB%98%E7%A0%82%E5%B8%82%20%E6%9B%BD%E6%A0%B9%E7%94%BA%20%E7%9C%8C%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="I23" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J23" s="7"/>
       <c r="K23" s="8" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="L23" s="10" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="N23" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.kobe-np.co.jp/news/richa/koutsuujiko/202610/0020903821.shtml","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O23" s="8"/>
+      <c r="P23" s="8" t="n">
+        <v>34.767</v>
+      </c>
+      <c r="Q23" s="8" t="n">
+        <v>134.775</v>
+      </c>
+      <c r="R23" s="8" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="n">
@@ -4603,23 +4871,23 @@
         <v>46302</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="G24" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%9F%BC%E7%8E%89%E7%9C%8C%E3%81%B5%E3%81%98%E3%81%BF%E9%87%8E%E5%B8%82%20%E3%81%86%E3%82%8C%E3%81%97%E9%87%8E1%E4%B8%81%E7%9B%AE%20%E7%9C%8C%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="I24" s="7" t="n">
         <v>1</v>
@@ -4628,19 +4896,28 @@
         <v>1</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="L24" s="10" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M24" s="11" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="N24" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261007de56188","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O24" s="8"/>
+      <c r="P24" s="8" t="n">
+        <v>35.88</v>
+      </c>
+      <c r="Q24" s="8" t="n">
+        <v>139.535</v>
+      </c>
+      <c r="R24" s="8" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="n">
@@ -4650,42 +4927,51 @@
         <v>46303</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="G25" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%8C%97%E6%B5%B7%E9%81%93%E6%97%AD%E5%B7%9D%E5%B8%82%20%E7%A5%9E%E6%A5%BD%E5%B2%A16%E6%9D%A16%E4%B8%81%E7%9B%AE%20%E5%B8%82%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="I25" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J25" s="7"/>
       <c r="K25" s="11" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="L25" s="10" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M25" s="8" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="N25" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/0f9db2f6fa5fe325add09fc111cb3852d3730e34","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O25" s="8"/>
+      <c r="P25" s="8" t="n">
+        <v>43.748</v>
+      </c>
+      <c r="Q25" s="8" t="n">
+        <v>142.383</v>
+      </c>
+      <c r="R25" s="8" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="n">
@@ -4695,43 +4981,52 @@
         <v>46303</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="G26" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%86%8A%E6%9C%AC%E7%9C%8C%E7%86%8A%E6%9C%AC%E5%B8%82","地図")</f>
         <v>地図</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="I26" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J26" s="7"/>
       <c r="K26" s="8" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="M26" s="8" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="N26" s="9" t="str">
         <f aca="false">HYPERLINK("https://kumanichi.com/articles/2044555","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O26" s="8" t="s">
-        <v>172</v>
+        <v>181</v>
+      </c>
+      <c r="P26" s="8" t="n">
+        <v>32.803</v>
+      </c>
+      <c r="Q26" s="8" t="n">
+        <v>130.708</v>
+      </c>
+      <c r="R26" s="8" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4742,43 +5037,52 @@
         <v>46303</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="G27" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A6%8F%E5%B2%A1%E7%9C%8C%E5%B7%9D%E5%B4%8E%E7%94%BA%EF%BC%88%E7%94%B0%E5%B7%9D%E9%83%A1%EF%BC%89","地図")</f>
         <v>地図</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="I27" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J27" s="7"/>
       <c r="K27" s="8" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="M27" s="8" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="N27" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.nishinippon.co.jp/category/kyushu/flash/","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O27" s="8" t="s">
-        <v>172</v>
+        <v>181</v>
+      </c>
+      <c r="P27" s="8" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="Q27" s="8" t="n">
+        <v>130.815</v>
+      </c>
+      <c r="R27" s="8" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4789,55 +5093,64 @@
         <v>46303</v>
       </c>
       <c r="C28" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D28" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="D28" s="8" t="s">
-        <v>49</v>
-      </c>
       <c r="E28" s="8" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="G28" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E9%95%B7%E9%87%8E%E7%9C%8C%E6%9D%BE%E6%9C%AC%E5%B8%82%20%E4%BF%A1%E5%8F%B7%E3%81%AE%E3%81%AA%E3%81%84%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
         <v>地図</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="I28" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J28" s="7"/>
       <c r="K28" s="8" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="M28" s="11" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="N28" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.nbs-tv.co.jp/news/","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O28" s="8" t="s">
-        <v>182</v>
+        <v>191</v>
+      </c>
+      <c r="P28" s="8" t="n">
+        <v>36.238</v>
+      </c>
+      <c r="Q28" s="8" t="n">
+        <v>137.972</v>
+      </c>
+      <c r="R28" s="8" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="14" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="B30" s="14" t="str">
         <f aca="false">COUNTA(D2:D28)&amp;"件"</f>
         <v>27件</v>
       </c>
       <c r="H30" s="14" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="I30" s="14" t="n">
         <f aca="false">SUM(I2:I28)</f>
@@ -4850,7 +5163,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -4882,18 +5195,18 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B2" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A2)</f>
@@ -4906,7 +5219,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="B3" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A3)</f>
@@ -4919,7 +5232,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="B4" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A4)</f>
@@ -4932,7 +5245,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="B5" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A5)</f>
@@ -4945,7 +5258,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B6" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A6)</f>
@@ -4958,7 +5271,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="B7" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A7)</f>
@@ -4971,7 +5284,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="B8" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A8)</f>
@@ -4984,7 +5297,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B9" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A9)</f>
@@ -4997,7 +5310,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B10" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A10)</f>
@@ -5010,7 +5323,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B11" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A11)</f>
@@ -5023,7 +5336,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="B12" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A12)</f>
@@ -5036,7 +5349,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B13" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A13)</f>
@@ -5049,7 +5362,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="B14" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A14)</f>
@@ -5062,7 +5375,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B15" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A15)</f>
@@ -5075,7 +5388,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="16" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="B16" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A16)</f>
@@ -5088,7 +5401,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="B17" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A17)</f>
@@ -5101,7 +5414,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="16" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="B18" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A18)</f>
@@ -5114,7 +5427,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="16" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="B19" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A19)</f>
@@ -5127,7 +5440,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="B20" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A20)</f>
@@ -5140,7 +5453,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="16" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B21" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A21)</f>
@@ -5153,7 +5466,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="16" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="B22" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A22)</f>
@@ -5166,7 +5479,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="16" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="B23" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A23)</f>
@@ -5179,7 +5492,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="16" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B24" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A24)</f>
@@ -5192,7 +5505,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="16" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B25" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A25)</f>
@@ -5205,7 +5518,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="16" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="B26" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A26)</f>
@@ -5218,7 +5531,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="16" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="B27" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A27)</f>
@@ -5231,7 +5544,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="16" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="B28" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A28)</f>
@@ -5244,7 +5557,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="16" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B29" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A29)</f>
@@ -5257,7 +5570,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="16" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="B30" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A30)</f>
@@ -5270,7 +5583,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="16" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="B31" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A31)</f>
@@ -5283,7 +5596,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="16" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B32" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A32)</f>
@@ -5296,7 +5609,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="16" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="B33" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A33)</f>
@@ -5309,7 +5622,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="16" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="B34" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A34)</f>
@@ -5322,7 +5635,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="16" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="B35" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A35)</f>
@@ -5335,7 +5648,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="16" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B36" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A36)</f>
@@ -5348,7 +5661,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="16" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="B37" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A37)</f>
@@ -5361,7 +5674,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="16" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="B38" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A38)</f>
@@ -5374,7 +5687,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="16" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="B39" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A39)</f>
@@ -5387,7 +5700,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="16" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="B40" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A40)</f>
@@ -5400,7 +5713,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="16" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B41" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A41)</f>
@@ -5413,7 +5726,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="16" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="B42" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A42)</f>
@@ -5426,7 +5739,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="16" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="B43" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A43)</f>
@@ -5439,7 +5752,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="16" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="B44" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A44)</f>
@@ -5452,7 +5765,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="16" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="B45" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A45)</f>
@@ -5465,7 +5778,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="16" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="B46" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A46)</f>
@@ -5478,7 +5791,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="16" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="B47" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A47)</f>
@@ -5491,7 +5804,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="16" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B48" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A48)</f>
@@ -5504,7 +5817,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="14" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="B49" s="14" t="n">
         <f aca="false">SUM(B2:B48)</f>
@@ -5542,16 +5855,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5559,7 +5872,7 @@
         <v>46294</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C2" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$B$2:$B$28,A2)</f>
@@ -5575,7 +5888,7 @@
         <v>46295</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C3" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$B$2:$B$28,A3)</f>
@@ -5591,7 +5904,7 @@
         <v>46296</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C4" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$B$2:$B$28,A4)</f>
@@ -5607,7 +5920,7 @@
         <v>46297</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="C5" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$B$2:$B$28,A5)</f>
@@ -5623,7 +5936,7 @@
         <v>46298</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C6" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$B$2:$B$28,A6)</f>
@@ -5639,7 +5952,7 @@
         <v>46299</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="C7" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$B$2:$B$28,A7)</f>
@@ -5655,7 +5968,7 @@
         <v>46300</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="C8" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$B$2:$B$28,A8)</f>
@@ -5671,7 +5984,7 @@
         <v>46301</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C9" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$B$2:$B$28,A9)</f>
@@ -5687,7 +6000,7 @@
         <v>46302</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C10" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$B$2:$B$28,A10)</f>
@@ -5703,7 +6016,7 @@
         <v>46303</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C11" s="16" t="n">
         <f aca="false">COUNTIF(事故一覧!$B$2:$B$28,A11)</f>
@@ -5716,7 +6029,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="B12" s="14"/>
       <c r="C12" s="14" t="n">
@@ -5759,28 +6072,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5788,22 +6101,22 @@
         <v>46299</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="H2" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261005de54398","記事を開く")</f>
@@ -5815,22 +6128,22 @@
         <v>46300</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="H3" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.kanaloco.jp/news/social/case","記事を開く")</f>
@@ -5842,22 +6155,22 @@
         <v>46301</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="H4" s="9" t="str">
         <f aca="false">HYPERLINK("https://chunichi.co.jp/article/1321634","記事を開く")</f>
@@ -5869,22 +6182,22 @@
         <v>46303</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="H5" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/7fb30b9e75ecfd206159127fe8dfd2e4f5581de1","記事を開く")</f>
@@ -5896,22 +6209,22 @@
         <v>46303</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H6" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/7d3b2684f57408afa39b1ea0ea5ad798fc8e659f","記事を開く")</f>
@@ -5923,22 +6236,22 @@
         <v>46303</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="H7" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.nbs-tv.co.jp/news/","記事を開く")</f>

--- a/全国交通事故データ.xlsx
+++ b/全国交通事故データ.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="263">
   <si>
     <t xml:space="preserve">このファイルについて</t>
   </si>
@@ -129,7 +129,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
     <r>
       <rPr>
@@ -2523,6 +2523,98 @@
     <t xml:space="preserve">発生日は掲載日から推定（前日の可能性あり）</t>
   </si>
   <si>
+    <t xml:space="preserve">金</t>
+  </si>
+  <si>
+    <t xml:space="preserve">新座市</t>
+  </si>
+  <si>
+    <t xml:space="preserve">栗原の市道</t>
+  </si>
+  <si>
+    <t xml:space="preserve">人対車両（左折車）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日未明、左折した乗用車が道路上の男性（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳の大学生）をひき、男性は病院で死亡。運転の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">78</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳の男を過失運転致傷の疑いで現行犯逮捕</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">テレ玉（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Yahoo!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ニュース配信）</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">合計</t>
   </si>
   <si>
@@ -2622,9 +2714,6 @@
     <t xml:space="preserve">日付</t>
   </si>
   <si>
-    <t xml:space="preserve">金</t>
-  </si>
-  <si>
     <t xml:space="preserve">場所</t>
   </si>
   <si>
@@ -2889,6 +2978,21 @@
       </rPr>
       <t xml:space="preserve">歳男性が死亡</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">西脇市</t>
+  </si>
+  <si>
+    <t xml:space="preserve">斎場の駐車場</t>
+  </si>
+  <si>
+    <t xml:space="preserve">道路外（駐車場から転落）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">車が斎場の駐車場から転落し、運転の男性が死亡、同乗の女性が重傷とみられる（発生日は掲載から推定）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">神戸新聞</t>
   </si>
 </sst>
 </file>
@@ -3258,8 +3362,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="事故一覧" displayName="事故一覧" ref="A1:R28" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:R28"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="事故一覧" displayName="事故一覧" ref="A1:R29" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:R29"/>
   <tableColumns count="18">
     <tableColumn id="1" name="No"/>
     <tableColumn id="2" name="発生日"/>
@@ -3569,7 +3673,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R31"/>
+  <dimension ref="A1:R32"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -5141,29 +5245,83 @@
         <v>47</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="14" t="s">
+    <row r="29" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>46304</v>
+      </c>
+      <c r="C29" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="B30" s="14" t="str">
-        <f aca="false">COUNTA(D2:D28)&amp;"件"</f>
-        <v>27件</v>
-      </c>
-      <c r="H30" s="14" t="s">
+      <c r="D29" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="E29" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="I30" s="14" t="n">
-        <f aca="false">SUM(I2:I28)</f>
-        <v>29</v>
-      </c>
-      <c r="J30" s="14" t="n">
-        <f aca="false">SUM(J2:J28)</f>
+      <c r="F29" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="G29" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%9F%BC%E7%8E%89%E7%9C%8C%E6%96%B0%E5%BA%A7%E5%B8%82%20%E6%A0%97%E5%8E%9F%E3%81%AE%E5%B8%82%E9%81%93","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="I29" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" s="7"/>
+      <c r="K29" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="L29" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M29" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="N29" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/aad5e62c6ab660cb6e49eb85990d0040b1ed24c0","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O29" s="8"/>
+      <c r="P29" s="8" t="n">
+        <v>35.797</v>
+      </c>
+      <c r="Q29" s="8" t="n">
+        <v>139.558</v>
+      </c>
+      <c r="R29" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="B31" s="14" t="str">
+        <f aca="false">COUNTA(D2:D29)&amp;"件"</f>
+        <v>28件</v>
+      </c>
+      <c r="H31" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="I31" s="14" t="n">
+        <f aca="false">SUM(I2:I29)</f>
+        <v>30</v>
+      </c>
+      <c r="J31" s="14" t="n">
+        <f aca="false">SUM(J2:J29)</f>
         <v>19</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="15" t="s">
-        <v>194</v>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="15" t="s">
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -5198,10 +5356,10 @@
         <v>18</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5209,11 +5367,11 @@
         <v>89</v>
       </c>
       <c r="B2" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A2)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A2)</f>
         <v>2</v>
       </c>
       <c r="C2" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A2,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A2,事故一覧!$I$2:$I$29)</f>
         <v>2</v>
       </c>
     </row>
@@ -5222,50 +5380,50 @@
         <v>83</v>
       </c>
       <c r="B3" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A3)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A3)</f>
         <v>1</v>
       </c>
       <c r="C3" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A3,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A3,事故一覧!$I$2:$I$29)</f>
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B4" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A4)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A4)</f>
         <v>0</v>
       </c>
       <c r="C4" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A4,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A4,事故一覧!$I$2:$I$29)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B5" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A5)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A5)</f>
         <v>0</v>
       </c>
       <c r="C5" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A5,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A5,事故一覧!$I$2:$I$29)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="B6" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A6)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A6)</f>
         <v>0</v>
       </c>
       <c r="C6" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A6,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A6,事故一覧!$I$2:$I$29)</f>
         <v>0</v>
       </c>
     </row>
@@ -5274,24 +5432,24 @@
         <v>132</v>
       </c>
       <c r="B7" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A7)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A7)</f>
         <v>1</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A7,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A7,事故一覧!$I$2:$I$29)</f>
         <v>1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="B8" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A8)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A8)</f>
         <v>0</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A8,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A8,事故一覧!$I$2:$I$29)</f>
         <v>0</v>
       </c>
     </row>
@@ -5300,24 +5458,24 @@
         <v>123</v>
       </c>
       <c r="B9" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A9)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A9)</f>
         <v>1</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A9,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A9,事故一覧!$I$2:$I$29)</f>
         <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B10" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A10)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A10)</f>
         <v>0</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A10,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A10,事故一覧!$I$2:$I$29)</f>
         <v>0</v>
       </c>
     </row>
@@ -5326,11 +5484,11 @@
         <v>117</v>
       </c>
       <c r="B11" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A11)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A11)</f>
         <v>1</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A11,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A11,事故一覧!$I$2:$I$29)</f>
         <v>1</v>
       </c>
     </row>
@@ -5339,12 +5497,12 @@
         <v>166</v>
       </c>
       <c r="B12" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A12)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A12)</f>
+        <v>2</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A12,事故一覧!$I$2:$I$28)</f>
-        <v>1</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A12,事故一覧!$I$2:$I$29)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5352,24 +5510,24 @@
         <v>34</v>
       </c>
       <c r="B13" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A13)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A13)</f>
         <v>1</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A13,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A13,事故一覧!$I$2:$I$29)</f>
         <v>3</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B14" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A14)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A14)</f>
         <v>0</v>
       </c>
       <c r="C14" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A14,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A14,事故一覧!$I$2:$I$29)</f>
         <v>0</v>
       </c>
     </row>
@@ -5378,76 +5536,76 @@
         <v>78</v>
       </c>
       <c r="B15" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A15)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A15)</f>
         <v>2</v>
       </c>
       <c r="C15" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A15,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A15,事故一覧!$I$2:$I$29)</f>
         <v>3</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="16" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B16" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A16)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A16)</f>
         <v>0</v>
       </c>
       <c r="C16" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A16,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A16,事故一覧!$I$2:$I$29)</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="B17" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A17)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A17)</f>
         <v>0</v>
       </c>
       <c r="C17" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A17,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A17,事故一覧!$I$2:$I$29)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="16" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B18" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A18)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A18)</f>
         <v>0</v>
       </c>
       <c r="C18" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A18,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A18,事故一覧!$I$2:$I$29)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="16" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B19" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A19)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A19)</f>
         <v>0</v>
       </c>
       <c r="C19" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A19,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A19,事故一覧!$I$2:$I$29)</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="B20" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A20)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A20)</f>
         <v>0</v>
       </c>
       <c r="C20" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A20,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A20,事故一覧!$I$2:$I$29)</f>
         <v>0</v>
       </c>
     </row>
@@ -5456,11 +5614,11 @@
         <v>55</v>
       </c>
       <c r="B21" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A21)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A21)</f>
         <v>2</v>
       </c>
       <c r="C21" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A21,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A21,事故一覧!$I$2:$I$29)</f>
         <v>2</v>
       </c>
     </row>
@@ -5469,11 +5627,11 @@
         <v>141</v>
       </c>
       <c r="B22" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A22)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A22)</f>
         <v>1</v>
       </c>
       <c r="C22" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A22,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A22,事故一覧!$I$2:$I$29)</f>
         <v>1</v>
       </c>
     </row>
@@ -5482,11 +5640,11 @@
         <v>152</v>
       </c>
       <c r="B23" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A23)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A23)</f>
         <v>1</v>
       </c>
       <c r="C23" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A23,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A23,事故一覧!$I$2:$I$29)</f>
         <v>1</v>
       </c>
     </row>
@@ -5495,50 +5653,50 @@
         <v>69</v>
       </c>
       <c r="B24" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A24)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A24)</f>
         <v>1</v>
       </c>
       <c r="C24" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A24,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A24,事故一覧!$I$2:$I$29)</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="16" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B25" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A25)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A25)</f>
         <v>0</v>
       </c>
       <c r="C25" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A25,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A25,事故一覧!$I$2:$I$29)</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="16" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B26" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A26)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A26)</f>
         <v>0</v>
       </c>
       <c r="C26" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A26,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A26,事故一覧!$I$2:$I$29)</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="16" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="B27" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A27)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A27)</f>
         <v>0</v>
       </c>
       <c r="C27" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A27,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A27,事故一覧!$I$2:$I$29)</f>
         <v>0</v>
       </c>
     </row>
@@ -5547,11 +5705,11 @@
         <v>94</v>
       </c>
       <c r="B28" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A28)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A28)</f>
         <v>1</v>
       </c>
       <c r="C28" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A28,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A28,事故一覧!$I$2:$I$29)</f>
         <v>1</v>
       </c>
     </row>
@@ -5560,37 +5718,37 @@
         <v>49</v>
       </c>
       <c r="B29" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A29)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A29)</f>
         <v>4</v>
       </c>
       <c r="C29" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A29,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A29,事故一覧!$I$2:$I$29)</f>
         <v>4</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="16" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B30" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A30)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A30)</f>
         <v>0</v>
       </c>
       <c r="C30" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A30,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A30,事故一覧!$I$2:$I$29)</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="16" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B31" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A31)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A31)</f>
         <v>0</v>
       </c>
       <c r="C31" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A31,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A31,事故一覧!$I$2:$I$29)</f>
         <v>0</v>
       </c>
     </row>
@@ -5599,37 +5757,37 @@
         <v>128</v>
       </c>
       <c r="B32" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A32)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A32)</f>
         <v>1</v>
       </c>
       <c r="C32" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A32,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A32,事故一覧!$I$2:$I$29)</f>
         <v>1</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="16" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B33" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A33)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A33)</f>
         <v>0</v>
       </c>
       <c r="C33" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A33,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A33,事故一覧!$I$2:$I$29)</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="16" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B34" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A34)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A34)</f>
         <v>0</v>
       </c>
       <c r="C34" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A34,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A34,事故一覧!$I$2:$I$29)</f>
         <v>0</v>
       </c>
     </row>
@@ -5638,11 +5796,11 @@
         <v>109</v>
       </c>
       <c r="B35" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A35)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A35)</f>
         <v>1</v>
       </c>
       <c r="C35" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A35,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A35,事故一覧!$I$2:$I$29)</f>
         <v>1</v>
       </c>
     </row>
@@ -5651,63 +5809,63 @@
         <v>102</v>
       </c>
       <c r="B36" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A36)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A36)</f>
         <v>1</v>
       </c>
       <c r="C36" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A36,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A36,事故一覧!$I$2:$I$29)</f>
         <v>1</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="16" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B37" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A37)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A37)</f>
         <v>0</v>
       </c>
       <c r="C37" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A37,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A37,事故一覧!$I$2:$I$29)</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="16" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="B38" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A38)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A38)</f>
         <v>0</v>
       </c>
       <c r="C38" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A38,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A38,事故一覧!$I$2:$I$29)</f>
         <v>0</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="16" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B39" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A39)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A39)</f>
         <v>0</v>
       </c>
       <c r="C39" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A39,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A39,事故一覧!$I$2:$I$29)</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="16" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B40" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A40)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A40)</f>
         <v>0</v>
       </c>
       <c r="C40" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A40,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A40,事故一覧!$I$2:$I$29)</f>
         <v>0</v>
       </c>
     </row>
@@ -5716,37 +5874,37 @@
         <v>42</v>
       </c>
       <c r="B41" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A41)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A41)</f>
         <v>2</v>
       </c>
       <c r="C41" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A41,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A41,事故一覧!$I$2:$I$29)</f>
         <v>2</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="16" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B42" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A42)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A42)</f>
         <v>0</v>
       </c>
       <c r="C42" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A42,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A42,事故一覧!$I$2:$I$29)</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="16" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="B43" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A43)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A43)</f>
         <v>0</v>
       </c>
       <c r="C43" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A43,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A43,事故一覧!$I$2:$I$29)</f>
         <v>0</v>
       </c>
     </row>
@@ -5755,50 +5913,50 @@
         <v>176</v>
       </c>
       <c r="B44" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A44)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A44)</f>
         <v>1</v>
       </c>
       <c r="C44" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A44,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A44,事故一覧!$I$2:$I$29)</f>
         <v>1</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="16" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="B45" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A45)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A45)</f>
         <v>0</v>
       </c>
       <c r="C45" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A45,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A45,事故一覧!$I$2:$I$29)</f>
         <v>0</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="16" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B46" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A46)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A46)</f>
         <v>0</v>
       </c>
       <c r="C46" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A46,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A46,事故一覧!$I$2:$I$29)</f>
         <v>0</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="16" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="B47" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A47)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A47)</f>
         <v>0</v>
       </c>
       <c r="C47" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A47,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A47,事故一覧!$I$2:$I$29)</f>
         <v>0</v>
       </c>
     </row>
@@ -5807,25 +5965,25 @@
         <v>135</v>
       </c>
       <c r="B48" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$28,A48)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A48)</f>
         <v>1</v>
       </c>
       <c r="C48" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$28,A48,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A48,事故一覧!$I$2:$I$29)</f>
         <v>1</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="14" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B49" s="14" t="n">
         <f aca="false">SUM(B2:B48)</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C49" s="14" t="n">
         <f aca="false">SUM(C2:C48)</f>
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -5844,7 +6002,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -5855,16 +6013,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5875,11 +6033,11 @@
         <v>33</v>
       </c>
       <c r="C2" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$28,A2)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$29,A2)</f>
         <v>2</v>
       </c>
       <c r="D2" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$28,A2,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$29,A2,事故一覧!$I$2:$I$29)</f>
         <v>4</v>
       </c>
     </row>
@@ -5891,11 +6049,11 @@
         <v>48</v>
       </c>
       <c r="C3" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$28,A3)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$29,A3)</f>
         <v>2</v>
       </c>
       <c r="D3" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$28,A3,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$29,A3,事故一覧!$I$2:$I$29)</f>
         <v>2</v>
       </c>
     </row>
@@ -5907,11 +6065,11 @@
         <v>62</v>
       </c>
       <c r="C4" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$28,A4)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$29,A4)</f>
         <v>4</v>
       </c>
       <c r="D4" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$28,A4,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$29,A4,事故一覧!$I$2:$I$29)</f>
         <v>4</v>
       </c>
     </row>
@@ -5920,14 +6078,14 @@
         <v>46297</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>225</v>
+        <v>192</v>
       </c>
       <c r="C5" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$28,A5)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$29,A5)</f>
         <v>0</v>
       </c>
       <c r="D5" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$28,A5,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$29,A5,事故一覧!$I$2:$I$29)</f>
         <v>0</v>
       </c>
     </row>
@@ -5939,11 +6097,11 @@
         <v>88</v>
       </c>
       <c r="C6" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$28,A6)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$29,A6)</f>
         <v>2</v>
       </c>
       <c r="D6" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$28,A6,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$29,A6,事故一覧!$I$2:$I$29)</f>
         <v>2</v>
       </c>
     </row>
@@ -5955,11 +6113,11 @@
         <v>101</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$28,A7)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$29,A7)</f>
         <v>5</v>
       </c>
       <c r="D7" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$28,A7,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$29,A7,事故一覧!$I$2:$I$29)</f>
         <v>5</v>
       </c>
     </row>
@@ -5971,11 +6129,11 @@
         <v>131</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$28,A8)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$29,A8)</f>
         <v>2</v>
       </c>
       <c r="D8" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$28,A8,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$29,A8,事故一覧!$I$2:$I$29)</f>
         <v>2</v>
       </c>
     </row>
@@ -5987,11 +6145,11 @@
         <v>33</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$28,A9)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$29,A9)</f>
         <v>3</v>
       </c>
       <c r="D9" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$28,A9,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$29,A9,事故一覧!$I$2:$I$29)</f>
         <v>3</v>
       </c>
     </row>
@@ -6003,11 +6161,11 @@
         <v>48</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$28,A10)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$29,A10)</f>
         <v>3</v>
       </c>
       <c r="D10" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$28,A10,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$29,A10,事故一覧!$I$2:$I$29)</f>
         <v>3</v>
       </c>
     </row>
@@ -6019,26 +6177,42 @@
         <v>62</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$28,A11)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$29,A11)</f>
         <v>4</v>
       </c>
       <c r="D11" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$28,A11,事故一覧!$I$2:$I$28)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$29,A11,事故一覧!$I$2:$I$29)</f>
         <v>4</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="17" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B12" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14" t="n">
-        <f aca="false">SUM(C2:C11)</f>
-        <v>27</v>
-      </c>
-      <c r="D12" s="14" t="n">
-        <f aca="false">SUM(D2:D11)</f>
-        <v>29</v>
+      <c r="C12" s="16" t="n">
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$29,A12)</f>
+        <v>1</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$29,A12,事故一覧!$I$2:$I$29)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14" t="n">
+        <f aca="false">SUM(C2:C12)</f>
+        <v>28</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <f aca="false">SUM(D2:D12)</f>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -6057,7 +6231,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
@@ -6081,10 +6255,10 @@
         <v>19</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>25</v>
@@ -6104,16 +6278,16 @@
         <v>55</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="G2" s="11" t="s">
         <v>60</v>
@@ -6131,16 +6305,16 @@
         <v>78</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>150</v>
@@ -6158,19 +6332,19 @@
         <v>78</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="H4" s="9" t="str">
         <f aca="false">HYPERLINK("https://chunichi.co.jp/article/1321634","記事を開く")</f>
@@ -6185,16 +6359,16 @@
         <v>89</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>175</v>
@@ -6212,19 +6386,19 @@
         <v>89</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="H6" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/7d3b2684f57408afa39b1ea0ea5ad798fc8e659f","記事を開く")</f>
@@ -6239,22 +6413,49 @@
         <v>55</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="G7" s="11" t="s">
         <v>190</v>
       </c>
       <c r="H7" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.nbs-tv.co.jp/news/","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="H8" s="9" t="str">
+        <f aca="false">HYPERLINK("https://kobe-np.co.jp/news/jiken/202610/0020910097.shtml","記事を開く")</f>
         <v>記事を開く</v>
       </c>
     </row>

--- a/全国交通事故データ.xlsx
+++ b/全国交通事故データ.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="316">
   <si>
     <t xml:space="preserve">このファイルについて</t>
   </si>
@@ -129,7 +129,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
     <r>
       <rPr>
@@ -939,6 +939,69 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">神戸市兵庫区</t>
+  </si>
+  <si>
+    <t xml:space="preserve">交差点</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歩行中の高齢男性が軽乗用車にはねられ死亡。運転の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">87</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳男を逮捕</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">見出しのみ</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">発生日は記事番号から</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10/1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ごろと推定</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">愛知県</t>
   </si>
   <si>
@@ -954,9 +1017,6 @@
     <t xml:space="preserve">渋滞の最後尾に乗用車が追突する死亡事故</t>
   </si>
   <si>
-    <t xml:space="preserve">見出しのみ</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -1229,6 +1289,81 @@
     <t xml:space="preserve">警察発表</t>
   </si>
   <si>
+    <t xml:space="preserve">茨城県</t>
+  </si>
+  <si>
+    <t xml:space="preserve">行方市</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（場所は未確認）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">車両対自転車</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午後、軽貨物車が自転車に衝突し、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">91</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳男性が搬送先の病院で死亡</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">KSB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ANN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">日</t>
   </si>
   <si>
@@ -1383,6 +1518,119 @@
     <t xml:space="preserve">ニュース記事で裏付けが取れていない</t>
   </si>
   <si>
+    <t xml:space="preserve">名古屋市天白区</t>
+  </si>
+  <si>
+    <t xml:space="preserve">道路（中央分離帯のある道路）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人対車両（横断中、車</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">夜、道路を横断中の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">代くらいの男性が車</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台にはねられ死亡。中央分離帯を越えて横断したか</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CBC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">テレビ（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Yahoo!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ニュース経由）</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">群馬県</t>
   </si>
   <si>
@@ -1417,9 +1665,6 @@
     <t xml:space="preserve">発生日は記事の掲載日から推定</t>
   </si>
   <si>
-    <t xml:space="preserve">茨城県</t>
-  </si>
-  <si>
     <t xml:space="preserve">土浦市</t>
   </si>
   <si>
@@ -1746,9 +1991,6 @@
     <t xml:space="preserve">鎌倉市</t>
   </si>
   <si>
-    <t xml:space="preserve">（場所は未確認）</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -2387,6 +2629,207 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">芦別市</t>
+  </si>
+  <si>
+    <t xml:space="preserve">幌内</t>
+  </si>
+  <si>
+    <t xml:space="preserve">車両相互（乗用車同士）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">乗用車同士の衝突で</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">90</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">代女性が死亡、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人が搬送。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日に運転の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">22</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳男を逮捕</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">STV</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ニュース北海道（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Yahoo!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ニュース経由）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10/10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の逮捕報道で判明した過去の事故</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">新潟県</t>
+  </si>
+  <si>
+    <t xml:space="preserve">新潟市西区</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鳥原の市道</t>
+  </si>
+  <si>
+    <t xml:space="preserve">車両相互（軽乗用車同士）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午後</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時半過ぎ、車同士が衝突し、軽乗用車を運転していた</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">85</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳男性が死亡。運転中に意識を失った可能性</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">新潟日報</t>
+  </si>
+  <si>
     <t xml:space="preserve">熊本県</t>
   </si>
   <si>
@@ -2615,6 +3058,365 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">琴塚の路上</t>
+  </si>
+  <si>
+    <t xml:space="preserve">車両対自転車（路線バス）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">左折しようと側道から本線に出た</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">71</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳男性の自転車が路線バスと衝突し、約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時間半後に死亡。乗客・運転手にけがなし</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">発生日は検索結果の記載（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日夕方）による</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">滋賀県</t>
+  </si>
+  <si>
+    <t xml:space="preserve">彦根市</t>
+  </si>
+  <si>
+    <t xml:space="preserve">日夏町の道路脇</t>
+  </si>
+  <si>
+    <t xml:space="preserve">人対車両（道路脇の用水路）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午後</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分ごろ、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">54</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳女性の軽トラックが道路脇で水をくんでいた</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">89</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳の義父に衝突。義父は用水路に落ち死亡</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">京都新聞（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Yahoo!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ニュース経由）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">福島県</t>
+  </si>
+  <si>
+    <t xml:space="preserve">郡山市</t>
+  </si>
+  <si>
+    <t xml:space="preserve">中田町柳橋・県道の信号のない交差点</t>
+  </si>
+  <si>
+    <t xml:space="preserve">車両相互（オートバイと軽乗用車、出合い頭）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午後</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">45</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分ごろ、オートバイの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">52</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳男性が軽乗用車と衝突し死亡</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">福島民友新聞</t>
+  </si>
+  <si>
+    <t xml:space="preserve">香川県</t>
+  </si>
+  <si>
+    <t xml:space="preserve">観音寺市</t>
+  </si>
+  <si>
+    <t xml:space="preserve">豊浜町の国道</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時ごろ、国道を歩いて横断していた</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">78</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳女性が軽乗用車にはねられ死亡。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">76</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳の運転手を現行犯逮捕</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NHK / KSB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">瀬戸内海放送</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">合計</t>
   </si>
   <si>
@@ -2639,18 +3441,12 @@
     <t xml:space="preserve">秋田県</t>
   </si>
   <si>
-    <t xml:space="preserve">福島県</t>
-  </si>
-  <si>
     <t xml:space="preserve">栃木県</t>
   </si>
   <si>
     <t xml:space="preserve">東京都</t>
   </si>
   <si>
-    <t xml:space="preserve">新潟県</t>
-  </si>
-  <si>
     <t xml:space="preserve">富山県</t>
   </si>
   <si>
@@ -2666,9 +3462,6 @@
     <t xml:space="preserve">三重県</t>
   </si>
   <si>
-    <t xml:space="preserve">滋賀県</t>
-  </si>
-  <si>
     <t xml:space="preserve">京都府</t>
   </si>
   <si>
@@ -2687,9 +3480,6 @@
     <t xml:space="preserve">徳島県</t>
   </si>
   <si>
-    <t xml:space="preserve">香川県</t>
-  </si>
-  <si>
     <t xml:space="preserve">愛媛県</t>
   </si>
   <si>
@@ -2908,22 +3698,136 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">STV</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ニュース北海道（</t>
+    <t xml:space="preserve">山ノ内町</t>
+  </si>
+  <si>
+    <t xml:space="preserve">スキー場</t>
+  </si>
+  <si>
+    <t xml:space="preserve">道路外（オフロードバイク）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">オフロードバイクの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">55</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳男性が死亡</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">富士宮市</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ガソリンスタンド</t>
+  </si>
+  <si>
+    <t xml:space="preserve">道路外（スタンドに車が突入）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午後</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時すぎ、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人が乗った車がガソリンスタンドに突っ込み、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人が死亡、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人がけが</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">静岡第一テレビ（</t>
     </r>
     <r>
       <rPr>
@@ -2944,42 +3848,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">山ノ内町</t>
-  </si>
-  <si>
-    <t xml:space="preserve">スキー場</t>
-  </si>
-  <si>
-    <t xml:space="preserve">道路外（オフロードバイク）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">オフロードバイクの</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">55</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">歳男性が死亡</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">西脇市</t>
   </si>
   <si>
@@ -2993,6 +3861,167 @@
   </si>
   <si>
     <t xml:space="preserve">神戸新聞</t>
+  </si>
+  <si>
+    <t xml:space="preserve">泉佐野市</t>
+  </si>
+  <si>
+    <t xml:space="preserve">交差点（右折中）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">祭礼の事故（だんじり）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時ごろ、右折中のだんじりが横転し、下敷きになった</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">51</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳の会社役員が死亡</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時事通信 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">読売新聞</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">泉大津市</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午後</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分ごろ、右折中のだんじりが転倒し、乗っていた</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">48</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳の会社員が死亡。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人がけが</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -3362,8 +4391,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="事故一覧" displayName="事故一覧" ref="A1:R29" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:R29"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="事故一覧" displayName="事故一覧" ref="A1:R38" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:R38"/>
   <tableColumns count="18">
     <tableColumn id="1" name="No"/>
     <tableColumn id="2" name="発生日"/>
@@ -3673,7 +4702,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R32"/>
+  <dimension ref="A1:R41"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -4038,47 +5067,49 @@
         <v>62</v>
       </c>
       <c r="D7" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="F7" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="F7" s="8" t="s">
-        <v>71</v>
-      </c>
       <c r="G7" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%84%9B%E7%9F%A5%E7%9C%8C%E5%B2%A1%E5%B4%8E%E5%B8%82%20%E6%9D%B1%E5%90%8D%E9%AB%98%E9%80%9F%E9%81%93%E8%B7%AF%20%E4%B8%8B%E3%82%8A%E7%B7%9A","地図")</f>
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%85%B5%E5%BA%AB%E7%9C%8C%E7%A5%9E%E6%88%B8%E5%B8%82%E5%85%B5%E5%BA%AB%E5%8C%BA%20%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
         <v>地図</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="I7" s="7"/>
+        <v>58</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="J7" s="7"/>
       <c r="K7" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="L7" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="N7" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.kobe-np.co.jp/news/richa/koutsuujiko/202610/0020881285.shtml","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O7" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="L7" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="M7" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="N7" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.chunichi.co.jp/aichi_news","記事を開く")</f>
-        <v>記事を開く</v>
-      </c>
-      <c r="O7" s="8" t="s">
-        <v>76</v>
-      </c>
       <c r="P7" s="8" t="n">
-        <v>34.924</v>
+        <v>34.68</v>
       </c>
       <c r="Q7" s="8" t="n">
-        <v>137.204</v>
+        <v>135.17</v>
       </c>
       <c r="R7" s="8" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4092,49 +5123,47 @@
         <v>62</v>
       </c>
       <c r="D8" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G8" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%84%9B%E7%9F%A5%E7%9C%8C%E5%B2%A1%E5%B4%8E%E5%B8%82%20%E6%9D%B1%E5%90%8D%E9%AB%98%E9%80%9F%E9%81%93%E8%B7%AF%20%E4%B8%8B%E3%82%8A%E7%B7%9A","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="L8" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="M8" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="N8" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.chunichi.co.jp/aichi_news","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O8" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="G8" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A5%9E%E5%A5%88%E5%B7%9D%E7%9C%8C%E5%B7%9D%E5%B4%8E%E5%B8%82%E5%B7%9D%E5%B4%8E%E5%8C%BA%20%E6%9D%B1%E4%BA%AC%E6%B9%BE%E3%82%A2%E3%82%AF%E3%82%A2%E3%83%A9%E3%82%A4%E3%83%B3","地図")</f>
-        <v>地図</v>
-      </c>
-      <c r="H8" s="8" t="s">
+      <c r="P8" s="8" t="n">
+        <v>34.924</v>
+      </c>
+      <c r="Q8" s="8" t="n">
+        <v>137.204</v>
+      </c>
+      <c r="R8" s="8" t="s">
         <v>81</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="L8" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M8" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="N8" s="9" t="str">
-        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261001de53536","記事を開く")</f>
-        <v>記事を開く</v>
-      </c>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="Q8" s="8" t="n">
-        <v>139.82</v>
-      </c>
-      <c r="R8" s="8" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4148,25 +5177,27 @@
         <v>62</v>
       </c>
       <c r="D9" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="F9" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="G9" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A5%9E%E5%A5%88%E5%B7%9D%E7%9C%8C%E5%B7%9D%E5%B4%8E%E5%B8%82%E5%B7%9D%E5%B4%8E%E5%8C%BA%20%E6%9D%B1%E4%BA%AC%E6%B9%BE%E3%82%A2%E3%82%AF%E3%82%A2%E3%83%A9%E3%82%A4%E3%83%B3","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H9" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="G9" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E9%9D%92%E6%A3%AE%E7%9C%8C%E5%85%AB%E6%88%B8%E5%B8%82%20%E6%96%B0%E4%BA%95%E7%94%B0%20%E5%9B%BD%E9%81%9345%E5%8F%B7%E3%81%AE%E6%A8%AA%E6%96%AD%E6%AD%A9%E9%81%93","地図")</f>
-        <v>地図</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>52</v>
-      </c>
       <c r="I9" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="7"/>
+        <v>2</v>
+      </c>
+      <c r="J9" s="7" t="n">
+        <v>3</v>
+      </c>
       <c r="K9" s="8" t="s">
         <v>86</v>
       </c>
@@ -4174,21 +5205,21 @@
         <v>39</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="N9" s="9" t="str">
-        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nb-6080031283","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261001de53536","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O9" s="8"/>
       <c r="P9" s="8" t="n">
-        <v>40.487</v>
+        <v>35.5</v>
       </c>
       <c r="Q9" s="8" t="n">
-        <v>141.545</v>
+        <v>139.82</v>
       </c>
       <c r="R9" s="8" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4196,169 +5227,165 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="n">
+        <v>46296</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="G10" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E9%9D%92%E6%A3%AE%E7%9C%8C%E5%85%AB%E6%88%B8%E5%B8%82%20%E6%96%B0%E4%BA%95%E7%94%B0%20%E5%9B%BD%E9%81%9345%E5%8F%B7%E3%81%AE%E6%A8%AA%E6%96%AD%E6%AD%A9%E9%81%93","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="7"/>
+      <c r="K10" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="L10" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="N10" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nb-6080031283","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8" t="n">
+        <v>40.487</v>
+      </c>
+      <c r="Q10" s="8" t="n">
+        <v>141.545</v>
+      </c>
+      <c r="R10" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="n">
         <v>46298</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G10" s="9" t="str">
+      <c r="C11" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="G11" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%8C%97%E6%B5%B7%E9%81%93%E5%AE%A4%E8%98%AD%E5%B8%82%20%E5%9B%BD%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
-      <c r="H10" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="I10" s="7" t="n">
+      <c r="H11" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="I11" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J10" s="7" t="n">
+      <c r="J11" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="K10" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="L10" s="10" t="s">
+      <c r="K11" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="L11" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M10" s="11" t="s">
+      <c r="M11" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="N10" s="9" t="str">
+      <c r="N11" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261004de54150","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O10" s="8"/>
-      <c r="P10" s="8" t="n">
+      <c r="O11" s="8"/>
+      <c r="P11" s="8" t="n">
         <v>42.33</v>
       </c>
-      <c r="Q10" s="8" t="n">
+      <c r="Q11" s="8" t="n">
         <v>140.98</v>
       </c>
-      <c r="R10" s="8" t="s">
+      <c r="R11" s="8" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="6" t="n">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="6" t="n">
         <v>46298</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="G11" s="9" t="str">
+      <c r="C12" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="G12" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%A4%A7%E9%98%AA%E5%BA%9C%E5%A0%BA%E5%B8%82%E5%8C%97%E5%8C%BA%20%E5%8D%97%E8%8A%B1%E7%94%B0%E7%94%BA%E3%81%AE%E8%B7%AF%E4%B8%8A","地図")</f>
         <v>地図</v>
       </c>
-      <c r="H11" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="I11" s="7" t="n">
+      <c r="H12" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="I12" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J11" s="7"/>
-      <c r="K11" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="L11" s="10" t="s">
+      <c r="J12" s="7"/>
+      <c r="K12" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="L12" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M11" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="N11" s="9" t="str">
+      <c r="M12" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="N12" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.police.pref.osaka.lg.jp/jiken/jiko/14349.html","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O11" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="P11" s="8" t="n">
+      <c r="O12" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="P12" s="8" t="n">
         <v>34.567</v>
       </c>
-      <c r="Q11" s="8" t="n">
+      <c r="Q12" s="8" t="n">
         <v>135.513</v>
       </c>
-      <c r="R11" s="8" t="s">
+      <c r="R12" s="8" t="s">
         <v>61</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="6" t="n">
-        <v>46299</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="G12" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%B1%B1%E5%8F%A3%E7%9C%8C%E5%B1%B1%E5%8F%A3%E5%B8%82%20%E6%B1%9F%E5%B4%8E%E3%81%AE%E5%9B%BD%E9%81%93","地図")</f>
-        <v>地図</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="I12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K12" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="L12" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M12" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="N12" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.pref.yamaguchi.lg.jp/site/police/151660.html","記事を開く")</f>
-        <v>記事を開く</v>
-      </c>
-      <c r="O12" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="P12" s="8" t="n">
-        <v>34.08</v>
-      </c>
-      <c r="Q12" s="8" t="n">
-        <v>131.4</v>
-      </c>
-      <c r="R12" s="8" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4366,58 +5393,56 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="n">
-        <v>46299</v>
+        <v>46298</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G13" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%BA%83%E5%B3%B6%E7%9C%8C%E5%B0%BE%E9%81%93%E5%B8%82%20%E7%89%87%E5%81%B41%E8%BB%8A%E7%B7%9A%E3%81%AE%E7%9C%8C%E9%81%93","地図")</f>
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E8%8C%A8%E5%9F%8E%E7%9C%8C%E8%A1%8C%E6%96%B9%E5%B8%82","地図")</f>
         <v>地図</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="I13" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J13" s="7"/>
       <c r="K13" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="L13" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="M13" s="8" t="s">
-        <v>115</v>
+        <v>109</v>
+      </c>
+      <c r="L13" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>110</v>
       </c>
       <c r="N13" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.think-sp.com/2026/10/08/tw-jitensha-miotosi","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://news.ksb.co.jp/ann/article/16938624","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O13" s="8" t="s">
-        <v>116</v>
-      </c>
+      <c r="O13" s="8"/>
       <c r="P13" s="8" t="n">
-        <v>34.409</v>
+        <v>35.99</v>
       </c>
       <c r="Q13" s="8" t="n">
-        <v>133.205</v>
+        <v>140.49</v>
       </c>
       <c r="R13" s="8" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="n">
         <v>13</v>
       </c>
@@ -4425,52 +5450,54 @@
         <v>46299</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G14" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%BE%A4%E9%A6%AC%E7%9C%8C%E9%A4%A8%E6%9E%97%E5%B8%82%20%E7%9C%8C%E9%81%93","地図")</f>
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%B1%B1%E5%8F%A3%E7%9C%8C%E5%B1%B1%E5%8F%A3%E5%B8%82%20%E6%B1%9F%E5%B4%8E%E3%81%AE%E5%9B%BD%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>58</v>
+        <v>115</v>
       </c>
       <c r="I14" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J14" s="7"/>
-      <c r="K14" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="L14" s="12" t="s">
-        <v>74</v>
+      <c r="J14" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="L14" s="10" t="s">
+        <v>39</v>
       </c>
       <c r="M14" s="8" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="N14" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.jomo-news.co.jp/subcategory/%E4%BA%8B%E4%BB%B6%E3%83%BB%E4%BA%8B%E6%95%85","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://www.pref.yamaguchi.lg.jp/site/police/151660.html","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O14" s="8" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="P14" s="8" t="n">
-        <v>36.245</v>
+        <v>34.08</v>
       </c>
       <c r="Q14" s="8" t="n">
-        <v>139.542</v>
+        <v>131.4</v>
       </c>
       <c r="R14" s="8" t="s">
-        <v>47</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4481,53 +5508,55 @@
         <v>46299</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G15" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E8%8C%A8%E5%9F%8E%E7%9C%8C%E5%9C%9F%E6%B5%A6%E5%B8%82%20%E7%9C%8C%E9%81%93%E3%81%AE%E5%8D%81%E5%AD%97%E8%B7%AF","地図")</f>
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%BA%83%E5%B3%B6%E7%9C%8C%E5%B0%BE%E9%81%93%E5%B8%82%20%E7%89%87%E5%81%B41%E8%BB%8A%E7%B7%9A%E3%81%AE%E7%9C%8C%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="I15" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J15" s="7"/>
       <c r="K15" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="L15" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M15" s="11" t="s">
-        <v>60</v>
+        <v>123</v>
+      </c>
+      <c r="L15" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="M15" s="8" t="s">
+        <v>125</v>
       </c>
       <c r="N15" s="9" t="str">
-        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261005de54731","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://www.think-sp.com/2026/10/08/tw-jitensha-miotosi","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O15" s="8"/>
+      <c r="O15" s="8" t="s">
+        <v>126</v>
+      </c>
       <c r="P15" s="8" t="n">
-        <v>36.072</v>
+        <v>34.409</v>
       </c>
       <c r="Q15" s="8" t="n">
-        <v>140.198</v>
+        <v>133.205</v>
       </c>
       <c r="R15" s="8" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="n">
         <v>15</v>
       </c>
@@ -4535,61 +5564,61 @@
         <v>46299</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="D16" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="F16" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="G16" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%84%9B%E7%9F%A5%E7%9C%8C%E5%90%8D%E5%8F%A4%E5%B1%8B%E5%B8%82%E5%A4%A9%E7%99%BD%E5%8C%BA%20%E9%81%93%E8%B7%AF","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H16" s="8" t="s">
         <v>129</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G16" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E9%B3%A5%E5%8F%96%E7%9C%8C%E7%B1%B3%E5%AD%90%E5%B8%82%20%E5%9B%BD%E9%81%93","地図")</f>
-        <v>地図</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>58</v>
       </c>
       <c r="I16" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J16" s="7"/>
-      <c r="K16" s="11" t="s">
+      <c r="K16" s="8" t="s">
         <v>130</v>
       </c>
       <c r="L16" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M16" s="11" t="s">
-        <v>60</v>
+        <v>131</v>
       </c>
       <c r="N16" s="9" t="str">
-        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261004de54296","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/2d229adf64509aacdcf58f84ae9c0811ab5c28d4","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O16" s="8"/>
       <c r="P16" s="8" t="n">
-        <v>35.428</v>
+        <v>35.13</v>
       </c>
       <c r="Q16" s="8" t="n">
-        <v>133.331</v>
+        <v>136.97</v>
       </c>
       <c r="R16" s="8" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="6" t="n">
-        <v>46300</v>
+        <v>46299</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>132</v>
@@ -4598,40 +5627,40 @@
         <v>133</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="G17" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%B1%B1%E5%BD%A2%E7%9C%8C%E9%B6%B4%E5%B2%A1%E5%B8%82%20%E7%9C%8C%E9%81%93","地図")</f>
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%BE%A4%E9%A6%AC%E7%9C%8C%E9%A4%A8%E6%9E%97%E5%B8%82%20%E7%9C%8C%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="I17" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J17" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K17" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="L17" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M17" s="11" t="s">
-        <v>60</v>
+      <c r="J17" s="7"/>
+      <c r="K17" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="L17" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="M17" s="8" t="s">
+        <v>136</v>
       </c>
       <c r="N17" s="9" t="str">
-        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261006de54976","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://www.jomo-news.co.jp/subcategory/%E4%BA%8B%E4%BB%B6%E3%83%BB%E4%BA%8B%E6%95%85","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O17" s="8"/>
+      <c r="O17" s="8" t="s">
+        <v>137</v>
+      </c>
       <c r="P17" s="8" t="n">
-        <v>38.727</v>
+        <v>36.245</v>
       </c>
       <c r="Q17" s="8" t="n">
-        <v>139.827</v>
+        <v>139.542</v>
       </c>
       <c r="R17" s="8" t="s">
         <v>47</v>
@@ -4642,111 +5671,107 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="n">
-        <v>46300</v>
+        <v>46299</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>135</v>
+        <v>105</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G18" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%B2%96%E7%B8%84%E7%9C%8C%E9%82%A3%E8%A6%87%E5%B8%82%20%E9%A6%96%E9%87%8C%E6%9C%AB%E5%90%89%E7%94%BA%20%E7%9C%8C%E9%81%9382%E5%8F%B7%E3%81%AE%E4%BF%A1%E5%8F%B7%E3%81%AE%E3%81%82%E3%82%8B%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E8%8C%A8%E5%9F%8E%E7%9C%8C%E5%9C%9F%E6%B5%A6%E5%B8%82%20%E7%9C%8C%E9%81%93%E3%81%AE%E5%8D%81%E5%AD%97%E8%B7%AF","地図")</f>
         <v>地図</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I18" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J18" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="J18" s="7"/>
       <c r="K18" s="8" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="L18" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M18" s="8" t="s">
-        <v>140</v>
+      <c r="M18" s="11" t="s">
+        <v>60</v>
       </c>
       <c r="N18" s="9" t="str">
-        <f aca="false">HYPERLINK("https://ryukyushimpo.jp/national/entry-5538964.html","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261005de54731","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O18" s="8"/>
       <c r="P18" s="8" t="n">
-        <v>26.226</v>
+        <v>36.072</v>
       </c>
       <c r="Q18" s="8" t="n">
-        <v>127.71</v>
+        <v>140.198</v>
       </c>
       <c r="R18" s="8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="6" t="n">
-        <v>46301</v>
+        <v>46299</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>33</v>
+        <v>111</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>143</v>
+        <v>95</v>
       </c>
       <c r="G19" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%B2%90%E9%98%9C%E7%9C%8C%E5%B2%90%E9%98%9C%E5%B8%82%20%E9%87%91%E8%8F%AF%E5%B1%B1%E3%83%89%E3%83%A9%E3%82%A4%E3%83%96%E3%82%A6%E3%82%A7%E3%82%A4%E3%81%AE%E3%83%98%E3%82%A2%E3%83%94%E3%83%B3%E3%82%AB%E3%83%BC%E3%83%96","地図")</f>
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E9%B3%A5%E5%8F%96%E7%9C%8C%E7%B1%B3%E5%AD%90%E5%B8%82%20%E5%9B%BD%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>144</v>
+        <v>58</v>
       </c>
       <c r="I19" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J19" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" s="8" t="s">
-        <v>145</v>
+      <c r="J19" s="7"/>
+      <c r="K19" s="11" t="s">
+        <v>144</v>
       </c>
       <c r="L19" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M19" s="11" t="s">
-        <v>146</v>
+        <v>60</v>
       </c>
       <c r="N19" s="9" t="str">
-        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/50988fd3cbfff6e6a97e45b98587bf9db84c27b3","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261004de54296","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O19" s="8"/>
       <c r="P19" s="8" t="n">
-        <v>35.433</v>
+        <v>35.428</v>
       </c>
       <c r="Q19" s="8" t="n">
-        <v>136.786</v>
+        <v>133.331</v>
       </c>
       <c r="R19" s="8" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4754,109 +5779,111 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="n">
-        <v>46301</v>
+        <v>46300</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>33</v>
+        <v>145</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>78</v>
+        <v>146</v>
       </c>
       <c r="E20" s="8" t="s">
         <v>147</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="G20" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A5%9E%E5%A5%88%E5%B7%9D%E7%9C%8C%E9%8E%8C%E5%80%89%E5%B8%82","地図")</f>
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%B1%B1%E5%BD%A2%E7%9C%8C%E9%B6%B4%E5%B2%A1%E5%B8%82%20%E7%9C%8C%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="I20" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J20" s="7"/>
+      <c r="J20" s="7" t="n">
+        <v>3</v>
+      </c>
       <c r="K20" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="L20" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="M20" s="8" t="s">
-        <v>150</v>
+        <v>148</v>
+      </c>
+      <c r="L20" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M20" s="11" t="s">
+        <v>60</v>
       </c>
       <c r="N20" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.kanaloco.jp/news/social/case","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261006de54976","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O20" s="8" t="s">
-        <v>151</v>
-      </c>
+      <c r="O20" s="8"/>
       <c r="P20" s="8" t="n">
-        <v>35.319</v>
+        <v>38.727</v>
       </c>
       <c r="Q20" s="8" t="n">
-        <v>139.547</v>
+        <v>139.827</v>
       </c>
       <c r="R20" s="8" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="6" t="n">
-        <v>46301</v>
+        <v>46300</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>33</v>
+        <v>145</v>
       </c>
       <c r="D21" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="G21" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%B2%96%E7%B8%84%E7%9C%8C%E9%82%A3%E8%A6%87%E5%B8%82%20%E9%A6%96%E9%87%8C%E6%9C%AB%E5%90%89%E7%94%BA%20%E7%9C%8C%E9%81%9382%E5%8F%B7%E3%81%AE%E4%BF%A1%E5%8F%B7%E3%81%AE%E3%81%82%E3%82%8B%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H21" s="8" t="s">
         <v>152</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="G21" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E9%9D%99%E5%B2%A1%E7%9C%8C%E5%BE%A1%E6%AE%BF%E5%A0%B4%E5%B8%82%20%E5%9B%BD%E9%81%93138%E5%8F%B7","地図")</f>
-        <v>地図</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>155</v>
       </c>
       <c r="I21" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J21" s="7"/>
+      <c r="J21" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="K21" s="8" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="L21" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="N21" s="9" t="str">
-        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/3b0fd061a9e7f49b11a18228d212989cc0b2a40a","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://ryukyushimpo.jp/national/entry-5538964.html","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O21" s="8"/>
       <c r="P21" s="8" t="n">
-        <v>35.3</v>
+        <v>26.226</v>
       </c>
       <c r="Q21" s="8" t="n">
-        <v>138.95</v>
+        <v>127.71</v>
       </c>
       <c r="R21" s="8" t="s">
-        <v>77</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4864,53 +5891,55 @@
         <v>21</v>
       </c>
       <c r="B22" s="6" t="n">
-        <v>46302</v>
+        <v>46301</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>49</v>
+        <v>155</v>
       </c>
       <c r="E22" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="G22" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%B2%90%E9%98%9C%E7%9C%8C%E5%B2%90%E9%98%9C%E5%B8%82%20%E9%87%91%E8%8F%AF%E5%B1%B1%E3%83%89%E3%83%A9%E3%82%A4%E3%83%96%E3%82%A6%E3%82%A7%E3%82%A4%E3%81%AE%E3%83%98%E3%82%A2%E3%83%94%E3%83%B3%E3%82%AB%E3%83%BC%E3%83%96","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H22" s="8" t="s">
         <v>158</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="G22" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%85%B5%E5%BA%AB%E7%9C%8C%E4%BC%8A%E4%B8%B9%E5%B8%82%20%E5%8D%97%E6%9C%AC%E7%94%BA4%E4%B8%81%E7%9B%AE%20%E7%9C%8C%E9%81%93%E3%81%AE%E4%BF%A1%E5%8F%B7%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
-        <v>地図</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>160</v>
       </c>
       <c r="I22" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J22" s="7"/>
+      <c r="J22" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="K22" s="8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="L22" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M22" s="8" t="s">
-        <v>54</v>
+      <c r="M22" s="11" t="s">
+        <v>160</v>
       </c>
       <c r="N22" s="9" t="str">
-        <f aca="false">HYPERLINK("https://kobe-np.co.jp/news/richa/koutsuujiko/202610/0020905694.shtml","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/50988fd3cbfff6e6a97e45b98587bf9db84c27b3","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O22" s="8"/>
       <c r="P22" s="8" t="n">
-        <v>34.774</v>
+        <v>35.433</v>
       </c>
       <c r="Q22" s="8" t="n">
-        <v>135.405</v>
+        <v>136.786</v>
       </c>
       <c r="R22" s="8" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4918,410 +5947,904 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="n">
+        <v>46301</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="G23" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A5%9E%E5%A5%88%E5%B7%9D%E7%9C%8C%E9%8E%8C%E5%80%89%E5%B8%82","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I23" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="7"/>
+      <c r="K23" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="L23" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="M23" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="N23" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.kanaloco.jp/news/social/case","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O23" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="P23" s="8" t="n">
+        <v>35.319</v>
+      </c>
+      <c r="Q23" s="8" t="n">
+        <v>139.547</v>
+      </c>
+      <c r="R23" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>46301</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="G24" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E9%9D%99%E5%B2%A1%E7%9C%8C%E5%BE%A1%E6%AE%BF%E5%A0%B4%E5%B8%82%20%E5%9B%BD%E9%81%93138%E5%8F%B7","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="7"/>
+      <c r="K24" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="L24" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M24" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="N24" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/3b0fd061a9e7f49b11a18228d212989cc0b2a40a","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O24" s="8"/>
+      <c r="P24" s="8" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="Q24" s="8" t="n">
+        <v>138.95</v>
+      </c>
+      <c r="R24" s="8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="6" t="n">
         <v>46302</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C25" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D25" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E23" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="G23" s="9" t="str">
+      <c r="E25" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="G25" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%85%B5%E5%BA%AB%E7%9C%8C%E4%BC%8A%E4%B8%B9%E5%B8%82%20%E5%8D%97%E6%9C%AC%E7%94%BA4%E4%B8%81%E7%9B%AE%20%E7%9C%8C%E9%81%93%E3%81%AE%E4%BF%A1%E5%8F%B7%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="7"/>
+      <c r="K25" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="L25" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M25" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="N25" s="9" t="str">
+        <f aca="false">HYPERLINK("https://kobe-np.co.jp/news/richa/koutsuujiko/202610/0020905694.shtml","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O25" s="8"/>
+      <c r="P25" s="8" t="n">
+        <v>34.774</v>
+      </c>
+      <c r="Q25" s="8" t="n">
+        <v>135.405</v>
+      </c>
+      <c r="R25" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>46302</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="G26" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%85%B5%E5%BA%AB%E7%9C%8C%E9%AB%98%E7%A0%82%E5%B8%82%20%E6%9B%BD%E6%A0%B9%E7%94%BA%20%E7%9C%8C%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
-      <c r="H23" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="I23" s="7" t="n">
+      <c r="H26" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="I26" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J23" s="7"/>
-      <c r="K23" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="L23" s="10" t="s">
+      <c r="J26" s="7"/>
+      <c r="K26" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="L26" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M23" s="8" t="s">
+      <c r="M26" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="N23" s="9" t="str">
+      <c r="N26" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.kobe-np.co.jp/news/richa/koutsuujiko/202610/0020903821.shtml","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O23" s="8"/>
-      <c r="P23" s="8" t="n">
+      <c r="O26" s="8"/>
+      <c r="P26" s="8" t="n">
         <v>34.767</v>
       </c>
-      <c r="Q23" s="8" t="n">
+      <c r="Q26" s="8" t="n">
         <v>134.775</v>
       </c>
-      <c r="R23" s="8" t="s">
+      <c r="R26" s="8" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="6" t="n">
+    <row r="27" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="6" t="n">
         <v>46302</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C27" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D24" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="G24" s="9" t="str">
+      <c r="D27" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="G27" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%9F%BC%E7%8E%89%E7%9C%8C%E3%81%B5%E3%81%98%E3%81%BF%E9%87%8E%E5%B8%82%20%E3%81%86%E3%82%8C%E3%81%97%E9%87%8E1%E4%B8%81%E7%9B%AE%20%E7%9C%8C%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
-      <c r="H24" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="I24" s="7" t="n">
+      <c r="H27" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="I27" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J24" s="7" t="n">
+      <c r="J27" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="K24" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="L24" s="10" t="s">
+      <c r="K27" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="L27" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M24" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="N24" s="9" t="str">
+      <c r="M27" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="N27" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261007de56188","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O24" s="8"/>
-      <c r="P24" s="8" t="n">
+      <c r="O27" s="8"/>
+      <c r="P27" s="8" t="n">
         <v>35.88</v>
       </c>
-      <c r="Q24" s="8" t="n">
+      <c r="Q27" s="8" t="n">
         <v>139.535</v>
       </c>
-      <c r="R24" s="8" t="s">
+      <c r="R27" s="8" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="6" t="n">
+    <row r="28" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="6" t="n">
         <v>46303</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C28" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="D25" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="G25" s="9" t="str">
+      <c r="D28" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="G28" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%8C%97%E6%B5%B7%E9%81%93%E6%97%AD%E5%B7%9D%E5%B8%82%20%E7%A5%9E%E6%A5%BD%E5%B2%A16%E6%9D%A16%E4%B8%81%E7%9B%AE%20%E5%B8%82%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
-      <c r="H25" s="8" t="s">
+      <c r="H28" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I25" s="7" t="n">
+      <c r="I28" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J25" s="7"/>
-      <c r="K25" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="L25" s="10" t="s">
+      <c r="J28" s="7"/>
+      <c r="K28" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="L28" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M25" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="N25" s="9" t="str">
+      <c r="M28" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="N28" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/0f9db2f6fa5fe325add09fc111cb3852d3730e34","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O25" s="8"/>
-      <c r="P25" s="8" t="n">
+      <c r="O28" s="8"/>
+      <c r="P28" s="8" t="n">
         <v>43.748</v>
       </c>
-      <c r="Q25" s="8" t="n">
+      <c r="Q28" s="8" t="n">
         <v>142.383</v>
       </c>
-      <c r="R25" s="8" t="s">
+      <c r="R28" s="8" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="6" t="n">
+    <row r="29" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="6" t="n">
         <v>46303</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C29" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="D26" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="G26" s="9" t="str">
+      <c r="D29" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="G29" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%8C%97%E6%B5%B7%E9%81%93%E8%8A%A6%E5%88%A5%E5%B8%82%20%E5%B9%8C%E5%86%85","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="I29" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K29" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="L29" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M29" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="N29" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/a5f96326b055568a54d25da884585e33ad80cc8c","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O29" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="P29" s="8" t="n">
+        <v>43.517</v>
+      </c>
+      <c r="Q29" s="8" t="n">
+        <v>142.183</v>
+      </c>
+      <c r="R29" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>46303</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="G30" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%96%B0%E6%BD%9F%E7%9C%8C%E6%96%B0%E6%BD%9F%E5%B8%82%E8%A5%BF%E5%8C%BA%20%E9%B3%A5%E5%8E%9F%E3%81%AE%E5%B8%82%E9%81%93","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="I30" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" s="7"/>
+      <c r="K30" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="L30" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M30" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="N30" s="9" t="str">
+        <f aca="false">HYPERLINK("https://niigata-nippo.co.jp/articles/-/921297","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O30" s="8"/>
+      <c r="P30" s="8" t="n">
+        <v>37.86</v>
+      </c>
+      <c r="Q30" s="8" t="n">
+        <v>138.93</v>
+      </c>
+      <c r="R30" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>46303</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="G31" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%86%8A%E6%9C%AC%E7%9C%8C%E7%86%8A%E6%9C%AC%E5%B8%82","地図")</f>
         <v>地図</v>
       </c>
-      <c r="H26" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="I26" s="7" t="n">
+      <c r="H31" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="I31" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J26" s="7"/>
-      <c r="K26" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="L26" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="M26" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="N26" s="9" t="str">
+      <c r="J31" s="7"/>
+      <c r="K31" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="L31" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="M31" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="N31" s="9" t="str">
         <f aca="false">HYPERLINK("https://kumanichi.com/articles/2044555","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O26" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="P26" s="8" t="n">
+      <c r="O31" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="P31" s="8" t="n">
         <v>32.803</v>
       </c>
-      <c r="Q26" s="8" t="n">
+      <c r="Q31" s="8" t="n">
         <v>130.708</v>
       </c>
-      <c r="R26" s="8" t="s">
+      <c r="R31" s="8" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="6" t="n">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="6" t="n">
         <v>46303</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C32" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="D32" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="E27" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="G27" s="9" t="str">
+      <c r="E32" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="G32" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A6%8F%E5%B2%A1%E7%9C%8C%E5%B7%9D%E5%B4%8E%E7%94%BA%EF%BC%88%E7%94%B0%E5%B7%9D%E9%83%A1%EF%BC%89","地図")</f>
         <v>地図</v>
       </c>
-      <c r="H27" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="I27" s="7" t="n">
+      <c r="H32" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="I32" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J27" s="7"/>
-      <c r="K27" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="L27" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="M27" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="N27" s="9" t="str">
+      <c r="J32" s="7"/>
+      <c r="K32" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="L32" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="M32" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="N32" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.nishinippon.co.jp/category/kyushu/flash/","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O27" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="P27" s="8" t="n">
+      <c r="O32" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="P32" s="8" t="n">
         <v>33.6</v>
       </c>
-      <c r="Q27" s="8" t="n">
+      <c r="Q32" s="8" t="n">
         <v>130.815</v>
       </c>
-      <c r="R27" s="8" t="s">
+      <c r="R32" s="8" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="6" t="n">
+    <row r="33" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="6" t="n">
         <v>46303</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C33" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="D33" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E28" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="G28" s="9" t="str">
+      <c r="E33" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="G33" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E9%95%B7%E9%87%8E%E7%9C%8C%E6%9D%BE%E6%9C%AC%E5%B8%82%20%E4%BF%A1%E5%8F%B7%E3%81%AE%E3%81%AA%E3%81%84%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
         <v>地図</v>
       </c>
-      <c r="H28" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="I28" s="7" t="n">
+      <c r="H33" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="I33" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J28" s="7"/>
-      <c r="K28" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="L28" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="M28" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="N28" s="9" t="str">
+      <c r="J33" s="7"/>
+      <c r="K33" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="L33" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="M33" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="N33" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.nbs-tv.co.jp/news/","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O28" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="P28" s="8" t="n">
+      <c r="O33" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="P33" s="8" t="n">
         <v>36.238</v>
       </c>
-      <c r="Q28" s="8" t="n">
+      <c r="Q33" s="8" t="n">
         <v>137.972</v>
       </c>
-      <c r="R28" s="8" t="s">
+      <c r="R33" s="8" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="6" t="n">
+    <row r="34" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="6" t="n">
         <v>46304</v>
       </c>
-      <c r="C29" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="G29" s="9" t="str">
+      <c r="C34" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="G34" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%9F%BC%E7%8E%89%E7%9C%8C%E6%96%B0%E5%BA%A7%E5%B8%82%20%E6%A0%97%E5%8E%9F%E3%81%AE%E5%B8%82%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
-      <c r="H29" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="I29" s="7" t="n">
+      <c r="H34" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="I34" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J29" s="7"/>
-      <c r="K29" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="L29" s="10" t="s">
+      <c r="J34" s="7"/>
+      <c r="K34" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="L34" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M29" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="N29" s="9" t="str">
+      <c r="M34" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="N34" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/aad5e62c6ab660cb6e49eb85990d0040b1ed24c0","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O29" s="8"/>
-      <c r="P29" s="8" t="n">
+      <c r="O34" s="8"/>
+      <c r="P34" s="8" t="n">
         <v>35.797</v>
       </c>
-      <c r="Q29" s="8" t="n">
+      <c r="Q34" s="8" t="n">
         <v>139.558</v>
       </c>
-      <c r="R29" s="8" t="s">
+      <c r="R34" s="8" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="14" t="s">
-        <v>198</v>
-      </c>
-      <c r="B31" s="14" t="str">
-        <f aca="false">COUNTA(D2:D29)&amp;"件"</f>
-        <v>28件</v>
-      </c>
-      <c r="H31" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="I31" s="14" t="n">
-        <f aca="false">SUM(I2:I29)</f>
-        <v>30</v>
-      </c>
-      <c r="J31" s="14" t="n">
-        <f aca="false">SUM(J2:J29)</f>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="15" t="s">
-        <v>200</v>
+    <row r="35" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>46305</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="G35" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%B2%90%E9%98%9C%E7%9C%8C%E5%B2%90%E9%98%9C%E5%B8%82%20%E7%90%B4%E5%A1%9A%E3%81%AE%E8%B7%AF%E4%B8%8A","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="I35" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="7"/>
+      <c r="K35" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="L35" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="M35" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="N35" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/320d09f263be0f0e087a9f5a872f4b62a55ee56a","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O35" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="P35" s="8" t="n">
+        <v>35.405</v>
+      </c>
+      <c r="Q35" s="8" t="n">
+        <v>136.766</v>
+      </c>
+      <c r="R35" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="6" t="n">
+        <v>46305</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="G36" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%BB%8B%E8%B3%80%E7%9C%8C%E5%BD%A6%E6%A0%B9%E5%B8%82%20%E6%97%A5%E5%A4%8F%E7%94%BA%E3%81%AE%E9%81%93%E8%B7%AF%E8%84%87","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H36" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="I36" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" s="7"/>
+      <c r="K36" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="L36" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M36" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="N36" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/b6b6518fd7e974552b652d275fd3240a159e1c74","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O36" s="8"/>
+      <c r="P36" s="8" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="Q36" s="8" t="n">
+        <v>136.24</v>
+      </c>
+      <c r="R36" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="6" t="n">
+        <v>46305</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="G37" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A6%8F%E5%B3%B6%E7%9C%8C%E9%83%A1%E5%B1%B1%E5%B8%82%20%E4%B8%AD%E7%94%B0%E7%94%BA%E6%9F%B3%E6%A9%8B%20%E7%9C%8C%E9%81%93%E3%81%AE%E4%BF%A1%E5%8F%B7%E3%81%AE%E3%81%AA%E3%81%84%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="I37" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" s="7"/>
+      <c r="K37" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="L37" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M37" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="N37" s="9" t="str">
+        <f aca="false">HYPERLINK("https://minyu-net.com/news/detail/2026101107353655857","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O37" s="8"/>
+      <c r="P37" s="8" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="Q37" s="8" t="n">
+        <v>140.36</v>
+      </c>
+      <c r="R37" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="6" t="n">
+        <v>46305</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="G38" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E9%A6%99%E5%B7%9D%E7%9C%8C%E8%A6%B3%E9%9F%B3%E5%AF%BA%E5%B8%82%20%E8%B1%8A%E6%B5%9C%E7%94%BA%E3%81%AE%E5%9B%BD%E9%81%93","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H38" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I38" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" s="7"/>
+      <c r="K38" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="L38" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M38" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="N38" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261010de57733","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O38" s="8"/>
+      <c r="P38" s="8" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="Q38" s="8" t="n">
+        <v>133.64</v>
+      </c>
+      <c r="R38" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="B40" s="14" t="str">
+        <f aca="false">COUNTA(D2:D38)&amp;"件"</f>
+        <v>37件</v>
+      </c>
+      <c r="H40" s="14" t="s">
+        <v>245</v>
+      </c>
+      <c r="I40" s="14" t="n">
+        <f aca="false">SUM(I2:I38)</f>
+        <v>39</v>
+      </c>
+      <c r="J40" s="14" t="n">
+        <f aca="false">SUM(J2:J38)</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="15" t="s">
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -5356,152 +6879,152 @@
         <v>18</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>201</v>
+        <v>247</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>202</v>
+        <v>248</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B2" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A2)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A2)</f>
+        <v>3</v>
       </c>
       <c r="C2" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A2,事故一覧!$I$2:$I$29)</f>
-        <v>2</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A2,事故一覧!$I$2:$I$38)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B3" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A3)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A3)</f>
         <v>1</v>
       </c>
       <c r="C3" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A3,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A3,事故一覧!$I$2:$I$38)</f>
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>203</v>
+        <v>249</v>
       </c>
       <c r="B4" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A4)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A4)</f>
         <v>0</v>
       </c>
       <c r="C4" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A4,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A4,事故一覧!$I$2:$I$38)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>204</v>
+        <v>250</v>
       </c>
       <c r="B5" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A5)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A5)</f>
         <v>0</v>
       </c>
       <c r="C5" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A5,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A5,事故一覧!$I$2:$I$38)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>205</v>
+        <v>251</v>
       </c>
       <c r="B6" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A6)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A6)</f>
         <v>0</v>
       </c>
       <c r="C6" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A6,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A6,事故一覧!$I$2:$I$38)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="B7" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A7)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A7)</f>
         <v>1</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A7,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A7,事故一覧!$I$2:$I$38)</f>
         <v>1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>206</v>
+        <v>233</v>
       </c>
       <c r="B8" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A8)</f>
-        <v>0</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A8)</f>
+        <v>1</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A8,事故一覧!$I$2:$I$29)</f>
-        <v>0</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A8,事故一覧!$I$2:$I$38)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="B9" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A9)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A9)</f>
+        <v>2</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A9,事故一覧!$I$2:$I$29)</f>
-        <v>1</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A9,事故一覧!$I$2:$I$38)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>207</v>
+        <v>252</v>
       </c>
       <c r="B10" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A10)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A10)</f>
         <v>0</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A10,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A10,事故一覧!$I$2:$I$38)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="B11" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A11)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A11)</f>
         <v>1</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A11,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A11,事故一覧!$I$2:$I$38)</f>
         <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="B12" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A12)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A12)</f>
         <v>2</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A12,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A12,事故一覧!$I$2:$I$38)</f>
         <v>2</v>
       </c>
     </row>
@@ -5510,102 +7033,102 @@
         <v>34</v>
       </c>
       <c r="B13" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A13)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A13)</f>
         <v>1</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A13,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A13,事故一覧!$I$2:$I$38)</f>
         <v>3</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>208</v>
+        <v>253</v>
       </c>
       <c r="B14" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A14)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A14)</f>
         <v>0</v>
       </c>
       <c r="C14" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A14,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A14,事故一覧!$I$2:$I$38)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B15" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A15)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A15)</f>
         <v>2</v>
       </c>
       <c r="C15" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A15,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A15,事故一覧!$I$2:$I$38)</f>
         <v>3</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="16" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="B16" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A16)</f>
-        <v>0</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A16)</f>
+        <v>1</v>
       </c>
       <c r="C16" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A16,事故一覧!$I$2:$I$29)</f>
-        <v>0</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A16,事故一覧!$I$2:$I$38)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
-        <v>210</v>
+        <v>254</v>
       </c>
       <c r="B17" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A17)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A17)</f>
         <v>0</v>
       </c>
       <c r="C17" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A17,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A17,事故一覧!$I$2:$I$38)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="16" t="s">
-        <v>211</v>
+        <v>255</v>
       </c>
       <c r="B18" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A18)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A18)</f>
         <v>0</v>
       </c>
       <c r="C18" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A18,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A18,事故一覧!$I$2:$I$38)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="16" t="s">
-        <v>212</v>
+        <v>256</v>
       </c>
       <c r="B19" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A19)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A19)</f>
         <v>0</v>
       </c>
       <c r="C19" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A19,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A19,事故一覧!$I$2:$I$38)</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>213</v>
+        <v>257</v>
       </c>
       <c r="B20" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A20)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A20)</f>
         <v>0</v>
       </c>
       <c r="C20" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A20,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A20,事故一覧!$I$2:$I$38)</f>
         <v>0</v>
       </c>
     </row>
@@ -5614,102 +7137,102 @@
         <v>55</v>
       </c>
       <c r="B21" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A21)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A21)</f>
         <v>2</v>
       </c>
       <c r="C21" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A21,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A21,事故一覧!$I$2:$I$38)</f>
         <v>2</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="16" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="B22" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A22)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A22)</f>
+        <v>2</v>
       </c>
       <c r="C22" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A22,事故一覧!$I$2:$I$29)</f>
-        <v>1</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A22,事故一覧!$I$2:$I$38)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="16" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="B23" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A23)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A23)</f>
         <v>1</v>
       </c>
       <c r="C23" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A23,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A23,事故一覧!$I$2:$I$38)</f>
         <v>1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="16" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B24" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A24)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A24)</f>
+        <v>2</v>
+      </c>
+      <c r="C24" s="16" t="n">
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A24,事故一覧!$I$2:$I$38)</f>
         <v>1</v>
-      </c>
-      <c r="C24" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A24,事故一覧!$I$2:$I$29)</f>
-        <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="16" t="s">
-        <v>214</v>
+        <v>258</v>
       </c>
       <c r="B25" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A25)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A25)</f>
         <v>0</v>
       </c>
       <c r="C25" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A25,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A25,事故一覧!$I$2:$I$38)</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="16" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="B26" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A26)</f>
-        <v>0</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A26)</f>
+        <v>1</v>
       </c>
       <c r="C26" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A26,事故一覧!$I$2:$I$29)</f>
-        <v>0</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A26,事故一覧!$I$2:$I$38)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="16" t="s">
-        <v>216</v>
+        <v>259</v>
       </c>
       <c r="B27" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A27)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A27)</f>
         <v>0</v>
       </c>
       <c r="C27" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A27,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A27,事故一覧!$I$2:$I$38)</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="16" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B28" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A28)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A28)</f>
         <v>1</v>
       </c>
       <c r="C28" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A28,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A28,事故一覧!$I$2:$I$38)</f>
         <v>1</v>
       </c>
     </row>
@@ -5718,154 +7241,154 @@
         <v>49</v>
       </c>
       <c r="B29" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A29)</f>
-        <v>4</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A29)</f>
+        <v>5</v>
       </c>
       <c r="C29" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A29,事故一覧!$I$2:$I$29)</f>
-        <v>4</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A29,事故一覧!$I$2:$I$38)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="16" t="s">
-        <v>217</v>
+        <v>260</v>
       </c>
       <c r="B30" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A30)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A30)</f>
         <v>0</v>
       </c>
       <c r="C30" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A30,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A30,事故一覧!$I$2:$I$38)</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="16" t="s">
-        <v>218</v>
+        <v>261</v>
       </c>
       <c r="B31" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A31)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A31)</f>
         <v>0</v>
       </c>
       <c r="C31" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A31,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A31,事故一覧!$I$2:$I$38)</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="16" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="B32" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A32)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A32)</f>
         <v>1</v>
       </c>
       <c r="C32" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A32,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A32,事故一覧!$I$2:$I$38)</f>
         <v>1</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="16" t="s">
-        <v>219</v>
+        <v>262</v>
       </c>
       <c r="B33" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A33)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A33)</f>
         <v>0</v>
       </c>
       <c r="C33" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A33,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A33,事故一覧!$I$2:$I$38)</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="16" t="s">
-        <v>220</v>
+        <v>263</v>
       </c>
       <c r="B34" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A34)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A34)</f>
         <v>0</v>
       </c>
       <c r="C34" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A34,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A34,事故一覧!$I$2:$I$38)</f>
         <v>0</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="16" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="B35" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A35)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A35)</f>
         <v>1</v>
       </c>
       <c r="C35" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A35,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A35,事故一覧!$I$2:$I$38)</f>
         <v>1</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="16" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B36" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A36)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A36)</f>
         <v>1</v>
       </c>
       <c r="C36" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A36,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A36,事故一覧!$I$2:$I$38)</f>
         <v>1</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="16" t="s">
-        <v>221</v>
+        <v>264</v>
       </c>
       <c r="B37" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A37)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A37)</f>
         <v>0</v>
       </c>
       <c r="C37" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A37,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A37,事故一覧!$I$2:$I$38)</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="16" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="B38" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A38)</f>
-        <v>0</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A38)</f>
+        <v>1</v>
       </c>
       <c r="C38" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A38,事故一覧!$I$2:$I$29)</f>
-        <v>0</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A38,事故一覧!$I$2:$I$38)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="16" t="s">
-        <v>223</v>
+        <v>265</v>
       </c>
       <c r="B39" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A39)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A39)</f>
         <v>0</v>
       </c>
       <c r="C39" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A39,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A39,事故一覧!$I$2:$I$38)</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="16" t="s">
-        <v>224</v>
+        <v>266</v>
       </c>
       <c r="B40" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A40)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A40)</f>
         <v>0</v>
       </c>
       <c r="C40" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A40,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A40,事故一覧!$I$2:$I$38)</f>
         <v>0</v>
       </c>
     </row>
@@ -5874,116 +7397,116 @@
         <v>42</v>
       </c>
       <c r="B41" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A41)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A41)</f>
         <v>2</v>
       </c>
       <c r="C41" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A41,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A41,事故一覧!$I$2:$I$38)</f>
         <v>2</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="16" t="s">
-        <v>225</v>
+        <v>267</v>
       </c>
       <c r="B42" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A42)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A42)</f>
         <v>0</v>
       </c>
       <c r="C42" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A42,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A42,事故一覧!$I$2:$I$38)</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="16" t="s">
-        <v>226</v>
+        <v>268</v>
       </c>
       <c r="B43" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A43)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A43)</f>
         <v>0</v>
       </c>
       <c r="C43" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A43,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A43,事故一覧!$I$2:$I$38)</f>
         <v>0</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="16" t="s">
-        <v>176</v>
+        <v>201</v>
       </c>
       <c r="B44" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A44)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A44)</f>
         <v>1</v>
       </c>
       <c r="C44" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A44,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A44,事故一覧!$I$2:$I$38)</f>
         <v>1</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="16" t="s">
-        <v>227</v>
+        <v>269</v>
       </c>
       <c r="B45" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A45)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A45)</f>
         <v>0</v>
       </c>
       <c r="C45" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A45,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A45,事故一覧!$I$2:$I$38)</f>
         <v>0</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="16" t="s">
-        <v>228</v>
+        <v>270</v>
       </c>
       <c r="B46" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A46)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A46)</f>
         <v>0</v>
       </c>
       <c r="C46" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A46,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A46,事故一覧!$I$2:$I$38)</f>
         <v>0</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="16" t="s">
-        <v>229</v>
+        <v>271</v>
       </c>
       <c r="B47" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A47)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A47)</f>
         <v>0</v>
       </c>
       <c r="C47" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A47,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A47,事故一覧!$I$2:$I$38)</f>
         <v>0</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="16" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B48" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$29,A48)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A48)</f>
         <v>1</v>
       </c>
       <c r="C48" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$29,A48,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A48,事故一覧!$I$2:$I$38)</f>
         <v>1</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="14" t="s">
-        <v>198</v>
+        <v>244</v>
       </c>
       <c r="B49" s="14" t="n">
         <f aca="false">SUM(B2:B48)</f>
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C49" s="14" t="n">
         <f aca="false">SUM(C2:C48)</f>
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -6002,7 +7525,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -6013,16 +7536,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>230</v>
+        <v>272</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>201</v>
+        <v>247</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>202</v>
+        <v>248</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6033,11 +7556,11 @@
         <v>33</v>
       </c>
       <c r="C2" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$29,A2)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$38,A2)</f>
         <v>2</v>
       </c>
       <c r="D2" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$29,A2,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$38,A2,事故一覧!$I$2:$I$38)</f>
         <v>4</v>
       </c>
     </row>
@@ -6049,11 +7572,11 @@
         <v>48</v>
       </c>
       <c r="C3" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$29,A3)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$38,A3)</f>
         <v>2</v>
       </c>
       <c r="D3" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$29,A3,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$38,A3,事故一覧!$I$2:$I$38)</f>
         <v>2</v>
       </c>
     </row>
@@ -6065,12 +7588,12 @@
         <v>62</v>
       </c>
       <c r="C4" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$29,A4)</f>
-        <v>4</v>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$38,A4)</f>
+        <v>5</v>
       </c>
       <c r="D4" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$29,A4,事故一覧!$I$2:$I$29)</f>
-        <v>4</v>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$38,A4,事故一覧!$I$2:$I$38)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6078,14 +7601,14 @@
         <v>46297</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="C5" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$29,A5)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$38,A5)</f>
         <v>0</v>
       </c>
       <c r="D5" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$29,A5,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$38,A5,事故一覧!$I$2:$I$38)</f>
         <v>0</v>
       </c>
     </row>
@@ -6094,15 +7617,15 @@
         <v>46298</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C6" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$29,A6)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$38,A6)</f>
+        <v>3</v>
       </c>
       <c r="D6" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$29,A6,事故一覧!$I$2:$I$29)</f>
-        <v>2</v>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$38,A6,事故一覧!$I$2:$I$38)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6110,15 +7633,15 @@
         <v>46299</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$29,A7)</f>
-        <v>5</v>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$38,A7)</f>
+        <v>6</v>
       </c>
       <c r="D7" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$29,A7,事故一覧!$I$2:$I$29)</f>
-        <v>5</v>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$38,A7,事故一覧!$I$2:$I$38)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6126,14 +7649,14 @@
         <v>46300</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$29,A8)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$38,A8)</f>
         <v>2</v>
       </c>
       <c r="D8" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$29,A8,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$38,A8,事故一覧!$I$2:$I$38)</f>
         <v>2</v>
       </c>
     </row>
@@ -6145,11 +7668,11 @@
         <v>33</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$29,A9)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$38,A9)</f>
         <v>3</v>
       </c>
       <c r="D9" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$29,A9,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$38,A9,事故一覧!$I$2:$I$38)</f>
         <v>3</v>
       </c>
     </row>
@@ -6161,11 +7684,11 @@
         <v>48</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$29,A10)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$38,A10)</f>
         <v>3</v>
       </c>
       <c r="D10" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$29,A10,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$38,A10,事故一覧!$I$2:$I$38)</f>
         <v>3</v>
       </c>
     </row>
@@ -6177,12 +7700,12 @@
         <v>62</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$29,A11)</f>
-        <v>4</v>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$38,A11)</f>
+        <v>6</v>
       </c>
       <c r="D11" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$29,A11,事故一覧!$I$2:$I$29)</f>
-        <v>4</v>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$38,A11,事故一覧!$I$2:$I$38)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6190,29 +7713,45 @@
         <v>46304</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$29,A12)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$38,A12)</f>
         <v>1</v>
       </c>
       <c r="D12" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$29,A12,事故一覧!$I$2:$I$29)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$38,A12,事故一覧!$I$2:$I$38)</f>
         <v>1</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14" t="s">
-        <v>198</v>
-      </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14" t="n">
-        <f aca="false">SUM(C2:C12)</f>
-        <v>28</v>
-      </c>
-      <c r="D13" s="14" t="n">
-        <f aca="false">SUM(D2:D12)</f>
-        <v>30</v>
+      <c r="A13" s="17" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C13" s="16" t="n">
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$38,A13)</f>
+        <v>4</v>
+      </c>
+      <c r="D13" s="16" t="n">
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$38,A13,事故一覧!$I$2:$I$38)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14" t="n">
+        <f aca="false">SUM(C2:C13)</f>
+        <v>37</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <f aca="false">SUM(D2:D13)</f>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -6231,7 +7770,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
@@ -6255,10 +7794,10 @@
         <v>19</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>231</v>
+        <v>273</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>232</v>
+        <v>274</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>25</v>
@@ -6278,16 +7817,16 @@
         <v>55</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>233</v>
+        <v>275</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>234</v>
+        <v>276</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>235</v>
+        <v>277</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>236</v>
+        <v>278</v>
       </c>
       <c r="G2" s="11" t="s">
         <v>60</v>
@@ -6302,22 +7841,22 @@
         <v>46300</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>237</v>
+        <v>279</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>238</v>
+        <v>280</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>239</v>
+        <v>281</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>240</v>
+        <v>282</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="H3" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.kanaloco.jp/news/social/case","記事を開く")</f>
@@ -6329,22 +7868,22 @@
         <v>46301</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>241</v>
+        <v>283</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>242</v>
+        <v>284</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>235</v>
+        <v>277</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>243</v>
+        <v>285</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>244</v>
+        <v>286</v>
       </c>
       <c r="H4" s="9" t="str">
         <f aca="false">HYPERLINK("https://chunichi.co.jp/article/1321634","記事を開く")</f>
@@ -6356,22 +7895,22 @@
         <v>46303</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>245</v>
+        <v>287</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>246</v>
+        <v>288</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>247</v>
+        <v>289</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>248</v>
+        <v>290</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="H5" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/7fb30b9e75ecfd206159127fe8dfd2e4f5581de1","記事を開く")</f>
@@ -6383,22 +7922,22 @@
         <v>46303</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>249</v>
+        <v>291</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>250</v>
+        <v>292</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>251</v>
+        <v>293</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>252</v>
+        <v>294</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>253</v>
+        <v>193</v>
       </c>
       <c r="H6" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/7d3b2684f57408afa39b1ea0ea5ad798fc8e659f","記事を開く")</f>
@@ -6413,49 +7952,130 @@
         <v>55</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>254</v>
+        <v>295</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>255</v>
+        <v>296</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>256</v>
+        <v>297</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>257</v>
+        <v>298</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="H7" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.nbs-tv.co.jp/news/","記事を開く")</f>
         <v>記事を開く</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="H8" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/06e1158a3abfa398275bfd5e1d8a4e62a117c2ab","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="n">
         <v>46304</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B9" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="H8" s="9" t="str">
+      <c r="C9" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="H9" s="9" t="str">
         <f aca="false">HYPERLINK("https://kobe-np.co.jp/news/jiken/202610/0020910097.shtml","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="H10" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.jiji.com/jc/article?k=2026101000399&amp;g=soc","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="H11" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261010de57740","記事を開く")</f>
         <v>記事を開く</v>
       </c>
     </row>

--- a/全国交通事故データ.xlsx
+++ b/全国交通事故データ.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="345">
   <si>
     <t xml:space="preserve">このファイルについて</t>
   </si>
@@ -129,7 +129,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
     <r>
       <rPr>
@@ -2833,19 +2833,19 @@
     <t xml:space="preserve">熊本県</t>
   </si>
   <si>
-    <t xml:space="preserve">熊本市</t>
-  </si>
-  <si>
-    <t xml:space="preserve">車両相互</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">車同士が衝突し</t>
+    <t xml:space="preserve">熊本市南区</t>
+  </si>
+  <si>
+    <t xml:space="preserve">車両相互（軽自動車同士）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午前、県道で軽自動車同士が衝突し、運転していた</t>
     </r>
     <r>
       <rPr>
@@ -2866,48 +2866,45 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">熊本日日新聞</t>
+    <t xml:space="preserve">川崎町（田川郡）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">車両単独（電柱に衝突）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">乗用車が電柱に衝突し</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">19</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳女性が死亡</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">西日本新聞（速報一覧）</t>
   </si>
   <si>
     <t xml:space="preserve">発生日は掲載日から推定</t>
   </si>
   <si>
-    <t xml:space="preserve">川崎町（田川郡）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">車両単独（電柱に衝突）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">乗用車が電柱に衝突し</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">19</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">歳女性が死亡</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">西日本新聞（速報一覧）</t>
-  </si>
-  <si>
     <t xml:space="preserve">松本市</t>
   </si>
   <si>
@@ -3058,7 +3055,142 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">琴塚の路上</t>
+    <t xml:space="preserve">川越市</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">石原町</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">丁目の市道交差点（信号・横断歩道あり）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分ごろ、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">77</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳女性が軽乗用車にはねられ死亡。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">59</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳の運転手を逮捕</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">埼玉新聞（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Yahoo!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ニュース経由）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">琴塚の県道</t>
   </si>
   <si>
     <t xml:space="preserve">車両対自転車（路線バス）</t>
@@ -3070,7 +3202,24 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">左折しようと側道から本線に出た</t>
+      <t xml:space="preserve">午後</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時半ごろ、側道から本線に入ろうとした</t>
     </r>
     <r>
       <rPr>
@@ -3087,7 +3236,73 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">歳男性の自転車が路線バスと衝突し、約</t>
+      <t xml:space="preserve">歳男性の自転車が路線バスと衝突し死亡。乗客・運転手にけがなし</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">テレビ朝日系（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ANN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">東海テレビ</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">滋賀県</t>
+  </si>
+  <si>
+    <t xml:space="preserve">彦根市</t>
+  </si>
+  <si>
+    <t xml:space="preserve">日夏町の道路脇</t>
+  </si>
+  <si>
+    <t xml:space="preserve">人対車両（道路脇の用水路）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午後</t>
     </r>
     <r>
       <rPr>
@@ -3104,18 +3319,1160 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">時間半後に死亡。乗客・運転手にけがなし</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">発生日は検索結果の記載（</t>
-    </r>
+      <t xml:space="preserve">時</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分ごろ、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">54</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳女性の軽トラックが道路脇で水をくんでいた</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">89</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳の義父に衝突。義父は用水路に落ち死亡</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">京都新聞（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Yahoo!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ニュース経由）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">熊本市中央区</t>
+  </si>
+  <si>
+    <t xml:space="preserve">車両対自転車（バイク）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">夕方、バイクと自転車が衝突し、自転車の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">75</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳男性が死亡。バイクの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">42</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳男性が鎖骨骨折の重傷</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TKU</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">テレビ熊本（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Yahoo!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ニュース経由）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">福島県</t>
+  </si>
+  <si>
+    <t xml:space="preserve">郡山市</t>
+  </si>
+  <si>
+    <t xml:space="preserve">中田町柳橋・県道の信号のない交差点</t>
+  </si>
+  <si>
+    <t xml:space="preserve">車両相互（オートバイと軽乗用車、出合い頭）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午後</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">45</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分ごろ、オートバイの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">52</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳男性が軽乗用車と衝突し死亡</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">福島民友新聞</t>
+  </si>
+  <si>
+    <t xml:space="preserve">香川県</t>
+  </si>
+  <si>
+    <t xml:space="preserve">観音寺市</t>
+  </si>
+  <si>
+    <t xml:space="preserve">豊浜町の国道</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時ごろ、国道を歩いて横断していた</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">78</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳女性が軽乗用車にはねられ死亡。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">76</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳の運転手を現行犯逮捕</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NHK / KSB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">瀬戸内海放送</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">長岡市</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">城岡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">丁目の市道</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">車両単独（ブロック塀に衝突）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午後、乗用車が民家のブロック塀に衝突し、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">56</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳男性が死亡。運転中に病気を発症した可能性</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">死因は心臓突然死とみられる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">松田町</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">国道</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">255</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">号</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">人対車両（横断中か）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">乗用車と衝突した女性が死亡。歩いて道路を横断中だった可能性</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">発生日は一覧の掲載日（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10/11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）から推定</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">横浜市金沢区</t>
+  </si>
+  <si>
+    <t xml:space="preserve">信号のある十字路交差点</t>
+  </si>
+  <si>
+    <t xml:space="preserve">人対車両（トラック）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">トラックにはねられた女性が死亡</t>
+  </si>
+  <si>
+    <t xml:space="preserve">古殿町</t>
+  </si>
+  <si>
+    <t xml:space="preserve">車両相互（軽ワゴン車と軽乗用車、正面衝突）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午後</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時半ごろ、軽ワゴン車と軽乗用車が正面衝突し、軽ワゴン車の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">82</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳男性が死亡、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人がけが</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">合計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">死者数計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">※ 死者数・負傷者数が空欄の行は、報道で人数を確認できなかったもの（合計には含まれない）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">件数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">死者数（判明分）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">岩手県</t>
+  </si>
+  <si>
+    <t xml:space="preserve">宮城県</t>
+  </si>
+  <si>
+    <t xml:space="preserve">秋田県</t>
+  </si>
+  <si>
+    <t xml:space="preserve">栃木県</t>
+  </si>
+  <si>
+    <t xml:space="preserve">東京都</t>
+  </si>
+  <si>
+    <t xml:space="preserve">富山県</t>
+  </si>
+  <si>
+    <t xml:space="preserve">石川県</t>
+  </si>
+  <si>
+    <t xml:space="preserve">福井県</t>
+  </si>
+  <si>
+    <t xml:space="preserve">山梨県</t>
+  </si>
+  <si>
+    <t xml:space="preserve">三重県</t>
+  </si>
+  <si>
+    <t xml:space="preserve">京都府</t>
+  </si>
+  <si>
+    <t xml:space="preserve">奈良県</t>
+  </si>
+  <si>
+    <t xml:space="preserve">和歌山県</t>
+  </si>
+  <si>
+    <t xml:space="preserve">島根県</t>
+  </si>
+  <si>
+    <t xml:space="preserve">岡山県</t>
+  </si>
+  <si>
+    <t xml:space="preserve">徳島県</t>
+  </si>
+  <si>
+    <t xml:space="preserve">愛媛県</t>
+  </si>
+  <si>
+    <t xml:space="preserve">高知県</t>
+  </si>
+  <si>
+    <t xml:space="preserve">佐賀県</t>
+  </si>
+  <si>
+    <t xml:space="preserve">長崎県</t>
+  </si>
+  <si>
+    <t xml:space="preserve">大分県</t>
+  </si>
+  <si>
+    <t xml:space="preserve">宮崎県</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鹿児島県</t>
+  </si>
+  <si>
+    <t xml:space="preserve">日付</t>
+  </si>
+  <si>
+    <t xml:space="preserve">場所</t>
+  </si>
+  <si>
+    <t xml:space="preserve">区分</t>
+  </si>
+  <si>
+    <t xml:space="preserve">大町市</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">JR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">大糸線の踏切</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">踏切（鉄道事故）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳の男子中学生が列車にはねられ死亡</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">横浜市</t>
+  </si>
+  <si>
+    <t xml:space="preserve">コインパーキング</t>
+  </si>
+  <si>
+    <t xml:space="preserve">駐車場内（道路外）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">草刈り中の男性が車にひかれ死亡</t>
+  </si>
+  <si>
+    <t xml:space="preserve">藤沢市</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">JR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">東海道線の踏切</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">シルバーカーを押していた</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">80</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳ぐらいの女性が電車にはねられ死亡</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中日新聞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Web</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">千歳市</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">JR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">千歳線 長都駅構内</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">鉄道事故</t>
+  </si>
+  <si>
+    <t xml:space="preserve">女性が列車にはねられ死亡</t>
+  </si>
+  <si>
+    <t xml:space="preserve">苫小牧市</t>
+  </si>
+  <si>
+    <t xml:space="preserve">一本松町・運送会社の敷地内</t>
+  </si>
+  <si>
+    <t xml:space="preserve">作業事故</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">トラックのタイヤ交換中、破裂に巻き込まれたとみられ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">代男性が死亡</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">山ノ内町</t>
+  </si>
+  <si>
+    <t xml:space="preserve">スキー場</t>
+  </si>
+  <si>
+    <t xml:space="preserve">道路外（オフロードバイク）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">オフロードバイクの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">55</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳男性が死亡</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">富士宮市</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ガソリンスタンド</t>
+  </si>
+  <si>
+    <t xml:space="preserve">道路外（スタンドに車が突入）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午後</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時すぎ、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人が乗った車がガソリンスタンドに突っ込み、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人が死亡、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人がけが</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">静岡第一テレビ（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Yahoo!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ニュース経由）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">西脇市</t>
+  </si>
+  <si>
+    <t xml:space="preserve">斎場の駐車場</t>
+  </si>
+  <si>
+    <t xml:space="preserve">道路外（駐車場から転落）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">車が斎場の駐車場から転落し、運転の男性が死亡、同乗の女性が重傷とみられる（発生日は掲載から推定）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">神戸新聞</t>
+  </si>
+  <si>
+    <t xml:space="preserve">泉佐野市</t>
+  </si>
+  <si>
+    <t xml:space="preserve">交差点（右折中）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">祭礼の事故（だんじり）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時ごろ、右折中のだんじりが横転し、下敷きになった</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">51</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳の会社役員が死亡</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時事通信 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">読売新聞</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">泉大津市</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午後</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分ごろ、右折中のだんじりが転倒し、乗っていた</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">48</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳の会社員が死亡。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人がけが</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">酒田市</t>
+  </si>
+  <si>
+    <t xml:space="preserve">酒田港の岸壁</t>
+  </si>
+  <si>
+    <t xml:space="preserve">道路外（港に車が転落）</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -3131,38 +4488,33 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">日夕方）による</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">滋賀県</t>
-  </si>
-  <si>
-    <t xml:space="preserve">彦根市</t>
-  </si>
-  <si>
-    <t xml:space="preserve">日夏町の道路脇</t>
-  </si>
-  <si>
-    <t xml:space="preserve">人対車両（道路脇の用水路）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">午後</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
+      <t xml:space="preserve">日夜、乗用車が酒田港で海に転落。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日午前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
     </r>
     <r>
       <rPr>
@@ -3179,59 +4531,102 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">分ごろ、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">54</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">歳女性の軽トラックが道路脇で水をくんでいた</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">89</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">歳の義父に衝突。義父は用水路に落ち死亡</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">京都新聞（</t>
+      <t xml:space="preserve">45</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分ごろ岸壁から</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">50m</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の海中で見つかり、乗っていた</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">代の男性が死亡</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">YBC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">山形放送（</t>
     </r>
     <r>
       <rPr>
@@ -3249,778 +4644,6 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">ニュース経由）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">福島県</t>
-  </si>
-  <si>
-    <t xml:space="preserve">郡山市</t>
-  </si>
-  <si>
-    <t xml:space="preserve">中田町柳橋・県道の信号のない交差点</t>
-  </si>
-  <si>
-    <t xml:space="preserve">車両相互（オートバイと軽乗用車、出合い頭）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">午後</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">時</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">45</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">分ごろ、オートバイの</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">52</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">歳男性が軽乗用車と衝突し死亡</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">福島民友新聞</t>
-  </si>
-  <si>
-    <t xml:space="preserve">香川県</t>
-  </si>
-  <si>
-    <t xml:space="preserve">観音寺市</t>
-  </si>
-  <si>
-    <t xml:space="preserve">豊浜町の国道</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">午前</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">時ごろ、国道を歩いて横断していた</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">78</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">歳女性が軽乗用車にはねられ死亡。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">76</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">歳の運転手を現行犯逮捕</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">NHK / KSB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">瀬戸内海放送</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">合計</t>
-  </si>
-  <si>
-    <t xml:space="preserve">死者数計</t>
-  </si>
-  <si>
-    <t xml:space="preserve">※ 死者数・負傷者数が空欄の行は、報道で人数を確認できなかったもの（合計には含まれない）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">件数</t>
-  </si>
-  <si>
-    <t xml:space="preserve">死者数（判明分）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">岩手県</t>
-  </si>
-  <si>
-    <t xml:space="preserve">宮城県</t>
-  </si>
-  <si>
-    <t xml:space="preserve">秋田県</t>
-  </si>
-  <si>
-    <t xml:space="preserve">栃木県</t>
-  </si>
-  <si>
-    <t xml:space="preserve">東京都</t>
-  </si>
-  <si>
-    <t xml:space="preserve">富山県</t>
-  </si>
-  <si>
-    <t xml:space="preserve">石川県</t>
-  </si>
-  <si>
-    <t xml:space="preserve">福井県</t>
-  </si>
-  <si>
-    <t xml:space="preserve">山梨県</t>
-  </si>
-  <si>
-    <t xml:space="preserve">三重県</t>
-  </si>
-  <si>
-    <t xml:space="preserve">京都府</t>
-  </si>
-  <si>
-    <t xml:space="preserve">奈良県</t>
-  </si>
-  <si>
-    <t xml:space="preserve">和歌山県</t>
-  </si>
-  <si>
-    <t xml:space="preserve">島根県</t>
-  </si>
-  <si>
-    <t xml:space="preserve">岡山県</t>
-  </si>
-  <si>
-    <t xml:space="preserve">徳島県</t>
-  </si>
-  <si>
-    <t xml:space="preserve">愛媛県</t>
-  </si>
-  <si>
-    <t xml:space="preserve">高知県</t>
-  </si>
-  <si>
-    <t xml:space="preserve">佐賀県</t>
-  </si>
-  <si>
-    <t xml:space="preserve">長崎県</t>
-  </si>
-  <si>
-    <t xml:space="preserve">大分県</t>
-  </si>
-  <si>
-    <t xml:space="preserve">宮崎県</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鹿児島県</t>
-  </si>
-  <si>
-    <t xml:space="preserve">日付</t>
-  </si>
-  <si>
-    <t xml:space="preserve">場所</t>
-  </si>
-  <si>
-    <t xml:space="preserve">区分</t>
-  </si>
-  <si>
-    <t xml:space="preserve">大町市</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">JR</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">大糸線の踏切</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">踏切（鉄道事故）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">15</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">歳の男子中学生が列車にはねられ死亡</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">横浜市</t>
-  </si>
-  <si>
-    <t xml:space="preserve">コインパーキング</t>
-  </si>
-  <si>
-    <t xml:space="preserve">駐車場内（道路外）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">草刈り中の男性が車にひかれ死亡</t>
-  </si>
-  <si>
-    <t xml:space="preserve">藤沢市</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">JR</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">東海道線の踏切</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">シルバーカーを押していた</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">80</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">歳ぐらいの女性が電車にはねられ死亡</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中日新聞</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Web</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">千歳市</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">JR</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">千歳線 長都駅構内</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">鉄道事故</t>
-  </si>
-  <si>
-    <t xml:space="preserve">女性が列車にはねられ死亡</t>
-  </si>
-  <si>
-    <t xml:space="preserve">苫小牧市</t>
-  </si>
-  <si>
-    <t xml:space="preserve">一本松町・運送会社の敷地内</t>
-  </si>
-  <si>
-    <t xml:space="preserve">作業事故</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">トラックのタイヤ交換中、破裂に巻き込まれたとみられ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">50</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">代男性が死亡</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">山ノ内町</t>
-  </si>
-  <si>
-    <t xml:space="preserve">スキー場</t>
-  </si>
-  <si>
-    <t xml:space="preserve">道路外（オフロードバイク）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">オフロードバイクの</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">55</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">歳男性が死亡</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">富士宮市</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ガソリンスタンド</t>
-  </si>
-  <si>
-    <t xml:space="preserve">道路外（スタンドに車が突入）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">午後</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">時すぎ、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">人が乗った車がガソリンスタンドに突っ込み、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">人が死亡、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">人がけが</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">静岡第一テレビ（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Yahoo!</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ニュース経由）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">西脇市</t>
-  </si>
-  <si>
-    <t xml:space="preserve">斎場の駐車場</t>
-  </si>
-  <si>
-    <t xml:space="preserve">道路外（駐車場から転落）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">車が斎場の駐車場から転落し、運転の男性が死亡、同乗の女性が重傷とみられる（発生日は掲載から推定）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">神戸新聞</t>
-  </si>
-  <si>
-    <t xml:space="preserve">泉佐野市</t>
-  </si>
-  <si>
-    <t xml:space="preserve">交差点（右折中）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">祭礼の事故（だんじり）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">午前</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">11</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">時ごろ、右折中のだんじりが横転し、下敷きになった</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">51</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">歳の会社役員が死亡</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">時事通信 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">読売新聞</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">泉大津市</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">午後</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">時</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">分ごろ、右折中のだんじりが転倒し、乗っていた</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">48</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">歳の会社員が死亡。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">人がけが</t>
     </r>
   </si>
 </sst>
@@ -4391,8 +5014,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="事故一覧" displayName="事故一覧" ref="A1:R38" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:R38"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="事故一覧" displayName="事故一覧" ref="A1:R44" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:R44"/>
   <tableColumns count="18">
     <tableColumn id="1" name="No"/>
     <tableColumn id="2" name="発生日"/>
@@ -4702,7 +5325,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R41"/>
+  <dimension ref="A1:R47"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -6382,7 +7005,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="n">
         <v>30</v>
       </c>
@@ -6399,10 +7022,10 @@
         <v>202</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="G31" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%86%8A%E6%9C%AC%E7%9C%8C%E7%86%8A%E6%9C%AC%E5%B8%82","地図")</f>
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%86%8A%E6%9C%AC%E7%9C%8C%E7%86%8A%E6%9C%AC%E5%B8%82%E5%8D%97%E5%8C%BA%20%E7%9C%8C%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
       <c r="H31" s="8" t="s">
@@ -6415,24 +7038,22 @@
       <c r="K31" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="L31" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="M31" s="8" t="s">
-        <v>205</v>
+      <c r="L31" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M31" s="11" t="s">
+        <v>60</v>
       </c>
       <c r="N31" s="9" t="str">
-        <f aca="false">HYPERLINK("https://kumanichi.com/articles/2044555","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261008de56617","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O31" s="8" t="s">
-        <v>206</v>
-      </c>
+      <c r="O31" s="8"/>
       <c r="P31" s="8" t="n">
-        <v>32.803</v>
+        <v>32.75</v>
       </c>
       <c r="Q31" s="8" t="n">
-        <v>130.708</v>
+        <v>130.7</v>
       </c>
       <c r="R31" s="8" t="s">
         <v>47</v>
@@ -6452,7 +7073,7 @@
         <v>42</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F32" s="8" t="s">
         <v>107</v>
@@ -6462,27 +7083,27 @@
         <v>地図</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="I32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J32" s="7"/>
       <c r="K32" s="8" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="L32" s="12" t="s">
         <v>72</v>
       </c>
       <c r="M32" s="8" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N32" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.nishinippon.co.jp/category/kyushu/flash/","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O32" s="8" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="P32" s="8" t="n">
         <v>33.6</v>
@@ -6508,37 +7129,37 @@
         <v>55</v>
       </c>
       <c r="E33" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="F33" s="8" t="s">
         <v>211</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>212</v>
       </c>
       <c r="G33" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E9%95%B7%E9%87%8E%E7%9C%8C%E6%9D%BE%E6%9C%AC%E5%B8%82%20%E4%BF%A1%E5%8F%B7%E3%81%AE%E3%81%AA%E3%81%84%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
         <v>地図</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I33" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J33" s="7"/>
       <c r="K33" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="L33" s="12" t="s">
         <v>72</v>
       </c>
       <c r="M33" s="11" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="N33" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.nbs-tv.co.jp/news/","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O33" s="8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P33" s="8" t="n">
         <v>36.238</v>
@@ -6558,36 +7179,36 @@
         <v>46304</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D34" s="8" t="s">
         <v>179</v>
       </c>
       <c r="E34" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="F34" s="8" t="s">
         <v>218</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>219</v>
       </c>
       <c r="G34" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%9F%BC%E7%8E%89%E7%9C%8C%E6%96%B0%E5%BA%A7%E5%B8%82%20%E6%A0%97%E5%8E%9F%E3%81%AE%E5%B8%82%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J34" s="7"/>
       <c r="K34" s="11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="L34" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M34" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="N34" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/aad5e62c6ab660cb6e49eb85990d0040b1ed24c0","記事を開く")</f>
@@ -6604,7 +7225,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="n">
         <v>34</v>
       </c>
@@ -6615,46 +7236,44 @@
         <v>92</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>156</v>
+        <v>222</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>223</v>
       </c>
       <c r="G35" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%B2%90%E9%98%9C%E7%9C%8C%E5%B2%90%E9%98%9C%E5%B8%82%20%E7%90%B4%E5%A1%9A%E3%81%AE%E8%B7%AF%E4%B8%8A","地図")</f>
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%9F%BC%E7%8E%89%E7%9C%8C%E5%B7%9D%E8%B6%8A%E5%B8%82%20%E7%9F%B3%E5%8E%9F%E7%94%BA1%E4%B8%81%E7%9B%AE%E3%81%AE%E5%B8%82%E9%81%93%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
         <v>地図</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>224</v>
+        <v>52</v>
       </c>
       <c r="I35" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J35" s="7"/>
       <c r="K35" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="L35" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M35" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="L35" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="M35" s="11" t="s">
-        <v>131</v>
-      </c>
       <c r="N35" s="9" t="str">
-        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/320d09f263be0f0e087a9f5a872f4b62a55ee56a","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/2ae0cd885c9590de27370d50c19c3b5cfe44b814","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O35" s="8" t="s">
-        <v>226</v>
-      </c>
+      <c r="O35" s="8"/>
       <c r="P35" s="8" t="n">
-        <v>35.405</v>
+        <v>35.925</v>
       </c>
       <c r="Q35" s="8" t="n">
-        <v>136.766</v>
+        <v>139.495</v>
       </c>
       <c r="R35" s="8" t="s">
         <v>61</v>
@@ -6671,44 +7290,44 @@
         <v>92</v>
       </c>
       <c r="D36" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="G36" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%B2%90%E9%98%9C%E7%9C%8C%E5%B2%90%E9%98%9C%E5%B8%82%20%E7%90%B4%E5%A1%9A%E3%81%AE%E7%9C%8C%E9%81%93","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H36" s="8" t="s">
         <v>227</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="F36" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="G36" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%BB%8B%E8%B3%80%E7%9C%8C%E5%BD%A6%E6%A0%B9%E5%B8%82%20%E6%97%A5%E5%A4%8F%E7%94%BA%E3%81%AE%E9%81%93%E8%B7%AF%E8%84%87","地図")</f>
-        <v>地図</v>
-      </c>
-      <c r="H36" s="8" t="s">
-        <v>230</v>
       </c>
       <c r="I36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J36" s="7"/>
       <c r="K36" s="8" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="L36" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M36" s="8" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="N36" s="9" t="str">
-        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/b6b6518fd7e974552b652d275fd3240a159e1c74","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://news.ksb.co.jp/ann/article/16957202","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O36" s="8"/>
       <c r="P36" s="8" t="n">
-        <v>35.3</v>
+        <v>35.405</v>
       </c>
       <c r="Q36" s="8" t="n">
-        <v>136.24</v>
+        <v>136.766</v>
       </c>
       <c r="R36" s="8" t="s">
         <v>61</v>
@@ -6725,47 +7344,47 @@
         <v>92</v>
       </c>
       <c r="D37" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="G37" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%BB%8B%E8%B3%80%E7%9C%8C%E5%BD%A6%E6%A0%B9%E5%B8%82%20%E6%97%A5%E5%A4%8F%E7%94%BA%E3%81%AE%E9%81%93%E8%B7%AF%E8%84%87","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H37" s="8" t="s">
         <v>233</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="F37" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="G37" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A6%8F%E5%B3%B6%E7%9C%8C%E9%83%A1%E5%B1%B1%E5%B8%82%20%E4%B8%AD%E7%94%B0%E7%94%BA%E6%9F%B3%E6%A9%8B%20%E7%9C%8C%E9%81%93%E3%81%AE%E4%BF%A1%E5%8F%B7%E3%81%AE%E3%81%AA%E3%81%84%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
-        <v>地図</v>
-      </c>
-      <c r="H37" s="8" t="s">
-        <v>236</v>
       </c>
       <c r="I37" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J37" s="7"/>
       <c r="K37" s="8" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="L37" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M37" s="8" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="N37" s="9" t="str">
-        <f aca="false">HYPERLINK("https://minyu-net.com/news/detail/2026101107353655857","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/b6b6518fd7e974552b652d275fd3240a159e1c74","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O37" s="8"/>
       <c r="P37" s="8" t="n">
-        <v>37.4</v>
+        <v>35.3</v>
       </c>
       <c r="Q37" s="8" t="n">
-        <v>140.36</v>
+        <v>136.24</v>
       </c>
       <c r="R37" s="8" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6779,72 +7398,406 @@
         <v>92</v>
       </c>
       <c r="D38" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="G38" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%86%8A%E6%9C%AC%E7%9C%8C%E7%86%8A%E6%9C%AC%E5%B8%82%E4%B8%AD%E5%A4%AE%E5%8C%BA%20%E7%9C%8C%E9%81%93","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H38" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="I38" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="L38" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M38" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="E38" s="8" t="s">
+      <c r="N38" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/1a327fce60e5134e7b5d69acda6911e914c90555","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O38" s="8"/>
+      <c r="P38" s="8" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="Q38" s="8" t="n">
+        <v>130.71</v>
+      </c>
+      <c r="R38" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="6" t="n">
+        <v>46305</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D39" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="F38" s="8" t="s">
+      <c r="E39" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="G38" s="9" t="str">
+      <c r="F39" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="G39" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A6%8F%E5%B3%B6%E7%9C%8C%E9%83%A1%E5%B1%B1%E5%B8%82%20%E4%B8%AD%E7%94%B0%E7%94%BA%E6%9F%B3%E6%A9%8B%20%E7%9C%8C%E9%81%93%E3%81%AE%E4%BF%A1%E5%8F%B7%E3%81%AE%E3%81%AA%E3%81%84%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H39" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="I39" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" s="7"/>
+      <c r="K39" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="L39" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M39" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="N39" s="9" t="str">
+        <f aca="false">HYPERLINK("https://minyu-net.com/news/detail/2026101107353655857","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O39" s="8"/>
+      <c r="P39" s="8" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="Q39" s="8" t="n">
+        <v>140.36</v>
+      </c>
+      <c r="R39" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="7" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="6" t="n">
+        <v>46305</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="G40" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E9%A6%99%E5%B7%9D%E7%9C%8C%E8%A6%B3%E9%9F%B3%E5%AF%BA%E5%B8%82%20%E8%B1%8A%E6%B5%9C%E7%94%BA%E3%81%AE%E5%9B%BD%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
-      <c r="H38" s="8" t="s">
+      <c r="H40" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I38" s="7" t="n">
+      <c r="I40" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J38" s="7"/>
-      <c r="K38" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="L38" s="10" t="s">
+      <c r="J40" s="7"/>
+      <c r="K40" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="L40" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M38" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="N38" s="9" t="str">
+      <c r="M40" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="N40" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261010de57733","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O38" s="8"/>
-      <c r="P38" s="8" t="n">
+      <c r="O40" s="8"/>
+      <c r="P40" s="8" t="n">
         <v>34.1</v>
       </c>
-      <c r="Q38" s="8" t="n">
+      <c r="Q40" s="8" t="n">
         <v>133.64</v>
       </c>
-      <c r="R38" s="8" t="s">
+      <c r="R40" s="8" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="14" t="s">
-        <v>244</v>
-      </c>
-      <c r="B40" s="14" t="str">
-        <f aca="false">COUNTA(D2:D38)&amp;"件"</f>
-        <v>37件</v>
-      </c>
-      <c r="H40" s="14" t="s">
-        <v>245</v>
-      </c>
-      <c r="I40" s="14" t="n">
-        <f aca="false">SUM(I2:I38)</f>
+    <row r="41" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="6" t="n">
+        <v>46306</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="G41" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%96%B0%E6%BD%9F%E7%9C%8C%E9%95%B7%E5%B2%A1%E5%B8%82%20%E5%9F%8E%E5%B2%A11%E4%B8%81%E7%9B%AE%E3%81%AE%E5%B8%82%E9%81%93","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H41" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="I41" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" s="7"/>
+      <c r="K41" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="L41" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="J40" s="14" t="n">
-        <f aca="false">SUM(J2:J38)</f>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="15" t="s">
-        <v>246</v>
+      <c r="M41" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="N41" s="9" t="str">
+        <f aca="false">HYPERLINK("https://niigata-nippo.co.jp/articles/-/922657","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O41" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="P41" s="8" t="n">
+        <v>37.45</v>
+      </c>
+      <c r="Q41" s="8" t="n">
+        <v>138.82</v>
+      </c>
+      <c r="R41" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="7" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="6" t="n">
+        <v>46306</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="G42" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A5%9E%E5%A5%88%E5%B7%9D%E7%9C%8C%E6%9D%BE%E7%94%B0%E7%94%BA%20%E5%9B%BD%E9%81%93255%E5%8F%B7","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H42" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="I42" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" s="7"/>
+      <c r="K42" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="L42" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="M42" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="N42" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.kanaloco.jp/news/social/case","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O42" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="P42" s="8" t="n">
+        <v>35.343</v>
+      </c>
+      <c r="Q42" s="8" t="n">
+        <v>139.139</v>
+      </c>
+      <c r="R42" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="6" t="n">
+        <v>46306</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="G43" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A5%9E%E5%A5%88%E5%B7%9D%E7%9C%8C%E6%A8%AA%E6%B5%9C%E5%B8%82%E9%87%91%E6%B2%A2%E5%8C%BA%20%E4%BF%A1%E5%8F%B7%E3%81%AE%E3%81%82%E3%82%8B%E5%8D%81%E5%AD%97%E8%B7%AF%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H43" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="I43" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" s="7"/>
+      <c r="K43" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="L43" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="M43" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="N43" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.kanaloco.jp/news/social/case","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O43" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="P43" s="8" t="n">
+        <v>35.335</v>
+      </c>
+      <c r="Q43" s="8" t="n">
+        <v>139.62</v>
+      </c>
+      <c r="R43" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="7" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="6" t="n">
+        <v>46306</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="G44" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A6%8F%E5%B3%B6%E7%9C%8C%E5%8F%A4%E6%AE%BF%E7%94%BA%20%E7%9C%8C%E9%81%93","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H44" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="I44" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K44" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L44" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M44" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="N44" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261012de58048","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O44" s="8"/>
+      <c r="P44" s="8" t="n">
+        <v>37.19</v>
+      </c>
+      <c r="Q44" s="8" t="n">
+        <v>140.55</v>
+      </c>
+      <c r="R44" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="B46" s="14" t="str">
+        <f aca="false">COUNTA(D2:D44)&amp;"件"</f>
+        <v>43件</v>
+      </c>
+      <c r="H46" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="I46" s="14" t="n">
+        <f aca="false">SUM(I2:I44)</f>
+        <v>45</v>
+      </c>
+      <c r="J46" s="14" t="n">
+        <f aca="false">SUM(J2:J44)</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="15" t="s">
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -6879,10 +7832,10 @@
         <v>18</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>247</v>
+        <v>271</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>248</v>
+        <v>272</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6890,11 +7843,11 @@
         <v>93</v>
       </c>
       <c r="B2" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A2)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A2)</f>
         <v>3</v>
       </c>
       <c r="C2" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A2,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A2,事故一覧!$I$2:$I$44)</f>
         <v>3</v>
       </c>
     </row>
@@ -6903,50 +7856,50 @@
         <v>87</v>
       </c>
       <c r="B3" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A3)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A3)</f>
         <v>1</v>
       </c>
       <c r="C3" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A3,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A3,事故一覧!$I$2:$I$44)</f>
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>249</v>
+        <v>273</v>
       </c>
       <c r="B4" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A4)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A4)</f>
         <v>0</v>
       </c>
       <c r="C4" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A4,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A4,事故一覧!$I$2:$I$44)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>250</v>
+        <v>274</v>
       </c>
       <c r="B5" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A5)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A5)</f>
         <v>0</v>
       </c>
       <c r="C5" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A5,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A5,事故一覧!$I$2:$I$44)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>251</v>
+        <v>275</v>
       </c>
       <c r="B6" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A6)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A6)</f>
         <v>0</v>
       </c>
       <c r="C6" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A6,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A6,事故一覧!$I$2:$I$44)</f>
         <v>0</v>
       </c>
     </row>
@@ -6955,25 +7908,25 @@
         <v>146</v>
       </c>
       <c r="B7" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A7)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A7)</f>
         <v>1</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A7,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A7,事故一覧!$I$2:$I$44)</f>
         <v>1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="B8" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A8)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A8)</f>
+        <v>2</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A8,事故一覧!$I$2:$I$38)</f>
-        <v>1</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A8,事故一覧!$I$2:$I$44)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6981,24 +7934,24 @@
         <v>105</v>
       </c>
       <c r="B9" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A9)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A9)</f>
         <v>2</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A9,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A9,事故一覧!$I$2:$I$44)</f>
         <v>2</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>252</v>
+        <v>276</v>
       </c>
       <c r="B10" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A10)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A10)</f>
         <v>0</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A10,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A10,事故一覧!$I$2:$I$44)</f>
         <v>0</v>
       </c>
     </row>
@@ -7007,11 +7960,11 @@
         <v>132</v>
       </c>
       <c r="B11" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A11)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A11)</f>
         <v>1</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A11,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A11,事故一覧!$I$2:$I$44)</f>
         <v>1</v>
       </c>
     </row>
@@ -7020,12 +7973,12 @@
         <v>179</v>
       </c>
       <c r="B12" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A12)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A12)</f>
+        <v>3</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A12,事故一覧!$I$2:$I$38)</f>
-        <v>2</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A12,事故一覧!$I$2:$I$44)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7033,24 +7986,24 @@
         <v>34</v>
       </c>
       <c r="B13" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A13)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A13)</f>
         <v>1</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A13,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A13,事故一覧!$I$2:$I$44)</f>
         <v>3</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>253</v>
+        <v>277</v>
       </c>
       <c r="B14" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A14)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A14)</f>
         <v>0</v>
       </c>
       <c r="C14" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A14,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A14,事故一覧!$I$2:$I$44)</f>
         <v>0</v>
       </c>
     </row>
@@ -7059,12 +8012,12 @@
         <v>82</v>
       </c>
       <c r="B15" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A15)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A15)</f>
+        <v>4</v>
       </c>
       <c r="C15" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A15,事故一覧!$I$2:$I$38)</f>
-        <v>3</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A15,事故一覧!$I$2:$I$44)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7072,63 +8025,63 @@
         <v>195</v>
       </c>
       <c r="B16" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A16)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A16)</f>
+        <v>2</v>
       </c>
       <c r="C16" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A16,事故一覧!$I$2:$I$38)</f>
-        <v>1</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A16,事故一覧!$I$2:$I$44)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
-        <v>254</v>
+        <v>278</v>
       </c>
       <c r="B17" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A17)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A17)</f>
         <v>0</v>
       </c>
       <c r="C17" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A17,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A17,事故一覧!$I$2:$I$44)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="16" t="s">
-        <v>255</v>
+        <v>279</v>
       </c>
       <c r="B18" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A18)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A18)</f>
         <v>0</v>
       </c>
       <c r="C18" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A18,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A18,事故一覧!$I$2:$I$44)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="16" t="s">
-        <v>256</v>
+        <v>280</v>
       </c>
       <c r="B19" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A19)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A19)</f>
         <v>0</v>
       </c>
       <c r="C19" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A19,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A19,事故一覧!$I$2:$I$44)</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>257</v>
+        <v>281</v>
       </c>
       <c r="B20" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A20)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A20)</f>
         <v>0</v>
       </c>
       <c r="C20" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A20,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A20,事故一覧!$I$2:$I$44)</f>
         <v>0</v>
       </c>
     </row>
@@ -7137,11 +8090,11 @@
         <v>55</v>
       </c>
       <c r="B21" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A21)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A21)</f>
         <v>2</v>
       </c>
       <c r="C21" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A21,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A21,事故一覧!$I$2:$I$44)</f>
         <v>2</v>
       </c>
     </row>
@@ -7150,11 +8103,11 @@
         <v>155</v>
       </c>
       <c r="B22" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A22)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A22)</f>
         <v>2</v>
       </c>
       <c r="C22" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A22,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A22,事故一覧!$I$2:$I$44)</f>
         <v>2</v>
       </c>
     </row>
@@ -7163,11 +8116,11 @@
         <v>165</v>
       </c>
       <c r="B23" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A23)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A23)</f>
         <v>1</v>
       </c>
       <c r="C23" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A23,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A23,事故一覧!$I$2:$I$44)</f>
         <v>1</v>
       </c>
     </row>
@@ -7176,50 +8129,50 @@
         <v>74</v>
       </c>
       <c r="B24" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A24)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A24)</f>
         <v>2</v>
       </c>
       <c r="C24" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A24,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A24,事故一覧!$I$2:$I$44)</f>
         <v>1</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="16" t="s">
-        <v>258</v>
+        <v>282</v>
       </c>
       <c r="B25" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A25)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A25)</f>
         <v>0</v>
       </c>
       <c r="C25" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A25,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A25,事故一覧!$I$2:$I$44)</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="16" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B26" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A26)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A26)</f>
         <v>1</v>
       </c>
       <c r="C26" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A26,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A26,事故一覧!$I$2:$I$44)</f>
         <v>1</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="16" t="s">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="B27" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A27)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A27)</f>
         <v>0</v>
       </c>
       <c r="C27" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A27,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A27,事故一覧!$I$2:$I$44)</f>
         <v>0</v>
       </c>
     </row>
@@ -7228,11 +8181,11 @@
         <v>98</v>
       </c>
       <c r="B28" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A28)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A28)</f>
         <v>1</v>
       </c>
       <c r="C28" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A28,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A28,事故一覧!$I$2:$I$44)</f>
         <v>1</v>
       </c>
     </row>
@@ -7241,37 +8194,37 @@
         <v>49</v>
       </c>
       <c r="B29" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A29)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A29)</f>
         <v>5</v>
       </c>
       <c r="C29" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A29,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A29,事故一覧!$I$2:$I$44)</f>
         <v>5</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="16" t="s">
-        <v>260</v>
+        <v>284</v>
       </c>
       <c r="B30" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A30)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A30)</f>
         <v>0</v>
       </c>
       <c r="C30" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A30,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A30,事故一覧!$I$2:$I$44)</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="16" t="s">
-        <v>261</v>
+        <v>285</v>
       </c>
       <c r="B31" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A31)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A31)</f>
         <v>0</v>
       </c>
       <c r="C31" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A31,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A31,事故一覧!$I$2:$I$44)</f>
         <v>0</v>
       </c>
     </row>
@@ -7280,37 +8233,37 @@
         <v>142</v>
       </c>
       <c r="B32" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A32)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A32)</f>
         <v>1</v>
       </c>
       <c r="C32" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A32,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A32,事故一覧!$I$2:$I$44)</f>
         <v>1</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="16" t="s">
-        <v>262</v>
+        <v>286</v>
       </c>
       <c r="B33" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A33)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A33)</f>
         <v>0</v>
       </c>
       <c r="C33" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A33,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A33,事故一覧!$I$2:$I$44)</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="16" t="s">
-        <v>263</v>
+        <v>287</v>
       </c>
       <c r="B34" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A34)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A34)</f>
         <v>0</v>
       </c>
       <c r="C34" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A34,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A34,事故一覧!$I$2:$I$44)</f>
         <v>0</v>
       </c>
     </row>
@@ -7319,11 +8272,11 @@
         <v>119</v>
       </c>
       <c r="B35" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A35)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A35)</f>
         <v>1</v>
       </c>
       <c r="C35" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A35,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A35,事故一覧!$I$2:$I$44)</f>
         <v>1</v>
       </c>
     </row>
@@ -7332,63 +8285,63 @@
         <v>112</v>
       </c>
       <c r="B36" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A36)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A36)</f>
         <v>1</v>
       </c>
       <c r="C36" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A36,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A36,事故一覧!$I$2:$I$44)</f>
         <v>1</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="16" t="s">
-        <v>264</v>
+        <v>288</v>
       </c>
       <c r="B37" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A37)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A37)</f>
         <v>0</v>
       </c>
       <c r="C37" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A37,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A37,事故一覧!$I$2:$I$44)</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="16" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="B38" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A38)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A38)</f>
         <v>1</v>
       </c>
       <c r="C38" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A38,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A38,事故一覧!$I$2:$I$44)</f>
         <v>1</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="16" t="s">
-        <v>265</v>
+        <v>289</v>
       </c>
       <c r="B39" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A39)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A39)</f>
         <v>0</v>
       </c>
       <c r="C39" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A39,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A39,事故一覧!$I$2:$I$44)</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="16" t="s">
-        <v>266</v>
+        <v>290</v>
       </c>
       <c r="B40" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A40)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A40)</f>
         <v>0</v>
       </c>
       <c r="C40" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A40,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A40,事故一覧!$I$2:$I$44)</f>
         <v>0</v>
       </c>
     </row>
@@ -7397,37 +8350,37 @@
         <v>42</v>
       </c>
       <c r="B41" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A41)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A41)</f>
         <v>2</v>
       </c>
       <c r="C41" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A41,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A41,事故一覧!$I$2:$I$44)</f>
         <v>2</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="16" t="s">
-        <v>267</v>
+        <v>291</v>
       </c>
       <c r="B42" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A42)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A42)</f>
         <v>0</v>
       </c>
       <c r="C42" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A42,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A42,事故一覧!$I$2:$I$44)</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="16" t="s">
-        <v>268</v>
+        <v>292</v>
       </c>
       <c r="B43" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A43)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A43)</f>
         <v>0</v>
       </c>
       <c r="C43" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A43,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A43,事故一覧!$I$2:$I$44)</f>
         <v>0</v>
       </c>
     </row>
@@ -7436,50 +8389,50 @@
         <v>201</v>
       </c>
       <c r="B44" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A44)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A44)</f>
+        <v>2</v>
       </c>
       <c r="C44" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A44,事故一覧!$I$2:$I$38)</f>
-        <v>1</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A44,事故一覧!$I$2:$I$44)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="16" t="s">
-        <v>269</v>
+        <v>293</v>
       </c>
       <c r="B45" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A45)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A45)</f>
         <v>0</v>
       </c>
       <c r="C45" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A45,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A45,事故一覧!$I$2:$I$44)</f>
         <v>0</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="16" t="s">
-        <v>270</v>
+        <v>294</v>
       </c>
       <c r="B46" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A46)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A46)</f>
         <v>0</v>
       </c>
       <c r="C46" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A46,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A46,事故一覧!$I$2:$I$44)</f>
         <v>0</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="16" t="s">
-        <v>271</v>
+        <v>295</v>
       </c>
       <c r="B47" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A47)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A47)</f>
         <v>0</v>
       </c>
       <c r="C47" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A47,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A47,事故一覧!$I$2:$I$44)</f>
         <v>0</v>
       </c>
     </row>
@@ -7488,25 +8441,25 @@
         <v>149</v>
       </c>
       <c r="B48" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$38,A48)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A48)</f>
         <v>1</v>
       </c>
       <c r="C48" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$38,A48,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A48,事故一覧!$I$2:$I$44)</f>
         <v>1</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="14" t="s">
-        <v>244</v>
+        <v>268</v>
       </c>
       <c r="B49" s="14" t="n">
         <f aca="false">SUM(B2:B48)</f>
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C49" s="14" t="n">
         <f aca="false">SUM(C2:C48)</f>
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -7525,7 +8478,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -7536,16 +8489,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>272</v>
+        <v>296</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>247</v>
+        <v>271</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>248</v>
+        <v>272</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7556,11 +8509,11 @@
         <v>33</v>
       </c>
       <c r="C2" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$38,A2)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$44,A2)</f>
         <v>2</v>
       </c>
       <c r="D2" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$38,A2,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$44,A2,事故一覧!$I$2:$I$44)</f>
         <v>4</v>
       </c>
     </row>
@@ -7572,11 +8525,11 @@
         <v>48</v>
       </c>
       <c r="C3" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$38,A3)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$44,A3)</f>
         <v>2</v>
       </c>
       <c r="D3" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$38,A3,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$44,A3,事故一覧!$I$2:$I$44)</f>
         <v>2</v>
       </c>
     </row>
@@ -7588,11 +8541,11 @@
         <v>62</v>
       </c>
       <c r="C4" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$38,A4)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$44,A4)</f>
         <v>5</v>
       </c>
       <c r="D4" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$38,A4,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$44,A4,事故一覧!$I$2:$I$44)</f>
         <v>5</v>
       </c>
     </row>
@@ -7601,14 +8554,14 @@
         <v>46297</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C5" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$38,A5)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$44,A5)</f>
         <v>0</v>
       </c>
       <c r="D5" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$38,A5,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$44,A5,事故一覧!$I$2:$I$44)</f>
         <v>0</v>
       </c>
     </row>
@@ -7620,11 +8573,11 @@
         <v>92</v>
       </c>
       <c r="C6" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$38,A6)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$44,A6)</f>
         <v>3</v>
       </c>
       <c r="D6" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$38,A6,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$44,A6,事故一覧!$I$2:$I$44)</f>
         <v>3</v>
       </c>
     </row>
@@ -7636,11 +8589,11 @@
         <v>111</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$38,A7)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$44,A7)</f>
         <v>6</v>
       </c>
       <c r="D7" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$38,A7,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$44,A7,事故一覧!$I$2:$I$44)</f>
         <v>6</v>
       </c>
     </row>
@@ -7652,11 +8605,11 @@
         <v>145</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$38,A8)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$44,A8)</f>
         <v>2</v>
       </c>
       <c r="D8" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$38,A8,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$44,A8,事故一覧!$I$2:$I$44)</f>
         <v>2</v>
       </c>
     </row>
@@ -7668,11 +8621,11 @@
         <v>33</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$38,A9)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$44,A9)</f>
         <v>3</v>
       </c>
       <c r="D9" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$38,A9,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$44,A9,事故一覧!$I$2:$I$44)</f>
         <v>3</v>
       </c>
     </row>
@@ -7684,11 +8637,11 @@
         <v>48</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$38,A10)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$44,A10)</f>
         <v>3</v>
       </c>
       <c r="D10" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$38,A10,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$44,A10,事故一覧!$I$2:$I$44)</f>
         <v>3</v>
       </c>
     </row>
@@ -7700,11 +8653,11 @@
         <v>62</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$38,A11)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$44,A11)</f>
         <v>6</v>
       </c>
       <c r="D11" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$38,A11,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$44,A11,事故一覧!$I$2:$I$44)</f>
         <v>6</v>
       </c>
     </row>
@@ -7713,14 +8666,14 @@
         <v>46304</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$38,A12)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$44,A12)</f>
         <v>1</v>
       </c>
       <c r="D12" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$38,A12,事故一覧!$I$2:$I$38)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$44,A12,事故一覧!$I$2:$I$44)</f>
         <v>1</v>
       </c>
     </row>
@@ -7732,26 +8685,42 @@
         <v>92</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$38,A13)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$44,A13)</f>
+        <v>6</v>
+      </c>
+      <c r="D13" s="16" t="n">
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$44,A13,事故一覧!$I$2:$I$44)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="17" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="C14" s="16" t="n">
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$44,A14)</f>
         <v>4</v>
       </c>
-      <c r="D13" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$38,A13,事故一覧!$I$2:$I$38)</f>
+      <c r="D14" s="16" t="n">
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$44,A14,事故一覧!$I$2:$I$44)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="14" t="s">
-        <v>244</v>
-      </c>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14" t="n">
-        <f aca="false">SUM(C2:C13)</f>
-        <v>37</v>
-      </c>
-      <c r="D14" s="14" t="n">
-        <f aca="false">SUM(D2:D13)</f>
-        <v>39</v>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14" t="n">
+        <f aca="false">SUM(C2:C14)</f>
+        <v>43</v>
+      </c>
+      <c r="D15" s="14" t="n">
+        <f aca="false">SUM(D2:D14)</f>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -7770,7 +8739,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
@@ -7794,10 +8763,10 @@
         <v>19</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>273</v>
+        <v>297</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>274</v>
+        <v>298</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>25</v>
@@ -7817,16 +8786,16 @@
         <v>55</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>275</v>
+        <v>299</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>276</v>
+        <v>300</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>277</v>
+        <v>301</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>278</v>
+        <v>302</v>
       </c>
       <c r="G2" s="11" t="s">
         <v>60</v>
@@ -7844,16 +8813,16 @@
         <v>82</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>279</v>
+        <v>303</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>280</v>
+        <v>304</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>281</v>
+        <v>305</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>282</v>
+        <v>306</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>163</v>
@@ -7871,19 +8840,19 @@
         <v>82</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>283</v>
+        <v>307</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>284</v>
+        <v>308</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>277</v>
+        <v>301</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>285</v>
+        <v>309</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>286</v>
+        <v>310</v>
       </c>
       <c r="H4" s="9" t="str">
         <f aca="false">HYPERLINK("https://chunichi.co.jp/article/1321634","記事を開く")</f>
@@ -7898,16 +8867,16 @@
         <v>93</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>287</v>
+        <v>311</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>288</v>
+        <v>312</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>289</v>
+        <v>313</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>290</v>
+        <v>314</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>188</v>
@@ -7925,16 +8894,16 @@
         <v>93</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>291</v>
+        <v>315</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>292</v>
+        <v>316</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>293</v>
+        <v>317</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>294</v>
+        <v>318</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>193</v>
@@ -7952,19 +8921,19 @@
         <v>55</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>295</v>
+        <v>319</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>297</v>
+        <v>321</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>298</v>
+        <v>322</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H7" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.nbs-tv.co.jp/news/","記事を開く")</f>
@@ -7979,19 +8948,19 @@
         <v>165</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>299</v>
+        <v>323</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>300</v>
+        <v>324</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>301</v>
+        <v>325</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>302</v>
+        <v>326</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>303</v>
+        <v>327</v>
       </c>
       <c r="H8" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/06e1158a3abfa398275bfd5e1d8a4e62a117c2ab","記事を開く")</f>
@@ -8006,19 +8975,19 @@
         <v>49</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>304</v>
+        <v>328</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>305</v>
+        <v>329</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>306</v>
+        <v>330</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>307</v>
+        <v>331</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>308</v>
+        <v>332</v>
       </c>
       <c r="H9" s="9" t="str">
         <f aca="false">HYPERLINK("https://kobe-np.co.jp/news/jiken/202610/0020910097.shtml","記事を開く")</f>
@@ -8033,19 +9002,19 @@
         <v>98</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>309</v>
+        <v>333</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>310</v>
+        <v>334</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>311</v>
+        <v>335</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>312</v>
+        <v>336</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>313</v>
+        <v>337</v>
       </c>
       <c r="H10" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.jiji.com/jc/article?k=2026101000399&amp;g=soc","記事を開く")</f>
@@ -8060,22 +9029,49 @@
         <v>98</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>310</v>
+        <v>334</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>311</v>
+        <v>335</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>315</v>
+        <v>339</v>
       </c>
       <c r="G11" s="11" t="s">
         <v>60</v>
       </c>
       <c r="H11" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261010de57740","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>344</v>
+      </c>
+      <c r="H12" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/db9ea8f1740207802faad3b369c648aebc074777","記事を開く")</f>
         <v>記事を開く</v>
       </c>
     </row>

--- a/全国交通事故データ.xlsx
+++ b/全国交通事故データ.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="369">
   <si>
     <t xml:space="preserve">このファイルについて</t>
   </si>
@@ -129,7 +129,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
     <r>
       <rPr>
@@ -564,6 +564,42 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10/12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">運転の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">19</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳男を過失運転致死傷容疑で逮捕（時事通信）</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">地点付近</t>
   </si>
   <si>
@@ -3190,6 +3226,93 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">大阪市生野区</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">国道</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">号</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">車両相互（トラックとバイク、ひき逃げ）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午前、トラックとバイクが接触し、はじかれたバイクが対向車線の乗用車と衝突。バイクの男性が死亡し、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">65</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳のトラック運転手をひき逃げ容疑で逮捕</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">読売テレビ（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">d </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">メニューニュース経由）</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">琴塚の県道</t>
   </si>
   <si>
@@ -3652,6 +3775,56 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">上尾市</t>
+  </si>
+  <si>
+    <t xml:space="preserve">車両相互（軽乗用車とバイク、炎上）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午後</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時半過ぎ、軽乗用車とバイクが衝突して車が炎上し、車内から運転手の遺体が見つかった。バイクの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳高校生が頭の骨を折る重傷</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">長岡市</t>
   </si>
   <si>
@@ -3715,6 +3888,153 @@
     <t xml:space="preserve">死因は心臓突然死とみられる</t>
   </si>
   <si>
+    <t xml:space="preserve">宜野湾市</t>
+  </si>
+  <si>
+    <t xml:space="preserve">国道の交差点</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">車両相互（軽乗用車</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">夕方、交差点で軽乗用車</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台が衝突し</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人が死亡、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人がけが。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日にも同じ交差点でバイクの事故があった</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RBC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">琉球放送（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Yahoo!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ニュース経由）</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">松田町</t>
   </si>
   <si>
@@ -3854,6 +4174,232 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">人がけが</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">魚沼市</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">車両相互（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台、運転中に病気発症か）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">運転中にくも膜下出血を発症したとみられ、車</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台が絡む事故で意識不明のまま搬送された軽トラックの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">86</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳男性が死亡</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BSN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">新潟放送（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Yahoo!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ニュース経由）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">発生日は検索結果の記載（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日）から推定。病気が原因とみられる</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">福岡市東区</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ふ頭の交差点</t>
+  </si>
+  <si>
+    <t xml:space="preserve">車両相互（右折の軽ライトバンと直進の大型バイク）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">朝、右折しようとした軽ライトバンと、対向から直進してきた大型バイクが衝突し、バイクの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">64</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳男性が死亡</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">KBC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">九州朝日放送 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ FBS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">福岡放送（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Yahoo!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ニュース経由）</t>
     </r>
   </si>
   <si>
@@ -5014,8 +5560,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="事故一覧" displayName="事故一覧" ref="A1:R44" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:R44"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="事故一覧" displayName="事故一覧" ref="A1:R49" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:R49"/>
   <tableColumns count="18">
     <tableColumn id="1" name="No"/>
     <tableColumn id="2" name="発生日"/>
@@ -5325,7 +5871,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R47"/>
+  <dimension ref="A1:R52"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -5448,7 +5994,9 @@
         <f aca="false">HYPERLINK("https://www.jiji.com/jc/article?k=2026092900387&amp;g=soc","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O2" s="8"/>
+      <c r="O2" s="11" t="s">
+        <v>41</v>
+      </c>
       <c r="P2" s="8" t="n">
         <v>35.572</v>
       </c>
@@ -5456,7 +6004,7 @@
         <v>140.128</v>
       </c>
       <c r="R2" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5470,13 +6018,13 @@
         <v>33</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G3" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A6%8F%E5%B2%A1%E7%9C%8C%E7%B2%95%E5%B1%8B%E7%94%BA","地図")</f>
@@ -5490,13 +6038,13 @@
       </c>
       <c r="J3" s="7"/>
       <c r="K3" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L3" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N3" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.google.com/read/CBMif0FVX3lxTFBzdkhIY1I4QzRMN204dE5lRWV3aDBRellDMU92NjMtTWxhZ0xjLVhMbkZMR2tGdnBIZzhBOG1mT2lTQ1R6Rno0ZUxET0FkM3VKSk5VbzRTU0U3NDRPUXZQU3BwUXpIWGlhSmFMQXNzTUJGN2NVSk9SeXJTWEVEYVE","記事を開く")</f>
@@ -5510,7 +6058,7 @@
         <v>130.481</v>
       </c>
       <c r="R3" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5521,36 +6069,36 @@
         <v>46295</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G4" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%85%B5%E5%BA%AB%E7%9C%8C%E8%A5%BF%E5%AE%AE%E5%B8%82%20%E5%9B%BD%E9%81%932%E5%8F%B7","地図")</f>
         <v>地図</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I4" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J4" s="7"/>
       <c r="K4" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L4" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N4" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.kobe-np.co.jp/news/richa/koutsuujiko/202610/0020879803.shtml","記事を開く")</f>
@@ -5564,7 +6112,7 @@
         <v>135.342</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5575,36 +6123,36 @@
         <v>46295</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G5" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E9%95%B7%E9%87%8E%E7%9C%8C%E4%B8%AD%E9%87%8E%E5%B8%82%20%E6%96%B0%E4%BA%95%20%E5%9B%BD%E9%81%93292%E5%8F%B7","地図")</f>
         <v>地図</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I5" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J5" s="7"/>
       <c r="K5" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L5" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N5" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nb-1010039588","記事を開く")</f>
@@ -5618,7 +6166,7 @@
         <v>138.395</v>
       </c>
       <c r="R5" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5629,23 +6177,23 @@
         <v>46296</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G6" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%85%B5%E5%BA%AB%E7%9C%8C%E7%A5%9E%E6%88%B8%E5%B8%82%E4%B8%AD%E5%A4%AE%E5%8C%BA%20%E4%B8%89%E5%AE%AE%20%E3%83%95%E3%83%A9%E3%83%AF%E3%83%BC%E3%83%AD%E3%83%BC%E3%83%89%E3%81%AE%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
         <v>地図</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I6" s="7" t="n">
         <v>1</v>
@@ -5654,20 +6202,20 @@
         <v>3</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L6" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="N6" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261001de53642","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P6" s="8" t="n">
         <v>34.6935</v>
@@ -5676,7 +6224,7 @@
         <v>135.1955</v>
       </c>
       <c r="R6" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5687,43 +6235,43 @@
         <v>46296</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G7" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%85%B5%E5%BA%AB%E7%9C%8C%E7%A5%9E%E6%88%B8%E5%B8%82%E5%85%B5%E5%BA%AB%E5%8C%BA%20%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
         <v>地図</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I7" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L7" s="12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N7" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.kobe-np.co.jp/news/richa/koutsuujiko/202610/0020881285.shtml","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O7" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P7" s="8" t="n">
         <v>34.68</v>
@@ -5732,7 +6280,7 @@
         <v>135.17</v>
       </c>
       <c r="R7" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5743,41 +6291,41 @@
         <v>46296</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G8" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%84%9B%E7%9F%A5%E7%9C%8C%E5%B2%A1%E5%B4%8E%E5%B8%82%20%E6%9D%B1%E5%90%8D%E9%AB%98%E9%80%9F%E9%81%93%E8%B7%AF%20%E4%B8%8B%E3%82%8A%E7%B7%9A","地図")</f>
         <v>地図</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
       <c r="K8" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N8" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.chunichi.co.jp/aichi_news","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O8" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P8" s="8" t="n">
         <v>34.924</v>
@@ -5786,7 +6334,7 @@
         <v>137.204</v>
       </c>
       <c r="R8" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5797,23 +6345,23 @@
         <v>46296</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G9" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A5%9E%E5%A5%88%E5%B7%9D%E7%9C%8C%E5%B7%9D%E5%B4%8E%E5%B8%82%E5%B7%9D%E5%B4%8E%E5%8C%BA%20%E6%9D%B1%E4%BA%AC%E6%B9%BE%E3%82%A2%E3%82%AF%E3%82%A2%E3%83%A9%E3%82%A4%E3%83%B3","地図")</f>
         <v>地図</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I9" s="7" t="n">
         <v>2</v>
@@ -5822,13 +6370,13 @@
         <v>3</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L9" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N9" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261001de53536","記事を開く")</f>
@@ -5842,7 +6390,7 @@
         <v>139.82</v>
       </c>
       <c r="R9" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5853,36 +6401,36 @@
         <v>46296</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G10" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E9%9D%92%E6%A3%AE%E7%9C%8C%E5%85%AB%E6%88%B8%E5%B8%82%20%E6%96%B0%E4%BA%95%E7%94%B0%20%E5%9B%BD%E9%81%9345%E5%8F%B7%E3%81%AE%E6%A8%AA%E6%96%AD%E6%AD%A9%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I10" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J10" s="7"/>
       <c r="K10" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L10" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N10" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nb-6080031283","記事を開く")</f>
@@ -5896,7 +6444,7 @@
         <v>141.545</v>
       </c>
       <c r="R10" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5907,23 +6455,23 @@
         <v>46298</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G11" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%8C%97%E6%B5%B7%E9%81%93%E5%AE%A4%E8%98%AD%E5%B8%82%20%E5%9B%BD%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I11" s="7" t="n">
         <v>1</v>
@@ -5932,13 +6480,13 @@
         <v>2</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L11" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N11" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261004de54150","記事を開く")</f>
@@ -5952,7 +6500,7 @@
         <v>140.98</v>
       </c>
       <c r="R11" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5963,43 +6511,43 @@
         <v>46298</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G12" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%A4%A7%E9%98%AA%E5%BA%9C%E5%A0%BA%E5%B8%82%E5%8C%97%E5%8C%BA%20%E5%8D%97%E8%8A%B1%E7%94%B0%E7%94%BA%E3%81%AE%E8%B7%AF%E4%B8%8A","地図")</f>
         <v>地図</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I12" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J12" s="7"/>
       <c r="K12" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L12" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N12" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.police.pref.osaka.lg.jp/jiken/jiko/14349.html","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O12" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P12" s="8" t="n">
         <v>34.567</v>
@@ -6008,7 +6556,7 @@
         <v>135.513</v>
       </c>
       <c r="R12" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6019,36 +6567,36 @@
         <v>46298</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G13" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E8%8C%A8%E5%9F%8E%E7%9C%8C%E8%A1%8C%E6%96%B9%E5%B8%82","地図")</f>
         <v>地図</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I13" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J13" s="7"/>
       <c r="K13" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L13" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N13" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.ksb.co.jp/ann/article/16938624","記事を開く")</f>
@@ -6062,7 +6610,7 @@
         <v>140.49</v>
       </c>
       <c r="R13" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6073,23 +6621,23 @@
         <v>46299</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G14" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%B1%B1%E5%8F%A3%E7%9C%8C%E5%B1%B1%E5%8F%A3%E5%B8%82%20%E6%B1%9F%E5%B4%8E%E3%81%AE%E5%9B%BD%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I14" s="7" t="n">
         <v>1</v>
@@ -6098,20 +6646,20 @@
         <v>3</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L14" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M14" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N14" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.pref.yamaguchi.lg.jp/site/police/151660.html","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O14" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P14" s="8" t="n">
         <v>34.08</v>
@@ -6120,7 +6668,7 @@
         <v>131.4</v>
       </c>
       <c r="R14" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6131,43 +6679,43 @@
         <v>46299</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G15" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%BA%83%E5%B3%B6%E7%9C%8C%E5%B0%BE%E9%81%93%E5%B8%82%20%E7%89%87%E5%81%B41%E8%BB%8A%E7%B7%9A%E3%81%AE%E7%9C%8C%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I15" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J15" s="7"/>
       <c r="K15" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L15" s="13" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N15" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.think-sp.com/2026/10/08/tw-jitensha-miotosi","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O15" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P15" s="8" t="n">
         <v>34.409</v>
@@ -6176,7 +6724,7 @@
         <v>133.205</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6187,36 +6735,36 @@
         <v>46299</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G16" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%84%9B%E7%9F%A5%E7%9C%8C%E5%90%8D%E5%8F%A4%E5%B1%8B%E5%B8%82%E5%A4%A9%E7%99%BD%E5%8C%BA%20%E9%81%93%E8%B7%AF","地図")</f>
         <v>地図</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I16" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J16" s="7"/>
       <c r="K16" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L16" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M16" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N16" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/2d229adf64509aacdcf58f84ae9c0811ab5c28d4","記事を開く")</f>
@@ -6230,7 +6778,7 @@
         <v>136.97</v>
       </c>
       <c r="R16" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6241,43 +6789,43 @@
         <v>46299</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G17" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%BE%A4%E9%A6%AC%E7%9C%8C%E9%A4%A8%E6%9E%97%E5%B8%82%20%E7%9C%8C%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I17" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J17" s="7"/>
       <c r="K17" s="11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N17" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.jomo-news.co.jp/subcategory/%E4%BA%8B%E4%BB%B6%E3%83%BB%E4%BA%8B%E6%95%85","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O17" s="8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P17" s="8" t="n">
         <v>36.245</v>
@@ -6286,7 +6834,7 @@
         <v>139.542</v>
       </c>
       <c r="R17" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6297,36 +6845,36 @@
         <v>46299</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G18" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E8%8C%A8%E5%9F%8E%E7%9C%8C%E5%9C%9F%E6%B5%A6%E5%B8%82%20%E7%9C%8C%E9%81%93%E3%81%AE%E5%8D%81%E5%AD%97%E8%B7%AF","地図")</f>
         <v>地図</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I18" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J18" s="7"/>
       <c r="K18" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L18" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M18" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N18" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261005de54731","記事を開く")</f>
@@ -6340,7 +6888,7 @@
         <v>140.198</v>
       </c>
       <c r="R18" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6351,36 +6899,36 @@
         <v>46299</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G19" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E9%B3%A5%E5%8F%96%E7%9C%8C%E7%B1%B3%E5%AD%90%E5%B8%82%20%E5%9B%BD%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I19" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L19" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M19" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N19" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261004de54296","記事を開く")</f>
@@ -6394,7 +6942,7 @@
         <v>133.331</v>
       </c>
       <c r="R19" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6405,23 +6953,23 @@
         <v>46300</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G20" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%B1%B1%E5%BD%A2%E7%9C%8C%E9%B6%B4%E5%B2%A1%E5%B8%82%20%E7%9C%8C%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I20" s="7" t="n">
         <v>1</v>
@@ -6430,13 +6978,13 @@
         <v>3</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L20" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M20" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N20" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261006de54976","記事を開く")</f>
@@ -6450,7 +6998,7 @@
         <v>139.827</v>
       </c>
       <c r="R20" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6461,23 +7009,23 @@
         <v>46300</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G21" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%B2%96%E7%B8%84%E7%9C%8C%E9%82%A3%E8%A6%87%E5%B8%82%20%E9%A6%96%E9%87%8C%E6%9C%AB%E5%90%89%E7%94%BA%20%E7%9C%8C%E9%81%9382%E5%8F%B7%E3%81%AE%E4%BF%A1%E5%8F%B7%E3%81%AE%E3%81%82%E3%82%8B%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
         <v>地図</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I21" s="7" t="n">
         <v>1</v>
@@ -6486,13 +7034,13 @@
         <v>1</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L21" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N21" s="9" t="str">
         <f aca="false">HYPERLINK("https://ryukyushimpo.jp/national/entry-5538964.html","記事を開く")</f>
@@ -6506,7 +7054,7 @@
         <v>127.71</v>
       </c>
       <c r="R21" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6520,20 +7068,20 @@
         <v>33</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G22" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%B2%90%E9%98%9C%E7%9C%8C%E5%B2%90%E9%98%9C%E5%B8%82%20%E9%87%91%E8%8F%AF%E5%B1%B1%E3%83%89%E3%83%A9%E3%82%A4%E3%83%96%E3%82%A6%E3%82%A7%E3%82%A4%E3%81%AE%E3%83%98%E3%82%A2%E3%83%94%E3%83%B3%E3%82%AB%E3%83%BC%E3%83%96","地図")</f>
         <v>地図</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I22" s="7" t="n">
         <v>1</v>
@@ -6542,13 +7090,13 @@
         <v>1</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L22" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M22" s="11" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N22" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/50988fd3cbfff6e6a97e45b98587bf9db84c27b3","記事を開く")</f>
@@ -6562,7 +7110,7 @@
         <v>136.786</v>
       </c>
       <c r="R22" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6576,40 +7124,40 @@
         <v>33</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G23" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A5%9E%E5%A5%88%E5%B7%9D%E7%9C%8C%E9%8E%8C%E5%80%89%E5%B8%82","地図")</f>
         <v>地図</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I23" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J23" s="7"/>
       <c r="K23" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N23" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.kanaloco.jp/news/social/case","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O23" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P23" s="8" t="n">
         <v>35.319</v>
@@ -6618,7 +7166,7 @@
         <v>139.547</v>
       </c>
       <c r="R23" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6632,33 +7180,33 @@
         <v>33</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G24" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E9%9D%99%E5%B2%A1%E7%9C%8C%E5%BE%A1%E6%AE%BF%E5%A0%B4%E5%B8%82%20%E5%9B%BD%E9%81%93138%E5%8F%B7","地図")</f>
         <v>地図</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J24" s="7"/>
       <c r="K24" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L24" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M24" s="8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N24" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/3b0fd061a9e7f49b11a18228d212989cc0b2a40a","記事を開く")</f>
@@ -6672,7 +7220,7 @@
         <v>138.95</v>
       </c>
       <c r="R24" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6683,36 +7231,36 @@
         <v>46302</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G25" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%85%B5%E5%BA%AB%E7%9C%8C%E4%BC%8A%E4%B8%B9%E5%B8%82%20%E5%8D%97%E6%9C%AC%E7%94%BA4%E4%B8%81%E7%9B%AE%20%E7%9C%8C%E9%81%93%E3%81%AE%E4%BF%A1%E5%8F%B7%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
         <v>地図</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I25" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J25" s="7"/>
       <c r="K25" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L25" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M25" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N25" s="9" t="str">
         <f aca="false">HYPERLINK("https://kobe-np.co.jp/news/richa/koutsuujiko/202610/0020905694.shtml","記事を開く")</f>
@@ -6726,7 +7274,7 @@
         <v>135.405</v>
       </c>
       <c r="R25" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6737,36 +7285,36 @@
         <v>46302</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G26" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%85%B5%E5%BA%AB%E7%9C%8C%E9%AB%98%E7%A0%82%E5%B8%82%20%E6%9B%BD%E6%A0%B9%E7%94%BA%20%E7%9C%8C%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I26" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J26" s="7"/>
       <c r="K26" s="8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L26" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M26" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N26" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.kobe-np.co.jp/news/richa/koutsuujiko/202610/0020903821.shtml","記事を開く")</f>
@@ -6780,7 +7328,7 @@
         <v>134.775</v>
       </c>
       <c r="R26" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6791,23 +7339,23 @@
         <v>46302</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G27" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%9F%BC%E7%8E%89%E7%9C%8C%E3%81%B5%E3%81%98%E3%81%BF%E9%87%8E%E5%B8%82%20%E3%81%86%E3%82%8C%E3%81%97%E9%87%8E1%E4%B8%81%E7%9B%AE%20%E7%9C%8C%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I27" s="7" t="n">
         <v>1</v>
@@ -6816,13 +7364,13 @@
         <v>1</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L27" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M27" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N27" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261007de56188","記事を開く")</f>
@@ -6836,7 +7384,7 @@
         <v>139.535</v>
       </c>
       <c r="R27" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6847,36 +7395,36 @@
         <v>46303</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G28" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%8C%97%E6%B5%B7%E9%81%93%E6%97%AD%E5%B7%9D%E5%B8%82%20%E7%A5%9E%E6%A5%BD%E5%B2%A16%E6%9D%A16%E4%B8%81%E7%9B%AE%20%E5%B8%82%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I28" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J28" s="7"/>
       <c r="K28" s="11" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L28" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M28" s="8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N28" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/0f9db2f6fa5fe325add09fc111cb3852d3730e34","記事を開く")</f>
@@ -6890,7 +7438,7 @@
         <v>142.383</v>
       </c>
       <c r="R28" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6901,23 +7449,23 @@
         <v>46303</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G29" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%8C%97%E6%B5%B7%E9%81%93%E8%8A%A6%E5%88%A5%E5%B8%82%20%E5%B9%8C%E5%86%85","地図")</f>
         <v>地図</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I29" s="7" t="n">
         <v>1</v>
@@ -6926,20 +7474,20 @@
         <v>3</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L29" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M29" s="11" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N29" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/a5f96326b055568a54d25da884585e33ad80cc8c","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O29" s="11" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P29" s="8" t="n">
         <v>43.517</v>
@@ -6948,7 +7496,7 @@
         <v>142.183</v>
       </c>
       <c r="R29" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6959,36 +7507,36 @@
         <v>46303</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G30" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%96%B0%E6%BD%9F%E7%9C%8C%E6%96%B0%E6%BD%9F%E5%B8%82%E8%A5%BF%E5%8C%BA%20%E9%B3%A5%E5%8E%9F%E3%81%AE%E5%B8%82%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I30" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J30" s="7"/>
       <c r="K30" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L30" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M30" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N30" s="9" t="str">
         <f aca="false">HYPERLINK("https://niigata-nippo.co.jp/articles/-/921297","記事を開く")</f>
@@ -7002,7 +7550,7 @@
         <v>138.93</v>
       </c>
       <c r="R30" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7013,36 +7561,36 @@
         <v>46303</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G31" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%86%8A%E6%9C%AC%E7%9C%8C%E7%86%8A%E6%9C%AC%E5%B8%82%E5%8D%97%E5%8C%BA%20%E7%9C%8C%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J31" s="7"/>
       <c r="K31" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L31" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M31" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N31" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261008de56617","記事を開く")</f>
@@ -7056,7 +7604,7 @@
         <v>130.7</v>
       </c>
       <c r="R31" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7067,43 +7615,43 @@
         <v>46303</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G32" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A6%8F%E5%B2%A1%E7%9C%8C%E5%B7%9D%E5%B4%8E%E7%94%BA%EF%BC%88%E7%94%B0%E5%B7%9D%E9%83%A1%EF%BC%89","地図")</f>
         <v>地図</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J32" s="7"/>
       <c r="K32" s="8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L32" s="12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M32" s="8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N32" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.nishinippon.co.jp/category/kyushu/flash/","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O32" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P32" s="8" t="n">
         <v>33.6</v>
@@ -7112,7 +7660,7 @@
         <v>130.815</v>
       </c>
       <c r="R32" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7123,43 +7671,43 @@
         <v>46303</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G33" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E9%95%B7%E9%87%8E%E7%9C%8C%E6%9D%BE%E6%9C%AC%E5%B8%82%20%E4%BF%A1%E5%8F%B7%E3%81%AE%E3%81%AA%E3%81%84%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
         <v>地図</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I33" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J33" s="7"/>
       <c r="K33" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L33" s="12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M33" s="11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N33" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.nbs-tv.co.jp/news/","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O33" s="8" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P33" s="8" t="n">
         <v>36.238</v>
@@ -7168,7 +7716,7 @@
         <v>137.972</v>
       </c>
       <c r="R33" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7179,36 +7727,36 @@
         <v>46304</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G34" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%9F%BC%E7%8E%89%E7%9C%8C%E6%96%B0%E5%BA%A7%E5%B8%82%20%E6%A0%97%E5%8E%9F%E3%81%AE%E5%B8%82%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J34" s="7"/>
       <c r="K34" s="11" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L34" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M34" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N34" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/aad5e62c6ab660cb6e49eb85990d0040b1ed24c0","記事を開く")</f>
@@ -7222,7 +7770,7 @@
         <v>139.558</v>
       </c>
       <c r="R34" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7233,36 +7781,36 @@
         <v>46305</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G35" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%9F%BC%E7%8E%89%E7%9C%8C%E5%B7%9D%E8%B6%8A%E5%B8%82%20%E7%9F%B3%E5%8E%9F%E7%94%BA1%E4%B8%81%E7%9B%AE%E3%81%AE%E5%B8%82%E9%81%93%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
         <v>地図</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I35" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J35" s="7"/>
       <c r="K35" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L35" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M35" s="8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N35" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/2ae0cd885c9590de27370d50c19c3b5cfe44b814","記事を開く")</f>
@@ -7276,10 +7824,10 @@
         <v>139.495</v>
       </c>
       <c r="R35" s="8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="n">
         <v>35</v>
       </c>
@@ -7287,50 +7835,50 @@
         <v>46305</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>155</v>
+        <v>99</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>156</v>
+        <v>227</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G36" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%B2%90%E9%98%9C%E7%9C%8C%E5%B2%90%E9%98%9C%E5%B8%82%20%E7%90%B4%E5%A1%9A%E3%81%AE%E7%9C%8C%E9%81%93","地図")</f>
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%A4%A7%E9%98%AA%E5%BA%9C%E5%A4%A7%E9%98%AA%E5%B8%82%E7%94%9F%E9%87%8E%E5%8C%BA%20%E5%9B%BD%E9%81%9325%E5%8F%B7","地図")</f>
         <v>地図</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="I36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J36" s="7"/>
       <c r="K36" s="8" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L36" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M36" s="8" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="N36" s="9" t="str">
-        <f aca="false">HYPERLINK("https://news.ksb.co.jp/ann/article/16957202","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://topics.smt.docomo.ne.jp/article/ytv/nation/ytv-2026101009554337","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O36" s="8"/>
       <c r="P36" s="8" t="n">
-        <v>35.405</v>
+        <v>34.66</v>
       </c>
       <c r="Q36" s="8" t="n">
-        <v>136.766</v>
+        <v>135.533</v>
       </c>
       <c r="R36" s="8" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7341,19 +7889,19 @@
         <v>46305</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>230</v>
+        <v>156</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>231</v>
+        <v>157</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>232</v>
       </c>
       <c r="G37" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%BB%8B%E8%B3%80%E7%9C%8C%E5%BD%A6%E6%A0%B9%E5%B8%82%20%E6%97%A5%E5%A4%8F%E7%94%BA%E3%81%AE%E9%81%93%E8%B7%AF%E8%84%87","地図")</f>
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%B2%90%E9%98%9C%E7%9C%8C%E5%B2%90%E9%98%9C%E5%B8%82%20%E7%90%B4%E5%A1%9A%E3%81%AE%E7%9C%8C%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
       <c r="H37" s="8" t="s">
@@ -7373,18 +7921,18 @@
         <v>235</v>
       </c>
       <c r="N37" s="9" t="str">
-        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/b6b6518fd7e974552b652d275fd3240a159e1c74","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://news.ksb.co.jp/ann/article/16957202","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O37" s="8"/>
       <c r="P37" s="8" t="n">
-        <v>35.3</v>
+        <v>35.405</v>
       </c>
       <c r="Q37" s="8" t="n">
-        <v>136.24</v>
+        <v>136.766</v>
       </c>
       <c r="R37" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7395,52 +7943,50 @@
         <v>46305</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>201</v>
+        <v>236</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>134</v>
+        <v>238</v>
       </c>
       <c r="G38" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%86%8A%E6%9C%AC%E7%9C%8C%E7%86%8A%E6%9C%AC%E5%B8%82%E4%B8%AD%E5%A4%AE%E5%8C%BA%20%E7%9C%8C%E9%81%93","地図")</f>
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%BB%8B%E8%B3%80%E7%9C%8C%E5%BD%A6%E6%A0%B9%E5%B8%82%20%E6%97%A5%E5%A4%8F%E7%94%BA%E3%81%AE%E9%81%93%E8%B7%AF%E8%84%87","地図")</f>
         <v>地図</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="I38" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J38" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="J38" s="7"/>
       <c r="K38" s="8" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L38" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M38" s="11" t="s">
-        <v>239</v>
+      <c r="M38" s="8" t="s">
+        <v>241</v>
       </c>
       <c r="N38" s="9" t="str">
-        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/1a327fce60e5134e7b5d69acda6911e914c90555","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/b6b6518fd7e974552b652d275fd3240a159e1c74","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O38" s="8"/>
       <c r="P38" s="8" t="n">
-        <v>32.8</v>
+        <v>35.3</v>
       </c>
       <c r="Q38" s="8" t="n">
-        <v>130.71</v>
+        <v>136.24</v>
       </c>
       <c r="R38" s="8" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7451,19 +7997,19 @@
         <v>46305</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>240</v>
+        <v>202</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>242</v>
+        <v>135</v>
       </c>
       <c r="G39" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A6%8F%E5%B3%B6%E7%9C%8C%E9%83%A1%E5%B1%B1%E5%B8%82%20%E4%B8%AD%E7%94%B0%E7%94%BA%E6%9F%B3%E6%A9%8B%20%E7%9C%8C%E9%81%93%E3%81%AE%E4%BF%A1%E5%8F%B7%E3%81%AE%E3%81%AA%E3%81%84%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%86%8A%E6%9C%AC%E7%9C%8C%E7%86%8A%E6%9C%AC%E5%B8%82%E4%B8%AD%E5%A4%AE%E5%8C%BA%20%E7%9C%8C%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
       <c r="H39" s="8" t="s">
@@ -7472,29 +8018,31 @@
       <c r="I39" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J39" s="7"/>
+      <c r="J39" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="K39" s="8" t="s">
         <v>244</v>
       </c>
       <c r="L39" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M39" s="8" t="s">
+      <c r="M39" s="11" t="s">
         <v>245</v>
       </c>
       <c r="N39" s="9" t="str">
-        <f aca="false">HYPERLINK("https://minyu-net.com/news/detail/2026101107353655857","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/1a327fce60e5134e7b5d69acda6911e914c90555","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O39" s="8"/>
       <c r="P39" s="8" t="n">
-        <v>37.4</v>
+        <v>32.8</v>
       </c>
       <c r="Q39" s="8" t="n">
-        <v>140.36</v>
+        <v>130.71</v>
       </c>
       <c r="R39" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7505,7 +8053,7 @@
         <v>46305</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D40" s="8" t="s">
         <v>246</v>
@@ -7517,38 +8065,38 @@
         <v>248</v>
       </c>
       <c r="G40" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E9%A6%99%E5%B7%9D%E7%9C%8C%E8%A6%B3%E9%9F%B3%E5%AF%BA%E5%B8%82%20%E8%B1%8A%E6%B5%9C%E7%94%BA%E3%81%AE%E5%9B%BD%E9%81%93","地図")</f>
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A6%8F%E5%B3%B6%E7%9C%8C%E9%83%A1%E5%B1%B1%E5%B8%82%20%E4%B8%AD%E7%94%B0%E7%94%BA%E6%9F%B3%E6%A9%8B%20%E7%9C%8C%E9%81%93%E3%81%AE%E4%BF%A1%E5%8F%B7%E3%81%AE%E3%81%AA%E3%81%84%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
         <v>地図</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>52</v>
+        <v>249</v>
       </c>
       <c r="I40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J40" s="7"/>
       <c r="K40" s="8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L40" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M40" s="11" t="s">
-        <v>250</v>
+      <c r="M40" s="8" t="s">
+        <v>251</v>
       </c>
       <c r="N40" s="9" t="str">
-        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261010de57733","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://minyu-net.com/news/detail/2026101107353655857","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O40" s="8"/>
       <c r="P40" s="8" t="n">
-        <v>34.1</v>
+        <v>37.4</v>
       </c>
       <c r="Q40" s="8" t="n">
-        <v>133.64</v>
+        <v>140.36</v>
       </c>
       <c r="R40" s="8" t="s">
-        <v>118</v>
+        <v>48</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7556,58 +8104,56 @@
         <v>40</v>
       </c>
       <c r="B41" s="6" t="n">
-        <v>46306</v>
+        <v>46305</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>195</v>
+        <v>252</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G41" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%96%B0%E6%BD%9F%E7%9C%8C%E9%95%B7%E5%B2%A1%E5%B8%82%20%E5%9F%8E%E5%B2%A11%E4%B8%81%E7%9B%AE%E3%81%AE%E5%B8%82%E9%81%93","地図")</f>
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E9%A6%99%E5%B7%9D%E7%9C%8C%E8%A6%B3%E9%9F%B3%E5%AF%BA%E5%B8%82%20%E8%B1%8A%E6%B5%9C%E7%94%BA%E3%81%AE%E5%9B%BD%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>253</v>
+        <v>53</v>
       </c>
       <c r="I41" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J41" s="7"/>
       <c r="K41" s="8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L41" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M41" s="8" t="s">
-        <v>200</v>
+      <c r="M41" s="11" t="s">
+        <v>256</v>
       </c>
       <c r="N41" s="9" t="str">
-        <f aca="false">HYPERLINK("https://niigata-nippo.co.jp/articles/-/922657","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261010de57733","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O41" s="8" t="s">
-        <v>255</v>
-      </c>
+      <c r="O41" s="8"/>
       <c r="P41" s="8" t="n">
-        <v>37.45</v>
+        <v>34.1</v>
       </c>
       <c r="Q41" s="8" t="n">
-        <v>138.82</v>
+        <v>133.64</v>
       </c>
       <c r="R41" s="8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="n">
         <v>41</v>
       </c>
@@ -7615,19 +8161,19 @@
         <v>46306</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>82</v>
+        <v>180</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>257</v>
+        <v>71</v>
       </c>
       <c r="G42" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A5%9E%E5%A5%88%E5%B7%9D%E7%9C%8C%E6%9D%BE%E7%94%B0%E7%94%BA%20%E5%9B%BD%E9%81%93255%E5%8F%B7","地図")</f>
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%9F%BC%E7%8E%89%E7%9C%8C%E4%B8%8A%E5%B0%BE%E5%B8%82%20%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
         <v>地図</v>
       </c>
       <c r="H42" s="8" t="s">
@@ -7636,31 +8182,31 @@
       <c r="I42" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J42" s="7"/>
+      <c r="J42" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="K42" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="L42" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="M42" s="8" t="s">
-        <v>163</v>
+      <c r="L42" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M42" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="N42" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.kanaloco.jp/news/social/case","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261012de58063","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O42" s="8" t="s">
-        <v>260</v>
-      </c>
+      <c r="O42" s="8"/>
       <c r="P42" s="8" t="n">
-        <v>35.343</v>
+        <v>35.977</v>
       </c>
       <c r="Q42" s="8" t="n">
-        <v>139.139</v>
+        <v>139.593</v>
       </c>
       <c r="R42" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7671,52 +8217,52 @@
         <v>46306</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>82</v>
+        <v>196</v>
       </c>
       <c r="E43" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="F43" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="F43" s="8" t="s">
+      <c r="G43" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%96%B0%E6%BD%9F%E7%9C%8C%E9%95%B7%E5%B2%A1%E5%B8%82%20%E5%9F%8E%E5%B2%A11%E4%B8%81%E7%9B%AE%E3%81%AE%E5%B8%82%E9%81%93","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H43" s="8" t="s">
         <v>262</v>
-      </c>
-      <c r="G43" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A5%9E%E5%A5%88%E5%B7%9D%E7%9C%8C%E6%A8%AA%E6%B5%9C%E5%B8%82%E9%87%91%E6%B2%A2%E5%8C%BA%20%E4%BF%A1%E5%8F%B7%E3%81%AE%E3%81%82%E3%82%8B%E5%8D%81%E5%AD%97%E8%B7%AF%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
-        <v>地図</v>
-      </c>
-      <c r="H43" s="8" t="s">
-        <v>263</v>
       </c>
       <c r="I43" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J43" s="7"/>
       <c r="K43" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="L43" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M43" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="N43" s="9" t="str">
+        <f aca="false">HYPERLINK("https://niigata-nippo.co.jp/articles/-/922657","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O43" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="L43" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="M43" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="N43" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.kanaloco.jp/news/social/case","記事を開く")</f>
-        <v>記事を開く</v>
-      </c>
-      <c r="O43" s="8" t="s">
-        <v>260</v>
-      </c>
       <c r="P43" s="8" t="n">
-        <v>35.335</v>
+        <v>37.45</v>
       </c>
       <c r="Q43" s="8" t="n">
-        <v>139.62</v>
+        <v>138.82</v>
       </c>
       <c r="R43" s="8" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7727,77 +8273,355 @@
         <v>46306</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>240</v>
+        <v>150</v>
       </c>
       <c r="E44" s="8" t="s">
         <v>265</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>134</v>
+        <v>266</v>
       </c>
       <c r="G44" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%B2%96%E7%B8%84%E7%9C%8C%E5%AE%9C%E9%87%8E%E6%B9%BE%E5%B8%82%20%E5%9B%BD%E9%81%93%E3%81%AE%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H44" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="I44" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K44" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="L44" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M44" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="N44" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/63af58045463fe7bfe0503cb05d10228b7ab385a","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O44" s="8"/>
+      <c r="P44" s="8" t="n">
+        <v>26.282</v>
+      </c>
+      <c r="Q44" s="8" t="n">
+        <v>127.778</v>
+      </c>
+      <c r="R44" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="6" t="n">
+        <v>46306</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="G45" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A5%9E%E5%A5%88%E5%B7%9D%E7%9C%8C%E6%9D%BE%E7%94%B0%E7%94%BA%20%E5%9B%BD%E9%81%93255%E5%8F%B7","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="I45" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" s="7"/>
+      <c r="K45" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="L45" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="M45" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="N45" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.kanaloco.jp/news/social/case","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O45" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="P45" s="8" t="n">
+        <v>35.343</v>
+      </c>
+      <c r="Q45" s="8" t="n">
+        <v>139.139</v>
+      </c>
+      <c r="R45" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="6" t="n">
+        <v>46306</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="G46" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A5%9E%E5%A5%88%E5%B7%9D%E7%9C%8C%E6%A8%AA%E6%B5%9C%E5%B8%82%E9%87%91%E6%B2%A2%E5%8C%BA%20%E4%BF%A1%E5%8F%B7%E3%81%AE%E3%81%82%E3%82%8B%E5%8D%81%E5%AD%97%E8%B7%AF%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H46" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="I46" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" s="7"/>
+      <c r="K46" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="L46" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="M46" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="N46" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.kanaloco.jp/news/social/case","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O46" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="P46" s="8" t="n">
+        <v>35.335</v>
+      </c>
+      <c r="Q46" s="8" t="n">
+        <v>139.62</v>
+      </c>
+      <c r="R46" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="6" t="n">
+        <v>46306</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="G47" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A6%8F%E5%B3%B6%E7%9C%8C%E5%8F%A4%E6%AE%BF%E7%94%BA%20%E7%9C%8C%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
-      <c r="H44" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="I44" s="7" t="n">
+      <c r="H47" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I47" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J44" s="7" t="n">
+      <c r="J47" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="K44" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="L44" s="10" t="s">
+      <c r="K47" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="L47" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M44" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="N44" s="9" t="str">
+      <c r="M47" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="N47" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261012de58048","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O44" s="8"/>
-      <c r="P44" s="8" t="n">
+      <c r="O47" s="8"/>
+      <c r="P47" s="8" t="n">
         <v>37.19</v>
       </c>
-      <c r="Q44" s="8" t="n">
+      <c r="Q47" s="8" t="n">
         <v>140.55</v>
       </c>
-      <c r="R44" s="8" t="s">
+      <c r="R47" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="7" t="n">
         <v>47</v>
       </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="14" t="s">
-        <v>268</v>
-      </c>
-      <c r="B46" s="14" t="str">
-        <f aca="false">COUNTA(D2:D44)&amp;"件"</f>
-        <v>43件</v>
-      </c>
-      <c r="H46" s="14" t="s">
-        <v>269</v>
-      </c>
-      <c r="I46" s="14" t="n">
-        <f aca="false">SUM(I2:I44)</f>
-        <v>45</v>
-      </c>
-      <c r="J46" s="14" t="n">
-        <f aca="false">SUM(J2:J44)</f>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="15" t="s">
-        <v>270</v>
+      <c r="B48" s="6" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="G48" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%96%B0%E6%BD%9F%E7%9C%8C%E9%AD%9A%E6%B2%BC%E5%B8%82","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H48" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="I48" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" s="7"/>
+      <c r="K48" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="L48" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="M48" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="N48" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/ab334fba4edce972adb2a6770aa3b1ad4f14b46a","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O48" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="P48" s="8" t="n">
+        <v>37.23</v>
+      </c>
+      <c r="Q48" s="8" t="n">
+        <v>138.96</v>
+      </c>
+      <c r="R48" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="7" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="6" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="G49" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A6%8F%E5%B2%A1%E7%9C%8C%E7%A6%8F%E5%B2%A1%E5%B8%82%E6%9D%B1%E5%8C%BA%20%E3%81%B5%E9%A0%AD%E3%81%AE%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H49" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="I49" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" s="7"/>
+      <c r="K49" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="L49" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M49" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N49" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/6843a963abe9ed0a34e99e653700dd67f3a0c986","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O49" s="8"/>
+      <c r="P49" s="8" t="n">
+        <v>33.66</v>
+      </c>
+      <c r="Q49" s="8" t="n">
+        <v>130.42</v>
+      </c>
+      <c r="R49" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="B51" s="14" t="str">
+        <f aca="false">COUNTA(D2:D49)&amp;"件"</f>
+        <v>48件</v>
+      </c>
+      <c r="H51" s="14" t="s">
+        <v>293</v>
+      </c>
+      <c r="I51" s="14" t="n">
+        <f aca="false">SUM(I2:I49)</f>
+        <v>50</v>
+      </c>
+      <c r="J51" s="14" t="n">
+        <f aca="false">SUM(J2:J49)</f>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="15" t="s">
+        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -7832,153 +8656,153 @@
         <v>18</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>271</v>
+        <v>295</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>272</v>
+        <v>296</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B2" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A2)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A2)</f>
         <v>3</v>
       </c>
       <c r="C2" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A2,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A2,事故一覧!$I$2:$I$49)</f>
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B3" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A3)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A3)</f>
         <v>1</v>
       </c>
       <c r="C3" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A3,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A3,事故一覧!$I$2:$I$49)</f>
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>273</v>
+        <v>297</v>
       </c>
       <c r="B4" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A4)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A4)</f>
         <v>0</v>
       </c>
       <c r="C4" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A4,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A4,事故一覧!$I$2:$I$49)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>274</v>
+        <v>298</v>
       </c>
       <c r="B5" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A5)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A5)</f>
         <v>0</v>
       </c>
       <c r="C5" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A5,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A5,事故一覧!$I$2:$I$49)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>275</v>
+        <v>299</v>
       </c>
       <c r="B6" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A6)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A6)</f>
         <v>0</v>
       </c>
       <c r="C6" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A6,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A6,事故一覧!$I$2:$I$49)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B7" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A7)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A7)</f>
         <v>1</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A7,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A7,事故一覧!$I$2:$I$49)</f>
         <v>1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B8" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A8)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A8)</f>
         <v>2</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A8,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A8,事故一覧!$I$2:$I$49)</f>
         <v>2</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B9" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A9)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A9)</f>
         <v>2</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A9,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A9,事故一覧!$I$2:$I$49)</f>
         <v>2</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>276</v>
+        <v>300</v>
       </c>
       <c r="B10" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A10)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A10)</f>
         <v>0</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A10,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A10,事故一覧!$I$2:$I$49)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B11" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A11)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A11)</f>
         <v>1</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A11,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A11,事故一覧!$I$2:$I$49)</f>
         <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B12" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A12)</f>
-        <v>3</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A12)</f>
+        <v>4</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A12,事故一覧!$I$2:$I$44)</f>
-        <v>3</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A12,事故一覧!$I$2:$I$49)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7986,480 +8810,480 @@
         <v>34</v>
       </c>
       <c r="B13" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A13)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A13)</f>
         <v>1</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A13,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A13,事故一覧!$I$2:$I$49)</f>
         <v>3</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>277</v>
+        <v>301</v>
       </c>
       <c r="B14" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A14)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A14)</f>
         <v>0</v>
       </c>
       <c r="C14" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A14,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A14,事故一覧!$I$2:$I$49)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B15" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A15)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A15)</f>
         <v>4</v>
       </c>
       <c r="C15" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A15,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A15,事故一覧!$I$2:$I$49)</f>
         <v>5</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="16" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B16" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A16)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A16)</f>
+        <v>3</v>
       </c>
       <c r="C16" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A16,事故一覧!$I$2:$I$44)</f>
-        <v>2</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A16,事故一覧!$I$2:$I$49)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
-        <v>278</v>
+        <v>302</v>
       </c>
       <c r="B17" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A17)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A17)</f>
         <v>0</v>
       </c>
       <c r="C17" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A17,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A17,事故一覧!$I$2:$I$49)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="16" t="s">
-        <v>279</v>
+        <v>303</v>
       </c>
       <c r="B18" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A18)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A18)</f>
         <v>0</v>
       </c>
       <c r="C18" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A18,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A18,事故一覧!$I$2:$I$49)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="16" t="s">
-        <v>280</v>
+        <v>304</v>
       </c>
       <c r="B19" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A19)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A19)</f>
         <v>0</v>
       </c>
       <c r="C19" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A19,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A19,事故一覧!$I$2:$I$49)</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>281</v>
+        <v>305</v>
       </c>
       <c r="B20" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A20)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A20)</f>
         <v>0</v>
       </c>
       <c r="C20" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A20,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A20,事故一覧!$I$2:$I$49)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B21" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A21)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A21)</f>
         <v>2</v>
       </c>
       <c r="C21" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A21,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A21,事故一覧!$I$2:$I$49)</f>
         <v>2</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="16" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B22" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A22)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A22)</f>
         <v>2</v>
       </c>
       <c r="C22" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A22,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A22,事故一覧!$I$2:$I$49)</f>
         <v>2</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="16" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B23" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A23)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A23)</f>
         <v>1</v>
       </c>
       <c r="C23" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A23,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A23,事故一覧!$I$2:$I$49)</f>
         <v>1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B24" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A24)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A24)</f>
         <v>2</v>
       </c>
       <c r="C24" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A24,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A24,事故一覧!$I$2:$I$49)</f>
         <v>1</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="16" t="s">
-        <v>282</v>
+        <v>306</v>
       </c>
       <c r="B25" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A25)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A25)</f>
         <v>0</v>
       </c>
       <c r="C25" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A25,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A25,事故一覧!$I$2:$I$49)</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="16" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="B26" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A26)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A26)</f>
         <v>1</v>
       </c>
       <c r="C26" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A26,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A26,事故一覧!$I$2:$I$49)</f>
         <v>1</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="16" t="s">
-        <v>283</v>
+        <v>307</v>
       </c>
       <c r="B27" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A27)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A27)</f>
         <v>0</v>
       </c>
       <c r="C27" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A27,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A27,事故一覧!$I$2:$I$49)</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="16" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B28" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A28)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A28)</f>
+        <v>2</v>
       </c>
       <c r="C28" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A28,事故一覧!$I$2:$I$44)</f>
-        <v>1</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A28,事故一覧!$I$2:$I$49)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B29" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A29)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A29)</f>
         <v>5</v>
       </c>
       <c r="C29" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A29,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A29,事故一覧!$I$2:$I$49)</f>
         <v>5</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="16" t="s">
-        <v>284</v>
+        <v>308</v>
       </c>
       <c r="B30" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A30)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A30)</f>
         <v>0</v>
       </c>
       <c r="C30" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A30,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A30,事故一覧!$I$2:$I$49)</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="16" t="s">
-        <v>285</v>
+        <v>309</v>
       </c>
       <c r="B31" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A31)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A31)</f>
         <v>0</v>
       </c>
       <c r="C31" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A31,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A31,事故一覧!$I$2:$I$49)</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="16" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B32" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A32)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A32)</f>
         <v>1</v>
       </c>
       <c r="C32" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A32,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A32,事故一覧!$I$2:$I$49)</f>
         <v>1</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="16" t="s">
-        <v>286</v>
+        <v>310</v>
       </c>
       <c r="B33" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A33)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A33)</f>
         <v>0</v>
       </c>
       <c r="C33" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A33,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A33,事故一覧!$I$2:$I$49)</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="16" t="s">
-        <v>287</v>
+        <v>311</v>
       </c>
       <c r="B34" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A34)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A34)</f>
         <v>0</v>
       </c>
       <c r="C34" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A34,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A34,事故一覧!$I$2:$I$49)</f>
         <v>0</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="16" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B35" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A35)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A35)</f>
         <v>1</v>
       </c>
       <c r="C35" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A35,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A35,事故一覧!$I$2:$I$49)</f>
         <v>1</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B36" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A36)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A36)</f>
         <v>1</v>
       </c>
       <c r="C36" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A36,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A36,事故一覧!$I$2:$I$49)</f>
         <v>1</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="16" t="s">
-        <v>288</v>
+        <v>312</v>
       </c>
       <c r="B37" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A37)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A37)</f>
         <v>0</v>
       </c>
       <c r="C37" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A37,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A37,事故一覧!$I$2:$I$49)</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="16" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B38" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A38)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A38)</f>
         <v>1</v>
       </c>
       <c r="C38" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A38,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A38,事故一覧!$I$2:$I$49)</f>
         <v>1</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="16" t="s">
-        <v>289</v>
+        <v>313</v>
       </c>
       <c r="B39" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A39)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A39)</f>
         <v>0</v>
       </c>
       <c r="C39" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A39,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A39,事故一覧!$I$2:$I$49)</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="16" t="s">
-        <v>290</v>
+        <v>314</v>
       </c>
       <c r="B40" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A40)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A40)</f>
         <v>0</v>
       </c>
       <c r="C40" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A40,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A40,事故一覧!$I$2:$I$49)</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B41" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A41)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A41)</f>
+        <v>3</v>
       </c>
       <c r="C41" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A41,事故一覧!$I$2:$I$44)</f>
-        <v>2</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A41,事故一覧!$I$2:$I$49)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="16" t="s">
-        <v>291</v>
+        <v>315</v>
       </c>
       <c r="B42" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A42)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A42)</f>
         <v>0</v>
       </c>
       <c r="C42" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A42,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A42,事故一覧!$I$2:$I$49)</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="16" t="s">
-        <v>292</v>
+        <v>316</v>
       </c>
       <c r="B43" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A43)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A43)</f>
         <v>0</v>
       </c>
       <c r="C43" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A43,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A43,事故一覧!$I$2:$I$49)</f>
         <v>0</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="16" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B44" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A44)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A44)</f>
         <v>2</v>
       </c>
       <c r="C44" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A44,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A44,事故一覧!$I$2:$I$49)</f>
         <v>2</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="16" t="s">
-        <v>293</v>
+        <v>317</v>
       </c>
       <c r="B45" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A45)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A45)</f>
         <v>0</v>
       </c>
       <c r="C45" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A45,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A45,事故一覧!$I$2:$I$49)</f>
         <v>0</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="16" t="s">
-        <v>294</v>
+        <v>318</v>
       </c>
       <c r="B46" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A46)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A46)</f>
         <v>0</v>
       </c>
       <c r="C46" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A46,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A46,事故一覧!$I$2:$I$49)</f>
         <v>0</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="16" t="s">
-        <v>295</v>
+        <v>319</v>
       </c>
       <c r="B47" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A47)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A47)</f>
         <v>0</v>
       </c>
       <c r="C47" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A47,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A47,事故一覧!$I$2:$I$49)</f>
         <v>0</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="16" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B48" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$44,A48)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A48)</f>
+        <v>2</v>
       </c>
       <c r="C48" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$44,A48,事故一覧!$I$2:$I$44)</f>
-        <v>1</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A48,事故一覧!$I$2:$I$49)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="14" t="s">
-        <v>268</v>
+        <v>292</v>
       </c>
       <c r="B49" s="14" t="n">
         <f aca="false">SUM(B2:B48)</f>
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C49" s="14" t="n">
         <f aca="false">SUM(C2:C48)</f>
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -8478,7 +9302,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -8489,16 +9313,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>271</v>
+        <v>295</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>272</v>
+        <v>296</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8509,11 +9333,11 @@
         <v>33</v>
       </c>
       <c r="C2" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$44,A2)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$49,A2)</f>
         <v>2</v>
       </c>
       <c r="D2" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$44,A2,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$49,A2,事故一覧!$I$2:$I$49)</f>
         <v>4</v>
       </c>
     </row>
@@ -8522,14 +9346,14 @@
         <v>46295</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C3" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$44,A3)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$49,A3)</f>
         <v>2</v>
       </c>
       <c r="D3" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$44,A3,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$49,A3,事故一覧!$I$2:$I$49)</f>
         <v>2</v>
       </c>
     </row>
@@ -8538,14 +9362,14 @@
         <v>46296</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C4" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$44,A4)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$49,A4)</f>
         <v>5</v>
       </c>
       <c r="D4" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$44,A4,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$49,A4,事故一覧!$I$2:$I$49)</f>
         <v>5</v>
       </c>
     </row>
@@ -8554,14 +9378,14 @@
         <v>46297</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C5" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$44,A5)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$49,A5)</f>
         <v>0</v>
       </c>
       <c r="D5" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$44,A5,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$49,A5,事故一覧!$I$2:$I$49)</f>
         <v>0</v>
       </c>
     </row>
@@ -8570,14 +9394,14 @@
         <v>46298</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C6" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$44,A6)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$49,A6)</f>
         <v>3</v>
       </c>
       <c r="D6" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$44,A6,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$49,A6,事故一覧!$I$2:$I$49)</f>
         <v>3</v>
       </c>
     </row>
@@ -8586,14 +9410,14 @@
         <v>46299</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$44,A7)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$49,A7)</f>
         <v>6</v>
       </c>
       <c r="D7" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$44,A7,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$49,A7,事故一覧!$I$2:$I$49)</f>
         <v>6</v>
       </c>
     </row>
@@ -8602,14 +9426,14 @@
         <v>46300</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$44,A8)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$49,A8)</f>
         <v>2</v>
       </c>
       <c r="D8" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$44,A8,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$49,A8,事故一覧!$I$2:$I$49)</f>
         <v>2</v>
       </c>
     </row>
@@ -8621,11 +9445,11 @@
         <v>33</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$44,A9)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$49,A9)</f>
         <v>3</v>
       </c>
       <c r="D9" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$44,A9,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$49,A9,事故一覧!$I$2:$I$49)</f>
         <v>3</v>
       </c>
     </row>
@@ -8634,14 +9458,14 @@
         <v>46302</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$44,A10)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$49,A10)</f>
         <v>3</v>
       </c>
       <c r="D10" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$44,A10,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$49,A10,事故一覧!$I$2:$I$49)</f>
         <v>3</v>
       </c>
     </row>
@@ -8650,14 +9474,14 @@
         <v>46303</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$44,A11)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$49,A11)</f>
         <v>6</v>
       </c>
       <c r="D11" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$44,A11,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$49,A11,事故一覧!$I$2:$I$49)</f>
         <v>6</v>
       </c>
     </row>
@@ -8666,14 +9490,14 @@
         <v>46304</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$44,A12)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$49,A12)</f>
         <v>1</v>
       </c>
       <c r="D12" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$44,A12,事故一覧!$I$2:$I$44)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$49,A12,事故一覧!$I$2:$I$49)</f>
         <v>1</v>
       </c>
     </row>
@@ -8682,15 +9506,15 @@
         <v>46305</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$44,A13)</f>
-        <v>6</v>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$49,A13)</f>
+        <v>7</v>
       </c>
       <c r="D13" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$44,A13,事故一覧!$I$2:$I$44)</f>
-        <v>6</v>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$49,A13,事故一覧!$I$2:$I$49)</f>
+        <v>7</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8698,29 +9522,45 @@
         <v>46306</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C14" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$44,A14)</f>
-        <v>4</v>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$49,A14)</f>
+        <v>6</v>
       </c>
       <c r="D14" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$44,A14,事故一覧!$I$2:$I$44)</f>
-        <v>4</v>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$49,A14,事故一覧!$I$2:$I$49)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14" t="s">
-        <v>268</v>
-      </c>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14" t="n">
-        <f aca="false">SUM(C2:C14)</f>
-        <v>43</v>
-      </c>
-      <c r="D15" s="14" t="n">
-        <f aca="false">SUM(D2:D14)</f>
-        <v>45</v>
+      <c r="A15" s="17" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="C15" s="16" t="n">
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$49,A15)</f>
+        <v>2</v>
+      </c>
+      <c r="D15" s="16" t="n">
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$49,A15,事故一覧!$I$2:$I$49)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14" t="n">
+        <f aca="false">SUM(C2:C15)</f>
+        <v>48</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <f aca="false">SUM(D2:D15)</f>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -8763,10 +9603,10 @@
         <v>19</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>297</v>
+        <v>321</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>298</v>
+        <v>322</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>25</v>
@@ -8783,22 +9623,22 @@
         <v>46299</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>299</v>
+        <v>323</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>300</v>
+        <v>324</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>301</v>
+        <v>325</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>302</v>
+        <v>326</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H2" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261005de54398","記事を開く")</f>
@@ -8810,22 +9650,22 @@
         <v>46300</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>303</v>
+        <v>327</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>304</v>
+        <v>328</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>305</v>
+        <v>329</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>306</v>
+        <v>330</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H3" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.kanaloco.jp/news/social/case","記事を開く")</f>
@@ -8837,22 +9677,22 @@
         <v>46301</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>307</v>
+        <v>331</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>308</v>
+        <v>332</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>301</v>
+        <v>325</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>309</v>
+        <v>333</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>310</v>
+        <v>334</v>
       </c>
       <c r="H4" s="9" t="str">
         <f aca="false">HYPERLINK("https://chunichi.co.jp/article/1321634","記事を開く")</f>
@@ -8864,22 +9704,22 @@
         <v>46303</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>311</v>
+        <v>335</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>312</v>
+        <v>336</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>313</v>
+        <v>337</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H5" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/7fb30b9e75ecfd206159127fe8dfd2e4f5581de1","記事を開く")</f>
@@ -8891,22 +9731,22 @@
         <v>46303</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>315</v>
+        <v>339</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>316</v>
+        <v>340</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>317</v>
+        <v>341</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>318</v>
+        <v>342</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H6" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/7d3b2684f57408afa39b1ea0ea5ad798fc8e659f","記事を開く")</f>
@@ -8918,22 +9758,22 @@
         <v>46303</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>319</v>
+        <v>343</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>320</v>
+        <v>344</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H7" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.nbs-tv.co.jp/news/","記事を開く")</f>
@@ -8945,22 +9785,22 @@
         <v>46303</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>323</v>
+        <v>347</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>324</v>
+        <v>348</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>325</v>
+        <v>349</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>326</v>
+        <v>350</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>327</v>
+        <v>351</v>
       </c>
       <c r="H8" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/06e1158a3abfa398275bfd5e1d8a4e62a117c2ab","記事を開く")</f>
@@ -8972,22 +9812,22 @@
         <v>46304</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>328</v>
+        <v>352</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>329</v>
+        <v>353</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>330</v>
+        <v>354</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>331</v>
+        <v>355</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>332</v>
+        <v>356</v>
       </c>
       <c r="H9" s="9" t="str">
         <f aca="false">HYPERLINK("https://kobe-np.co.jp/news/jiken/202610/0020910097.shtml","記事を開く")</f>
@@ -8999,22 +9839,22 @@
         <v>46305</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>333</v>
+        <v>357</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>334</v>
+        <v>358</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>335</v>
+        <v>359</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>336</v>
+        <v>360</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>337</v>
+        <v>361</v>
       </c>
       <c r="H10" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.jiji.com/jc/article?k=2026101000399&amp;g=soc","記事を開く")</f>
@@ -9026,22 +9866,22 @@
         <v>46305</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>338</v>
+        <v>362</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>334</v>
+        <v>358</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>335</v>
+        <v>359</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>339</v>
+        <v>363</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H11" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261010de57740","記事を開く")</f>
@@ -9053,22 +9893,22 @@
         <v>46305</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>340</v>
+        <v>364</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>341</v>
+        <v>365</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>343</v>
+        <v>367</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>344</v>
+        <v>368</v>
       </c>
       <c r="H12" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/db9ea8f1740207802faad3b369c648aebc074777","記事を開く")</f>

--- a/全国交通事故データ.xlsx
+++ b/全国交通事故データ.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="394">
   <si>
     <t xml:space="preserve">このファイルについて</t>
   </si>
@@ -129,7 +129,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
     <r>
       <rPr>
@@ -4177,6 +4177,260 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">占冠村</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ニニウの国道</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">274</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">号</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">車両単独（大型バイクの転倒）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時ごろ、ツーリング中の大型バイクが登坂車線で転倒し、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">22</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳男性が死亡</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">北海道ニュース</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">UHB / STV</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ニュース北海道（ニュース一覧）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個別記事の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">URL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は未確認。死亡の報道は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">13</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日付</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">米沢市</t>
+  </si>
+  <si>
+    <t xml:space="preserve">市道</t>
+  </si>
+  <si>
+    <t xml:space="preserve">人対車両（後ろから）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時すぎ、車道の左側を歩いていた</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">代の会社員男性が後ろから来た車にはねられ、午前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時ごろ死亡が確認された</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FNN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">tenki.jp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">経由）</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">魚沼市</t>
   </si>
   <si>
@@ -4403,6 +4657,346 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">堺市</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">阪和自動車道 上り線・美原</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">JCT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">付近</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">車両相互（追突・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時ごろ、トラックが渋滞の最後尾に追突して</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台が絡む玉突き事故。軽自動車の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">73</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳女性が死亡し、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">33</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳のトラック運転手を逮捕。居眠りが原因とみられる</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NHK / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">読売テレビ</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">美濃加茂市</t>
+  </si>
+  <si>
+    <t xml:space="preserve">歩道（道路脇の自動販売機）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">人対車両（歩道に乗り上げ）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時すぎ、歩道に乗り上げた車が、道路脇の自販機で補充作業をしていた</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳男性をはね、車と柱の間に挟まれて死亡。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">67</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳の女を無免許運転の疑いで現行犯逮捕</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NHK / CBC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">テレビ</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">浜松市</t>
+  </si>
+  <si>
+    <t xml:space="preserve">信号のある交差点</t>
+  </si>
+  <si>
+    <t xml:space="preserve">車両対自転車（ダンプカーの左折巻き込み）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">45</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分ごろ、左折しようとしたダンプカーに自転車が巻き込まれ、女性が死亡。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">62</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳の運転手を現行犯逮捕</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">静岡第一テレビ（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Yahoo!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ニュース経由）</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">合計</t>
   </si>
   <si>
@@ -4804,33 +5398,6 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">人がけが</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">静岡第一テレビ（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Yahoo!</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ニュース経由）</t>
     </r>
   </si>
   <si>
@@ -5560,8 +6127,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="事故一覧" displayName="事故一覧" ref="A1:R49" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:R49"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="事故一覧" displayName="事故一覧" ref="A1:R54" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:R54"/>
   <tableColumns count="18">
     <tableColumn id="1" name="No"/>
     <tableColumn id="2" name="発生日"/>
@@ -5871,7 +6438,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R52"/>
+  <dimension ref="A1:R57"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -8500,46 +9067,46 @@
         <v>146</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>196</v>
+        <v>94</v>
       </c>
       <c r="E48" s="8" t="s">
         <v>282</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>108</v>
+        <v>283</v>
       </c>
       <c r="G48" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%96%B0%E6%BD%9F%E7%9C%8C%E9%AD%9A%E6%B2%BC%E5%B8%82","地図")</f>
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%8C%97%E6%B5%B7%E9%81%93%E5%8D%A0%E5%86%A0%E6%9D%91%20%E3%83%8B%E3%83%8B%E3%82%A6%E3%81%AE%E5%9B%BD%E9%81%93274%E5%8F%B7","地図")</f>
         <v>地図</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I48" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J48" s="7"/>
       <c r="K48" s="8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L48" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="M48" s="11" t="s">
-        <v>285</v>
+      <c r="M48" s="8" t="s">
+        <v>286</v>
       </c>
       <c r="N48" s="9" t="str">
-        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/ab334fba4edce972adb2a6770aa3b1ad4f14b46a","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://www.uhb.jp/news/","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O48" s="8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P48" s="8" t="n">
-        <v>37.23</v>
+        <v>43</v>
       </c>
       <c r="Q48" s="8" t="n">
-        <v>138.96</v>
+        <v>142.4</v>
       </c>
       <c r="R48" s="8" t="s">
         <v>48</v>
@@ -8556,72 +9123,344 @@
         <v>146</v>
       </c>
       <c r="D49" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="G49" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%B1%B1%E5%BD%A2%E7%9C%8C%E7%B1%B3%E6%B2%A2%E5%B8%82%20%E5%B8%82%E9%81%93","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H49" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="I49" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" s="7"/>
+      <c r="K49" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="L49" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M49" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="N49" s="9" t="str">
+        <f aca="false">HYPERLINK("https://tenki.jp/news/fnn/7ccd7aa9-d4d9-4789-8e1e-cab7d8bdc2b2.html","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O49" s="8"/>
+      <c r="P49" s="8" t="n">
+        <v>37.922</v>
+      </c>
+      <c r="Q49" s="8" t="n">
+        <v>140.116</v>
+      </c>
+      <c r="R49" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="7" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="6" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="G50" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%96%B0%E6%BD%9F%E7%9C%8C%E9%AD%9A%E6%B2%BC%E5%B8%82","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H50" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="I50" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" s="7"/>
+      <c r="K50" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="L50" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="M50" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="N50" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/ab334fba4edce972adb2a6770aa3b1ad4f14b46a","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O50" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="P50" s="8" t="n">
+        <v>37.23</v>
+      </c>
+      <c r="Q50" s="8" t="n">
+        <v>138.96</v>
+      </c>
+      <c r="R50" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="6" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D51" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E49" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="F49" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="G49" s="9" t="str">
+      <c r="E51" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="G51" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A6%8F%E5%B2%A1%E7%9C%8C%E7%A6%8F%E5%B2%A1%E5%B8%82%E6%9D%B1%E5%8C%BA%20%E3%81%B5%E9%A0%AD%E3%81%AE%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
         <v>地図</v>
       </c>
-      <c r="H49" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="I49" s="7" t="n">
+      <c r="H51" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="I51" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J49" s="7"/>
-      <c r="K49" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="L49" s="10" t="s">
+      <c r="J51" s="7"/>
+      <c r="K51" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="L51" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M49" s="11" t="s">
-        <v>291</v>
-      </c>
-      <c r="N49" s="9" t="str">
+      <c r="M51" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="N51" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/6843a963abe9ed0a34e99e653700dd67f3a0c986","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O49" s="8"/>
-      <c r="P49" s="8" t="n">
+      <c r="O51" s="8"/>
+      <c r="P51" s="8" t="n">
         <v>33.66</v>
       </c>
-      <c r="Q49" s="8" t="n">
+      <c r="Q51" s="8" t="n">
         <v>130.42</v>
       </c>
-      <c r="R49" s="8" t="s">
+      <c r="R51" s="8" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="14" t="s">
-        <v>292</v>
-      </c>
-      <c r="B51" s="14" t="str">
-        <f aca="false">COUNTA(D2:D49)&amp;"件"</f>
-        <v>48件</v>
-      </c>
-      <c r="H51" s="14" t="s">
-        <v>293</v>
-      </c>
-      <c r="I51" s="14" t="n">
-        <f aca="false">SUM(I2:I49)</f>
-        <v>50</v>
-      </c>
-      <c r="J51" s="14" t="n">
-        <f aca="false">SUM(J2:J49)</f>
+    <row r="52" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="7" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="6" t="n">
+        <v>46308</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="G52" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%A4%A7%E9%98%AA%E5%BA%9C%E5%A0%BA%E5%B8%82%20%E9%98%AA%E5%92%8C%E8%87%AA%E5%8B%95%E8%BB%8A%E9%81%93%20%E4%B8%8A%E3%82%8A%E7%B7%9A%20%E7%BE%8E%E5%8E%9FJCT%E4%BB%98%E8%BF%91","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H52" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="I52" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" s="7"/>
+      <c r="K52" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="L52" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M52" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="N52" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261013de58428","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O52" s="8"/>
+      <c r="P52" s="8" t="n">
+        <v>34.555</v>
+      </c>
+      <c r="Q52" s="8" t="n">
+        <v>135.56</v>
+      </c>
+      <c r="R52" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="6" t="n">
+        <v>46308</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="G53" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%B2%90%E9%98%9C%E7%9C%8C%E7%BE%8E%E6%BF%83%E5%8A%A0%E8%8C%82%E5%B8%82%20%E6%AD%A9%E9%81%93","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H53" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="I53" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" s="7"/>
+      <c r="K53" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="L53" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M53" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="N53" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261013de58817","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O53" s="8"/>
+      <c r="P53" s="8" t="n">
+        <v>35.44</v>
+      </c>
+      <c r="Q53" s="8" t="n">
+        <v>137.015</v>
+      </c>
+      <c r="R53" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="7" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="6" t="n">
+        <v>46308</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="G54" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E9%9D%99%E5%B2%A1%E7%9C%8C%E6%B5%9C%E6%9D%BE%E5%B8%82%20%E4%BF%A1%E5%8F%B7%E3%81%AE%E3%81%82%E3%82%8B%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H54" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="I54" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" s="7"/>
+      <c r="K54" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="L54" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M54" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="N54" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/8dfba36c6fd0292b2243591d891611acc31d627b","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O54" s="8"/>
+      <c r="P54" s="8" t="n">
+        <v>34.71</v>
+      </c>
+      <c r="Q54" s="8" t="n">
+        <v>137.726</v>
+      </c>
+      <c r="R54" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="14" t="s">
+        <v>318</v>
+      </c>
+      <c r="B56" s="14" t="str">
+        <f aca="false">COUNTA(D2:D54)&amp;"件"</f>
+        <v>53件</v>
+      </c>
+      <c r="H56" s="14" t="s">
+        <v>319</v>
+      </c>
+      <c r="I56" s="14" t="n">
+        <f aca="false">SUM(I2:I54)</f>
+        <v>55</v>
+      </c>
+      <c r="J56" s="14" t="n">
+        <f aca="false">SUM(J2:J54)</f>
         <v>31</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="15" t="s">
-        <v>294</v>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="15" t="s">
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -8656,10 +9495,10 @@
         <v>18</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>295</v>
+        <v>321</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>296</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8667,12 +9506,12 @@
         <v>94</v>
       </c>
       <c r="B2" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A2)</f>
-        <v>3</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A2)</f>
+        <v>4</v>
       </c>
       <c r="C2" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A2,事故一覧!$I$2:$I$49)</f>
-        <v>3</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A2,事故一覧!$I$2:$I$54)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8680,50 +9519,50 @@
         <v>88</v>
       </c>
       <c r="B3" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A3)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A3)</f>
         <v>1</v>
       </c>
       <c r="C3" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A3,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A3,事故一覧!$I$2:$I$54)</f>
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>297</v>
+        <v>323</v>
       </c>
       <c r="B4" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A4)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A4)</f>
         <v>0</v>
       </c>
       <c r="C4" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A4,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A4,事故一覧!$I$2:$I$54)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>298</v>
+        <v>324</v>
       </c>
       <c r="B5" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A5)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A5)</f>
         <v>0</v>
       </c>
       <c r="C5" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A5,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A5,事故一覧!$I$2:$I$54)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>299</v>
+        <v>325</v>
       </c>
       <c r="B6" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A6)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A6)</f>
         <v>0</v>
       </c>
       <c r="C6" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A6,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A6,事故一覧!$I$2:$I$54)</f>
         <v>0</v>
       </c>
     </row>
@@ -8732,12 +9571,12 @@
         <v>147</v>
       </c>
       <c r="B7" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A7)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A7)</f>
+        <v>2</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A7,事故一覧!$I$2:$I$49)</f>
-        <v>1</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A7,事故一覧!$I$2:$I$54)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8745,11 +9584,11 @@
         <v>246</v>
       </c>
       <c r="B8" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A8)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A8)</f>
         <v>2</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A8,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A8,事故一覧!$I$2:$I$54)</f>
         <v>2</v>
       </c>
     </row>
@@ -8758,24 +9597,24 @@
         <v>106</v>
       </c>
       <c r="B9" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A9)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A9)</f>
         <v>2</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A9,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A9,事故一覧!$I$2:$I$54)</f>
         <v>2</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>300</v>
+        <v>326</v>
       </c>
       <c r="B10" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A10)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A10)</f>
         <v>0</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A10,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A10,事故一覧!$I$2:$I$54)</f>
         <v>0</v>
       </c>
     </row>
@@ -8784,11 +9623,11 @@
         <v>133</v>
       </c>
       <c r="B11" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A11)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A11)</f>
         <v>1</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A11,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A11,事故一覧!$I$2:$I$54)</f>
         <v>1</v>
       </c>
     </row>
@@ -8797,11 +9636,11 @@
         <v>180</v>
       </c>
       <c r="B12" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A12)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A12)</f>
         <v>4</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A12,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A12,事故一覧!$I$2:$I$54)</f>
         <v>4</v>
       </c>
     </row>
@@ -8810,24 +9649,24 @@
         <v>34</v>
       </c>
       <c r="B13" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A13)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A13)</f>
         <v>1</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A13,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A13,事故一覧!$I$2:$I$54)</f>
         <v>3</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>301</v>
+        <v>327</v>
       </c>
       <c r="B14" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A14)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A14)</f>
         <v>0</v>
       </c>
       <c r="C14" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A14,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A14,事故一覧!$I$2:$I$54)</f>
         <v>0</v>
       </c>
     </row>
@@ -8836,11 +9675,11 @@
         <v>83</v>
       </c>
       <c r="B15" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A15)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A15)</f>
         <v>4</v>
       </c>
       <c r="C15" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A15,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A15,事故一覧!$I$2:$I$54)</f>
         <v>5</v>
       </c>
     </row>
@@ -8849,63 +9688,63 @@
         <v>196</v>
       </c>
       <c r="B16" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A16)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A16)</f>
         <v>3</v>
       </c>
       <c r="C16" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A16,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A16,事故一覧!$I$2:$I$54)</f>
         <v>3</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
-        <v>302</v>
+        <v>328</v>
       </c>
       <c r="B17" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A17)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A17)</f>
         <v>0</v>
       </c>
       <c r="C17" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A17,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A17,事故一覧!$I$2:$I$54)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="16" t="s">
-        <v>303</v>
+        <v>329</v>
       </c>
       <c r="B18" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A18)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A18)</f>
         <v>0</v>
       </c>
       <c r="C18" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A18,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A18,事故一覧!$I$2:$I$54)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="16" t="s">
-        <v>304</v>
+        <v>330</v>
       </c>
       <c r="B19" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A19)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A19)</f>
         <v>0</v>
       </c>
       <c r="C19" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A19,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A19,事故一覧!$I$2:$I$54)</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>305</v>
+        <v>331</v>
       </c>
       <c r="B20" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A20)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A20)</f>
         <v>0</v>
       </c>
       <c r="C20" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A20,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A20,事故一覧!$I$2:$I$54)</f>
         <v>0</v>
       </c>
     </row>
@@ -8914,11 +9753,11 @@
         <v>56</v>
       </c>
       <c r="B21" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A21)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A21)</f>
         <v>2</v>
       </c>
       <c r="C21" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A21,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A21,事故一覧!$I$2:$I$54)</f>
         <v>2</v>
       </c>
     </row>
@@ -8927,12 +9766,12 @@
         <v>156</v>
       </c>
       <c r="B22" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A22)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A22)</f>
+        <v>3</v>
       </c>
       <c r="C22" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A22,事故一覧!$I$2:$I$49)</f>
-        <v>2</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A22,事故一覧!$I$2:$I$54)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8940,12 +9779,12 @@
         <v>166</v>
       </c>
       <c r="B23" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A23)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A23)</f>
+        <v>2</v>
       </c>
       <c r="C23" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A23,事故一覧!$I$2:$I$49)</f>
-        <v>1</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A23,事故一覧!$I$2:$I$54)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8953,24 +9792,24 @@
         <v>75</v>
       </c>
       <c r="B24" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A24)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A24)</f>
         <v>2</v>
       </c>
       <c r="C24" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A24,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A24,事故一覧!$I$2:$I$54)</f>
         <v>1</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="16" t="s">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="B25" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A25)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A25)</f>
         <v>0</v>
       </c>
       <c r="C25" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A25,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A25,事故一覧!$I$2:$I$54)</f>
         <v>0</v>
       </c>
     </row>
@@ -8979,24 +9818,24 @@
         <v>236</v>
       </c>
       <c r="B26" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A26)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A26)</f>
         <v>1</v>
       </c>
       <c r="C26" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A26,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A26,事故一覧!$I$2:$I$54)</f>
         <v>1</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="16" t="s">
-        <v>307</v>
+        <v>333</v>
       </c>
       <c r="B27" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A27)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A27)</f>
         <v>0</v>
       </c>
       <c r="C27" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A27,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A27,事故一覧!$I$2:$I$54)</f>
         <v>0</v>
       </c>
     </row>
@@ -9005,12 +9844,12 @@
         <v>99</v>
       </c>
       <c r="B28" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A28)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A28)</f>
+        <v>3</v>
       </c>
       <c r="C28" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A28,事故一覧!$I$2:$I$49)</f>
-        <v>2</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A28,事故一覧!$I$2:$I$54)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9018,37 +9857,37 @@
         <v>50</v>
       </c>
       <c r="B29" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A29)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A29)</f>
         <v>5</v>
       </c>
       <c r="C29" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A29,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A29,事故一覧!$I$2:$I$54)</f>
         <v>5</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="16" t="s">
-        <v>308</v>
+        <v>334</v>
       </c>
       <c r="B30" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A30)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A30)</f>
         <v>0</v>
       </c>
       <c r="C30" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A30,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A30,事故一覧!$I$2:$I$54)</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="16" t="s">
-        <v>309</v>
+        <v>335</v>
       </c>
       <c r="B31" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A31)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A31)</f>
         <v>0</v>
       </c>
       <c r="C31" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A31,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A31,事故一覧!$I$2:$I$54)</f>
         <v>0</v>
       </c>
     </row>
@@ -9057,37 +9896,37 @@
         <v>143</v>
       </c>
       <c r="B32" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A32)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A32)</f>
         <v>1</v>
       </c>
       <c r="C32" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A32,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A32,事故一覧!$I$2:$I$54)</f>
         <v>1</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="16" t="s">
-        <v>310</v>
+        <v>336</v>
       </c>
       <c r="B33" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A33)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A33)</f>
         <v>0</v>
       </c>
       <c r="C33" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A33,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A33,事故一覧!$I$2:$I$54)</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="16" t="s">
-        <v>311</v>
+        <v>337</v>
       </c>
       <c r="B34" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A34)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A34)</f>
         <v>0</v>
       </c>
       <c r="C34" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A34,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A34,事故一覧!$I$2:$I$54)</f>
         <v>0</v>
       </c>
     </row>
@@ -9096,11 +9935,11 @@
         <v>120</v>
       </c>
       <c r="B35" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A35)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A35)</f>
         <v>1</v>
       </c>
       <c r="C35" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A35,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A35,事故一覧!$I$2:$I$54)</f>
         <v>1</v>
       </c>
     </row>
@@ -9109,24 +9948,24 @@
         <v>113</v>
       </c>
       <c r="B36" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A36)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A36)</f>
         <v>1</v>
       </c>
       <c r="C36" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A36,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A36,事故一覧!$I$2:$I$54)</f>
         <v>1</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="16" t="s">
-        <v>312</v>
+        <v>338</v>
       </c>
       <c r="B37" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A37)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A37)</f>
         <v>0</v>
       </c>
       <c r="C37" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A37,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A37,事故一覧!$I$2:$I$54)</f>
         <v>0</v>
       </c>
     </row>
@@ -9135,37 +9974,37 @@
         <v>252</v>
       </c>
       <c r="B38" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A38)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A38)</f>
         <v>1</v>
       </c>
       <c r="C38" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A38,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A38,事故一覧!$I$2:$I$54)</f>
         <v>1</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="16" t="s">
-        <v>313</v>
+        <v>339</v>
       </c>
       <c r="B39" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A39)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A39)</f>
         <v>0</v>
       </c>
       <c r="C39" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A39,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A39,事故一覧!$I$2:$I$54)</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="16" t="s">
-        <v>314</v>
+        <v>340</v>
       </c>
       <c r="B40" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A40)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A40)</f>
         <v>0</v>
       </c>
       <c r="C40" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A40,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A40,事故一覧!$I$2:$I$54)</f>
         <v>0</v>
       </c>
     </row>
@@ -9174,37 +10013,37 @@
         <v>43</v>
       </c>
       <c r="B41" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A41)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A41)</f>
         <v>3</v>
       </c>
       <c r="C41" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A41,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A41,事故一覧!$I$2:$I$54)</f>
         <v>3</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="16" t="s">
-        <v>315</v>
+        <v>341</v>
       </c>
       <c r="B42" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A42)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A42)</f>
         <v>0</v>
       </c>
       <c r="C42" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A42,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A42,事故一覧!$I$2:$I$54)</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="16" t="s">
-        <v>316</v>
+        <v>342</v>
       </c>
       <c r="B43" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A43)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A43)</f>
         <v>0</v>
       </c>
       <c r="C43" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A43,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A43,事故一覧!$I$2:$I$54)</f>
         <v>0</v>
       </c>
     </row>
@@ -9213,50 +10052,50 @@
         <v>202</v>
       </c>
       <c r="B44" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A44)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A44)</f>
         <v>2</v>
       </c>
       <c r="C44" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A44,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A44,事故一覧!$I$2:$I$54)</f>
         <v>2</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="16" t="s">
-        <v>317</v>
+        <v>343</v>
       </c>
       <c r="B45" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A45)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A45)</f>
         <v>0</v>
       </c>
       <c r="C45" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A45,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A45,事故一覧!$I$2:$I$54)</f>
         <v>0</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="16" t="s">
-        <v>318</v>
+        <v>344</v>
       </c>
       <c r="B46" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A46)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A46)</f>
         <v>0</v>
       </c>
       <c r="C46" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A46,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A46,事故一覧!$I$2:$I$54)</f>
         <v>0</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="16" t="s">
-        <v>319</v>
+        <v>345</v>
       </c>
       <c r="B47" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A47)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A47)</f>
         <v>0</v>
       </c>
       <c r="C47" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A47,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A47,事故一覧!$I$2:$I$54)</f>
         <v>0</v>
       </c>
     </row>
@@ -9265,25 +10104,25 @@
         <v>150</v>
       </c>
       <c r="B48" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$49,A48)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A48)</f>
         <v>2</v>
       </c>
       <c r="C48" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$49,A48,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A48,事故一覧!$I$2:$I$54)</f>
         <v>2</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="14" t="s">
-        <v>292</v>
+        <v>318</v>
       </c>
       <c r="B49" s="14" t="n">
         <f aca="false">SUM(B2:B48)</f>
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C49" s="14" t="n">
         <f aca="false">SUM(C2:C48)</f>
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -9302,7 +10141,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -9313,16 +10152,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>320</v>
+        <v>346</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>295</v>
+        <v>321</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>296</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9333,11 +10172,11 @@
         <v>33</v>
       </c>
       <c r="C2" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$49,A2)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$54,A2)</f>
         <v>2</v>
       </c>
       <c r="D2" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$49,A2,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$54,A2,事故一覧!$I$2:$I$54)</f>
         <v>4</v>
       </c>
     </row>
@@ -9349,11 +10188,11 @@
         <v>49</v>
       </c>
       <c r="C3" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$49,A3)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$54,A3)</f>
         <v>2</v>
       </c>
       <c r="D3" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$49,A3,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$54,A3,事故一覧!$I$2:$I$54)</f>
         <v>2</v>
       </c>
     </row>
@@ -9365,11 +10204,11 @@
         <v>63</v>
       </c>
       <c r="C4" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$49,A4)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$54,A4)</f>
         <v>5</v>
       </c>
       <c r="D4" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$49,A4,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$54,A4,事故一覧!$I$2:$I$54)</f>
         <v>5</v>
       </c>
     </row>
@@ -9381,11 +10220,11 @@
         <v>217</v>
       </c>
       <c r="C5" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$49,A5)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$54,A5)</f>
         <v>0</v>
       </c>
       <c r="D5" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$49,A5,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$54,A5,事故一覧!$I$2:$I$54)</f>
         <v>0</v>
       </c>
     </row>
@@ -9397,11 +10236,11 @@
         <v>93</v>
       </c>
       <c r="C6" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$49,A6)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$54,A6)</f>
         <v>3</v>
       </c>
       <c r="D6" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$49,A6,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$54,A6,事故一覧!$I$2:$I$54)</f>
         <v>3</v>
       </c>
     </row>
@@ -9413,11 +10252,11 @@
         <v>112</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$49,A7)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$54,A7)</f>
         <v>6</v>
       </c>
       <c r="D7" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$49,A7,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$54,A7,事故一覧!$I$2:$I$54)</f>
         <v>6</v>
       </c>
     </row>
@@ -9429,11 +10268,11 @@
         <v>146</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$49,A8)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$54,A8)</f>
         <v>2</v>
       </c>
       <c r="D8" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$49,A8,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$54,A8,事故一覧!$I$2:$I$54)</f>
         <v>2</v>
       </c>
     </row>
@@ -9445,11 +10284,11 @@
         <v>33</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$49,A9)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$54,A9)</f>
         <v>3</v>
       </c>
       <c r="D9" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$49,A9,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$54,A9,事故一覧!$I$2:$I$54)</f>
         <v>3</v>
       </c>
     </row>
@@ -9461,11 +10300,11 @@
         <v>49</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$49,A10)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$54,A10)</f>
         <v>3</v>
       </c>
       <c r="D10" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$49,A10,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$54,A10,事故一覧!$I$2:$I$54)</f>
         <v>3</v>
       </c>
     </row>
@@ -9477,11 +10316,11 @@
         <v>63</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$49,A11)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$54,A11)</f>
         <v>6</v>
       </c>
       <c r="D11" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$49,A11,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$54,A11,事故一覧!$I$2:$I$54)</f>
         <v>6</v>
       </c>
     </row>
@@ -9493,11 +10332,11 @@
         <v>217</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$49,A12)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$54,A12)</f>
         <v>1</v>
       </c>
       <c r="D12" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$49,A12,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$54,A12,事故一覧!$I$2:$I$54)</f>
         <v>1</v>
       </c>
     </row>
@@ -9509,11 +10348,11 @@
         <v>93</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$49,A13)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$54,A13)</f>
         <v>7</v>
       </c>
       <c r="D13" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$49,A13,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$54,A13,事故一覧!$I$2:$I$54)</f>
         <v>7</v>
       </c>
     </row>
@@ -9525,11 +10364,11 @@
         <v>112</v>
       </c>
       <c r="C14" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$49,A14)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$54,A14)</f>
         <v>6</v>
       </c>
       <c r="D14" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$49,A14,事故一覧!$I$2:$I$49)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$54,A14,事故一覧!$I$2:$I$54)</f>
         <v>6</v>
       </c>
     </row>
@@ -9541,26 +10380,42 @@
         <v>146</v>
       </c>
       <c r="C15" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$49,A15)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$54,A15)</f>
+        <v>4</v>
       </c>
       <c r="D15" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$49,A15,事故一覧!$I$2:$I$49)</f>
-        <v>2</v>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$54,A15,事故一覧!$I$2:$I$54)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="14" t="s">
-        <v>292</v>
-      </c>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14" t="n">
-        <f aca="false">SUM(C2:C15)</f>
-        <v>48</v>
-      </c>
-      <c r="D16" s="14" t="n">
-        <f aca="false">SUM(D2:D15)</f>
-        <v>50</v>
+      <c r="A16" s="17" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="16" t="n">
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$54,A16)</f>
+        <v>3</v>
+      </c>
+      <c r="D16" s="16" t="n">
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$54,A16,事故一覧!$I$2:$I$54)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="14" t="s">
+        <v>318</v>
+      </c>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14" t="n">
+        <f aca="false">SUM(C2:C16)</f>
+        <v>53</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <f aca="false">SUM(D2:D16)</f>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -9603,10 +10458,10 @@
         <v>19</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>321</v>
+        <v>347</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>322</v>
+        <v>348</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>25</v>
@@ -9626,16 +10481,16 @@
         <v>56</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>323</v>
+        <v>349</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>324</v>
+        <v>350</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>326</v>
+        <v>352</v>
       </c>
       <c r="G2" s="11" t="s">
         <v>61</v>
@@ -9653,16 +10508,16 @@
         <v>83</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>327</v>
+        <v>353</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>328</v>
+        <v>354</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>329</v>
+        <v>355</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>330</v>
+        <v>356</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>164</v>
@@ -9680,19 +10535,19 @@
         <v>83</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>331</v>
+        <v>357</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>332</v>
+        <v>358</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>333</v>
+        <v>359</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>334</v>
+        <v>360</v>
       </c>
       <c r="H4" s="9" t="str">
         <f aca="false">HYPERLINK("https://chunichi.co.jp/article/1321634","記事を開く")</f>
@@ -9707,16 +10562,16 @@
         <v>94</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>335</v>
+        <v>361</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>336</v>
+        <v>362</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>337</v>
+        <v>363</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>338</v>
+        <v>364</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>189</v>
@@ -9734,16 +10589,16 @@
         <v>94</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>339</v>
+        <v>365</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>340</v>
+        <v>366</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>341</v>
+        <v>367</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>194</v>
@@ -9761,16 +10616,16 @@
         <v>56</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>343</v>
+        <v>369</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>344</v>
+        <v>370</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>345</v>
+        <v>371</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>346</v>
+        <v>372</v>
       </c>
       <c r="G7" s="11" t="s">
         <v>215</v>
@@ -9788,19 +10643,19 @@
         <v>166</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>347</v>
+        <v>373</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>348</v>
+        <v>374</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>349</v>
+        <v>375</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>350</v>
+        <v>376</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>351</v>
+        <v>317</v>
       </c>
       <c r="H8" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/06e1158a3abfa398275bfd5e1d8a4e62a117c2ab","記事を開く")</f>
@@ -9815,19 +10670,19 @@
         <v>50</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>352</v>
+        <v>377</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>353</v>
+        <v>378</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>354</v>
+        <v>379</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>355</v>
+        <v>380</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H9" s="9" t="str">
         <f aca="false">HYPERLINK("https://kobe-np.co.jp/news/jiken/202610/0020910097.shtml","記事を開く")</f>
@@ -9842,19 +10697,19 @@
         <v>99</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>357</v>
+        <v>382</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>358</v>
+        <v>383</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>359</v>
+        <v>384</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>360</v>
+        <v>385</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>361</v>
+        <v>386</v>
       </c>
       <c r="H10" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.jiji.com/jc/article?k=2026101000399&amp;g=soc","記事を開く")</f>
@@ -9869,16 +10724,16 @@
         <v>99</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>362</v>
+        <v>387</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>358</v>
+        <v>383</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>359</v>
+        <v>384</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>363</v>
+        <v>388</v>
       </c>
       <c r="G11" s="11" t="s">
         <v>61</v>
@@ -9896,19 +10751,19 @@
         <v>147</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>364</v>
+        <v>389</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>365</v>
+        <v>390</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>366</v>
+        <v>391</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>367</v>
+        <v>392</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>368</v>
+        <v>393</v>
       </c>
       <c r="H12" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/db9ea8f1740207802faad3b369c648aebc074777","記事を開く")</f>

--- a/全国交通事故データ.xlsx
+++ b/全国交通事故データ.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="422">
   <si>
     <t xml:space="preserve">このファイルについて</t>
   </si>
@@ -129,7 +129,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
     <r>
       <rPr>
@@ -4440,6 +4440,33 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">国道</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">号</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">車両相互（</t>
     </r>
     <r>
@@ -4457,17 +4484,269 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">台、運転中に病気発症か）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">運転中にくも膜下出血を発症したとみられ、車</t>
+      <t xml:space="preserve">台、軽トラックが対向車線にはみ出し）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午後、軽トラックが対向車線にはみ出して乗用車と大型トラックに衝突し、運転していた</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">86</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳男性が死亡。死因はくも膜下出血とみられる</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BSN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">新潟放送（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Yahoo!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ニュース </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ MSN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">経由）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">死因は病気（くも膜下出血）とみられる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">福岡市東区</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ふ頭の交差点</t>
+  </si>
+  <si>
+    <t xml:space="preserve">車両相互（右折の軽ライトバンと直進の大型バイク）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">朝、右折しようとした軽ライトバンと、対向から直進してきた大型バイクが衝突し、バイクの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">64</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳男性が死亡</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">KBC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">九州朝日放送 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ FBS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">福岡放送（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Yahoo!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ニュース経由）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">松伏町</t>
+  </si>
+  <si>
+    <t xml:space="preserve">車両単独（バイクが木と縁石に衝突）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時半ごろ、走行中のバイクが縁石や木に衝突して転倒し、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">58</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳男性が搬送先の病院で死亡。原因は不明</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">堺市</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">阪和自動車道 上り線・美原</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">JCT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">付近</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">車両相互（追突・</t>
     </r>
     <r>
       <rPr>
@@ -4484,16 +4763,255 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">台が絡む事故で意識不明のまま搬送された軽トラックの</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">86</t>
+      <t xml:space="preserve">台）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時ごろ、トラックが渋滞の最後尾に追突して</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台が絡む玉突き事故。軽自動車の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">73</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳女性が死亡し、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">33</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳のトラック運転手を逮捕。居眠りが原因とみられる</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NHK / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">読売テレビ</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">美濃加茂市</t>
+  </si>
+  <si>
+    <t xml:space="preserve">歩道（道路脇の自動販売機）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">人対車両（歩道に乗り上げ）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時すぎ、歩道に乗り上げた車が、道路脇の自販機で補充作業をしていた</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳男性をはね、車と柱の間に挟まれて死亡。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">67</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳の女を無免許運転の疑いで現行犯逮捕</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NHK / CBC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">テレビ</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">広島市西区</t>
+  </si>
+  <si>
+    <t xml:space="preserve">井口・西広島バイパス上り線（鈴が峰トンネル入口）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">車両単独（トンネル入口の壁に衝突）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分ごろ、乗用車がトンネル入口の壁に衝突し、運転していた</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">76</t>
     </r>
     <r>
       <rPr>
@@ -4508,19 +5026,10 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">BSN</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">新潟放送（</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">テレビ新広島（</t>
     </r>
     <r>
       <rPr>
@@ -4541,58 +5050,406 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">発生日は検索結果の記載（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日）から推定。病気が原因とみられる</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">福岡市東区</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ふ頭の交差点</t>
-  </si>
-  <si>
-    <t xml:space="preserve">車両相互（右折の軽ライトバンと直進の大型バイク）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">朝、右折しようとした軽ライトバンと、対向から直進してきた大型バイクが衝突し、バイクの</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">64</t>
+    <t xml:space="preserve">浜松市</t>
+  </si>
+  <si>
+    <t xml:space="preserve">信号のある交差点</t>
+  </si>
+  <si>
+    <t xml:space="preserve">車両対自転車（ダンプカーの左折巻き込み）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">45</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分ごろ、左折しようとしたダンプカーに自転車が巻き込まれ、女性が死亡。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">62</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳の運転手を現行犯逮捕</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">静岡第一テレビ（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Yahoo!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ニュース経由）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">神戸市北区</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">山田町中・国道</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">428</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">号（片側</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">車線のカーブ）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">車両単独（オートバイの転倒）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午後</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時半ごろ、オートバイが転倒し、運転していた</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">80</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">代の男性が死亡</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">神戸新聞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NEXT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Yahoo!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ニュース経由）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">周防大島町</t>
+  </si>
+  <si>
+    <t xml:space="preserve">町道（中央線のない生活道路のカーブ）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">車両相互（軽四貨物車と原付バイク）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分ごろ、軽四貨物自動車と原付きバイクが衝突し、バイクの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">33</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳の男性（町職員）が死亡</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NHK / tys</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">テレビ山口</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">東京都</t>
+  </si>
+  <si>
+    <t xml:space="preserve">府中市</t>
+  </si>
+  <si>
+    <t xml:space="preserve">車両相互（右折の乗用車と対向のバイク）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午後</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分ごろ、右折した乗用車と対向のバイクが衝突し、バイクの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">28</t>
     </r>
     <r>
       <rPr>
@@ -4607,36 +5464,27 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">KBC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">九州朝日放送 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/ FBS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">福岡放送（</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">テレビ朝日系（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ANN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）（</t>
     </r>
     <r>
       <rPr>
@@ -4657,343 +5505,34 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">堺市</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">阪和自動車道 上り線・美原</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">JCT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">付近</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">車両相互（追突・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">午前</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">時ごろ、トラックが渋滞の最後尾に追突して</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台が絡む玉突き事故。軽自動車の</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">73</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">歳女性が死亡し、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">33</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">歳のトラック運転手を逮捕。居眠りが原因とみられる</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">NHK / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">読売テレビ</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">美濃加茂市</t>
-  </si>
-  <si>
-    <t xml:space="preserve">歩道（道路脇の自動販売機）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">人対車両（歩道に乗り上げ）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">午前</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">時すぎ、歩道に乗り上げた車が、道路脇の自販機で補充作業をしていた</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">60</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">歳男性をはね、車と柱の間に挟まれて死亡。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">67</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">歳の女を無免許運転の疑いで現行犯逮捕</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">NHK / CBC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">テレビ</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">浜松市</t>
-  </si>
-  <si>
-    <t xml:space="preserve">信号のある交差点</t>
-  </si>
-  <si>
-    <t xml:space="preserve">車両対自転車（ダンプカーの左折巻き込み）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">午前</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">時</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">45</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">分ごろ、左折しようとしたダンプカーに自転車が巻き込まれ、女性が死亡。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">62</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">歳の運転手を現行犯逮捕</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">静岡第一テレビ（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Yahoo!</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ニュース経由）</t>
+    <t xml:space="preserve">三豊市</t>
+  </si>
+  <si>
+    <t xml:space="preserve">高松自動車道 下り線</t>
+  </si>
+  <si>
+    <t xml:space="preserve">車両相互（追突・トラック）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">大型トラックが小型トラックに追突し、小型トラックの運転手が死亡。大型トラックの運転手を現場で逮捕</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NHK / OHK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">岡山放送</t>
     </r>
   </si>
   <si>
@@ -5022,9 +5561,6 @@
   </si>
   <si>
     <t xml:space="preserve">栃木県</t>
-  </si>
-  <si>
-    <t xml:space="preserve">東京都</t>
   </si>
   <si>
     <t xml:space="preserve">富山県</t>
@@ -6127,8 +6663,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="事故一覧" displayName="事故一覧" ref="A1:R54" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:R54"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="事故一覧" displayName="事故一覧" ref="A1:R60" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:R60"/>
   <tableColumns count="18">
     <tableColumn id="1" name="No"/>
     <tableColumn id="2" name="発生日"/>
@@ -6438,7 +6974,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R57"/>
+  <dimension ref="A1:R63"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -9183,34 +9719,34 @@
         <v>293</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>108</v>
+        <v>294</v>
       </c>
       <c r="G50" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%96%B0%E6%BD%9F%E7%9C%8C%E9%AD%9A%E6%B2%BC%E5%B8%82","地図")</f>
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%96%B0%E6%BD%9F%E7%9C%8C%E9%AD%9A%E6%B2%BC%E5%B8%82%20%E5%9B%BD%E9%81%9317%E5%8F%B7","地図")</f>
         <v>地図</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I50" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J50" s="7"/>
       <c r="K50" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="L50" s="12" t="s">
-        <v>73</v>
+        <v>296</v>
+      </c>
+      <c r="L50" s="10" t="s">
+        <v>39</v>
       </c>
       <c r="M50" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N50" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/ab334fba4edce972adb2a6770aa3b1ad4f14b46a","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O50" s="8" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P50" s="8" t="n">
         <v>37.23</v>
@@ -9236,30 +9772,30 @@
         <v>43</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G51" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A6%8F%E5%B2%A1%E7%9C%8C%E7%A6%8F%E5%B2%A1%E5%B8%82%E6%9D%B1%E5%8C%BA%20%E3%81%B5%E9%A0%AD%E3%81%AE%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
         <v>地図</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I51" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J51" s="7"/>
       <c r="K51" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L51" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M51" s="11" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N51" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/6843a963abe9ed0a34e99e653700dd67f3a0c986","記事を開く")</f>
@@ -9276,7 +9812,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="n">
         <v>51</v>
       </c>
@@ -9287,16 +9823,16 @@
         <v>33</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>99</v>
+        <v>180</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>304</v>
+        <v>108</v>
       </c>
       <c r="G52" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%A4%A7%E9%98%AA%E5%BA%9C%E5%A0%BA%E5%B8%82%20%E9%98%AA%E5%92%8C%E8%87%AA%E5%8B%95%E8%BB%8A%E9%81%93%20%E4%B8%8A%E3%82%8A%E7%B7%9A%20%E7%BE%8E%E5%8E%9FJCT%E4%BB%98%E8%BF%91","地図")</f>
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%9F%BC%E7%8E%89%E7%9C%8C%E6%9D%BE%E4%BC%8F%E7%94%BA","地図")</f>
         <v>地図</v>
       </c>
       <c r="H52" s="8" t="s">
@@ -9312,22 +9848,22 @@
       <c r="L52" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M52" s="11" t="s">
-        <v>307</v>
+      <c r="M52" s="8" t="s">
+        <v>226</v>
       </c>
       <c r="N52" s="9" t="str">
-        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261013de58428","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/21ea92b0726a5c99be7ef527e25ec26aabd9626c","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O52" s="8"/>
       <c r="P52" s="8" t="n">
-        <v>34.555</v>
+        <v>35.938</v>
       </c>
       <c r="Q52" s="8" t="n">
-        <v>135.56</v>
+        <v>139.8</v>
       </c>
       <c r="R52" s="8" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9341,126 +9877,450 @@
         <v>33</v>
       </c>
       <c r="D53" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="G53" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%A4%A7%E9%98%AA%E5%BA%9C%E5%A0%BA%E5%B8%82%20%E9%98%AA%E5%92%8C%E8%87%AA%E5%8B%95%E8%BB%8A%E9%81%93%20%E4%B8%8A%E3%82%8A%E7%B7%9A%20%E7%BE%8E%E5%8E%9FJCT%E4%BB%98%E8%BF%91","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H53" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="I53" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" s="7"/>
+      <c r="K53" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="L53" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M53" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="N53" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261013de58428","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O53" s="8"/>
+      <c r="P53" s="8" t="n">
+        <v>34.555</v>
+      </c>
+      <c r="Q53" s="8" t="n">
+        <v>135.56</v>
+      </c>
+      <c r="R53" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="7" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="6" t="n">
+        <v>46308</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D54" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="E53" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="F53" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="G53" s="9" t="str">
+      <c r="E54" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="G54" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%B2%90%E9%98%9C%E7%9C%8C%E7%BE%8E%E6%BF%83%E5%8A%A0%E8%8C%82%E5%B8%82%20%E6%AD%A9%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
-      <c r="H53" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="I53" s="7" t="n">
+      <c r="H54" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="I54" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J53" s="7"/>
-      <c r="K53" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="L53" s="10" t="s">
+      <c r="J54" s="7"/>
+      <c r="K54" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="L54" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M53" s="11" t="s">
-        <v>312</v>
-      </c>
-      <c r="N53" s="9" t="str">
+      <c r="M54" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="N54" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261013de58817","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O53" s="8"/>
-      <c r="P53" s="8" t="n">
+      <c r="O54" s="8"/>
+      <c r="P54" s="8" t="n">
         <v>35.44</v>
       </c>
-      <c r="Q53" s="8" t="n">
+      <c r="Q54" s="8" t="n">
         <v>137.015</v>
       </c>
-      <c r="R53" s="8" t="s">
+      <c r="R54" s="8" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="7" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" s="6" t="n">
+    <row r="55" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="6" t="n">
         <v>46308</v>
       </c>
-      <c r="C54" s="7" t="s">
+      <c r="C55" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D54" s="8" t="s">
+      <c r="D55" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="G55" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%BA%83%E5%B3%B6%E7%9C%8C%E5%BA%83%E5%B3%B6%E5%B8%82%E8%A5%BF%E5%8C%BA%20%E4%BA%95%E5%8F%A3%20%E8%A5%BF%E5%BA%83%E5%B3%B6%E3%83%90%E3%82%A4%E3%83%91%E3%82%B9%E4%B8%8A%E3%82%8A%E7%B7%9A","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H55" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="I55" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" s="7"/>
+      <c r="K55" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="L55" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M55" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="N55" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/4ea3250b843c6cbc3b20753d257b3743cb03ea40","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O55" s="8"/>
+      <c r="P55" s="8" t="n">
+        <v>34.37</v>
+      </c>
+      <c r="Q55" s="8" t="n">
+        <v>132.38</v>
+      </c>
+      <c r="R55" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="6" t="n">
+        <v>46308</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D56" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="E54" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="F54" s="8" t="s">
-        <v>314</v>
-      </c>
-      <c r="G54" s="9" t="str">
+      <c r="E56" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="G56" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E9%9D%99%E5%B2%A1%E7%9C%8C%E6%B5%9C%E6%9D%BE%E5%B8%82%20%E4%BF%A1%E5%8F%B7%E3%81%AE%E3%81%82%E3%82%8B%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
         <v>地図</v>
       </c>
-      <c r="H54" s="8" t="s">
-        <v>315</v>
-      </c>
-      <c r="I54" s="7" t="n">
+      <c r="H56" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="I56" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J54" s="7"/>
-      <c r="K54" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="L54" s="10" t="s">
+      <c r="J56" s="7"/>
+      <c r="K56" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="L56" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M54" s="8" t="s">
-        <v>317</v>
-      </c>
-      <c r="N54" s="9" t="str">
+      <c r="M56" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="N56" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/8dfba36c6fd0292b2243591d891611acc31d627b","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O54" s="8"/>
-      <c r="P54" s="8" t="n">
+      <c r="O56" s="8"/>
+      <c r="P56" s="8" t="n">
         <v>34.71</v>
       </c>
-      <c r="Q54" s="8" t="n">
+      <c r="Q56" s="8" t="n">
         <v>137.726</v>
       </c>
-      <c r="R54" s="8" t="s">
+      <c r="R56" s="8" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="14" t="s">
-        <v>318</v>
-      </c>
-      <c r="B56" s="14" t="str">
-        <f aca="false">COUNTA(D2:D54)&amp;"件"</f>
-        <v>53件</v>
-      </c>
-      <c r="H56" s="14" t="s">
-        <v>319</v>
-      </c>
-      <c r="I56" s="14" t="n">
-        <f aca="false">SUM(I2:I54)</f>
-        <v>55</v>
-      </c>
-      <c r="J56" s="14" t="n">
-        <f aca="false">SUM(J2:J54)</f>
+    <row r="57" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="6" t="n">
+        <v>46309</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="G57" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%85%B5%E5%BA%AB%E7%9C%8C%E7%A5%9E%E6%88%B8%E5%B8%82%E5%8C%97%E5%8C%BA%20%E5%B1%B1%E7%94%B0%E7%94%BA%E4%B8%AD%20%E5%9B%BD%E9%81%93428%E5%8F%B7","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H57" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="I57" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" s="7"/>
+      <c r="K57" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="L57" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M57" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="N57" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/2d6eca6ff0736fb55bc3f8509de47deb988f31c8","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O57" s="8"/>
+      <c r="P57" s="8" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="Q57" s="8" t="n">
+        <v>135.15</v>
+      </c>
+      <c r="R57" s="8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="7" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="6" t="n">
+        <v>46309</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="G58" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%B1%B1%E5%8F%A3%E7%9C%8C%E5%91%A8%E9%98%B2%E5%A4%A7%E5%B3%B6%E7%94%BA%20%E7%94%BA%E9%81%93","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H58" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="I58" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" s="7"/>
+      <c r="K58" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="L58" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M58" s="11" t="s">
+        <v>336</v>
+      </c>
+      <c r="N58" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261014de59231","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O58" s="8"/>
+      <c r="P58" s="8" t="n">
+        <v>33.925</v>
+      </c>
+      <c r="Q58" s="8" t="n">
+        <v>132.22</v>
+      </c>
+      <c r="R58" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="6" t="n">
+        <v>46309</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="G59" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%9D%B1%E4%BA%AC%E9%83%BD%E5%BA%9C%E4%B8%AD%E5%B8%82%20%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H59" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="I59" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" s="7"/>
+      <c r="K59" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="L59" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M59" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="N59" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/92f4495e528c1b67d996016b077456f2dc7e00b6","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O59" s="8"/>
+      <c r="P59" s="8" t="n">
+        <v>35.669</v>
+      </c>
+      <c r="Q59" s="8" t="n">
+        <v>139.478</v>
+      </c>
+      <c r="R59" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="6" t="n">
+        <v>46309</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="G60" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E9%A6%99%E5%B7%9D%E7%9C%8C%E4%B8%89%E8%B1%8A%E5%B8%82%20%E9%AB%98%E6%9D%BE%E8%87%AA%E5%8B%95%E8%BB%8A%E9%81%93%20%E4%B8%8B%E3%82%8A%E7%B7%9A","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H60" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="I60" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J60" s="7"/>
+      <c r="K60" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="L60" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M60" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="N60" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261014de59449","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O60" s="8"/>
+      <c r="P60" s="8" t="n">
+        <v>34.16</v>
+      </c>
+      <c r="Q60" s="8" t="n">
+        <v>133.7</v>
+      </c>
+      <c r="R60" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="14" t="s">
+        <v>347</v>
+      </c>
+      <c r="B62" s="14" t="str">
+        <f aca="false">COUNTA(D2:D60)&amp;"件"</f>
+        <v>59件</v>
+      </c>
+      <c r="H62" s="14" t="s">
+        <v>348</v>
+      </c>
+      <c r="I62" s="14" t="n">
+        <f aca="false">SUM(I2:I60)</f>
+        <v>61</v>
+      </c>
+      <c r="J62" s="14" t="n">
+        <f aca="false">SUM(J2:J60)</f>
         <v>31</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="15" t="s">
-        <v>320</v>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="15" t="s">
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -9495,10 +10355,10 @@
         <v>18</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>321</v>
+        <v>350</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>322</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9506,11 +10366,11 @@
         <v>94</v>
       </c>
       <c r="B2" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A2)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A2)</f>
         <v>4</v>
       </c>
       <c r="C2" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A2,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A2,事故一覧!$I$2:$I$60)</f>
         <v>4</v>
       </c>
     </row>
@@ -9519,50 +10379,50 @@
         <v>88</v>
       </c>
       <c r="B3" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A3)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A3)</f>
         <v>1</v>
       </c>
       <c r="C3" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A3,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A3,事故一覧!$I$2:$I$60)</f>
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>323</v>
+        <v>352</v>
       </c>
       <c r="B4" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A4)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A4)</f>
         <v>0</v>
       </c>
       <c r="C4" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A4,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A4,事故一覧!$I$2:$I$60)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>324</v>
+        <v>353</v>
       </c>
       <c r="B5" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A5)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A5)</f>
         <v>0</v>
       </c>
       <c r="C5" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A5,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A5,事故一覧!$I$2:$I$60)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>325</v>
+        <v>354</v>
       </c>
       <c r="B6" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A6)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A6)</f>
         <v>0</v>
       </c>
       <c r="C6" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A6,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A6,事故一覧!$I$2:$I$60)</f>
         <v>0</v>
       </c>
     </row>
@@ -9571,11 +10431,11 @@
         <v>147</v>
       </c>
       <c r="B7" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A7)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A7)</f>
         <v>2</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A7,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A7,事故一覧!$I$2:$I$60)</f>
         <v>2</v>
       </c>
     </row>
@@ -9584,11 +10444,11 @@
         <v>246</v>
       </c>
       <c r="B8" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A8)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A8)</f>
         <v>2</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A8,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A8,事故一覧!$I$2:$I$60)</f>
         <v>2</v>
       </c>
     </row>
@@ -9597,24 +10457,24 @@
         <v>106</v>
       </c>
       <c r="B9" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A9)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A9)</f>
         <v>2</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A9,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A9,事故一覧!$I$2:$I$60)</f>
         <v>2</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>326</v>
+        <v>355</v>
       </c>
       <c r="B10" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A10)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A10)</f>
         <v>0</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A10,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A10,事故一覧!$I$2:$I$60)</f>
         <v>0</v>
       </c>
     </row>
@@ -9623,11 +10483,11 @@
         <v>133</v>
       </c>
       <c r="B11" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A11)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A11)</f>
         <v>1</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A11,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A11,事故一覧!$I$2:$I$60)</f>
         <v>1</v>
       </c>
     </row>
@@ -9636,12 +10496,12 @@
         <v>180</v>
       </c>
       <c r="B12" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A12)</f>
-        <v>4</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A12)</f>
+        <v>5</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A12,事故一覧!$I$2:$I$54)</f>
-        <v>4</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A12,事故一覧!$I$2:$I$60)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9649,25 +10509,25 @@
         <v>34</v>
       </c>
       <c r="B13" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A13)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A13)</f>
         <v>1</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A13,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A13,事故一覧!$I$2:$I$60)</f>
         <v>3</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="B14" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A14)</f>
-        <v>0</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A14)</f>
+        <v>1</v>
       </c>
       <c r="C14" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A14,事故一覧!$I$2:$I$54)</f>
-        <v>0</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A14,事故一覧!$I$2:$I$60)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9675,11 +10535,11 @@
         <v>83</v>
       </c>
       <c r="B15" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A15)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A15)</f>
         <v>4</v>
       </c>
       <c r="C15" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A15,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A15,事故一覧!$I$2:$I$60)</f>
         <v>5</v>
       </c>
     </row>
@@ -9688,63 +10548,63 @@
         <v>196</v>
       </c>
       <c r="B16" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A16)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A16)</f>
         <v>3</v>
       </c>
       <c r="C16" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A16,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A16,事故一覧!$I$2:$I$60)</f>
         <v>3</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="B17" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A17)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A17)</f>
         <v>0</v>
       </c>
       <c r="C17" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A17,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A17,事故一覧!$I$2:$I$60)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="16" t="s">
-        <v>329</v>
+        <v>357</v>
       </c>
       <c r="B18" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A18)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A18)</f>
         <v>0</v>
       </c>
       <c r="C18" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A18,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A18,事故一覧!$I$2:$I$60)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="16" t="s">
-        <v>330</v>
+        <v>358</v>
       </c>
       <c r="B19" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A19)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A19)</f>
         <v>0</v>
       </c>
       <c r="C19" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A19,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A19,事故一覧!$I$2:$I$60)</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>331</v>
+        <v>359</v>
       </c>
       <c r="B20" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A20)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A20)</f>
         <v>0</v>
       </c>
       <c r="C20" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A20,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A20,事故一覧!$I$2:$I$60)</f>
         <v>0</v>
       </c>
     </row>
@@ -9753,11 +10613,11 @@
         <v>56</v>
       </c>
       <c r="B21" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A21)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A21)</f>
         <v>2</v>
       </c>
       <c r="C21" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A21,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A21,事故一覧!$I$2:$I$60)</f>
         <v>2</v>
       </c>
     </row>
@@ -9766,11 +10626,11 @@
         <v>156</v>
       </c>
       <c r="B22" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A22)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A22)</f>
         <v>3</v>
       </c>
       <c r="C22" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A22,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A22,事故一覧!$I$2:$I$60)</f>
         <v>3</v>
       </c>
     </row>
@@ -9779,11 +10639,11 @@
         <v>166</v>
       </c>
       <c r="B23" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A23)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A23)</f>
         <v>2</v>
       </c>
       <c r="C23" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A23,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A23,事故一覧!$I$2:$I$60)</f>
         <v>2</v>
       </c>
     </row>
@@ -9792,24 +10652,24 @@
         <v>75</v>
       </c>
       <c r="B24" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A24)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A24)</f>
         <v>2</v>
       </c>
       <c r="C24" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A24,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A24,事故一覧!$I$2:$I$60)</f>
         <v>1</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="16" t="s">
-        <v>332</v>
+        <v>360</v>
       </c>
       <c r="B25" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A25)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A25)</f>
         <v>0</v>
       </c>
       <c r="C25" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A25,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A25,事故一覧!$I$2:$I$60)</f>
         <v>0</v>
       </c>
     </row>
@@ -9818,24 +10678,24 @@
         <v>236</v>
       </c>
       <c r="B26" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A26)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A26)</f>
         <v>1</v>
       </c>
       <c r="C26" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A26,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A26,事故一覧!$I$2:$I$60)</f>
         <v>1</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="16" t="s">
-        <v>333</v>
+        <v>361</v>
       </c>
       <c r="B27" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A27)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A27)</f>
         <v>0</v>
       </c>
       <c r="C27" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A27,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A27,事故一覧!$I$2:$I$60)</f>
         <v>0</v>
       </c>
     </row>
@@ -9844,11 +10704,11 @@
         <v>99</v>
       </c>
       <c r="B28" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A28)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A28)</f>
         <v>3</v>
       </c>
       <c r="C28" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A28,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A28,事故一覧!$I$2:$I$60)</f>
         <v>3</v>
       </c>
     </row>
@@ -9857,37 +10717,37 @@
         <v>50</v>
       </c>
       <c r="B29" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A29)</f>
-        <v>5</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A29)</f>
+        <v>6</v>
       </c>
       <c r="C29" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A29,事故一覧!$I$2:$I$54)</f>
-        <v>5</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A29,事故一覧!$I$2:$I$60)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="16" t="s">
-        <v>334</v>
+        <v>362</v>
       </c>
       <c r="B30" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A30)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A30)</f>
         <v>0</v>
       </c>
       <c r="C30" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A30,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A30,事故一覧!$I$2:$I$60)</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="16" t="s">
-        <v>335</v>
+        <v>363</v>
       </c>
       <c r="B31" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A31)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A31)</f>
         <v>0</v>
       </c>
       <c r="C31" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A31,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A31,事故一覧!$I$2:$I$60)</f>
         <v>0</v>
       </c>
     </row>
@@ -9896,37 +10756,37 @@
         <v>143</v>
       </c>
       <c r="B32" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A32)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A32)</f>
         <v>1</v>
       </c>
       <c r="C32" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A32,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A32,事故一覧!$I$2:$I$60)</f>
         <v>1</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="16" t="s">
-        <v>336</v>
+        <v>364</v>
       </c>
       <c r="B33" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A33)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A33)</f>
         <v>0</v>
       </c>
       <c r="C33" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A33,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A33,事故一覧!$I$2:$I$60)</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="16" t="s">
-        <v>337</v>
+        <v>365</v>
       </c>
       <c r="B34" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A34)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A34)</f>
         <v>0</v>
       </c>
       <c r="C34" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A34,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A34,事故一覧!$I$2:$I$60)</f>
         <v>0</v>
       </c>
     </row>
@@ -9935,12 +10795,12 @@
         <v>120</v>
       </c>
       <c r="B35" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A35)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A35)</f>
+        <v>2</v>
       </c>
       <c r="C35" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A35,事故一覧!$I$2:$I$54)</f>
-        <v>1</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A35,事故一覧!$I$2:$I$60)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9948,24 +10808,24 @@
         <v>113</v>
       </c>
       <c r="B36" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A36)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A36)</f>
+        <v>2</v>
       </c>
       <c r="C36" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A36,事故一覧!$I$2:$I$54)</f>
-        <v>1</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A36,事故一覧!$I$2:$I$60)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="16" t="s">
-        <v>338</v>
+        <v>366</v>
       </c>
       <c r="B37" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A37)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A37)</f>
         <v>0</v>
       </c>
       <c r="C37" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A37,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A37,事故一覧!$I$2:$I$60)</f>
         <v>0</v>
       </c>
     </row>
@@ -9974,37 +10834,37 @@
         <v>252</v>
       </c>
       <c r="B38" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A38)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A38)</f>
+        <v>2</v>
       </c>
       <c r="C38" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A38,事故一覧!$I$2:$I$54)</f>
-        <v>1</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A38,事故一覧!$I$2:$I$60)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="16" t="s">
-        <v>339</v>
+        <v>367</v>
       </c>
       <c r="B39" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A39)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A39)</f>
         <v>0</v>
       </c>
       <c r="C39" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A39,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A39,事故一覧!$I$2:$I$60)</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="16" t="s">
-        <v>340</v>
+        <v>368</v>
       </c>
       <c r="B40" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A40)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A40)</f>
         <v>0</v>
       </c>
       <c r="C40" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A40,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A40,事故一覧!$I$2:$I$60)</f>
         <v>0</v>
       </c>
     </row>
@@ -10013,37 +10873,37 @@
         <v>43</v>
       </c>
       <c r="B41" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A41)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A41)</f>
         <v>3</v>
       </c>
       <c r="C41" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A41,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A41,事故一覧!$I$2:$I$60)</f>
         <v>3</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="16" t="s">
-        <v>341</v>
+        <v>369</v>
       </c>
       <c r="B42" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A42)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A42)</f>
         <v>0</v>
       </c>
       <c r="C42" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A42,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A42,事故一覧!$I$2:$I$60)</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="16" t="s">
-        <v>342</v>
+        <v>370</v>
       </c>
       <c r="B43" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A43)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A43)</f>
         <v>0</v>
       </c>
       <c r="C43" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A43,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A43,事故一覧!$I$2:$I$60)</f>
         <v>0</v>
       </c>
     </row>
@@ -10052,50 +10912,50 @@
         <v>202</v>
       </c>
       <c r="B44" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A44)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A44)</f>
         <v>2</v>
       </c>
       <c r="C44" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A44,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A44,事故一覧!$I$2:$I$60)</f>
         <v>2</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="16" t="s">
-        <v>343</v>
+        <v>371</v>
       </c>
       <c r="B45" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A45)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A45)</f>
         <v>0</v>
       </c>
       <c r="C45" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A45,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A45,事故一覧!$I$2:$I$60)</f>
         <v>0</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="16" t="s">
-        <v>344</v>
+        <v>372</v>
       </c>
       <c r="B46" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A46)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A46)</f>
         <v>0</v>
       </c>
       <c r="C46" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A46,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A46,事故一覧!$I$2:$I$60)</f>
         <v>0</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="16" t="s">
-        <v>345</v>
+        <v>373</v>
       </c>
       <c r="B47" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A47)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A47)</f>
         <v>0</v>
       </c>
       <c r="C47" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A47,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A47,事故一覧!$I$2:$I$60)</f>
         <v>0</v>
       </c>
     </row>
@@ -10104,25 +10964,25 @@
         <v>150</v>
       </c>
       <c r="B48" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$54,A48)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A48)</f>
         <v>2</v>
       </c>
       <c r="C48" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$54,A48,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A48,事故一覧!$I$2:$I$60)</f>
         <v>2</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="14" t="s">
-        <v>318</v>
+        <v>347</v>
       </c>
       <c r="B49" s="14" t="n">
         <f aca="false">SUM(B2:B48)</f>
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C49" s="14" t="n">
         <f aca="false">SUM(C2:C48)</f>
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -10141,7 +11001,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -10152,16 +11012,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>346</v>
+        <v>374</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>321</v>
+        <v>350</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>322</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10172,11 +11032,11 @@
         <v>33</v>
       </c>
       <c r="C2" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$54,A2)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$60,A2)</f>
         <v>2</v>
       </c>
       <c r="D2" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$54,A2,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$60,A2,事故一覧!$I$2:$I$60)</f>
         <v>4</v>
       </c>
     </row>
@@ -10188,11 +11048,11 @@
         <v>49</v>
       </c>
       <c r="C3" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$54,A3)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$60,A3)</f>
         <v>2</v>
       </c>
       <c r="D3" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$54,A3,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$60,A3,事故一覧!$I$2:$I$60)</f>
         <v>2</v>
       </c>
     </row>
@@ -10204,11 +11064,11 @@
         <v>63</v>
       </c>
       <c r="C4" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$54,A4)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$60,A4)</f>
         <v>5</v>
       </c>
       <c r="D4" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$54,A4,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$60,A4,事故一覧!$I$2:$I$60)</f>
         <v>5</v>
       </c>
     </row>
@@ -10220,11 +11080,11 @@
         <v>217</v>
       </c>
       <c r="C5" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$54,A5)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$60,A5)</f>
         <v>0</v>
       </c>
       <c r="D5" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$54,A5,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$60,A5,事故一覧!$I$2:$I$60)</f>
         <v>0</v>
       </c>
     </row>
@@ -10236,11 +11096,11 @@
         <v>93</v>
       </c>
       <c r="C6" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$54,A6)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$60,A6)</f>
         <v>3</v>
       </c>
       <c r="D6" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$54,A6,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$60,A6,事故一覧!$I$2:$I$60)</f>
         <v>3</v>
       </c>
     </row>
@@ -10252,11 +11112,11 @@
         <v>112</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$54,A7)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$60,A7)</f>
         <v>6</v>
       </c>
       <c r="D7" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$54,A7,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$60,A7,事故一覧!$I$2:$I$60)</f>
         <v>6</v>
       </c>
     </row>
@@ -10268,11 +11128,11 @@
         <v>146</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$54,A8)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$60,A8)</f>
         <v>2</v>
       </c>
       <c r="D8" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$54,A8,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$60,A8,事故一覧!$I$2:$I$60)</f>
         <v>2</v>
       </c>
     </row>
@@ -10284,11 +11144,11 @@
         <v>33</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$54,A9)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$60,A9)</f>
         <v>3</v>
       </c>
       <c r="D9" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$54,A9,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$60,A9,事故一覧!$I$2:$I$60)</f>
         <v>3</v>
       </c>
     </row>
@@ -10300,11 +11160,11 @@
         <v>49</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$54,A10)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$60,A10)</f>
         <v>3</v>
       </c>
       <c r="D10" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$54,A10,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$60,A10,事故一覧!$I$2:$I$60)</f>
         <v>3</v>
       </c>
     </row>
@@ -10316,11 +11176,11 @@
         <v>63</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$54,A11)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$60,A11)</f>
         <v>6</v>
       </c>
       <c r="D11" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$54,A11,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$60,A11,事故一覧!$I$2:$I$60)</f>
         <v>6</v>
       </c>
     </row>
@@ -10332,11 +11192,11 @@
         <v>217</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$54,A12)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$60,A12)</f>
         <v>1</v>
       </c>
       <c r="D12" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$54,A12,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$60,A12,事故一覧!$I$2:$I$60)</f>
         <v>1</v>
       </c>
     </row>
@@ -10348,11 +11208,11 @@
         <v>93</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$54,A13)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$60,A13)</f>
         <v>7</v>
       </c>
       <c r="D13" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$54,A13,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$60,A13,事故一覧!$I$2:$I$60)</f>
         <v>7</v>
       </c>
     </row>
@@ -10364,11 +11224,11 @@
         <v>112</v>
       </c>
       <c r="C14" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$54,A14)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$60,A14)</f>
         <v>6</v>
       </c>
       <c r="D14" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$54,A14,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$60,A14,事故一覧!$I$2:$I$60)</f>
         <v>6</v>
       </c>
     </row>
@@ -10380,11 +11240,11 @@
         <v>146</v>
       </c>
       <c r="C15" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$54,A15)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$60,A15)</f>
         <v>4</v>
       </c>
       <c r="D15" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$54,A15,事故一覧!$I$2:$I$54)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$60,A15,事故一覧!$I$2:$I$60)</f>
         <v>4</v>
       </c>
     </row>
@@ -10396,26 +11256,42 @@
         <v>33</v>
       </c>
       <c r="C16" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$54,A16)</f>
-        <v>3</v>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$60,A16)</f>
+        <v>5</v>
       </c>
       <c r="D16" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$54,A16,事故一覧!$I$2:$I$54)</f>
-        <v>3</v>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$60,A16,事故一覧!$I$2:$I$60)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="14" t="s">
-        <v>318</v>
-      </c>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14" t="n">
-        <f aca="false">SUM(C2:C16)</f>
-        <v>53</v>
-      </c>
-      <c r="D17" s="14" t="n">
-        <f aca="false">SUM(D2:D16)</f>
-        <v>55</v>
+      <c r="A17" s="17" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="16" t="n">
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$60,A17)</f>
+        <v>4</v>
+      </c>
+      <c r="D17" s="16" t="n">
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$60,A17,事故一覧!$I$2:$I$60)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="14" t="s">
+        <v>347</v>
+      </c>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14" t="n">
+        <f aca="false">SUM(C2:C17)</f>
+        <v>59</v>
+      </c>
+      <c r="D18" s="14" t="n">
+        <f aca="false">SUM(D2:D17)</f>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -10458,10 +11334,10 @@
         <v>19</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>347</v>
+        <v>375</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>348</v>
+        <v>376</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>25</v>
@@ -10481,16 +11357,16 @@
         <v>56</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>349</v>
+        <v>377</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>350</v>
+        <v>378</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>351</v>
+        <v>379</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>352</v>
+        <v>380</v>
       </c>
       <c r="G2" s="11" t="s">
         <v>61</v>
@@ -10508,16 +11384,16 @@
         <v>83</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>353</v>
+        <v>381</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>354</v>
+        <v>382</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>355</v>
+        <v>383</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>356</v>
+        <v>384</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>164</v>
@@ -10535,19 +11411,19 @@
         <v>83</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>357</v>
+        <v>385</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>358</v>
+        <v>386</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>351</v>
+        <v>379</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>359</v>
+        <v>387</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>360</v>
+        <v>388</v>
       </c>
       <c r="H4" s="9" t="str">
         <f aca="false">HYPERLINK("https://chunichi.co.jp/article/1321634","記事を開く")</f>
@@ -10562,16 +11438,16 @@
         <v>94</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>361</v>
+        <v>389</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>362</v>
+        <v>390</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>363</v>
+        <v>391</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>364</v>
+        <v>392</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>189</v>
@@ -10589,16 +11465,16 @@
         <v>94</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>365</v>
+        <v>393</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>367</v>
+        <v>395</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>368</v>
+        <v>396</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>194</v>
@@ -10616,16 +11492,16 @@
         <v>56</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>369</v>
+        <v>397</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>370</v>
+        <v>398</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>371</v>
+        <v>399</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>372</v>
+        <v>400</v>
       </c>
       <c r="G7" s="11" t="s">
         <v>215</v>
@@ -10643,19 +11519,19 @@
         <v>166</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>373</v>
+        <v>401</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>374</v>
+        <v>402</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>375</v>
+        <v>403</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>376</v>
+        <v>404</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="H8" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/06e1158a3abfa398275bfd5e1d8a4e62a117c2ab","記事を開く")</f>
@@ -10670,19 +11546,19 @@
         <v>50</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>377</v>
+        <v>405</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>378</v>
+        <v>406</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>379</v>
+        <v>407</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>380</v>
+        <v>408</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>381</v>
+        <v>409</v>
       </c>
       <c r="H9" s="9" t="str">
         <f aca="false">HYPERLINK("https://kobe-np.co.jp/news/jiken/202610/0020910097.shtml","記事を開く")</f>
@@ -10697,19 +11573,19 @@
         <v>99</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>382</v>
+        <v>410</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>383</v>
+        <v>411</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>384</v>
+        <v>412</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>385</v>
+        <v>413</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>386</v>
+        <v>414</v>
       </c>
       <c r="H10" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.jiji.com/jc/article?k=2026101000399&amp;g=soc","記事を開く")</f>
@@ -10724,16 +11600,16 @@
         <v>99</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>387</v>
+        <v>415</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>383</v>
+        <v>411</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>384</v>
+        <v>412</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>388</v>
+        <v>416</v>
       </c>
       <c r="G11" s="11" t="s">
         <v>61</v>
@@ -10751,19 +11627,19 @@
         <v>147</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>389</v>
+        <v>417</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>390</v>
+        <v>418</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>391</v>
+        <v>419</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>392</v>
+        <v>420</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>393</v>
+        <v>421</v>
       </c>
       <c r="H12" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/db9ea8f1740207802faad3b369c648aebc074777","記事を開く")</f>

--- a/全国交通事故データ.xlsx
+++ b/全国交通事故データ.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="437">
   <si>
     <t xml:space="preserve">このファイルについて</t>
   </si>
@@ -129,7 +129,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
     <r>
       <rPr>
@@ -971,7 +971,41 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">人</t>
+      <t xml:space="preserve">人／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10/15 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">運転の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">58</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳の会社役員を過失致死傷容疑で逮捕（「覚えていない」と供述）</t>
     </r>
   </si>
   <si>
@@ -5302,6 +5336,116 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">信号のない市道交差点の横断歩道</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午後</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時ごろ、横断歩道を渡っていた</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">91</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳男性が走ってきた車にはねられ死亡。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">54</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳の運転手を現行犯逮捕</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NHK / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">サンテレビ</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同じ日に北区の国道</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">428</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">号でもオートバイの死亡事故あり（別件）</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">周防大島町</t>
   </si>
   <si>
@@ -5533,6 +5677,279 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">岡山放送</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">（道路は未確認）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">車両相互（軽乗用車と路線バスの正面衝突）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午後</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分ごろ、軽乗用車が路線バスと正面衝突し、運転の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">73</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳男性が死亡、同乗の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳の孫娘が意識不明の重体</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Yahoo!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ニュース </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">読売新聞（配信）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">バス乗客のけが人は未確認</t>
+  </si>
+  <si>
+    <t xml:space="preserve">飯塚市</t>
+  </si>
+  <si>
+    <t xml:space="preserve">歩道</t>
+  </si>
+  <si>
+    <t xml:space="preserve">人対車両（歩道に座っていた女性）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歩道に座っていた</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">82</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳女性が車にひかれて死亡。運転していた自称パートの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">72</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳の男を逮捕</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RKB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">毎日放送（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Yahoo!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ニュース経由）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">発生日は検索結果の記載（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日午後）から推定。運転手の年齢は報道により</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">72</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">75</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳</t>
     </r>
   </si>
   <si>
@@ -6663,8 +7080,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="事故一覧" displayName="事故一覧" ref="A1:R60" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:R60"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="事故一覧" displayName="事故一覧" ref="A1:R63" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:R63"/>
   <tableColumns count="18">
     <tableColumn id="1" name="No"/>
     <tableColumn id="2" name="発生日"/>
@@ -6974,7 +7391,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R63"/>
+  <dimension ref="A1:R66"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -7272,7 +7689,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="n">
         <v>5</v>
       </c>
@@ -10147,44 +10564,46 @@
         <v>49</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>113</v>
+        <v>50</v>
       </c>
       <c r="E58" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="F58" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="F58" s="8" t="s">
-        <v>333</v>
-      </c>
       <c r="G58" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%B1%B1%E5%8F%A3%E7%9C%8C%E5%91%A8%E9%98%B2%E5%A4%A7%E5%B3%B6%E7%94%BA%20%E7%94%BA%E9%81%93","地図")</f>
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%85%B5%E5%BA%AB%E7%9C%8C%E7%A5%9E%E6%88%B8%E5%B8%82%E5%8C%97%E5%8C%BA%20%E4%BF%A1%E5%8F%B7%E3%81%AE%E3%81%AA%E3%81%84%E5%B8%82%E9%81%93%E4%BA%A4%E5%B7%AE%E7%82%B9%E3%81%AE%E6%A8%AA%E6%96%AD%E6%AD%A9%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>334</v>
+        <v>53</v>
       </c>
       <c r="I58" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J58" s="7"/>
       <c r="K58" s="8" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="L58" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M58" s="11" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="N58" s="9" t="str">
-        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261014de59231","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261015de59544","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O58" s="8"/>
+      <c r="O58" s="8" t="s">
+        <v>335</v>
+      </c>
       <c r="P58" s="8" t="n">
-        <v>33.925</v>
+        <v>34.86</v>
       </c>
       <c r="Q58" s="8" t="n">
-        <v>132.22</v>
+        <v>135.17</v>
       </c>
       <c r="R58" s="8" t="s">
         <v>48</v>
@@ -10201,44 +10620,44 @@
         <v>49</v>
       </c>
       <c r="D59" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="F59" s="8" t="s">
         <v>337</v>
       </c>
-      <c r="E59" s="8" t="s">
+      <c r="G59" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%B1%B1%E5%8F%A3%E7%9C%8C%E5%91%A8%E9%98%B2%E5%A4%A7%E5%B3%B6%E7%94%BA%20%E7%94%BA%E9%81%93","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H59" s="8" t="s">
         <v>338</v>
-      </c>
-      <c r="F59" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="G59" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%9D%B1%E4%BA%AC%E9%83%BD%E5%BA%9C%E4%B8%AD%E5%B8%82%20%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
-        <v>地図</v>
-      </c>
-      <c r="H59" s="8" t="s">
-        <v>339</v>
       </c>
       <c r="I59" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J59" s="7"/>
       <c r="K59" s="8" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="L59" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M59" s="8" t="s">
-        <v>341</v>
+      <c r="M59" s="11" t="s">
+        <v>340</v>
       </c>
       <c r="N59" s="9" t="str">
-        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/92f4495e528c1b67d996016b077456f2dc7e00b6","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261014de59231","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O59" s="8"/>
       <c r="P59" s="8" t="n">
-        <v>35.669</v>
+        <v>33.925</v>
       </c>
       <c r="Q59" s="8" t="n">
-        <v>139.478</v>
+        <v>132.22</v>
       </c>
       <c r="R59" s="8" t="s">
         <v>48</v>
@@ -10255,72 +10674,238 @@
         <v>49</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>252</v>
+        <v>341</v>
       </c>
       <c r="E60" s="8" t="s">
         <v>342</v>
       </c>
       <c r="F60" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="G60" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%9D%B1%E4%BA%AC%E9%83%BD%E5%BA%9C%E4%B8%AD%E5%B8%82%20%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H60" s="8" t="s">
         <v>343</v>
       </c>
-      <c r="G60" s="9" t="str">
+      <c r="I60" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J60" s="7"/>
+      <c r="K60" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="L60" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M60" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="N60" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/92f4495e528c1b67d996016b077456f2dc7e00b6","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O60" s="8"/>
+      <c r="P60" s="8" t="n">
+        <v>35.669</v>
+      </c>
+      <c r="Q60" s="8" t="n">
+        <v>139.478</v>
+      </c>
+      <c r="R60" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="6" t="n">
+        <v>46309</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="G61" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E9%A6%99%E5%B7%9D%E7%9C%8C%E4%B8%89%E8%B1%8A%E5%B8%82%20%E9%AB%98%E6%9D%BE%E8%87%AA%E5%8B%95%E8%BB%8A%E9%81%93%20%E4%B8%8B%E3%82%8A%E7%B7%9A","地図")</f>
         <v>地図</v>
       </c>
-      <c r="H60" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="I60" s="7" t="n">
+      <c r="H61" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="I61" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J60" s="7"/>
-      <c r="K60" s="8" t="s">
-        <v>345</v>
-      </c>
-      <c r="L60" s="10" t="s">
+      <c r="J61" s="7"/>
+      <c r="K61" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="L61" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M60" s="11" t="s">
-        <v>346</v>
-      </c>
-      <c r="N60" s="9" t="str">
+      <c r="M61" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="N61" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261014de59449","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O60" s="8"/>
-      <c r="P60" s="8" t="n">
+      <c r="O61" s="8"/>
+      <c r="P61" s="8" t="n">
         <v>34.16</v>
       </c>
-      <c r="Q60" s="8" t="n">
+      <c r="Q61" s="8" t="n">
         <v>133.7</v>
       </c>
-      <c r="R60" s="8" t="s">
+      <c r="R61" s="8" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="14" t="s">
-        <v>347</v>
-      </c>
-      <c r="B62" s="14" t="str">
-        <f aca="false">COUNTA(D2:D60)&amp;"件"</f>
-        <v>59件</v>
-      </c>
-      <c r="H62" s="14" t="s">
-        <v>348</v>
-      </c>
-      <c r="I62" s="14" t="n">
-        <f aca="false">SUM(I2:I60)</f>
+    <row r="62" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="7" t="n">
         <v>61</v>
       </c>
-      <c r="J62" s="14" t="n">
-        <f aca="false">SUM(J2:J60)</f>
+      <c r="B62" s="6" t="n">
+        <v>46310</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="G62" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%BA%83%E5%B3%B6%E7%9C%8C%E5%B0%BE%E9%81%93%E5%B8%82","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H62" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="I62" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" s="7"/>
+      <c r="K62" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="L62" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M62" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="N62" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/pickup/6598906","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O62" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="P62" s="8" t="n">
+        <v>34.409</v>
+      </c>
+      <c r="Q62" s="8" t="n">
+        <v>133.205</v>
+      </c>
+      <c r="R62" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="7" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="6" t="n">
+        <v>46310</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="G63" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A6%8F%E5%B2%A1%E7%9C%8C%E9%A3%AF%E5%A1%9A%E5%B8%82%20%E6%AD%A9%E9%81%93","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H63" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="I63" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" s="7"/>
+      <c r="K63" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="L63" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="M63" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="N63" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/7cd6e8368f2d684a52eb4341c19faab4655da4bf","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O63" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="P63" s="8" t="n">
+        <v>33.645</v>
+      </c>
+      <c r="Q63" s="8" t="n">
+        <v>130.69</v>
+      </c>
+      <c r="R63" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="14" t="s">
+        <v>362</v>
+      </c>
+      <c r="B65" s="14" t="str">
+        <f aca="false">COUNTA(D2:D63)&amp;"件"</f>
+        <v>62件</v>
+      </c>
+      <c r="H65" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="I65" s="14" t="n">
+        <f aca="false">SUM(I2:I63)</f>
+        <v>64</v>
+      </c>
+      <c r="J65" s="14" t="n">
+        <f aca="false">SUM(J2:J63)</f>
         <v>31</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="15" t="s">
-        <v>349</v>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="15" t="s">
+        <v>364</v>
       </c>
     </row>
   </sheetData>
@@ -10355,10 +10940,10 @@
         <v>18</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>350</v>
+        <v>365</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>351</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10366,11 +10951,11 @@
         <v>94</v>
       </c>
       <c r="B2" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A2)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A2)</f>
         <v>4</v>
       </c>
       <c r="C2" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A2,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A2,事故一覧!$I$2:$I$63)</f>
         <v>4</v>
       </c>
     </row>
@@ -10379,50 +10964,50 @@
         <v>88</v>
       </c>
       <c r="B3" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A3)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A3)</f>
         <v>1</v>
       </c>
       <c r="C3" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A3,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A3,事故一覧!$I$2:$I$63)</f>
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>352</v>
+        <v>367</v>
       </c>
       <c r="B4" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A4)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A4)</f>
         <v>0</v>
       </c>
       <c r="C4" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A4,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A4,事故一覧!$I$2:$I$63)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>353</v>
+        <v>368</v>
       </c>
       <c r="B5" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A5)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A5)</f>
         <v>0</v>
       </c>
       <c r="C5" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A5,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A5,事故一覧!$I$2:$I$63)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>354</v>
+        <v>369</v>
       </c>
       <c r="B6" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A6)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A6)</f>
         <v>0</v>
       </c>
       <c r="C6" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A6,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A6,事故一覧!$I$2:$I$63)</f>
         <v>0</v>
       </c>
     </row>
@@ -10431,11 +11016,11 @@
         <v>147</v>
       </c>
       <c r="B7" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A7)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A7)</f>
         <v>2</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A7,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A7,事故一覧!$I$2:$I$63)</f>
         <v>2</v>
       </c>
     </row>
@@ -10444,11 +11029,11 @@
         <v>246</v>
       </c>
       <c r="B8" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A8)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A8)</f>
         <v>2</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A8,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A8,事故一覧!$I$2:$I$63)</f>
         <v>2</v>
       </c>
     </row>
@@ -10457,24 +11042,24 @@
         <v>106</v>
       </c>
       <c r="B9" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A9)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A9)</f>
         <v>2</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A9,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A9,事故一覧!$I$2:$I$63)</f>
         <v>2</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>355</v>
+        <v>370</v>
       </c>
       <c r="B10" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A10)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A10)</f>
         <v>0</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A10,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A10,事故一覧!$I$2:$I$63)</f>
         <v>0</v>
       </c>
     </row>
@@ -10483,11 +11068,11 @@
         <v>133</v>
       </c>
       <c r="B11" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A11)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A11)</f>
         <v>1</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A11,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A11,事故一覧!$I$2:$I$63)</f>
         <v>1</v>
       </c>
     </row>
@@ -10496,11 +11081,11 @@
         <v>180</v>
       </c>
       <c r="B12" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A12)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A12)</f>
         <v>5</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A12,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A12,事故一覧!$I$2:$I$63)</f>
         <v>5</v>
       </c>
     </row>
@@ -10509,24 +11094,24 @@
         <v>34</v>
       </c>
       <c r="B13" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A13)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A13)</f>
         <v>1</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A13,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A13,事故一覧!$I$2:$I$63)</f>
         <v>3</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B14" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A14)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A14)</f>
         <v>1</v>
       </c>
       <c r="C14" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A14,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A14,事故一覧!$I$2:$I$63)</f>
         <v>1</v>
       </c>
     </row>
@@ -10535,11 +11120,11 @@
         <v>83</v>
       </c>
       <c r="B15" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A15)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A15)</f>
         <v>4</v>
       </c>
       <c r="C15" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A15,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A15,事故一覧!$I$2:$I$63)</f>
         <v>5</v>
       </c>
     </row>
@@ -10548,63 +11133,63 @@
         <v>196</v>
       </c>
       <c r="B16" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A16)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A16)</f>
         <v>3</v>
       </c>
       <c r="C16" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A16,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A16,事故一覧!$I$2:$I$63)</f>
         <v>3</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
-        <v>356</v>
+        <v>371</v>
       </c>
       <c r="B17" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A17)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A17)</f>
         <v>0</v>
       </c>
       <c r="C17" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A17,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A17,事故一覧!$I$2:$I$63)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="16" t="s">
-        <v>357</v>
+        <v>372</v>
       </c>
       <c r="B18" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A18)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A18)</f>
         <v>0</v>
       </c>
       <c r="C18" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A18,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A18,事故一覧!$I$2:$I$63)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="16" t="s">
-        <v>358</v>
+        <v>373</v>
       </c>
       <c r="B19" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A19)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A19)</f>
         <v>0</v>
       </c>
       <c r="C19" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A19,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A19,事故一覧!$I$2:$I$63)</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>359</v>
+        <v>374</v>
       </c>
       <c r="B20" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A20)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A20)</f>
         <v>0</v>
       </c>
       <c r="C20" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A20,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A20,事故一覧!$I$2:$I$63)</f>
         <v>0</v>
       </c>
     </row>
@@ -10613,11 +11198,11 @@
         <v>56</v>
       </c>
       <c r="B21" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A21)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A21)</f>
         <v>2</v>
       </c>
       <c r="C21" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A21,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A21,事故一覧!$I$2:$I$63)</f>
         <v>2</v>
       </c>
     </row>
@@ -10626,11 +11211,11 @@
         <v>156</v>
       </c>
       <c r="B22" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A22)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A22)</f>
         <v>3</v>
       </c>
       <c r="C22" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A22,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A22,事故一覧!$I$2:$I$63)</f>
         <v>3</v>
       </c>
     </row>
@@ -10639,11 +11224,11 @@
         <v>166</v>
       </c>
       <c r="B23" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A23)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A23)</f>
         <v>2</v>
       </c>
       <c r="C23" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A23,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A23,事故一覧!$I$2:$I$63)</f>
         <v>2</v>
       </c>
     </row>
@@ -10652,24 +11237,24 @@
         <v>75</v>
       </c>
       <c r="B24" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A24)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A24)</f>
         <v>2</v>
       </c>
       <c r="C24" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A24,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A24,事故一覧!$I$2:$I$63)</f>
         <v>1</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="16" t="s">
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="B25" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A25)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A25)</f>
         <v>0</v>
       </c>
       <c r="C25" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A25,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A25,事故一覧!$I$2:$I$63)</f>
         <v>0</v>
       </c>
     </row>
@@ -10678,24 +11263,24 @@
         <v>236</v>
       </c>
       <c r="B26" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A26)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A26)</f>
         <v>1</v>
       </c>
       <c r="C26" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A26,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A26,事故一覧!$I$2:$I$63)</f>
         <v>1</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="16" t="s">
-        <v>361</v>
+        <v>376</v>
       </c>
       <c r="B27" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A27)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A27)</f>
         <v>0</v>
       </c>
       <c r="C27" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A27,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A27,事故一覧!$I$2:$I$63)</f>
         <v>0</v>
       </c>
     </row>
@@ -10704,11 +11289,11 @@
         <v>99</v>
       </c>
       <c r="B28" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A28)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A28)</f>
         <v>3</v>
       </c>
       <c r="C28" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A28,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A28,事故一覧!$I$2:$I$63)</f>
         <v>3</v>
       </c>
     </row>
@@ -10717,37 +11302,37 @@
         <v>50</v>
       </c>
       <c r="B29" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A29)</f>
-        <v>6</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A29)</f>
+        <v>7</v>
       </c>
       <c r="C29" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A29,事故一覧!$I$2:$I$60)</f>
-        <v>6</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A29,事故一覧!$I$2:$I$63)</f>
+        <v>7</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="16" t="s">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="B30" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A30)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A30)</f>
         <v>0</v>
       </c>
       <c r="C30" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A30,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A30,事故一覧!$I$2:$I$63)</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="16" t="s">
-        <v>363</v>
+        <v>378</v>
       </c>
       <c r="B31" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A31)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A31)</f>
         <v>0</v>
       </c>
       <c r="C31" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A31,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A31,事故一覧!$I$2:$I$63)</f>
         <v>0</v>
       </c>
     </row>
@@ -10756,37 +11341,37 @@
         <v>143</v>
       </c>
       <c r="B32" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A32)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A32)</f>
         <v>1</v>
       </c>
       <c r="C32" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A32,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A32,事故一覧!$I$2:$I$63)</f>
         <v>1</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="16" t="s">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="B33" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A33)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A33)</f>
         <v>0</v>
       </c>
       <c r="C33" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A33,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A33,事故一覧!$I$2:$I$63)</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="16" t="s">
-        <v>365</v>
+        <v>380</v>
       </c>
       <c r="B34" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A34)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A34)</f>
         <v>0</v>
       </c>
       <c r="C34" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A34,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A34,事故一覧!$I$2:$I$63)</f>
         <v>0</v>
       </c>
     </row>
@@ -10795,12 +11380,12 @@
         <v>120</v>
       </c>
       <c r="B35" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A35)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A35)</f>
+        <v>3</v>
       </c>
       <c r="C35" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A35,事故一覧!$I$2:$I$60)</f>
-        <v>2</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A35,事故一覧!$I$2:$I$63)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10808,24 +11393,24 @@
         <v>113</v>
       </c>
       <c r="B36" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A36)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A36)</f>
         <v>2</v>
       </c>
       <c r="C36" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A36,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A36,事故一覧!$I$2:$I$63)</f>
         <v>2</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="16" t="s">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="B37" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A37)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A37)</f>
         <v>0</v>
       </c>
       <c r="C37" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A37,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A37,事故一覧!$I$2:$I$63)</f>
         <v>0</v>
       </c>
     </row>
@@ -10834,37 +11419,37 @@
         <v>252</v>
       </c>
       <c r="B38" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A38)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A38)</f>
         <v>2</v>
       </c>
       <c r="C38" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A38,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A38,事故一覧!$I$2:$I$63)</f>
         <v>2</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="16" t="s">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="B39" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A39)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A39)</f>
         <v>0</v>
       </c>
       <c r="C39" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A39,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A39,事故一覧!$I$2:$I$63)</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="16" t="s">
-        <v>368</v>
+        <v>383</v>
       </c>
       <c r="B40" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A40)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A40)</f>
         <v>0</v>
       </c>
       <c r="C40" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A40,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A40,事故一覧!$I$2:$I$63)</f>
         <v>0</v>
       </c>
     </row>
@@ -10873,37 +11458,37 @@
         <v>43</v>
       </c>
       <c r="B41" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A41)</f>
-        <v>3</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A41)</f>
+        <v>4</v>
       </c>
       <c r="C41" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A41,事故一覧!$I$2:$I$60)</f>
-        <v>3</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A41,事故一覧!$I$2:$I$63)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="16" t="s">
-        <v>369</v>
+        <v>384</v>
       </c>
       <c r="B42" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A42)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A42)</f>
         <v>0</v>
       </c>
       <c r="C42" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A42,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A42,事故一覧!$I$2:$I$63)</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="16" t="s">
-        <v>370</v>
+        <v>385</v>
       </c>
       <c r="B43" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A43)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A43)</f>
         <v>0</v>
       </c>
       <c r="C43" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A43,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A43,事故一覧!$I$2:$I$63)</f>
         <v>0</v>
       </c>
     </row>
@@ -10912,50 +11497,50 @@
         <v>202</v>
       </c>
       <c r="B44" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A44)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A44)</f>
         <v>2</v>
       </c>
       <c r="C44" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A44,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A44,事故一覧!$I$2:$I$63)</f>
         <v>2</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="16" t="s">
-        <v>371</v>
+        <v>386</v>
       </c>
       <c r="B45" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A45)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A45)</f>
         <v>0</v>
       </c>
       <c r="C45" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A45,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A45,事故一覧!$I$2:$I$63)</f>
         <v>0</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="16" t="s">
-        <v>372</v>
+        <v>387</v>
       </c>
       <c r="B46" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A46)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A46)</f>
         <v>0</v>
       </c>
       <c r="C46" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A46,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A46,事故一覧!$I$2:$I$63)</f>
         <v>0</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="16" t="s">
-        <v>373</v>
+        <v>388</v>
       </c>
       <c r="B47" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A47)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A47)</f>
         <v>0</v>
       </c>
       <c r="C47" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A47,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A47,事故一覧!$I$2:$I$63)</f>
         <v>0</v>
       </c>
     </row>
@@ -10964,25 +11549,25 @@
         <v>150</v>
       </c>
       <c r="B48" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$60,A48)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A48)</f>
         <v>2</v>
       </c>
       <c r="C48" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$60,A48,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A48,事故一覧!$I$2:$I$63)</f>
         <v>2</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="14" t="s">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="B49" s="14" t="n">
         <f aca="false">SUM(B2:B48)</f>
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C49" s="14" t="n">
         <f aca="false">SUM(C2:C48)</f>
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -11001,7 +11586,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -11012,16 +11597,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>374</v>
+        <v>389</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>350</v>
+        <v>365</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>351</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11032,11 +11617,11 @@
         <v>33</v>
       </c>
       <c r="C2" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$60,A2)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$63,A2)</f>
         <v>2</v>
       </c>
       <c r="D2" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$60,A2,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$63,A2,事故一覧!$I$2:$I$63)</f>
         <v>4</v>
       </c>
     </row>
@@ -11048,11 +11633,11 @@
         <v>49</v>
       </c>
       <c r="C3" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$60,A3)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$63,A3)</f>
         <v>2</v>
       </c>
       <c r="D3" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$60,A3,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$63,A3,事故一覧!$I$2:$I$63)</f>
         <v>2</v>
       </c>
     </row>
@@ -11064,11 +11649,11 @@
         <v>63</v>
       </c>
       <c r="C4" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$60,A4)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$63,A4)</f>
         <v>5</v>
       </c>
       <c r="D4" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$60,A4,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$63,A4,事故一覧!$I$2:$I$63)</f>
         <v>5</v>
       </c>
     </row>
@@ -11080,11 +11665,11 @@
         <v>217</v>
       </c>
       <c r="C5" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$60,A5)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$63,A5)</f>
         <v>0</v>
       </c>
       <c r="D5" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$60,A5,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$63,A5,事故一覧!$I$2:$I$63)</f>
         <v>0</v>
       </c>
     </row>
@@ -11096,11 +11681,11 @@
         <v>93</v>
       </c>
       <c r="C6" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$60,A6)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$63,A6)</f>
         <v>3</v>
       </c>
       <c r="D6" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$60,A6,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$63,A6,事故一覧!$I$2:$I$63)</f>
         <v>3</v>
       </c>
     </row>
@@ -11112,11 +11697,11 @@
         <v>112</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$60,A7)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$63,A7)</f>
         <v>6</v>
       </c>
       <c r="D7" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$60,A7,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$63,A7,事故一覧!$I$2:$I$63)</f>
         <v>6</v>
       </c>
     </row>
@@ -11128,11 +11713,11 @@
         <v>146</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$60,A8)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$63,A8)</f>
         <v>2</v>
       </c>
       <c r="D8" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$60,A8,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$63,A8,事故一覧!$I$2:$I$63)</f>
         <v>2</v>
       </c>
     </row>
@@ -11144,11 +11729,11 @@
         <v>33</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$60,A9)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$63,A9)</f>
         <v>3</v>
       </c>
       <c r="D9" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$60,A9,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$63,A9,事故一覧!$I$2:$I$63)</f>
         <v>3</v>
       </c>
     </row>
@@ -11160,11 +11745,11 @@
         <v>49</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$60,A10)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$63,A10)</f>
         <v>3</v>
       </c>
       <c r="D10" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$60,A10,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$63,A10,事故一覧!$I$2:$I$63)</f>
         <v>3</v>
       </c>
     </row>
@@ -11176,11 +11761,11 @@
         <v>63</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$60,A11)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$63,A11)</f>
         <v>6</v>
       </c>
       <c r="D11" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$60,A11,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$63,A11,事故一覧!$I$2:$I$63)</f>
         <v>6</v>
       </c>
     </row>
@@ -11192,11 +11777,11 @@
         <v>217</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$60,A12)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$63,A12)</f>
         <v>1</v>
       </c>
       <c r="D12" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$60,A12,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$63,A12,事故一覧!$I$2:$I$63)</f>
         <v>1</v>
       </c>
     </row>
@@ -11208,11 +11793,11 @@
         <v>93</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$60,A13)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$63,A13)</f>
         <v>7</v>
       </c>
       <c r="D13" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$60,A13,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$63,A13,事故一覧!$I$2:$I$63)</f>
         <v>7</v>
       </c>
     </row>
@@ -11224,11 +11809,11 @@
         <v>112</v>
       </c>
       <c r="C14" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$60,A14)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$63,A14)</f>
         <v>6</v>
       </c>
       <c r="D14" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$60,A14,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$63,A14,事故一覧!$I$2:$I$63)</f>
         <v>6</v>
       </c>
     </row>
@@ -11240,11 +11825,11 @@
         <v>146</v>
       </c>
       <c r="C15" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$60,A15)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$63,A15)</f>
         <v>4</v>
       </c>
       <c r="D15" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$60,A15,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$63,A15,事故一覧!$I$2:$I$63)</f>
         <v>4</v>
       </c>
     </row>
@@ -11256,11 +11841,11 @@
         <v>33</v>
       </c>
       <c r="C16" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$60,A16)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$63,A16)</f>
         <v>5</v>
       </c>
       <c r="D16" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$60,A16,事故一覧!$I$2:$I$60)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$63,A16,事故一覧!$I$2:$I$63)</f>
         <v>5</v>
       </c>
     </row>
@@ -11272,26 +11857,42 @@
         <v>49</v>
       </c>
       <c r="C17" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$60,A17)</f>
-        <v>4</v>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$63,A17)</f>
+        <v>5</v>
       </c>
       <c r="D17" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$60,A17,事故一覧!$I$2:$I$60)</f>
-        <v>4</v>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$63,A17,事故一覧!$I$2:$I$63)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="14" t="s">
-        <v>347</v>
-      </c>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14" t="n">
-        <f aca="false">SUM(C2:C17)</f>
-        <v>59</v>
-      </c>
-      <c r="D18" s="14" t="n">
-        <f aca="false">SUM(D2:D17)</f>
-        <v>61</v>
+      <c r="A18" s="17" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="16" t="n">
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$63,A18)</f>
+        <v>2</v>
+      </c>
+      <c r="D18" s="16" t="n">
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$63,A18,事故一覧!$I$2:$I$63)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="14" t="s">
+        <v>362</v>
+      </c>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14" t="n">
+        <f aca="false">SUM(C2:C18)</f>
+        <v>62</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <f aca="false">SUM(D2:D18)</f>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -11334,10 +11935,10 @@
         <v>19</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>375</v>
+        <v>390</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>376</v>
+        <v>391</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>25</v>
@@ -11357,16 +11958,16 @@
         <v>56</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>377</v>
+        <v>392</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>378</v>
+        <v>393</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>379</v>
+        <v>394</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>380</v>
+        <v>395</v>
       </c>
       <c r="G2" s="11" t="s">
         <v>61</v>
@@ -11384,16 +11985,16 @@
         <v>83</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>381</v>
+        <v>396</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>382</v>
+        <v>397</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>383</v>
+        <v>398</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>164</v>
@@ -11411,19 +12012,19 @@
         <v>83</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>385</v>
+        <v>400</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>386</v>
+        <v>401</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>379</v>
+        <v>394</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>387</v>
+        <v>402</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="H4" s="9" t="str">
         <f aca="false">HYPERLINK("https://chunichi.co.jp/article/1321634","記事を開く")</f>
@@ -11438,16 +12039,16 @@
         <v>94</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>389</v>
+        <v>404</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>391</v>
+        <v>406</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>392</v>
+        <v>407</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>189</v>
@@ -11465,16 +12066,16 @@
         <v>94</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>393</v>
+        <v>408</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>394</v>
+        <v>409</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>194</v>
@@ -11492,16 +12093,16 @@
         <v>56</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>398</v>
+        <v>413</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>400</v>
+        <v>415</v>
       </c>
       <c r="G7" s="11" t="s">
         <v>215</v>
@@ -11519,16 +12120,16 @@
         <v>166</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>401</v>
+        <v>416</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>402</v>
+        <v>417</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>404</v>
+        <v>419</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>326</v>
@@ -11546,19 +12147,19 @@
         <v>50</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>405</v>
+        <v>420</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>406</v>
+        <v>421</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>407</v>
+        <v>422</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>408</v>
+        <v>423</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>409</v>
+        <v>424</v>
       </c>
       <c r="H9" s="9" t="str">
         <f aca="false">HYPERLINK("https://kobe-np.co.jp/news/jiken/202610/0020910097.shtml","記事を開く")</f>
@@ -11573,19 +12174,19 @@
         <v>99</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>410</v>
+        <v>425</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>411</v>
+        <v>426</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>412</v>
+        <v>427</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>413</v>
+        <v>428</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>414</v>
+        <v>429</v>
       </c>
       <c r="H10" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.jiji.com/jc/article?k=2026101000399&amp;g=soc","記事を開く")</f>
@@ -11600,16 +12201,16 @@
         <v>99</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>415</v>
+        <v>430</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>411</v>
+        <v>426</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>412</v>
+        <v>427</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="G11" s="11" t="s">
         <v>61</v>
@@ -11627,19 +12228,19 @@
         <v>147</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>417</v>
+        <v>432</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>418</v>
+        <v>433</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>419</v>
+        <v>434</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>421</v>
+        <v>436</v>
       </c>
       <c r="H12" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/db9ea8f1740207802faad3b369c648aebc074777","記事を開く")</f>

--- a/全国交通事故データ.xlsx
+++ b/全国交通事故データ.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="466">
   <si>
     <t xml:space="preserve">このファイルについて</t>
   </si>
@@ -129,7 +129,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
     <r>
       <rPr>
@@ -5680,6 +5680,103 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">千葉市若葉区</t>
+  </si>
+  <si>
+    <t xml:space="preserve">高品町の市道</t>
+  </si>
+  <si>
+    <t xml:space="preserve">車両対自転車（横断中）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午後</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分ごろ、道路を自転車で横断していた</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">70</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">代男性が、直進してきた乗用車と衝突して死亡</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">千葉日報（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Yahoo!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ニュース経由）</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">（道路は未確認）</t>
   </si>
   <si>
@@ -5803,6 +5900,100 @@
     <t xml:space="preserve">バス乗客のけが人は未確認</t>
   </si>
   <si>
+    <t xml:space="preserve">豊明市</t>
+  </si>
+  <si>
+    <t xml:space="preserve">人対車両（道路に横たわっていた男性ら）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">夜、道路に横たわっていた男性と介抱していた男性の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人が車にはねられ、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">代ぐらいの男性が死亡、介抱していた男性は意識不明の重体。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">58</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳の会社員を現行犯逮捕</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">名古屋テレビ（メ〜テレ）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">東海テレビ</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">飯塚市</t>
   </si>
   <si>
@@ -5953,6 +6144,259 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">横断歩道</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時すぎ、横断歩道を渡っていた</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">93</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳女性が左折してきた軽四貨物車にはねられ死亡</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">横浜市鶴見区</t>
+  </si>
+  <si>
+    <t xml:space="preserve">佃野町の市道交差点</t>
+  </si>
+  <si>
+    <t xml:space="preserve">車両相互（乗用車とミニバイク）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">45</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分ごろ、乗用車とミニバイクが衝突し、ミニバイクの女性が死亡。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">34</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳の運転手を現行犯逮捕</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">神奈川新聞カナロコ</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">近藤町・国道</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">122</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">号の交差点</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">車両対自転車（ダンプカーの左折）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時半ごろ、自転車の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">83</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳女性が左折してきたダンプカーにはねられ死亡。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">72</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳の運転手を現行犯逮捕</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">上毛新聞</t>
+  </si>
+  <si>
+    <t xml:space="preserve">伯耆町</t>
+  </si>
+  <si>
+    <t xml:space="preserve">車両相互（ミニバイクと乗用車）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ミニバイクと乗用車が衝突し、運転していた男性が死亡</t>
+  </si>
+  <si>
+    <t xml:space="preserve">日本海新聞</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">発生日は検索結果の記載（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日）から推定。詳細は未確認</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">合計</t>
   </si>
   <si>
@@ -6710,6 +7154,76 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">ニュース経由）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">宝塚市</t>
+  </si>
+  <si>
+    <t xml:space="preserve">阪急今津線の平林寺踏切</t>
+  </si>
+  <si>
+    <t xml:space="preserve">踏切事故（鉄道）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午後</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分ごろ、踏切内の男性が普通電車と接触してその場で死亡。運休・遅れで約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9,100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人に影響</t>
     </r>
   </si>
 </sst>
@@ -7080,8 +7594,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="事故一覧" displayName="事故一覧" ref="A1:R63" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:R63"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="事故一覧" displayName="事故一覧" ref="A1:R69" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:R69"/>
   <tableColumns count="18">
     <tableColumn id="1" name="No"/>
     <tableColumn id="2" name="発生日"/>
@@ -7391,7 +7905,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R66"/>
+  <dimension ref="A1:R72"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -10782,130 +11296,458 @@
         <v>63</v>
       </c>
       <c r="D62" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="G62" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%8D%83%E8%91%89%E7%9C%8C%E5%8D%83%E8%91%89%E5%B8%82%E8%8B%A5%E8%91%89%E5%8C%BA%20%E9%AB%98%E5%93%81%E7%94%BA%E3%81%AE%E5%B8%82%E9%81%93","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H62" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="I62" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" s="7"/>
+      <c r="K62" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="L62" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M62" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="N62" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/414c9a8e4c5464cba4001c15ac1f71b3a2d10fe6","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O62" s="8"/>
+      <c r="P62" s="8" t="n">
+        <v>35.62</v>
+      </c>
+      <c r="Q62" s="8" t="n">
+        <v>140.15</v>
+      </c>
+      <c r="R62" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="7" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="6" t="n">
+        <v>46310</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D63" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="E62" s="8" t="s">
+      <c r="E63" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="F62" s="8" t="s">
-        <v>351</v>
-      </c>
-      <c r="G62" s="9" t="str">
+      <c r="F63" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="G63" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%BA%83%E5%B3%B6%E7%9C%8C%E5%B0%BE%E9%81%93%E5%B8%82","地図")</f>
         <v>地図</v>
       </c>
-      <c r="H62" s="8" t="s">
-        <v>352</v>
-      </c>
-      <c r="I62" s="7" t="n">
+      <c r="H63" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I63" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J62" s="7"/>
-      <c r="K62" s="8" t="s">
-        <v>353</v>
-      </c>
-      <c r="L62" s="10" t="s">
+      <c r="J63" s="7"/>
+      <c r="K63" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="L63" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M62" s="11" t="s">
-        <v>354</v>
-      </c>
-      <c r="N62" s="9" t="str">
+      <c r="M63" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="N63" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/pickup/6598906","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O62" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="P62" s="8" t="n">
+      <c r="O63" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="P63" s="8" t="n">
         <v>34.409</v>
       </c>
-      <c r="Q62" s="8" t="n">
+      <c r="Q63" s="8" t="n">
         <v>133.205</v>
       </c>
-      <c r="R62" s="8" t="s">
+      <c r="R63" s="8" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="7" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" s="6" t="n">
+    <row r="64" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="7" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="6" t="n">
         <v>46310</v>
       </c>
-      <c r="C63" s="7" t="s">
+      <c r="C64" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="D63" s="8" t="s">
+      <c r="D64" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="G64" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%84%9B%E7%9F%A5%E7%9C%8C%E8%B1%8A%E6%98%8E%E5%B8%82%20%E5%9B%BD%E9%81%93","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H64" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="I64" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K64" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="L64" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M64" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="N64" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.nagoyatv.com/news/?id=037609","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O64" s="8"/>
+      <c r="P64" s="8" t="n">
+        <v>35.056</v>
+      </c>
+      <c r="Q64" s="8" t="n">
+        <v>136.992</v>
+      </c>
+      <c r="R64" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="7" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="6" t="n">
+        <v>46310</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D65" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E63" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="F63" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="G63" s="9" t="str">
+      <c r="E65" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="G65" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A6%8F%E5%B2%A1%E7%9C%8C%E9%A3%AF%E5%A1%9A%E5%B8%82%20%E6%AD%A9%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
-      <c r="H63" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="I63" s="7" t="n">
+      <c r="H65" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="I65" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J63" s="7"/>
-      <c r="K63" s="8" t="s">
-        <v>359</v>
-      </c>
-      <c r="L63" s="12" t="s">
+      <c r="J65" s="7"/>
+      <c r="K65" s="8" t="s">
+        <v>368</v>
+      </c>
+      <c r="L65" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="M63" s="11" t="s">
-        <v>360</v>
-      </c>
-      <c r="N63" s="9" t="str">
+      <c r="M65" s="11" t="s">
+        <v>369</v>
+      </c>
+      <c r="N65" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/7cd6e8368f2d684a52eb4341c19faab4655da4bf","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O63" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="P63" s="8" t="n">
+      <c r="O65" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="P65" s="8" t="n">
         <v>33.645</v>
       </c>
-      <c r="Q63" s="8" t="n">
+      <c r="Q65" s="8" t="n">
         <v>130.69</v>
       </c>
-      <c r="R63" s="8" t="s">
+      <c r="R65" s="8" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="14" t="s">
-        <v>362</v>
-      </c>
-      <c r="B65" s="14" t="str">
-        <f aca="false">COUNTA(D2:D63)&amp;"件"</f>
-        <v>62件</v>
-      </c>
-      <c r="H65" s="14" t="s">
-        <v>363</v>
-      </c>
-      <c r="I65" s="14" t="n">
-        <f aca="false">SUM(I2:I63)</f>
-        <v>64</v>
-      </c>
-      <c r="J65" s="14" t="n">
-        <f aca="false">SUM(J2:J63)</f>
-        <v>31</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="15" t="s">
-        <v>364</v>
+    <row r="66" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="7" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="6" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="G66" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%B1%B1%E5%8F%A3%E7%9C%8C%E5%B1%B1%E5%8F%A3%E5%B8%82%20%E6%A8%AA%E6%96%AD%E6%AD%A9%E9%81%93","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H66" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="I66" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J66" s="7"/>
+      <c r="K66" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="L66" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M66" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="N66" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261016de60546","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O66" s="8"/>
+      <c r="P66" s="8" t="n">
+        <v>34.178</v>
+      </c>
+      <c r="Q66" s="8" t="n">
+        <v>131.474</v>
+      </c>
+      <c r="R66" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="7" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="6" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="G67" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A5%9E%E5%A5%88%E5%B7%9D%E7%9C%8C%E6%A8%AA%E6%B5%9C%E5%B8%82%E9%B6%B4%E8%A6%8B%E5%8C%BA%20%E4%BD%83%E9%87%8E%E7%94%BA%E3%81%AE%E5%B8%82%E9%81%93%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H67" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="I67" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J67" s="7"/>
+      <c r="K67" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="L67" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M67" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="N67" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.kanaloco.jp/news/social/case/article-1313006.html","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O67" s="8"/>
+      <c r="P67" s="8" t="n">
+        <v>35.508</v>
+      </c>
+      <c r="Q67" s="8" t="n">
+        <v>139.677</v>
+      </c>
+      <c r="R67" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="7" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="6" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="G68" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%BE%A4%E9%A6%AC%E7%9C%8C%E9%A4%A8%E6%9E%97%E5%B8%82%20%E8%BF%91%E8%97%A4%E7%94%BA%20%E5%9B%BD%E9%81%93122%E5%8F%B7%E3%81%AE%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H68" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="I68" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J68" s="7"/>
+      <c r="K68" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="L68" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M68" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="N68" s="9" t="str">
+        <f aca="false">HYPERLINK("https://jomo-news.co.jp/articles/-/1045465","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O68" s="8"/>
+      <c r="P68" s="8" t="n">
+        <v>36.245</v>
+      </c>
+      <c r="Q68" s="8" t="n">
+        <v>139.542</v>
+      </c>
+      <c r="R68" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="7" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="6" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="G69" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E9%B3%A5%E5%8F%96%E7%9C%8C%E4%BC%AF%E8%80%86%E7%94%BA%20%E7%9C%8C%E9%81%93","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H69" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="I69" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J69" s="7"/>
+      <c r="K69" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="L69" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="M69" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="N69" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.nnn.co.jp/articles/-/815243","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O69" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="P69" s="8" t="n">
+        <v>35.383</v>
+      </c>
+      <c r="Q69" s="8" t="n">
+        <v>133.483</v>
+      </c>
+      <c r="R69" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="14" t="s">
+        <v>387</v>
+      </c>
+      <c r="B71" s="14" t="str">
+        <f aca="false">COUNTA(D2:D69)&amp;"件"</f>
+        <v>68件</v>
+      </c>
+      <c r="H71" s="14" t="s">
+        <v>388</v>
+      </c>
+      <c r="I71" s="14" t="n">
+        <f aca="false">SUM(I2:I69)</f>
+        <v>70</v>
+      </c>
+      <c r="J71" s="14" t="n">
+        <f aca="false">SUM(J2:J69)</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="15" t="s">
+        <v>389</v>
       </c>
     </row>
   </sheetData>
@@ -10940,10 +11782,10 @@
         <v>18</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>365</v>
+        <v>390</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>366</v>
+        <v>391</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10951,11 +11793,11 @@
         <v>94</v>
       </c>
       <c r="B2" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A2)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A2)</f>
         <v>4</v>
       </c>
       <c r="C2" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A2,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A2,事故一覧!$I$2:$I$69)</f>
         <v>4</v>
       </c>
     </row>
@@ -10964,50 +11806,50 @@
         <v>88</v>
       </c>
       <c r="B3" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A3)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A3)</f>
         <v>1</v>
       </c>
       <c r="C3" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A3,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A3,事故一覧!$I$2:$I$69)</f>
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>367</v>
+        <v>392</v>
       </c>
       <c r="B4" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A4)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A4)</f>
         <v>0</v>
       </c>
       <c r="C4" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A4,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A4,事故一覧!$I$2:$I$69)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>368</v>
+        <v>393</v>
       </c>
       <c r="B5" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A5)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A5)</f>
         <v>0</v>
       </c>
       <c r="C5" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A5,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A5,事故一覧!$I$2:$I$69)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>369</v>
+        <v>394</v>
       </c>
       <c r="B6" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A6)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A6)</f>
         <v>0</v>
       </c>
       <c r="C6" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A6,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A6,事故一覧!$I$2:$I$69)</f>
         <v>0</v>
       </c>
     </row>
@@ -11016,11 +11858,11 @@
         <v>147</v>
       </c>
       <c r="B7" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A7)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A7)</f>
         <v>2</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A7,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A7,事故一覧!$I$2:$I$69)</f>
         <v>2</v>
       </c>
     </row>
@@ -11029,11 +11871,11 @@
         <v>246</v>
       </c>
       <c r="B8" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A8)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A8)</f>
         <v>2</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A8,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A8,事故一覧!$I$2:$I$69)</f>
         <v>2</v>
       </c>
     </row>
@@ -11042,24 +11884,24 @@
         <v>106</v>
       </c>
       <c r="B9" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A9)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A9)</f>
         <v>2</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A9,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A9,事故一覧!$I$2:$I$69)</f>
         <v>2</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>370</v>
+        <v>395</v>
       </c>
       <c r="B10" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A10)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A10)</f>
         <v>0</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A10,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A10,事故一覧!$I$2:$I$69)</f>
         <v>0</v>
       </c>
     </row>
@@ -11068,12 +11910,12 @@
         <v>133</v>
       </c>
       <c r="B11" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A11)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A11)</f>
+        <v>2</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A11,事故一覧!$I$2:$I$63)</f>
-        <v>1</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A11,事故一覧!$I$2:$I$69)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11081,11 +11923,11 @@
         <v>180</v>
       </c>
       <c r="B12" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A12)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A12)</f>
         <v>5</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A12,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A12,事故一覧!$I$2:$I$69)</f>
         <v>5</v>
       </c>
     </row>
@@ -11094,12 +11936,12 @@
         <v>34</v>
       </c>
       <c r="B13" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A13)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A13)</f>
+        <v>2</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A13,事故一覧!$I$2:$I$63)</f>
-        <v>3</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A13,事故一覧!$I$2:$I$69)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11107,11 +11949,11 @@
         <v>341</v>
       </c>
       <c r="B14" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A14)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A14)</f>
         <v>1</v>
       </c>
       <c r="C14" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A14,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A14,事故一覧!$I$2:$I$69)</f>
         <v>1</v>
       </c>
     </row>
@@ -11120,12 +11962,12 @@
         <v>83</v>
       </c>
       <c r="B15" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A15)</f>
-        <v>4</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A15)</f>
+        <v>5</v>
       </c>
       <c r="C15" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A15,事故一覧!$I$2:$I$63)</f>
-        <v>5</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A15,事故一覧!$I$2:$I$69)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11133,63 +11975,63 @@
         <v>196</v>
       </c>
       <c r="B16" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A16)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A16)</f>
         <v>3</v>
       </c>
       <c r="C16" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A16,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A16,事故一覧!$I$2:$I$69)</f>
         <v>3</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
-        <v>371</v>
+        <v>396</v>
       </c>
       <c r="B17" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A17)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A17)</f>
         <v>0</v>
       </c>
       <c r="C17" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A17,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A17,事故一覧!$I$2:$I$69)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="16" t="s">
-        <v>372</v>
+        <v>397</v>
       </c>
       <c r="B18" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A18)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A18)</f>
         <v>0</v>
       </c>
       <c r="C18" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A18,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A18,事故一覧!$I$2:$I$69)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="16" t="s">
-        <v>373</v>
+        <v>398</v>
       </c>
       <c r="B19" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A19)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A19)</f>
         <v>0</v>
       </c>
       <c r="C19" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A19,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A19,事故一覧!$I$2:$I$69)</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>374</v>
+        <v>399</v>
       </c>
       <c r="B20" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A20)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A20)</f>
         <v>0</v>
       </c>
       <c r="C20" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A20,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A20,事故一覧!$I$2:$I$69)</f>
         <v>0</v>
       </c>
     </row>
@@ -11198,11 +12040,11 @@
         <v>56</v>
       </c>
       <c r="B21" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A21)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A21)</f>
         <v>2</v>
       </c>
       <c r="C21" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A21,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A21,事故一覧!$I$2:$I$69)</f>
         <v>2</v>
       </c>
     </row>
@@ -11211,11 +12053,11 @@
         <v>156</v>
       </c>
       <c r="B22" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A22)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A22)</f>
         <v>3</v>
       </c>
       <c r="C22" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A22,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A22,事故一覧!$I$2:$I$69)</f>
         <v>3</v>
       </c>
     </row>
@@ -11224,11 +12066,11 @@
         <v>166</v>
       </c>
       <c r="B23" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A23)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A23)</f>
         <v>2</v>
       </c>
       <c r="C23" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A23,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A23,事故一覧!$I$2:$I$69)</f>
         <v>2</v>
       </c>
     </row>
@@ -11237,24 +12079,24 @@
         <v>75</v>
       </c>
       <c r="B24" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A24)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A24)</f>
+        <v>3</v>
+      </c>
+      <c r="C24" s="16" t="n">
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A24,事故一覧!$I$2:$I$69)</f>
         <v>2</v>
-      </c>
-      <c r="C24" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A24,事故一覧!$I$2:$I$63)</f>
-        <v>1</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="16" t="s">
-        <v>375</v>
+        <v>400</v>
       </c>
       <c r="B25" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A25)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A25)</f>
         <v>0</v>
       </c>
       <c r="C25" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A25,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A25,事故一覧!$I$2:$I$69)</f>
         <v>0</v>
       </c>
     </row>
@@ -11263,24 +12105,24 @@
         <v>236</v>
       </c>
       <c r="B26" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A26)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A26)</f>
         <v>1</v>
       </c>
       <c r="C26" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A26,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A26,事故一覧!$I$2:$I$69)</f>
         <v>1</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="16" t="s">
-        <v>376</v>
+        <v>401</v>
       </c>
       <c r="B27" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A27)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A27)</f>
         <v>0</v>
       </c>
       <c r="C27" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A27,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A27,事故一覧!$I$2:$I$69)</f>
         <v>0</v>
       </c>
     </row>
@@ -11289,11 +12131,11 @@
         <v>99</v>
       </c>
       <c r="B28" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A28)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A28)</f>
         <v>3</v>
       </c>
       <c r="C28" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A28,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A28,事故一覧!$I$2:$I$69)</f>
         <v>3</v>
       </c>
     </row>
@@ -11302,37 +12144,37 @@
         <v>50</v>
       </c>
       <c r="B29" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A29)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A29)</f>
         <v>7</v>
       </c>
       <c r="C29" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A29,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A29,事故一覧!$I$2:$I$69)</f>
         <v>7</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="16" t="s">
-        <v>377</v>
+        <v>402</v>
       </c>
       <c r="B30" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A30)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A30)</f>
         <v>0</v>
       </c>
       <c r="C30" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A30,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A30,事故一覧!$I$2:$I$69)</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="16" t="s">
-        <v>378</v>
+        <v>403</v>
       </c>
       <c r="B31" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A31)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A31)</f>
         <v>0</v>
       </c>
       <c r="C31" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A31,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A31,事故一覧!$I$2:$I$69)</f>
         <v>0</v>
       </c>
     </row>
@@ -11341,37 +12183,37 @@
         <v>143</v>
       </c>
       <c r="B32" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A32)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A32)</f>
+        <v>2</v>
       </c>
       <c r="C32" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A32,事故一覧!$I$2:$I$63)</f>
-        <v>1</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A32,事故一覧!$I$2:$I$69)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="16" t="s">
-        <v>379</v>
+        <v>404</v>
       </c>
       <c r="B33" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A33)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A33)</f>
         <v>0</v>
       </c>
       <c r="C33" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A33,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A33,事故一覧!$I$2:$I$69)</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="16" t="s">
-        <v>380</v>
+        <v>405</v>
       </c>
       <c r="B34" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A34)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A34)</f>
         <v>0</v>
       </c>
       <c r="C34" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A34,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A34,事故一覧!$I$2:$I$69)</f>
         <v>0</v>
       </c>
     </row>
@@ -11380,11 +12222,11 @@
         <v>120</v>
       </c>
       <c r="B35" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A35)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A35)</f>
         <v>3</v>
       </c>
       <c r="C35" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A35,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A35,事故一覧!$I$2:$I$69)</f>
         <v>3</v>
       </c>
     </row>
@@ -11393,24 +12235,24 @@
         <v>113</v>
       </c>
       <c r="B36" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A36)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A36)</f>
+        <v>3</v>
       </c>
       <c r="C36" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A36,事故一覧!$I$2:$I$63)</f>
-        <v>2</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A36,事故一覧!$I$2:$I$69)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="16" t="s">
-        <v>381</v>
+        <v>406</v>
       </c>
       <c r="B37" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A37)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A37)</f>
         <v>0</v>
       </c>
       <c r="C37" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A37,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A37,事故一覧!$I$2:$I$69)</f>
         <v>0</v>
       </c>
     </row>
@@ -11419,37 +12261,37 @@
         <v>252</v>
       </c>
       <c r="B38" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A38)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A38)</f>
         <v>2</v>
       </c>
       <c r="C38" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A38,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A38,事故一覧!$I$2:$I$69)</f>
         <v>2</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="16" t="s">
-        <v>382</v>
+        <v>407</v>
       </c>
       <c r="B39" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A39)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A39)</f>
         <v>0</v>
       </c>
       <c r="C39" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A39,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A39,事故一覧!$I$2:$I$69)</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="16" t="s">
-        <v>383</v>
+        <v>408</v>
       </c>
       <c r="B40" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A40)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A40)</f>
         <v>0</v>
       </c>
       <c r="C40" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A40,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A40,事故一覧!$I$2:$I$69)</f>
         <v>0</v>
       </c>
     </row>
@@ -11458,37 +12300,37 @@
         <v>43</v>
       </c>
       <c r="B41" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A41)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A41)</f>
         <v>4</v>
       </c>
       <c r="C41" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A41,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A41,事故一覧!$I$2:$I$69)</f>
         <v>4</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="16" t="s">
-        <v>384</v>
+        <v>409</v>
       </c>
       <c r="B42" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A42)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A42)</f>
         <v>0</v>
       </c>
       <c r="C42" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A42,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A42,事故一覧!$I$2:$I$69)</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="16" t="s">
-        <v>385</v>
+        <v>410</v>
       </c>
       <c r="B43" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A43)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A43)</f>
         <v>0</v>
       </c>
       <c r="C43" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A43,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A43,事故一覧!$I$2:$I$69)</f>
         <v>0</v>
       </c>
     </row>
@@ -11497,50 +12339,50 @@
         <v>202</v>
       </c>
       <c r="B44" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A44)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A44)</f>
         <v>2</v>
       </c>
       <c r="C44" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A44,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A44,事故一覧!$I$2:$I$69)</f>
         <v>2</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="16" t="s">
-        <v>386</v>
+        <v>411</v>
       </c>
       <c r="B45" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A45)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A45)</f>
         <v>0</v>
       </c>
       <c r="C45" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A45,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A45,事故一覧!$I$2:$I$69)</f>
         <v>0</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="16" t="s">
-        <v>387</v>
+        <v>412</v>
       </c>
       <c r="B46" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A46)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A46)</f>
         <v>0</v>
       </c>
       <c r="C46" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A46,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A46,事故一覧!$I$2:$I$69)</f>
         <v>0</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="16" t="s">
-        <v>388</v>
+        <v>413</v>
       </c>
       <c r="B47" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A47)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A47)</f>
         <v>0</v>
       </c>
       <c r="C47" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A47,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A47,事故一覧!$I$2:$I$69)</f>
         <v>0</v>
       </c>
     </row>
@@ -11549,25 +12391,25 @@
         <v>150</v>
       </c>
       <c r="B48" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$63,A48)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A48)</f>
         <v>2</v>
       </c>
       <c r="C48" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$63,A48,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A48,事故一覧!$I$2:$I$69)</f>
         <v>2</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="14" t="s">
-        <v>362</v>
+        <v>387</v>
       </c>
       <c r="B49" s="14" t="n">
         <f aca="false">SUM(B2:B48)</f>
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C49" s="14" t="n">
         <f aca="false">SUM(C2:C48)</f>
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -11586,7 +12428,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -11597,16 +12439,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>389</v>
+        <v>414</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>365</v>
+        <v>390</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>366</v>
+        <v>391</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11617,11 +12459,11 @@
         <v>33</v>
       </c>
       <c r="C2" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$63,A2)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$69,A2)</f>
         <v>2</v>
       </c>
       <c r="D2" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$63,A2,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$69,A2,事故一覧!$I$2:$I$69)</f>
         <v>4</v>
       </c>
     </row>
@@ -11633,11 +12475,11 @@
         <v>49</v>
       </c>
       <c r="C3" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$63,A3)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$69,A3)</f>
         <v>2</v>
       </c>
       <c r="D3" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$63,A3,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$69,A3,事故一覧!$I$2:$I$69)</f>
         <v>2</v>
       </c>
     </row>
@@ -11649,11 +12491,11 @@
         <v>63</v>
       </c>
       <c r="C4" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$63,A4)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$69,A4)</f>
         <v>5</v>
       </c>
       <c r="D4" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$63,A4,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$69,A4,事故一覧!$I$2:$I$69)</f>
         <v>5</v>
       </c>
     </row>
@@ -11665,11 +12507,11 @@
         <v>217</v>
       </c>
       <c r="C5" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$63,A5)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$69,A5)</f>
         <v>0</v>
       </c>
       <c r="D5" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$63,A5,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$69,A5,事故一覧!$I$2:$I$69)</f>
         <v>0</v>
       </c>
     </row>
@@ -11681,11 +12523,11 @@
         <v>93</v>
       </c>
       <c r="C6" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$63,A6)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$69,A6)</f>
         <v>3</v>
       </c>
       <c r="D6" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$63,A6,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$69,A6,事故一覧!$I$2:$I$69)</f>
         <v>3</v>
       </c>
     </row>
@@ -11697,11 +12539,11 @@
         <v>112</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$63,A7)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$69,A7)</f>
         <v>6</v>
       </c>
       <c r="D7" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$63,A7,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$69,A7,事故一覧!$I$2:$I$69)</f>
         <v>6</v>
       </c>
     </row>
@@ -11713,11 +12555,11 @@
         <v>146</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$63,A8)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$69,A8)</f>
         <v>2</v>
       </c>
       <c r="D8" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$63,A8,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$69,A8,事故一覧!$I$2:$I$69)</f>
         <v>2</v>
       </c>
     </row>
@@ -11729,11 +12571,11 @@
         <v>33</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$63,A9)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$69,A9)</f>
         <v>3</v>
       </c>
       <c r="D9" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$63,A9,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$69,A9,事故一覧!$I$2:$I$69)</f>
         <v>3</v>
       </c>
     </row>
@@ -11745,11 +12587,11 @@
         <v>49</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$63,A10)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$69,A10)</f>
         <v>3</v>
       </c>
       <c r="D10" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$63,A10,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$69,A10,事故一覧!$I$2:$I$69)</f>
         <v>3</v>
       </c>
     </row>
@@ -11761,11 +12603,11 @@
         <v>63</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$63,A11)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$69,A11)</f>
         <v>6</v>
       </c>
       <c r="D11" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$63,A11,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$69,A11,事故一覧!$I$2:$I$69)</f>
         <v>6</v>
       </c>
     </row>
@@ -11777,11 +12619,11 @@
         <v>217</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$63,A12)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$69,A12)</f>
         <v>1</v>
       </c>
       <c r="D12" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$63,A12,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$69,A12,事故一覧!$I$2:$I$69)</f>
         <v>1</v>
       </c>
     </row>
@@ -11793,11 +12635,11 @@
         <v>93</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$63,A13)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$69,A13)</f>
         <v>7</v>
       </c>
       <c r="D13" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$63,A13,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$69,A13,事故一覧!$I$2:$I$69)</f>
         <v>7</v>
       </c>
     </row>
@@ -11809,11 +12651,11 @@
         <v>112</v>
       </c>
       <c r="C14" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$63,A14)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$69,A14)</f>
         <v>6</v>
       </c>
       <c r="D14" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$63,A14,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$69,A14,事故一覧!$I$2:$I$69)</f>
         <v>6</v>
       </c>
     </row>
@@ -11825,11 +12667,11 @@
         <v>146</v>
       </c>
       <c r="C15" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$63,A15)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$69,A15)</f>
         <v>4</v>
       </c>
       <c r="D15" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$63,A15,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$69,A15,事故一覧!$I$2:$I$69)</f>
         <v>4</v>
       </c>
     </row>
@@ -11841,11 +12683,11 @@
         <v>33</v>
       </c>
       <c r="C16" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$63,A16)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$69,A16)</f>
         <v>5</v>
       </c>
       <c r="D16" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$63,A16,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$69,A16,事故一覧!$I$2:$I$69)</f>
         <v>5</v>
       </c>
     </row>
@@ -11857,11 +12699,11 @@
         <v>49</v>
       </c>
       <c r="C17" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$63,A17)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$69,A17)</f>
         <v>5</v>
       </c>
       <c r="D17" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$63,A17,事故一覧!$I$2:$I$63)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$69,A17,事故一覧!$I$2:$I$69)</f>
         <v>5</v>
       </c>
     </row>
@@ -11873,26 +12715,42 @@
         <v>63</v>
       </c>
       <c r="C18" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$63,A18)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$69,A18)</f>
+        <v>4</v>
       </c>
       <c r="D18" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$63,A18,事故一覧!$I$2:$I$63)</f>
-        <v>2</v>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$69,A18,事故一覧!$I$2:$I$69)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="14" t="s">
-        <v>362</v>
-      </c>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14" t="n">
-        <f aca="false">SUM(C2:C18)</f>
-        <v>62</v>
-      </c>
-      <c r="D19" s="14" t="n">
-        <f aca="false">SUM(D2:D18)</f>
-        <v>64</v>
+      <c r="A19" s="17" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>217</v>
+      </c>
+      <c r="C19" s="16" t="n">
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$69,A19)</f>
+        <v>4</v>
+      </c>
+      <c r="D19" s="16" t="n">
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$69,A19,事故一覧!$I$2:$I$69)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="14" t="s">
+        <v>387</v>
+      </c>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14" t="n">
+        <f aca="false">SUM(C2:C19)</f>
+        <v>68</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <f aca="false">SUM(D2:D19)</f>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -11911,7 +12769,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
@@ -11935,10 +12793,10 @@
         <v>19</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>390</v>
+        <v>415</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>391</v>
+        <v>416</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>25</v>
@@ -11958,16 +12816,16 @@
         <v>56</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>392</v>
+        <v>417</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>393</v>
+        <v>418</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>394</v>
+        <v>419</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>395</v>
+        <v>420</v>
       </c>
       <c r="G2" s="11" t="s">
         <v>61</v>
@@ -11985,16 +12843,16 @@
         <v>83</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>396</v>
+        <v>421</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>397</v>
+        <v>422</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>398</v>
+        <v>423</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>399</v>
+        <v>424</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>164</v>
@@ -12012,19 +12870,19 @@
         <v>83</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>400</v>
+        <v>425</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>401</v>
+        <v>426</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>394</v>
+        <v>419</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>402</v>
+        <v>427</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>403</v>
+        <v>428</v>
       </c>
       <c r="H4" s="9" t="str">
         <f aca="false">HYPERLINK("https://chunichi.co.jp/article/1321634","記事を開く")</f>
@@ -12039,16 +12897,16 @@
         <v>94</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>404</v>
+        <v>429</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>405</v>
+        <v>430</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>406</v>
+        <v>431</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>407</v>
+        <v>432</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>189</v>
@@ -12066,16 +12924,16 @@
         <v>94</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>408</v>
+        <v>433</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>409</v>
+        <v>434</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>410</v>
+        <v>435</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>411</v>
+        <v>436</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>194</v>
@@ -12093,16 +12951,16 @@
         <v>56</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>412</v>
+        <v>437</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>413</v>
+        <v>438</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>414</v>
+        <v>439</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="G7" s="11" t="s">
         <v>215</v>
@@ -12120,16 +12978,16 @@
         <v>166</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>416</v>
+        <v>441</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>417</v>
+        <v>442</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>418</v>
+        <v>443</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>419</v>
+        <v>444</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>326</v>
@@ -12147,19 +13005,19 @@
         <v>50</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>420</v>
+        <v>445</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>421</v>
+        <v>446</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>422</v>
+        <v>447</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>423</v>
+        <v>448</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>424</v>
+        <v>449</v>
       </c>
       <c r="H9" s="9" t="str">
         <f aca="false">HYPERLINK("https://kobe-np.co.jp/news/jiken/202610/0020910097.shtml","記事を開く")</f>
@@ -12174,19 +13032,19 @@
         <v>99</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>425</v>
+        <v>450</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>426</v>
+        <v>451</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>427</v>
+        <v>452</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>428</v>
+        <v>453</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>429</v>
+        <v>454</v>
       </c>
       <c r="H10" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.jiji.com/jc/article?k=2026101000399&amp;g=soc","記事を開く")</f>
@@ -12201,16 +13059,16 @@
         <v>99</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>430</v>
+        <v>455</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>426</v>
+        <v>451</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>427</v>
+        <v>452</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>431</v>
+        <v>456</v>
       </c>
       <c r="G11" s="11" t="s">
         <v>61</v>
@@ -12228,22 +13086,49 @@
         <v>147</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>432</v>
+        <v>457</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>433</v>
+        <v>458</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>434</v>
+        <v>459</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>435</v>
+        <v>460</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>436</v>
+        <v>461</v>
       </c>
       <c r="H12" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/db9ea8f1740207802faad3b369c648aebc074777","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>463</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>464</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>465</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="H13" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/369ec569ebac16e8ff06c233e3feafceedfde989","記事を開く")</f>
         <v>記事を開く</v>
       </c>
     </row>

--- a/全国交通事故データ.xlsx
+++ b/全国交通事故データ.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="486">
   <si>
     <t xml:space="preserve">このファイルについて</t>
   </si>
@@ -129,7 +129,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
     <r>
       <rPr>
@@ -2900,6 +2900,83 @@
     <t xml:space="preserve">新潟日報</t>
   </si>
   <si>
+    <t xml:space="preserve">中城村</t>
+  </si>
+  <si>
+    <t xml:space="preserve">車両単独（街路樹に衝突して炎上）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">軽自動車が街路樹に衝突して炎上し、車内から遺体が見つかった。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日に宜野湾署が名護市の女子大学生（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）と発表</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">身元の発表は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">熊本県</t>
   </si>
   <si>
@@ -3441,6 +3518,61 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">東広島市</t>
+  </si>
+  <si>
+    <t xml:space="preserve">市道</t>
+  </si>
+  <si>
+    <t xml:space="preserve">人対車両（トラック）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午前、市道でトラックが歩行者をはね、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">70</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">代女性が死亡</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HOME</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">広島ホームテレビ</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">滋賀県</t>
   </si>
   <si>
@@ -4138,9 +4270,6 @@
     <t xml:space="preserve">信号のある十字路交差点</t>
   </si>
   <si>
-    <t xml:space="preserve">人対車両（トラック）</t>
-  </si>
-  <si>
     <t xml:space="preserve">トラックにはねられた女性が死亡</t>
   </si>
   <si>
@@ -4362,9 +4491,6 @@
     <t xml:space="preserve">米沢市</t>
   </si>
   <si>
-    <t xml:space="preserve">市道</t>
-  </si>
-  <si>
     <t xml:space="preserve">人対車両（後ろから）</t>
   </si>
   <si>
@@ -6361,40 +6487,385 @@
     <t xml:space="preserve">伯耆町</t>
   </si>
   <si>
-    <t xml:space="preserve">車両相互（ミニバイクと乗用車）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ミニバイクと乗用車が衝突し、運転していた男性が死亡</t>
-  </si>
-  <si>
-    <t xml:space="preserve">日本海新聞</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">発生日は検索結果の記載（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">16</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日）から推定。詳細は未確認</t>
-    </r>
+    <t xml:space="preserve">車両相互（乗用車と原付バイクの正面衝突）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">夜、県道で乗用車と原付きバイクが正面衝突し、バイクを運転していた男性が死亡</t>
+  </si>
+  <si>
+    <t xml:space="preserve">標津町</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">道道</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">774</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">号（街灯のない直線）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">車両相互（軽乗用車と乗用車の正面衝突）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午後</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分ごろ、軽乗用車と乗用車が正面衝突し、軽乗用車の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">70</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">代の男女</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人が死亡、乗用車の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">代男性が軽傷。雨上がりで路面は濡れていた</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NHK / HTB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">北海道ニュース</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">福島市</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">東北自動車道 下り線（福島飯坂</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜桑折</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">JCT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">間）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">車両相互（追突・停車中の軽乗用車にトラック）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時半ごろ、大型トラックが路肩に停車していた軽乗用車に追突し、青森市の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">38</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳女性が死亡、男女</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人が搬送された。トラック運転手にけがなし</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">福島テレビ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ KFB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">福島放送（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Yahoo!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ニュース経由）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">佐久市</t>
+  </si>
+  <si>
+    <t xml:space="preserve">香坂・上信越自動車道 上り線のトンネル</t>
+  </si>
+  <si>
+    <t xml:space="preserve">車両単独（軽トラックがトンネルの壁に衝突）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分ごろ、軽トラックがトンネルの壁面に衝突し、運転していた新潟県上越市の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">77</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳男性が死亡。同乗者なし</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">共同通信（東京新聞デジタル配信）</t>
   </si>
   <si>
     <t xml:space="preserve">合計</t>
@@ -7594,8 +8065,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="事故一覧" displayName="事故一覧" ref="A1:R69" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:R69"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="事故一覧" displayName="事故一覧" ref="A1:R74" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:R74"/>
   <tableColumns count="18">
     <tableColumn id="1" name="No"/>
     <tableColumn id="2" name="発生日"/>
@@ -7905,7 +8376,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R72"/>
+  <dimension ref="A1:R77"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -9587,7 +10058,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="n">
         <v>30</v>
       </c>
@@ -9598,324 +10069,326 @@
         <v>63</v>
       </c>
       <c r="D31" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="E31" s="8" t="s">
         <v>202</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>203</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>135</v>
       </c>
       <c r="G31" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%B2%96%E7%B8%84%E7%9C%8C%E4%B8%AD%E5%9F%8E%E6%9D%91%20%E7%9C%8C%E9%81%93","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="I31" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" s="7"/>
+      <c r="K31" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="L31" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M31" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="N31" s="9" t="str">
+        <f aca="false">HYPERLINK("https://ryukyushimpo.jp/national/entry-5558943.html","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O31" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="P31" s="8" t="n">
+        <v>26.245</v>
+      </c>
+      <c r="Q31" s="8" t="n">
+        <v>127.795</v>
+      </c>
+      <c r="R31" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>46303</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="G32" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%86%8A%E6%9C%AC%E7%9C%8C%E7%86%8A%E6%9C%AC%E5%B8%82%E5%8D%97%E5%8C%BA%20%E7%9C%8C%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
-      <c r="H31" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="I31" s="7" t="n">
+      <c r="H32" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="I32" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J31" s="7"/>
-      <c r="K31" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="L31" s="10" t="s">
+      <c r="J32" s="7"/>
+      <c r="K32" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="L32" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M31" s="11" t="s">
+      <c r="M32" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="N31" s="9" t="str">
+      <c r="N32" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261008de56617","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O31" s="8"/>
-      <c r="P31" s="8" t="n">
+      <c r="O32" s="8"/>
+      <c r="P32" s="8" t="n">
         <v>32.75</v>
       </c>
-      <c r="Q31" s="8" t="n">
+      <c r="Q32" s="8" t="n">
         <v>130.7</v>
       </c>
-      <c r="R31" s="8" t="s">
+      <c r="R32" s="8" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="7" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="6" t="n">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="6" t="n">
         <v>46303</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C33" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="D32" s="8" t="s">
+      <c r="D33" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E32" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="F32" s="8" t="s">
+      <c r="E33" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="F33" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="G32" s="9" t="str">
+      <c r="G33" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A6%8F%E5%B2%A1%E7%9C%8C%E5%B7%9D%E5%B4%8E%E7%94%BA%EF%BC%88%E7%94%B0%E5%B7%9D%E9%83%A1%EF%BC%89","地図")</f>
         <v>地図</v>
       </c>
-      <c r="H32" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="I32" s="7" t="n">
+      <c r="H33" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="I33" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J32" s="7"/>
-      <c r="K32" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="L32" s="12" t="s">
+      <c r="J33" s="7"/>
+      <c r="K33" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="L33" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="M32" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="N32" s="9" t="str">
+      <c r="M33" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="N33" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.nishinippon.co.jp/category/kyushu/flash/","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O32" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="P32" s="8" t="n">
+      <c r="O33" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="P33" s="8" t="n">
         <v>33.6</v>
       </c>
-      <c r="Q32" s="8" t="n">
+      <c r="Q33" s="8" t="n">
         <v>130.815</v>
       </c>
-      <c r="R32" s="8" t="s">
+      <c r="R33" s="8" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="6" t="n">
+    <row r="34" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="6" t="n">
         <v>46303</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C34" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="D33" s="8" t="s">
+      <c r="D34" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="E33" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="G33" s="9" t="str">
+      <c r="E34" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="G34" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E9%95%B7%E9%87%8E%E7%9C%8C%E6%9D%BE%E6%9C%AC%E5%B8%82%20%E4%BF%A1%E5%8F%B7%E3%81%AE%E3%81%AA%E3%81%84%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
         <v>地図</v>
       </c>
-      <c r="H33" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="I33" s="7" t="n">
+      <c r="H34" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="I34" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="7"/>
-      <c r="K33" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="L33" s="12" t="s">
+      <c r="J34" s="7"/>
+      <c r="K34" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="L34" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="M33" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="N33" s="9" t="str">
+      <c r="M34" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="N34" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.nbs-tv.co.jp/news/","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O33" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="P33" s="8" t="n">
+      <c r="O34" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="P34" s="8" t="n">
         <v>36.238</v>
       </c>
-      <c r="Q33" s="8" t="n">
+      <c r="Q34" s="8" t="n">
         <v>137.972</v>
       </c>
-      <c r="R33" s="8" t="s">
+      <c r="R34" s="8" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="7" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="6" t="n">
+    <row r="35" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="6" t="n">
         <v>46304</v>
       </c>
-      <c r="C34" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="D34" s="8" t="s">
+      <c r="C35" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="D35" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="E34" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="G34" s="9" t="str">
+      <c r="E35" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="G35" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%9F%BC%E7%8E%89%E7%9C%8C%E6%96%B0%E5%BA%A7%E5%B8%82%20%E6%A0%97%E5%8E%9F%E3%81%AE%E5%B8%82%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
-      <c r="H34" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="I34" s="7" t="n">
+      <c r="H35" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="I35" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J34" s="7"/>
-      <c r="K34" s="11" t="s">
-        <v>221</v>
-      </c>
-      <c r="L34" s="10" t="s">
+      <c r="J35" s="7"/>
+      <c r="K35" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="L35" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M34" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="N34" s="9" t="str">
+      <c r="M35" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="N35" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/aad5e62c6ab660cb6e49eb85990d0040b1ed24c0","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O34" s="8"/>
-      <c r="P34" s="8" t="n">
+      <c r="O35" s="8"/>
+      <c r="P35" s="8" t="n">
         <v>35.797</v>
       </c>
-      <c r="Q34" s="8" t="n">
+      <c r="Q35" s="8" t="n">
         <v>139.558</v>
       </c>
-      <c r="R34" s="8" t="s">
+      <c r="R35" s="8" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="6" t="n">
+    <row r="36" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="6" t="n">
         <v>46305</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C36" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="D36" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="E35" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="G35" s="9" t="str">
+      <c r="E36" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="G36" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%9F%BC%E7%8E%89%E7%9C%8C%E5%B7%9D%E8%B6%8A%E5%B8%82%20%E7%9F%B3%E5%8E%9F%E7%94%BA1%E4%B8%81%E7%9B%AE%E3%81%AE%E5%B8%82%E9%81%93%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
         <v>地図</v>
       </c>
-      <c r="H35" s="8" t="s">
+      <c r="H36" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="I35" s="7" t="n">
+      <c r="I36" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J35" s="7"/>
-      <c r="K35" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="L35" s="10" t="s">
+      <c r="J36" s="7"/>
+      <c r="K36" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="L36" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M35" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="N35" s="9" t="str">
+      <c r="M36" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="N36" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/2ae0cd885c9590de27370d50c19c3b5cfe44b814","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O35" s="8"/>
-      <c r="P35" s="8" t="n">
-        <v>35.925</v>
-      </c>
-      <c r="Q35" s="8" t="n">
-        <v>139.495</v>
-      </c>
-      <c r="R35" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="6" t="n">
-        <v>46305</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="F36" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="G36" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%A4%A7%E9%98%AA%E5%BA%9C%E5%A4%A7%E9%98%AA%E5%B8%82%E7%94%9F%E9%87%8E%E5%8C%BA%20%E5%9B%BD%E9%81%9325%E5%8F%B7","地図")</f>
-        <v>地図</v>
-      </c>
-      <c r="H36" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="I36" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" s="7"/>
-      <c r="K36" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="L36" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M36" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="N36" s="9" t="str">
-        <f aca="false">HYPERLINK("https://topics.smt.docomo.ne.jp/article/ytv/nation/ytv-2026101009554337","記事を開く")</f>
-        <v>記事を開く</v>
-      </c>
       <c r="O36" s="8"/>
       <c r="P36" s="8" t="n">
-        <v>34.66</v>
+        <v>35.925</v>
       </c>
       <c r="Q36" s="8" t="n">
-        <v>135.533</v>
+        <v>139.495</v>
       </c>
       <c r="R36" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="n">
         <v>36</v>
       </c>
@@ -9926,16 +10399,16 @@
         <v>93</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>156</v>
+        <v>99</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>157</v>
+        <v>231</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>232</v>
       </c>
       <c r="G37" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%B2%90%E9%98%9C%E7%9C%8C%E5%B2%90%E9%98%9C%E5%B8%82%20%E7%90%B4%E5%A1%9A%E3%81%AE%E7%9C%8C%E9%81%93","地図")</f>
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%A4%A7%E9%98%AA%E5%BA%9C%E5%A4%A7%E9%98%AA%E5%B8%82%E7%94%9F%E9%87%8E%E5%8C%BA%20%E5%9B%BD%E9%81%9325%E5%8F%B7","地図")</f>
         <v>地図</v>
       </c>
       <c r="H37" s="8" t="s">
@@ -9955,18 +10428,18 @@
         <v>235</v>
       </c>
       <c r="N37" s="9" t="str">
-        <f aca="false">HYPERLINK("https://news.ksb.co.jp/ann/article/16957202","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://topics.smt.docomo.ne.jp/article/ytv/nation/ytv-2026101009554337","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O37" s="8"/>
       <c r="P37" s="8" t="n">
-        <v>35.405</v>
+        <v>34.66</v>
       </c>
       <c r="Q37" s="8" t="n">
-        <v>136.766</v>
+        <v>135.533</v>
       </c>
       <c r="R37" s="8" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9980,50 +10453,50 @@
         <v>93</v>
       </c>
       <c r="D38" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="F38" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="E38" s="8" t="s">
+      <c r="G38" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%B2%90%E9%98%9C%E7%9C%8C%E5%B2%90%E9%98%9C%E5%B8%82%20%E7%90%B4%E5%A1%9A%E3%81%AE%E7%9C%8C%E9%81%93","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H38" s="8" t="s">
         <v>237</v>
-      </c>
-      <c r="F38" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="G38" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%BB%8B%E8%B3%80%E7%9C%8C%E5%BD%A6%E6%A0%B9%E5%B8%82%20%E6%97%A5%E5%A4%8F%E7%94%BA%E3%81%AE%E9%81%93%E8%B7%AF%E8%84%87","地図")</f>
-        <v>地図</v>
-      </c>
-      <c r="H38" s="8" t="s">
-        <v>239</v>
       </c>
       <c r="I38" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J38" s="7"/>
       <c r="K38" s="8" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="L38" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M38" s="8" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="N38" s="9" t="str">
-        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/b6b6518fd7e974552b652d275fd3240a159e1c74","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://news.ksb.co.jp/ann/article/16957202","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O38" s="8"/>
       <c r="P38" s="8" t="n">
-        <v>35.3</v>
+        <v>35.405</v>
       </c>
       <c r="Q38" s="8" t="n">
-        <v>136.24</v>
+        <v>136.766</v>
       </c>
       <c r="R38" s="8" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="n">
         <v>38</v>
       </c>
@@ -10034,46 +10507,44 @@
         <v>93</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>202</v>
+        <v>120</v>
       </c>
       <c r="E39" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="G39" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%BA%83%E5%B3%B6%E7%9C%8C%E6%9D%B1%E5%BA%83%E5%B3%B6%E5%B8%82%20%E5%B8%82%E9%81%93","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H39" s="8" t="s">
         <v>242</v>
-      </c>
-      <c r="F39" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="G39" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%86%8A%E6%9C%AC%E7%9C%8C%E7%86%8A%E6%9C%AC%E5%B8%82%E4%B8%AD%E5%A4%AE%E5%8C%BA%20%E7%9C%8C%E9%81%93","地図")</f>
-        <v>地図</v>
-      </c>
-      <c r="H39" s="8" t="s">
-        <v>243</v>
       </c>
       <c r="I39" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J39" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="J39" s="7"/>
       <c r="K39" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L39" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M39" s="11" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="N39" s="9" t="str">
-        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/1a327fce60e5134e7b5d69acda6911e914c90555","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://www.home-tv.co.jp/news/content/?news_id=20261010374679","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O39" s="8"/>
       <c r="P39" s="8" t="n">
-        <v>32.8</v>
+        <v>34.43</v>
       </c>
       <c r="Q39" s="8" t="n">
-        <v>130.71</v>
+        <v>132.74</v>
       </c>
       <c r="R39" s="8" t="s">
         <v>48</v>
@@ -10090,47 +10561,47 @@
         <v>93</v>
       </c>
       <c r="D40" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="E40" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="E40" s="8" t="s">
+      <c r="F40" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="F40" s="8" t="s">
+      <c r="G40" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%BB%8B%E8%B3%80%E7%9C%8C%E5%BD%A6%E6%A0%B9%E5%B8%82%20%E6%97%A5%E5%A4%8F%E7%94%BA%E3%81%AE%E9%81%93%E8%B7%AF%E8%84%87","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H40" s="8" t="s">
         <v>248</v>
-      </c>
-      <c r="G40" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A6%8F%E5%B3%B6%E7%9C%8C%E9%83%A1%E5%B1%B1%E5%B8%82%20%E4%B8%AD%E7%94%B0%E7%94%BA%E6%9F%B3%E6%A9%8B%20%E7%9C%8C%E9%81%93%E3%81%AE%E4%BF%A1%E5%8F%B7%E3%81%AE%E3%81%AA%E3%81%84%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
-        <v>地図</v>
-      </c>
-      <c r="H40" s="8" t="s">
-        <v>249</v>
       </c>
       <c r="I40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J40" s="7"/>
       <c r="K40" s="8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="L40" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M40" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="N40" s="9" t="str">
-        <f aca="false">HYPERLINK("https://minyu-net.com/news/detail/2026101107353655857","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/b6b6518fd7e974552b652d275fd3240a159e1c74","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O40" s="8"/>
       <c r="P40" s="8" t="n">
-        <v>37.4</v>
+        <v>35.3</v>
       </c>
       <c r="Q40" s="8" t="n">
-        <v>140.36</v>
+        <v>136.24</v>
       </c>
       <c r="R40" s="8" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10144,70 +10615,72 @@
         <v>93</v>
       </c>
       <c r="D41" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="G41" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%86%8A%E6%9C%AC%E7%9C%8C%E7%86%8A%E6%9C%AC%E5%B8%82%E4%B8%AD%E5%A4%AE%E5%8C%BA%20%E7%9C%8C%E9%81%93","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H41" s="8" t="s">
         <v>252</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="F41" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="G41" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E9%A6%99%E5%B7%9D%E7%9C%8C%E8%A6%B3%E9%9F%B3%E5%AF%BA%E5%B8%82%20%E8%B1%8A%E6%B5%9C%E7%94%BA%E3%81%AE%E5%9B%BD%E9%81%93","地図")</f>
-        <v>地図</v>
-      </c>
-      <c r="H41" s="8" t="s">
-        <v>53</v>
       </c>
       <c r="I41" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J41" s="7"/>
+      <c r="J41" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="K41" s="8" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="L41" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M41" s="11" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="N41" s="9" t="str">
-        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261010de57733","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/1a327fce60e5134e7b5d69acda6911e914c90555","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O41" s="8"/>
       <c r="P41" s="8" t="n">
-        <v>34.1</v>
+        <v>32.8</v>
       </c>
       <c r="Q41" s="8" t="n">
-        <v>133.64</v>
+        <v>130.71</v>
       </c>
       <c r="R41" s="8" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="n">
         <v>41</v>
       </c>
       <c r="B42" s="6" t="n">
-        <v>46306</v>
+        <v>46305</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="E42" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="F42" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="F42" s="8" t="s">
-        <v>71</v>
-      </c>
       <c r="G42" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%9F%BC%E7%8E%89%E7%9C%8C%E4%B8%8A%E5%B0%BE%E5%B8%82%20%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A6%8F%E5%B3%B6%E7%9C%8C%E9%83%A1%E5%B1%B1%E5%B8%82%20%E4%B8%AD%E7%94%B0%E7%94%BA%E6%9F%B3%E6%A9%8B%20%E7%9C%8C%E9%81%93%E3%81%AE%E4%BF%A1%E5%8F%B7%E3%81%AE%E3%81%AA%E3%81%84%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
         <v>地図</v>
       </c>
       <c r="H42" s="8" t="s">
@@ -10216,28 +10689,26 @@
       <c r="I42" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J42" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="J42" s="7"/>
       <c r="K42" s="8" t="s">
         <v>259</v>
       </c>
       <c r="L42" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M42" s="11" t="s">
-        <v>61</v>
+      <c r="M42" s="8" t="s">
+        <v>260</v>
       </c>
       <c r="N42" s="9" t="str">
-        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261012de58063","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://minyu-net.com/news/detail/2026101107353655857","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O42" s="8"/>
       <c r="P42" s="8" t="n">
-        <v>35.977</v>
+        <v>37.4</v>
       </c>
       <c r="Q42" s="8" t="n">
-        <v>139.593</v>
+        <v>140.36</v>
       </c>
       <c r="R42" s="8" t="s">
         <v>48</v>
@@ -10248,58 +10719,56 @@
         <v>42</v>
       </c>
       <c r="B43" s="6" t="n">
-        <v>46306</v>
+        <v>46305</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>196</v>
+        <v>261</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G43" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%96%B0%E6%BD%9F%E7%9C%8C%E9%95%B7%E5%B2%A1%E5%B8%82%20%E5%9F%8E%E5%B2%A11%E4%B8%81%E7%9B%AE%E3%81%AE%E5%B8%82%E9%81%93","地図")</f>
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E9%A6%99%E5%B7%9D%E7%9C%8C%E8%A6%B3%E9%9F%B3%E5%AF%BA%E5%B8%82%20%E8%B1%8A%E6%B5%9C%E7%94%BA%E3%81%AE%E5%9B%BD%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>262</v>
+        <v>53</v>
       </c>
       <c r="I43" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J43" s="7"/>
       <c r="K43" s="8" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L43" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M43" s="8" t="s">
-        <v>201</v>
+      <c r="M43" s="11" t="s">
+        <v>265</v>
       </c>
       <c r="N43" s="9" t="str">
-        <f aca="false">HYPERLINK("https://niigata-nippo.co.jp/articles/-/922657","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261010de57733","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O43" s="8" t="s">
-        <v>264</v>
-      </c>
+      <c r="O43" s="8"/>
       <c r="P43" s="8" t="n">
-        <v>37.45</v>
+        <v>34.1</v>
       </c>
       <c r="Q43" s="8" t="n">
-        <v>138.82</v>
+        <v>133.64</v>
       </c>
       <c r="R43" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="n">
         <v>43</v>
       </c>
@@ -10310,16 +10779,16 @@
         <v>112</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>266</v>
+        <v>71</v>
       </c>
       <c r="G44" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%B2%96%E7%B8%84%E7%9C%8C%E5%AE%9C%E9%87%8E%E6%B9%BE%E5%B8%82%20%E5%9B%BD%E9%81%93%E3%81%AE%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%9F%BC%E7%8E%89%E7%9C%8C%E4%B8%8A%E5%B0%BE%E5%B8%82%20%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
         <v>地図</v>
       </c>
       <c r="H44" s="8" t="s">
@@ -10329,7 +10798,7 @@
         <v>1</v>
       </c>
       <c r="J44" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K44" s="8" t="s">
         <v>268</v>
@@ -10338,18 +10807,18 @@
         <v>39</v>
       </c>
       <c r="M44" s="11" t="s">
-        <v>269</v>
+        <v>61</v>
       </c>
       <c r="N44" s="9" t="str">
-        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/63af58045463fe7bfe0503cb05d10228b7ab385a","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261012de58063","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O44" s="8"/>
       <c r="P44" s="8" t="n">
-        <v>26.282</v>
+        <v>35.977</v>
       </c>
       <c r="Q44" s="8" t="n">
-        <v>127.778</v>
+        <v>139.593</v>
       </c>
       <c r="R44" s="8" t="s">
         <v>48</v>
@@ -10366,49 +10835,49 @@
         <v>112</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>83</v>
+        <v>196</v>
       </c>
       <c r="E45" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="F45" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="F45" s="8" t="s">
+      <c r="G45" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%96%B0%E6%BD%9F%E7%9C%8C%E9%95%B7%E5%B2%A1%E5%B8%82%20%E5%9F%8E%E5%B2%A11%E4%B8%81%E7%9B%AE%E3%81%AE%E5%B8%82%E9%81%93","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H45" s="8" t="s">
         <v>271</v>
-      </c>
-      <c r="G45" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A5%9E%E5%A5%88%E5%B7%9D%E7%9C%8C%E6%9D%BE%E7%94%B0%E7%94%BA%20%E5%9B%BD%E9%81%93255%E5%8F%B7","地図")</f>
-        <v>地図</v>
-      </c>
-      <c r="H45" s="8" t="s">
-        <v>272</v>
       </c>
       <c r="I45" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J45" s="7"/>
       <c r="K45" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="L45" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M45" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="N45" s="9" t="str">
+        <f aca="false">HYPERLINK("https://niigata-nippo.co.jp/articles/-/922657","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O45" s="8" t="s">
         <v>273</v>
       </c>
-      <c r="L45" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="M45" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="N45" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.kanaloco.jp/news/social/case","記事を開く")</f>
-        <v>記事を開く</v>
-      </c>
-      <c r="O45" s="8" t="s">
-        <v>274</v>
-      </c>
       <c r="P45" s="8" t="n">
-        <v>35.343</v>
+        <v>37.45</v>
       </c>
       <c r="Q45" s="8" t="n">
-        <v>139.139</v>
+        <v>138.82</v>
       </c>
       <c r="R45" s="8" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10422,46 +10891,46 @@
         <v>112</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="E46" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="F46" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="F46" s="8" t="s">
+      <c r="G46" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%B2%96%E7%B8%84%E7%9C%8C%E5%AE%9C%E9%87%8E%E6%B9%BE%E5%B8%82%20%E5%9B%BD%E9%81%93%E3%81%AE%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H46" s="8" t="s">
         <v>276</v>
-      </c>
-      <c r="G46" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A5%9E%E5%A5%88%E5%B7%9D%E7%9C%8C%E6%A8%AA%E6%B5%9C%E5%B8%82%E9%87%91%E6%B2%A2%E5%8C%BA%20%E4%BF%A1%E5%8F%B7%E3%81%AE%E3%81%82%E3%82%8B%E5%8D%81%E5%AD%97%E8%B7%AF%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
-        <v>地図</v>
-      </c>
-      <c r="H46" s="8" t="s">
-        <v>277</v>
       </c>
       <c r="I46" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J46" s="7"/>
+      <c r="J46" s="7" t="n">
+        <v>3</v>
+      </c>
       <c r="K46" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="L46" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M46" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="L46" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="M46" s="8" t="s">
-        <v>164</v>
-      </c>
       <c r="N46" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.kanaloco.jp/news/social/case","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/63af58045463fe7bfe0503cb05d10228b7ab385a","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O46" s="8" t="s">
-        <v>274</v>
-      </c>
+      <c r="O46" s="8"/>
       <c r="P46" s="8" t="n">
-        <v>35.335</v>
+        <v>26.282</v>
       </c>
       <c r="Q46" s="8" t="n">
-        <v>139.62</v>
+        <v>127.778</v>
       </c>
       <c r="R46" s="8" t="s">
         <v>48</v>
@@ -10478,156 +10947,158 @@
         <v>112</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>246</v>
+        <v>83</v>
       </c>
       <c r="E47" s="8" t="s">
         <v>279</v>
       </c>
       <c r="F47" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="G47" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A5%9E%E5%A5%88%E5%B7%9D%E7%9C%8C%E6%9D%BE%E7%94%B0%E7%94%BA%20%E5%9B%BD%E9%81%93255%E5%8F%B7","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H47" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="I47" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" s="7"/>
+      <c r="K47" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="L47" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="M47" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="N47" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.kanaloco.jp/news/social/case","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O47" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="P47" s="8" t="n">
+        <v>35.343</v>
+      </c>
+      <c r="Q47" s="8" t="n">
+        <v>139.139</v>
+      </c>
+      <c r="R47" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="7" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="6" t="n">
+        <v>46306</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="G48" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A5%9E%E5%A5%88%E5%B7%9D%E7%9C%8C%E6%A8%AA%E6%B5%9C%E5%B8%82%E9%87%91%E6%B2%A2%E5%8C%BA%20%E4%BF%A1%E5%8F%B7%E3%81%AE%E3%81%82%E3%82%8B%E5%8D%81%E5%AD%97%E8%B7%AF%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H48" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="I48" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" s="7"/>
+      <c r="K48" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="L48" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="M48" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="N48" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.kanaloco.jp/news/social/case","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O48" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="P48" s="8" t="n">
+        <v>35.335</v>
+      </c>
+      <c r="Q48" s="8" t="n">
+        <v>139.62</v>
+      </c>
+      <c r="R48" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="7" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="6" t="n">
+        <v>46306</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="F49" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="G47" s="9" t="str">
+      <c r="G49" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A6%8F%E5%B3%B6%E7%9C%8C%E5%8F%A4%E6%AE%BF%E7%94%BA%20%E7%9C%8C%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
-      <c r="H47" s="8" t="s">
-        <v>280</v>
-      </c>
-      <c r="I47" s="7" t="n">
+      <c r="H49" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="I49" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J47" s="7" t="n">
+      <c r="J49" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="K47" s="8" t="s">
-        <v>281</v>
-      </c>
-      <c r="L47" s="10" t="s">
+      <c r="K49" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="L49" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M47" s="11" t="s">
+      <c r="M49" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="N47" s="9" t="str">
+      <c r="N49" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261012de58048","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O47" s="8"/>
-      <c r="P47" s="8" t="n">
-        <v>37.19</v>
-      </c>
-      <c r="Q47" s="8" t="n">
-        <v>140.55</v>
-      </c>
-      <c r="R47" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="7" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" s="6" t="n">
-        <v>46307</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="D48" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="F48" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="G48" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%8C%97%E6%B5%B7%E9%81%93%E5%8D%A0%E5%86%A0%E6%9D%91%20%E3%83%8B%E3%83%8B%E3%82%A6%E3%81%AE%E5%9B%BD%E9%81%93274%E5%8F%B7","地図")</f>
-        <v>地図</v>
-      </c>
-      <c r="H48" s="8" t="s">
-        <v>284</v>
-      </c>
-      <c r="I48" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" s="7"/>
-      <c r="K48" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="L48" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="M48" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="N48" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.uhb.jp/news/","記事を開く")</f>
-        <v>記事を開く</v>
-      </c>
-      <c r="O48" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="P48" s="8" t="n">
-        <v>43</v>
-      </c>
-      <c r="Q48" s="8" t="n">
-        <v>142.4</v>
-      </c>
-      <c r="R48" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="7" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" s="6" t="n">
-        <v>46307</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="D49" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="F49" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="G49" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%B1%B1%E5%BD%A2%E7%9C%8C%E7%B1%B3%E6%B2%A2%E5%B8%82%20%E5%B8%82%E9%81%93","地図")</f>
-        <v>地図</v>
-      </c>
-      <c r="H49" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="I49" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J49" s="7"/>
-      <c r="K49" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="L49" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M49" s="11" t="s">
-        <v>292</v>
-      </c>
-      <c r="N49" s="9" t="str">
-        <f aca="false">HYPERLINK("https://tenki.jp/news/fnn/7ccd7aa9-d4d9-4789-8e1e-cab7d8bdc2b2.html","記事を開く")</f>
-        <v>記事を開く</v>
-      </c>
       <c r="O49" s="8"/>
       <c r="P49" s="8" t="n">
-        <v>37.922</v>
+        <v>37.19</v>
       </c>
       <c r="Q49" s="8" t="n">
-        <v>140.116</v>
+        <v>140.55</v>
       </c>
       <c r="R49" s="8" t="s">
         <v>48</v>
@@ -10644,46 +11115,46 @@
         <v>146</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>196</v>
+        <v>94</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="G50" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%96%B0%E6%BD%9F%E7%9C%8C%E9%AD%9A%E6%B2%BC%E5%B8%82%20%E5%9B%BD%E9%81%9317%E5%8F%B7","地図")</f>
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%8C%97%E6%B5%B7%E9%81%93%E5%8D%A0%E5%86%A0%E6%9D%91%20%E3%83%8B%E3%83%8B%E3%82%A6%E3%81%AE%E5%9B%BD%E9%81%93274%E5%8F%B7","地図")</f>
         <v>地図</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="I50" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J50" s="7"/>
       <c r="K50" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="L50" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M50" s="11" t="s">
-        <v>297</v>
+        <v>293</v>
+      </c>
+      <c r="L50" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="M50" s="8" t="s">
+        <v>294</v>
       </c>
       <c r="N50" s="9" t="str">
-        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/ab334fba4edce972adb2a6770aa3b1ad4f14b46a","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://www.uhb.jp/news/","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O50" s="8" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="P50" s="8" t="n">
-        <v>37.23</v>
+        <v>43</v>
       </c>
       <c r="Q50" s="8" t="n">
-        <v>138.96</v>
+        <v>142.4</v>
       </c>
       <c r="R50" s="8" t="s">
         <v>48</v>
@@ -10700,98 +11171,100 @@
         <v>146</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>43</v>
+        <v>147</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>300</v>
+        <v>241</v>
       </c>
       <c r="G51" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A6%8F%E5%B2%A1%E7%9C%8C%E7%A6%8F%E5%B2%A1%E5%B8%82%E6%9D%B1%E5%8C%BA%20%E3%81%B5%E9%A0%AD%E3%81%AE%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%B1%B1%E5%BD%A2%E7%9C%8C%E7%B1%B3%E6%B2%A2%E5%B8%82%20%E5%B8%82%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="I51" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J51" s="7"/>
       <c r="K51" s="8" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="L51" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M51" s="11" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="N51" s="9" t="str">
-        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/6843a963abe9ed0a34e99e653700dd67f3a0c986","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://tenki.jp/news/fnn/7ccd7aa9-d4d9-4789-8e1e-cab7d8bdc2b2.html","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O51" s="8"/>
       <c r="P51" s="8" t="n">
-        <v>33.66</v>
+        <v>37.922</v>
       </c>
       <c r="Q51" s="8" t="n">
-        <v>130.42</v>
+        <v>140.116</v>
       </c>
       <c r="R51" s="8" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="n">
         <v>51</v>
       </c>
       <c r="B52" s="6" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>33</v>
+        <v>146</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>108</v>
+        <v>301</v>
       </c>
       <c r="G52" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%9F%BC%E7%8E%89%E7%9C%8C%E6%9D%BE%E4%BC%8F%E7%94%BA","地図")</f>
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%96%B0%E6%BD%9F%E7%9C%8C%E9%AD%9A%E6%B2%BC%E5%B8%82%20%E5%9B%BD%E9%81%9317%E5%8F%B7","地図")</f>
         <v>地図</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="I52" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J52" s="7"/>
       <c r="K52" s="8" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="L52" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M52" s="8" t="s">
-        <v>226</v>
+      <c r="M52" s="11" t="s">
+        <v>304</v>
       </c>
       <c r="N52" s="9" t="str">
-        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/21ea92b0726a5c99be7ef527e25ec26aabd9626c","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/ab334fba4edce972adb2a6770aa3b1ad4f14b46a","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O52" s="8"/>
+      <c r="O52" s="8" t="s">
+        <v>305</v>
+      </c>
       <c r="P52" s="8" t="n">
-        <v>35.938</v>
+        <v>37.23</v>
       </c>
       <c r="Q52" s="8" t="n">
-        <v>139.8</v>
+        <v>138.96</v>
       </c>
       <c r="R52" s="8" t="s">
         <v>48</v>
@@ -10802,212 +11275,212 @@
         <v>52</v>
       </c>
       <c r="B53" s="6" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="G53" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A6%8F%E5%B2%A1%E7%9C%8C%E7%A6%8F%E5%B2%A1%E5%B8%82%E6%9D%B1%E5%8C%BA%20%E3%81%B5%E9%A0%AD%E3%81%AE%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H53" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="I53" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" s="7"/>
+      <c r="K53" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="L53" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M53" s="11" t="s">
+        <v>310</v>
+      </c>
+      <c r="N53" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/6843a963abe9ed0a34e99e653700dd67f3a0c986","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O53" s="8"/>
+      <c r="P53" s="8" t="n">
+        <v>33.66</v>
+      </c>
+      <c r="Q53" s="8" t="n">
+        <v>130.42</v>
+      </c>
+      <c r="R53" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="7" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="6" t="n">
         <v>46308</v>
       </c>
-      <c r="C53" s="7" t="s">
+      <c r="C54" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D53" s="8" t="s">
+      <c r="D54" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="G54" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%9F%BC%E7%8E%89%E7%9C%8C%E6%9D%BE%E4%BC%8F%E7%94%BA","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H54" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="I54" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" s="7"/>
+      <c r="K54" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="L54" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M54" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="N54" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/21ea92b0726a5c99be7ef527e25ec26aabd9626c","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O54" s="8"/>
+      <c r="P54" s="8" t="n">
+        <v>35.938</v>
+      </c>
+      <c r="Q54" s="8" t="n">
+        <v>139.8</v>
+      </c>
+      <c r="R54" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="6" t="n">
+        <v>46308</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D55" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="E53" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="F53" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="G53" s="9" t="str">
+      <c r="E55" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="G55" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%A4%A7%E9%98%AA%E5%BA%9C%E5%A0%BA%E5%B8%82%20%E9%98%AA%E5%92%8C%E8%87%AA%E5%8B%95%E8%BB%8A%E9%81%93%20%E4%B8%8A%E3%82%8A%E7%B7%9A%20%E7%BE%8E%E5%8E%9FJCT%E4%BB%98%E8%BF%91","地図")</f>
         <v>地図</v>
       </c>
-      <c r="H53" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="I53" s="7" t="n">
+      <c r="H55" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="I55" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J53" s="7"/>
-      <c r="K53" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="L53" s="10" t="s">
+      <c r="J55" s="7"/>
+      <c r="K55" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="L55" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M53" s="11" t="s">
-        <v>311</v>
-      </c>
-      <c r="N53" s="9" t="str">
+      <c r="M55" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="N55" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261013de58428","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O53" s="8"/>
-      <c r="P53" s="8" t="n">
+      <c r="O55" s="8"/>
+      <c r="P55" s="8" t="n">
         <v>34.555</v>
       </c>
-      <c r="Q53" s="8" t="n">
+      <c r="Q55" s="8" t="n">
         <v>135.56</v>
       </c>
-      <c r="R53" s="8" t="s">
+      <c r="R55" s="8" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="7" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" s="6" t="n">
+    <row r="56" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="6" t="n">
         <v>46308</v>
       </c>
-      <c r="C54" s="7" t="s">
+      <c r="C56" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D54" s="8" t="s">
+      <c r="D56" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="E54" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="F54" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="G54" s="9" t="str">
+      <c r="E56" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="G56" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%B2%90%E9%98%9C%E7%9C%8C%E7%BE%8E%E6%BF%83%E5%8A%A0%E8%8C%82%E5%B8%82%20%E6%AD%A9%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
-      <c r="H54" s="8" t="s">
-        <v>314</v>
-      </c>
-      <c r="I54" s="7" t="n">
+      <c r="H56" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="I56" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J54" s="7"/>
-      <c r="K54" s="8" t="s">
-        <v>315</v>
-      </c>
-      <c r="L54" s="10" t="s">
+      <c r="J56" s="7"/>
+      <c r="K56" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="L56" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M54" s="11" t="s">
-        <v>316</v>
-      </c>
-      <c r="N54" s="9" t="str">
+      <c r="M56" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="N56" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261013de58817","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O54" s="8"/>
-      <c r="P54" s="8" t="n">
-        <v>35.44</v>
-      </c>
-      <c r="Q54" s="8" t="n">
-        <v>137.015</v>
-      </c>
-      <c r="R54" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" s="6" t="n">
-        <v>46308</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D55" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="E55" s="8" t="s">
-        <v>317</v>
-      </c>
-      <c r="F55" s="8" t="s">
-        <v>318</v>
-      </c>
-      <c r="G55" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%BA%83%E5%B3%B6%E7%9C%8C%E5%BA%83%E5%B3%B6%E5%B8%82%E8%A5%BF%E5%8C%BA%20%E4%BA%95%E5%8F%A3%20%E8%A5%BF%E5%BA%83%E5%B3%B6%E3%83%90%E3%82%A4%E3%83%91%E3%82%B9%E4%B8%8A%E3%82%8A%E7%B7%9A","地図")</f>
-        <v>地図</v>
-      </c>
-      <c r="H55" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="I55" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J55" s="7"/>
-      <c r="K55" s="8" t="s">
-        <v>320</v>
-      </c>
-      <c r="L55" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M55" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="N55" s="9" t="str">
-        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/4ea3250b843c6cbc3b20753d257b3743cb03ea40","記事を開く")</f>
-        <v>記事を開く</v>
-      </c>
-      <c r="O55" s="8"/>
-      <c r="P55" s="8" t="n">
-        <v>34.37</v>
-      </c>
-      <c r="Q55" s="8" t="n">
-        <v>132.38</v>
-      </c>
-      <c r="R55" s="8" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="7" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" s="6" t="n">
-        <v>46308</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D56" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="F56" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="G56" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E9%9D%99%E5%B2%A1%E7%9C%8C%E6%B5%9C%E6%9D%BE%E5%B8%82%20%E4%BF%A1%E5%8F%B7%E3%81%AE%E3%81%82%E3%82%8B%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
-        <v>地図</v>
-      </c>
-      <c r="H56" s="8" t="s">
-        <v>324</v>
-      </c>
-      <c r="I56" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J56" s="7"/>
-      <c r="K56" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="L56" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M56" s="8" t="s">
-        <v>326</v>
-      </c>
-      <c r="N56" s="9" t="str">
-        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/8dfba36c6fd0292b2243591d891611acc31d627b","記事を開く")</f>
-        <v>記事を開く</v>
-      </c>
       <c r="O56" s="8"/>
       <c r="P56" s="8" t="n">
-        <v>34.71</v>
+        <v>35.44</v>
       </c>
       <c r="Q56" s="8" t="n">
-        <v>137.726</v>
+        <v>137.015</v>
       </c>
       <c r="R56" s="8" t="s">
         <v>48</v>
@@ -11018,53 +11491,53 @@
         <v>56</v>
       </c>
       <c r="B57" s="6" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="G57" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%85%B5%E5%BA%AB%E7%9C%8C%E7%A5%9E%E6%88%B8%E5%B8%82%E5%8C%97%E5%8C%BA%20%E5%B1%B1%E7%94%B0%E7%94%BA%E4%B8%AD%20%E5%9B%BD%E9%81%93428%E5%8F%B7","地図")</f>
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%BA%83%E5%B3%B6%E7%9C%8C%E5%BA%83%E5%B3%B6%E5%B8%82%E8%A5%BF%E5%8C%BA%20%E4%BA%95%E5%8F%A3%20%E8%A5%BF%E5%BA%83%E5%B3%B6%E3%83%90%E3%82%A4%E3%83%91%E3%82%B9%E4%B8%8A%E3%82%8A%E7%B7%9A","地図")</f>
         <v>地図</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="I57" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J57" s="7"/>
       <c r="K57" s="8" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="L57" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M57" s="8" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="N57" s="9" t="str">
-        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/2d6eca6ff0736fb55bc3f8509de47deb988f31c8","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/4ea3250b843c6cbc3b20753d257b3743cb03ea40","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O57" s="8"/>
       <c r="P57" s="8" t="n">
-        <v>34.8</v>
+        <v>34.37</v>
       </c>
       <c r="Q57" s="8" t="n">
-        <v>135.15</v>
+        <v>132.38</v>
       </c>
       <c r="R57" s="8" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11072,52 +11545,50 @@
         <v>57</v>
       </c>
       <c r="B58" s="6" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>50</v>
+        <v>166</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G58" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%85%B5%E5%BA%AB%E7%9C%8C%E7%A5%9E%E6%88%B8%E5%B8%82%E5%8C%97%E5%8C%BA%20%E4%BF%A1%E5%8F%B7%E3%81%AE%E3%81%AA%E3%81%84%E5%B8%82%E9%81%93%E4%BA%A4%E5%B7%AE%E7%82%B9%E3%81%AE%E6%A8%AA%E6%96%AD%E6%AD%A9%E9%81%93","地図")</f>
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E9%9D%99%E5%B2%A1%E7%9C%8C%E6%B5%9C%E6%9D%BE%E5%B8%82%20%E4%BF%A1%E5%8F%B7%E3%81%AE%E3%81%82%E3%82%8B%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
         <v>地図</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>53</v>
+        <v>331</v>
       </c>
       <c r="I58" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J58" s="7"/>
       <c r="K58" s="8" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="L58" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M58" s="11" t="s">
-        <v>334</v>
+      <c r="M58" s="8" t="s">
+        <v>333</v>
       </c>
       <c r="N58" s="9" t="str">
-        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261015de59544","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/8dfba36c6fd0292b2243591d891611acc31d627b","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O58" s="8" t="s">
-        <v>335</v>
-      </c>
+      <c r="O58" s="8"/>
       <c r="P58" s="8" t="n">
-        <v>34.86</v>
+        <v>34.71</v>
       </c>
       <c r="Q58" s="8" t="n">
-        <v>135.17</v>
+        <v>137.726</v>
       </c>
       <c r="R58" s="8" t="s">
         <v>48</v>
@@ -11134,47 +11605,47 @@
         <v>49</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>113</v>
+        <v>50</v>
       </c>
       <c r="E59" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="G59" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%85%B5%E5%BA%AB%E7%9C%8C%E7%A5%9E%E6%88%B8%E5%B8%82%E5%8C%97%E5%8C%BA%20%E5%B1%B1%E7%94%B0%E7%94%BA%E4%B8%AD%20%E5%9B%BD%E9%81%93428%E5%8F%B7","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H59" s="8" t="s">
         <v>336</v>
-      </c>
-      <c r="F59" s="8" t="s">
-        <v>337</v>
-      </c>
-      <c r="G59" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%B1%B1%E5%8F%A3%E7%9C%8C%E5%91%A8%E9%98%B2%E5%A4%A7%E5%B3%B6%E7%94%BA%20%E7%94%BA%E9%81%93","地図")</f>
-        <v>地図</v>
-      </c>
-      <c r="H59" s="8" t="s">
-        <v>338</v>
       </c>
       <c r="I59" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J59" s="7"/>
       <c r="K59" s="8" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="L59" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M59" s="11" t="s">
-        <v>340</v>
+      <c r="M59" s="8" t="s">
+        <v>338</v>
       </c>
       <c r="N59" s="9" t="str">
-        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261014de59231","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/2d6eca6ff0736fb55bc3f8509de47deb988f31c8","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O59" s="8"/>
       <c r="P59" s="8" t="n">
-        <v>33.925</v>
+        <v>34.8</v>
       </c>
       <c r="Q59" s="8" t="n">
-        <v>132.22</v>
+        <v>135.15</v>
       </c>
       <c r="R59" s="8" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11188,44 +11659,46 @@
         <v>49</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>341</v>
+        <v>50</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>71</v>
+        <v>339</v>
       </c>
       <c r="G60" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%9D%B1%E4%BA%AC%E9%83%BD%E5%BA%9C%E4%B8%AD%E5%B8%82%20%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%85%B5%E5%BA%AB%E7%9C%8C%E7%A5%9E%E6%88%B8%E5%B8%82%E5%8C%97%E5%8C%BA%20%E4%BF%A1%E5%8F%B7%E3%81%AE%E3%81%AA%E3%81%84%E5%B8%82%E9%81%93%E4%BA%A4%E5%B7%AE%E7%82%B9%E3%81%AE%E6%A8%AA%E6%96%AD%E6%AD%A9%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>343</v>
+        <v>53</v>
       </c>
       <c r="I60" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J60" s="7"/>
       <c r="K60" s="8" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="L60" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M60" s="8" t="s">
-        <v>345</v>
+      <c r="M60" s="11" t="s">
+        <v>341</v>
       </c>
       <c r="N60" s="9" t="str">
-        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/92f4495e528c1b67d996016b077456f2dc7e00b6","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261015de59544","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O60" s="8"/>
+      <c r="O60" s="8" t="s">
+        <v>342</v>
+      </c>
       <c r="P60" s="8" t="n">
-        <v>35.669</v>
+        <v>34.86</v>
       </c>
       <c r="Q60" s="8" t="n">
-        <v>139.478</v>
+        <v>135.17</v>
       </c>
       <c r="R60" s="8" t="s">
         <v>48</v>
@@ -11242,47 +11715,47 @@
         <v>49</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>252</v>
+        <v>113</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="G61" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E9%A6%99%E5%B7%9D%E7%9C%8C%E4%B8%89%E8%B1%8A%E5%B8%82%20%E9%AB%98%E6%9D%BE%E8%87%AA%E5%8B%95%E8%BB%8A%E9%81%93%20%E4%B8%8B%E3%82%8A%E7%B7%9A","地図")</f>
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%B1%B1%E5%8F%A3%E7%9C%8C%E5%91%A8%E9%98%B2%E5%A4%A7%E5%B3%B6%E7%94%BA%20%E7%94%BA%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="I61" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J61" s="7"/>
       <c r="K61" s="8" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="L61" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M61" s="11" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="N61" s="9" t="str">
-        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261014de59449","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261014de59231","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O61" s="8"/>
       <c r="P61" s="8" t="n">
-        <v>34.16</v>
+        <v>33.925</v>
       </c>
       <c r="Q61" s="8" t="n">
-        <v>133.7</v>
+        <v>132.22</v>
       </c>
       <c r="R61" s="8" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11290,50 +11763,50 @@
         <v>61</v>
       </c>
       <c r="B62" s="6" t="n">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>34</v>
+        <v>348</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>352</v>
+        <v>71</v>
       </c>
       <c r="G62" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%8D%83%E8%91%89%E7%9C%8C%E5%8D%83%E8%91%89%E5%B8%82%E8%8B%A5%E8%91%89%E5%8C%BA%20%E9%AB%98%E5%93%81%E7%94%BA%E3%81%AE%E5%B8%82%E9%81%93","地図")</f>
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%9D%B1%E4%BA%AC%E9%83%BD%E5%BA%9C%E4%B8%AD%E5%B8%82%20%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
         <v>地図</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="I62" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J62" s="7"/>
       <c r="K62" s="8" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="L62" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M62" s="8" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="N62" s="9" t="str">
-        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/414c9a8e4c5464cba4001c15ac1f71b3a2d10fe6","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/92f4495e528c1b67d996016b077456f2dc7e00b6","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O62" s="8"/>
       <c r="P62" s="8" t="n">
-        <v>35.62</v>
+        <v>35.669</v>
       </c>
       <c r="Q62" s="8" t="n">
-        <v>140.15</v>
+        <v>139.478</v>
       </c>
       <c r="R62" s="8" t="s">
         <v>48</v>
@@ -11344,272 +11817,272 @@
         <v>62</v>
       </c>
       <c r="B63" s="6" t="n">
+        <v>46309</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="G63" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E9%A6%99%E5%B7%9D%E7%9C%8C%E4%B8%89%E8%B1%8A%E5%B8%82%20%E9%AB%98%E6%9D%BE%E8%87%AA%E5%8B%95%E8%BB%8A%E9%81%93%20%E4%B8%8B%E3%82%8A%E7%B7%9A","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H63" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="I63" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" s="7"/>
+      <c r="K63" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="L63" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M63" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="N63" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261014de59449","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O63" s="8"/>
+      <c r="P63" s="8" t="n">
+        <v>34.16</v>
+      </c>
+      <c r="Q63" s="8" t="n">
+        <v>133.7</v>
+      </c>
+      <c r="R63" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="7" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="6" t="n">
         <v>46310</v>
       </c>
-      <c r="C63" s="7" t="s">
+      <c r="C64" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="D63" s="8" t="s">
+      <c r="D64" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="G64" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%8D%83%E8%91%89%E7%9C%8C%E5%8D%83%E8%91%89%E5%B8%82%E8%8B%A5%E8%91%89%E5%8C%BA%20%E9%AB%98%E5%93%81%E7%94%BA%E3%81%AE%E5%B8%82%E9%81%93","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H64" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="I64" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" s="7"/>
+      <c r="K64" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="L64" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M64" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="N64" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/414c9a8e4c5464cba4001c15ac1f71b3a2d10fe6","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O64" s="8"/>
+      <c r="P64" s="8" t="n">
+        <v>35.62</v>
+      </c>
+      <c r="Q64" s="8" t="n">
+        <v>140.15</v>
+      </c>
+      <c r="R64" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="7" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="6" t="n">
+        <v>46310</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D65" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="E63" s="8" t="s">
+      <c r="E65" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="F63" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="G63" s="9" t="str">
+      <c r="F65" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="G65" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%BA%83%E5%B3%B6%E7%9C%8C%E5%B0%BE%E9%81%93%E5%B8%82","地図")</f>
         <v>地図</v>
       </c>
-      <c r="H63" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="I63" s="7" t="n">
+      <c r="H65" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="I65" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J63" s="7"/>
-      <c r="K63" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="L63" s="10" t="s">
+      <c r="J65" s="7"/>
+      <c r="K65" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="L65" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M63" s="11" t="s">
-        <v>359</v>
-      </c>
-      <c r="N63" s="9" t="str">
+      <c r="M65" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="N65" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/pickup/6598906","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O63" s="8" t="s">
-        <v>360</v>
-      </c>
-      <c r="P63" s="8" t="n">
+      <c r="O65" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="P65" s="8" t="n">
         <v>34.409</v>
       </c>
-      <c r="Q63" s="8" t="n">
+      <c r="Q65" s="8" t="n">
         <v>133.205</v>
       </c>
-      <c r="R63" s="8" t="s">
+      <c r="R65" s="8" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="7" t="n">
+    <row r="66" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="7" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="6" t="n">
+        <v>46310</v>
+      </c>
+      <c r="C66" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B64" s="6" t="n">
-        <v>46310</v>
-      </c>
-      <c r="C64" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="D64" s="8" t="s">
+      <c r="D66" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="E64" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="F64" s="8" t="s">
+      <c r="E66" s="8" t="s">
+        <v>368</v>
+      </c>
+      <c r="F66" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="G64" s="9" t="str">
+      <c r="G66" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%84%9B%E7%9F%A5%E7%9C%8C%E8%B1%8A%E6%98%8E%E5%B8%82%20%E5%9B%BD%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
-      <c r="H64" s="8" t="s">
-        <v>362</v>
-      </c>
-      <c r="I64" s="7" t="n">
+      <c r="H66" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="I66" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J64" s="7" t="n">
+      <c r="J66" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="K64" s="8" t="s">
-        <v>363</v>
-      </c>
-      <c r="L64" s="10" t="s">
+      <c r="K66" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="L66" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M64" s="8" t="s">
-        <v>364</v>
-      </c>
-      <c r="N64" s="9" t="str">
+      <c r="M66" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="N66" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.nagoyatv.com/news/?id=037609","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O64" s="8"/>
-      <c r="P64" s="8" t="n">
+      <c r="O66" s="8"/>
+      <c r="P66" s="8" t="n">
         <v>35.056</v>
       </c>
-      <c r="Q64" s="8" t="n">
+      <c r="Q66" s="8" t="n">
         <v>136.992</v>
       </c>
-      <c r="R64" s="8" t="s">
+      <c r="R66" s="8" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="7" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" s="6" t="n">
+    <row r="67" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="7" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="6" t="n">
         <v>46310</v>
       </c>
-      <c r="C65" s="7" t="s">
+      <c r="C67" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="D65" s="8" t="s">
+      <c r="D67" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E65" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="F65" s="8" t="s">
-        <v>366</v>
-      </c>
-      <c r="G65" s="9" t="str">
+      <c r="E67" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="G67" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A6%8F%E5%B2%A1%E7%9C%8C%E9%A3%AF%E5%A1%9A%E5%B8%82%20%E6%AD%A9%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
-      <c r="H65" s="8" t="s">
-        <v>367</v>
-      </c>
-      <c r="I65" s="7" t="n">
+      <c r="H67" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="I67" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J65" s="7"/>
-      <c r="K65" s="8" t="s">
-        <v>368</v>
-      </c>
-      <c r="L65" s="12" t="s">
+      <c r="J67" s="7"/>
+      <c r="K67" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="L67" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="M65" s="11" t="s">
-        <v>369</v>
-      </c>
-      <c r="N65" s="9" t="str">
+      <c r="M67" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="N67" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/7cd6e8368f2d684a52eb4341c19faab4655da4bf","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O65" s="8" t="s">
-        <v>370</v>
-      </c>
-      <c r="P65" s="8" t="n">
+      <c r="O67" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="P67" s="8" t="n">
         <v>33.645</v>
       </c>
-      <c r="Q65" s="8" t="n">
+      <c r="Q67" s="8" t="n">
         <v>130.69</v>
-      </c>
-      <c r="R65" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" s="6" t="n">
-        <v>46311</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="D66" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="E66" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="F66" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="G66" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%B1%B1%E5%8F%A3%E7%9C%8C%E5%B1%B1%E5%8F%A3%E5%B8%82%20%E6%A8%AA%E6%96%AD%E6%AD%A9%E9%81%93","地図")</f>
-        <v>地図</v>
-      </c>
-      <c r="H66" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="I66" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J66" s="7"/>
-      <c r="K66" s="8" t="s">
-        <v>372</v>
-      </c>
-      <c r="L66" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M66" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="N66" s="9" t="str">
-        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261016de60546","記事を開く")</f>
-        <v>記事を開く</v>
-      </c>
-      <c r="O66" s="8"/>
-      <c r="P66" s="8" t="n">
-        <v>34.178</v>
-      </c>
-      <c r="Q66" s="8" t="n">
-        <v>131.474</v>
-      </c>
-      <c r="R66" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="7" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" s="6" t="n">
-        <v>46311</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="D67" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="E67" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="F67" s="8" t="s">
-        <v>374</v>
-      </c>
-      <c r="G67" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A5%9E%E5%A5%88%E5%B7%9D%E7%9C%8C%E6%A8%AA%E6%B5%9C%E5%B8%82%E9%B6%B4%E8%A6%8B%E5%8C%BA%20%E4%BD%83%E9%87%8E%E7%94%BA%E3%81%AE%E5%B8%82%E9%81%93%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
-        <v>地図</v>
-      </c>
-      <c r="H67" s="8" t="s">
-        <v>375</v>
-      </c>
-      <c r="I67" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J67" s="7"/>
-      <c r="K67" s="8" t="s">
-        <v>376</v>
-      </c>
-      <c r="L67" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M67" s="8" t="s">
-        <v>377</v>
-      </c>
-      <c r="N67" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.kanaloco.jp/news/social/case/article-1313006.html","記事を開く")</f>
-        <v>記事を開く</v>
-      </c>
-      <c r="O67" s="8"/>
-      <c r="P67" s="8" t="n">
-        <v>35.508</v>
-      </c>
-      <c r="Q67" s="8" t="n">
-        <v>139.677</v>
       </c>
       <c r="R67" s="8" t="s">
         <v>48</v>
@@ -11623,47 +12096,47 @@
         <v>46311</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="F68" s="8" t="s">
         <v>378</v>
       </c>
       <c r="G68" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%BE%A4%E9%A6%AC%E7%9C%8C%E9%A4%A8%E6%9E%97%E5%B8%82%20%E8%BF%91%E8%97%A4%E7%94%BA%20%E5%9B%BD%E9%81%93122%E5%8F%B7%E3%81%AE%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%B1%B1%E5%8F%A3%E7%9C%8C%E5%B1%B1%E5%8F%A3%E5%B8%82%20%E6%A8%AA%E6%96%AD%E6%AD%A9%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
       <c r="H68" s="8" t="s">
-        <v>379</v>
+        <v>224</v>
       </c>
       <c r="I68" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J68" s="7"/>
       <c r="K68" s="8" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="L68" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M68" s="8" t="s">
-        <v>381</v>
+      <c r="M68" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="N68" s="9" t="str">
-        <f aca="false">HYPERLINK("https://jomo-news.co.jp/articles/-/1045465","記事を開く")</f>
+        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261016de60546","記事を開く")</f>
         <v>記事を開く</v>
       </c>
       <c r="O68" s="8"/>
       <c r="P68" s="8" t="n">
-        <v>36.245</v>
+        <v>34.178</v>
       </c>
       <c r="Q68" s="8" t="n">
-        <v>139.542</v>
+        <v>131.474</v>
       </c>
       <c r="R68" s="8" t="s">
         <v>48</v>
@@ -11677,77 +12150,349 @@
         <v>46311</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D69" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="G69" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A5%9E%E5%A5%88%E5%B7%9D%E7%9C%8C%E6%A8%AA%E6%B5%9C%E5%B8%82%E9%B6%B4%E8%A6%8B%E5%8C%BA%20%E4%BD%83%E9%87%8E%E7%94%BA%E3%81%AE%E5%B8%82%E9%81%93%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H69" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="I69" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J69" s="7"/>
+      <c r="K69" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="L69" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M69" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="N69" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.kanaloco.jp/news/social/case/article-1313006.html","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O69" s="8"/>
+      <c r="P69" s="8" t="n">
+        <v>35.508</v>
+      </c>
+      <c r="Q69" s="8" t="n">
+        <v>139.677</v>
+      </c>
+      <c r="R69" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="7" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="6" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="G70" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%BE%A4%E9%A6%AC%E7%9C%8C%E9%A4%A8%E6%9E%97%E5%B8%82%20%E8%BF%91%E8%97%A4%E7%94%BA%20%E5%9B%BD%E9%81%93122%E5%8F%B7%E3%81%AE%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H70" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="I70" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J70" s="7"/>
+      <c r="K70" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="L70" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M70" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="N70" s="9" t="str">
+        <f aca="false">HYPERLINK("https://jomo-news.co.jp/articles/-/1045465","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O70" s="8"/>
+      <c r="P70" s="8" t="n">
+        <v>36.245</v>
+      </c>
+      <c r="Q70" s="8" t="n">
+        <v>139.542</v>
+      </c>
+      <c r="R70" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="6" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="D71" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="E69" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="F69" s="8" t="s">
+      <c r="E71" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="F71" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="G69" s="9" t="str">
+      <c r="G71" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E9%B3%A5%E5%8F%96%E7%9C%8C%E4%BC%AF%E8%80%86%E7%94%BA%20%E7%9C%8C%E9%81%93","地図")</f>
         <v>地図</v>
       </c>
-      <c r="H69" s="8" t="s">
-        <v>383</v>
-      </c>
-      <c r="I69" s="7" t="n">
+      <c r="H71" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="I71" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J69" s="7"/>
-      <c r="K69" s="8" t="s">
-        <v>384</v>
-      </c>
-      <c r="L69" s="12" t="s">
+      <c r="J71" s="7"/>
+      <c r="K71" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="L71" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M71" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="N71" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261017de60865","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O71" s="8"/>
+      <c r="P71" s="8" t="n">
+        <v>35.383</v>
+      </c>
+      <c r="Q71" s="8" t="n">
+        <v>133.483</v>
+      </c>
+      <c r="R71" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="7" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="6" t="n">
+        <v>46312</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="G72" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%8C%97%E6%B5%B7%E9%81%93%E6%A8%99%E6%B4%A5%E7%94%BA%20%E9%81%93%E9%81%93774%E5%8F%B7","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H72" s="8" t="s">
+        <v>394</v>
+      </c>
+      <c r="I72" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J72" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K72" s="8" t="s">
+        <v>395</v>
+      </c>
+      <c r="L72" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M72" s="11" t="s">
+        <v>396</v>
+      </c>
+      <c r="N72" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261017de61040","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O72" s="8"/>
+      <c r="P72" s="8" t="n">
+        <v>43.66</v>
+      </c>
+      <c r="Q72" s="8" t="n">
+        <v>145.13</v>
+      </c>
+      <c r="R72" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="7" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="6" t="n">
+        <v>46312</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="G73" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A6%8F%E5%B3%B6%E7%9C%8C%E7%A6%8F%E5%B3%B6%E5%B8%82%20%E6%9D%B1%E5%8C%97%E8%87%AA%E5%8B%95%E8%BB%8A%E9%81%93%20%E4%B8%8B%E3%82%8A%E7%B7%9A","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H73" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="I73" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J73" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K73" s="8" t="s">
+        <v>400</v>
+      </c>
+      <c r="L73" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M73" s="8" t="s">
+        <v>401</v>
+      </c>
+      <c r="N73" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/b51bf42efd30e865cc3c8bfd906eca0854053bec","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O73" s="8"/>
+      <c r="P73" s="8" t="n">
+        <v>37.84</v>
+      </c>
+      <c r="Q73" s="8" t="n">
+        <v>140.46</v>
+      </c>
+      <c r="R73" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="7" t="n">
         <v>73</v>
       </c>
-      <c r="M69" s="8" t="s">
-        <v>385</v>
-      </c>
-      <c r="N69" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.nnn.co.jp/articles/-/815243","記事を開く")</f>
+      <c r="B74" s="6" t="n">
+        <v>46312</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>403</v>
+      </c>
+      <c r="G74" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E9%95%B7%E9%87%8E%E7%9C%8C%E4%BD%90%E4%B9%85%E5%B8%82%20%E9%A6%99%E5%9D%82%20%E4%B8%8A%E4%BF%A1%E8%B6%8A%E8%87%AA%E5%8B%95%E8%BB%8A%E9%81%93%20%E4%B8%8A%E3%82%8A%E7%B7%9A%E3%81%AE%E3%83%88%E3%83%B3%E3%83%8D%E3%83%AB","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H74" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="I74" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J74" s="7"/>
+      <c r="K74" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="L74" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M74" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="N74" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.tokyo-np.co.jp/article/522213","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O69" s="8" t="s">
-        <v>386</v>
-      </c>
-      <c r="P69" s="8" t="n">
-        <v>35.383</v>
-      </c>
-      <c r="Q69" s="8" t="n">
-        <v>133.483</v>
-      </c>
-      <c r="R69" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="14" t="s">
-        <v>387</v>
-      </c>
-      <c r="B71" s="14" t="str">
-        <f aca="false">COUNTA(D2:D69)&amp;"件"</f>
-        <v>68件</v>
-      </c>
-      <c r="H71" s="14" t="s">
-        <v>388</v>
-      </c>
-      <c r="I71" s="14" t="n">
-        <f aca="false">SUM(I2:I69)</f>
-        <v>70</v>
-      </c>
-      <c r="J71" s="14" t="n">
-        <f aca="false">SUM(J2:J69)</f>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="15" t="s">
-        <v>389</v>
+      <c r="O74" s="8"/>
+      <c r="P74" s="8" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="Q74" s="8" t="n">
+        <v>138.55</v>
+      </c>
+      <c r="R74" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="14" t="s">
+        <v>407</v>
+      </c>
+      <c r="B76" s="14" t="str">
+        <f aca="false">COUNTA(D2:D74)&amp;"件"</f>
+        <v>73件</v>
+      </c>
+      <c r="H76" s="14" t="s">
+        <v>408</v>
+      </c>
+      <c r="I76" s="14" t="n">
+        <f aca="false">SUM(I2:I74)</f>
+        <v>76</v>
+      </c>
+      <c r="J76" s="14" t="n">
+        <f aca="false">SUM(J2:J74)</f>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="15" t="s">
+        <v>409</v>
       </c>
     </row>
   </sheetData>
@@ -11782,10 +12527,10 @@
         <v>18</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>391</v>
+        <v>411</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11793,12 +12538,12 @@
         <v>94</v>
       </c>
       <c r="B2" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A2)</f>
-        <v>4</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A2)</f>
+        <v>5</v>
       </c>
       <c r="C2" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A2,事故一覧!$I$2:$I$69)</f>
-        <v>4</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A2,事故一覧!$I$2:$I$74)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11806,50 +12551,50 @@
         <v>88</v>
       </c>
       <c r="B3" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A3)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A3)</f>
         <v>1</v>
       </c>
       <c r="C3" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A3,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A3,事故一覧!$I$2:$I$74)</f>
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="B4" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A4)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A4)</f>
         <v>0</v>
       </c>
       <c r="C4" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A4,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A4,事故一覧!$I$2:$I$74)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="B5" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A5)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A5)</f>
         <v>0</v>
       </c>
       <c r="C5" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A5,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A5,事故一覧!$I$2:$I$74)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="B6" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A6)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A6)</f>
         <v>0</v>
       </c>
       <c r="C6" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A6,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A6,事故一覧!$I$2:$I$74)</f>
         <v>0</v>
       </c>
     </row>
@@ -11858,25 +12603,25 @@
         <v>147</v>
       </c>
       <c r="B7" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A7)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A7)</f>
         <v>2</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A7,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A7,事故一覧!$I$2:$I$74)</f>
         <v>2</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="B8" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A8)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A8)</f>
+        <v>3</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A8,事故一覧!$I$2:$I$69)</f>
-        <v>2</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A8,事故一覧!$I$2:$I$74)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11884,24 +12629,24 @@
         <v>106</v>
       </c>
       <c r="B9" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A9)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A9)</f>
         <v>2</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A9,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A9,事故一覧!$I$2:$I$74)</f>
         <v>2</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="B10" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A10)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A10)</f>
         <v>0</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A10,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A10,事故一覧!$I$2:$I$74)</f>
         <v>0</v>
       </c>
     </row>
@@ -11910,11 +12655,11 @@
         <v>133</v>
       </c>
       <c r="B11" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A11)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A11)</f>
         <v>2</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A11,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A11,事故一覧!$I$2:$I$74)</f>
         <v>2</v>
       </c>
     </row>
@@ -11923,11 +12668,11 @@
         <v>180</v>
       </c>
       <c r="B12" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A12)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A12)</f>
         <v>5</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A12,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A12,事故一覧!$I$2:$I$74)</f>
         <v>5</v>
       </c>
     </row>
@@ -11936,24 +12681,24 @@
         <v>34</v>
       </c>
       <c r="B13" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A13)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A13)</f>
         <v>2</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A13,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A13,事故一覧!$I$2:$I$74)</f>
         <v>4</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="B14" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A14)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A14)</f>
         <v>1</v>
       </c>
       <c r="C14" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A14,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A14,事故一覧!$I$2:$I$74)</f>
         <v>1</v>
       </c>
     </row>
@@ -11962,11 +12707,11 @@
         <v>83</v>
       </c>
       <c r="B15" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A15)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A15)</f>
         <v>5</v>
       </c>
       <c r="C15" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A15,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A15,事故一覧!$I$2:$I$74)</f>
         <v>6</v>
       </c>
     </row>
@@ -11975,63 +12720,63 @@
         <v>196</v>
       </c>
       <c r="B16" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A16)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A16)</f>
         <v>3</v>
       </c>
       <c r="C16" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A16,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A16,事故一覧!$I$2:$I$74)</f>
         <v>3</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="B17" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A17)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A17)</f>
         <v>0</v>
       </c>
       <c r="C17" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A17,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A17,事故一覧!$I$2:$I$74)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="16" t="s">
-        <v>397</v>
+        <v>417</v>
       </c>
       <c r="B18" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A18)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A18)</f>
         <v>0</v>
       </c>
       <c r="C18" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A18,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A18,事故一覧!$I$2:$I$74)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="16" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="B19" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A19)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A19)</f>
         <v>0</v>
       </c>
       <c r="C19" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A19,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A19,事故一覧!$I$2:$I$74)</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="B20" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A20)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A20)</f>
         <v>0</v>
       </c>
       <c r="C20" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A20,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A20,事故一覧!$I$2:$I$74)</f>
         <v>0</v>
       </c>
     </row>
@@ -12040,12 +12785,12 @@
         <v>56</v>
       </c>
       <c r="B21" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A21)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A21)</f>
+        <v>3</v>
       </c>
       <c r="C21" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A21,事故一覧!$I$2:$I$69)</f>
-        <v>2</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A21,事故一覧!$I$2:$I$74)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12053,11 +12798,11 @@
         <v>156</v>
       </c>
       <c r="B22" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A22)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A22)</f>
         <v>3</v>
       </c>
       <c r="C22" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A22,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A22,事故一覧!$I$2:$I$74)</f>
         <v>3</v>
       </c>
     </row>
@@ -12066,11 +12811,11 @@
         <v>166</v>
       </c>
       <c r="B23" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A23)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A23)</f>
         <v>2</v>
       </c>
       <c r="C23" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A23,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A23,事故一覧!$I$2:$I$74)</f>
         <v>2</v>
       </c>
     </row>
@@ -12079,50 +12824,50 @@
         <v>75</v>
       </c>
       <c r="B24" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A24)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A24)</f>
         <v>3</v>
       </c>
       <c r="C24" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A24,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A24,事故一覧!$I$2:$I$74)</f>
         <v>2</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="16" t="s">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="B25" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A25)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A25)</f>
         <v>0</v>
       </c>
       <c r="C25" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A25,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A25,事故一覧!$I$2:$I$74)</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="16" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="B26" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A26)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A26)</f>
         <v>1</v>
       </c>
       <c r="C26" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A26,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A26,事故一覧!$I$2:$I$74)</f>
         <v>1</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="16" t="s">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="B27" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A27)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A27)</f>
         <v>0</v>
       </c>
       <c r="C27" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A27,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A27,事故一覧!$I$2:$I$74)</f>
         <v>0</v>
       </c>
     </row>
@@ -12131,11 +12876,11 @@
         <v>99</v>
       </c>
       <c r="B28" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A28)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A28)</f>
         <v>3</v>
       </c>
       <c r="C28" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A28,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A28,事故一覧!$I$2:$I$74)</f>
         <v>3</v>
       </c>
     </row>
@@ -12144,37 +12889,37 @@
         <v>50</v>
       </c>
       <c r="B29" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A29)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A29)</f>
         <v>7</v>
       </c>
       <c r="C29" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A29,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A29,事故一覧!$I$2:$I$74)</f>
         <v>7</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="16" t="s">
-        <v>402</v>
+        <v>422</v>
       </c>
       <c r="B30" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A30)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A30)</f>
         <v>0</v>
       </c>
       <c r="C30" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A30,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A30,事故一覧!$I$2:$I$74)</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="16" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="B31" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A31)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A31)</f>
         <v>0</v>
       </c>
       <c r="C31" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A31,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A31,事故一覧!$I$2:$I$74)</f>
         <v>0</v>
       </c>
     </row>
@@ -12183,37 +12928,37 @@
         <v>143</v>
       </c>
       <c r="B32" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A32)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A32)</f>
         <v>2</v>
       </c>
       <c r="C32" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A32,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A32,事故一覧!$I$2:$I$74)</f>
         <v>2</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="16" t="s">
-        <v>404</v>
+        <v>424</v>
       </c>
       <c r="B33" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A33)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A33)</f>
         <v>0</v>
       </c>
       <c r="C33" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A33,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A33,事故一覧!$I$2:$I$74)</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="16" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="B34" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A34)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A34)</f>
         <v>0</v>
       </c>
       <c r="C34" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A34,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A34,事故一覧!$I$2:$I$74)</f>
         <v>0</v>
       </c>
     </row>
@@ -12222,12 +12967,12 @@
         <v>120</v>
       </c>
       <c r="B35" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A35)</f>
-        <v>3</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A35)</f>
+        <v>4</v>
       </c>
       <c r="C35" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A35,事故一覧!$I$2:$I$69)</f>
-        <v>3</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A35,事故一覧!$I$2:$I$74)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12235,63 +12980,63 @@
         <v>113</v>
       </c>
       <c r="B36" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A36)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A36)</f>
         <v>3</v>
       </c>
       <c r="C36" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A36,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A36,事故一覧!$I$2:$I$74)</f>
         <v>3</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="16" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
       <c r="B37" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A37)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A37)</f>
         <v>0</v>
       </c>
       <c r="C37" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A37,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A37,事故一覧!$I$2:$I$74)</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="16" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="B38" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A38)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A38)</f>
         <v>2</v>
       </c>
       <c r="C38" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A38,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A38,事故一覧!$I$2:$I$74)</f>
         <v>2</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="16" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="B39" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A39)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A39)</f>
         <v>0</v>
       </c>
       <c r="C39" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A39,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A39,事故一覧!$I$2:$I$74)</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="16" t="s">
-        <v>408</v>
+        <v>428</v>
       </c>
       <c r="B40" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A40)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A40)</f>
         <v>0</v>
       </c>
       <c r="C40" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A40,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A40,事故一覧!$I$2:$I$74)</f>
         <v>0</v>
       </c>
     </row>
@@ -12300,89 +13045,89 @@
         <v>43</v>
       </c>
       <c r="B41" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A41)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A41)</f>
         <v>4</v>
       </c>
       <c r="C41" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A41,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A41,事故一覧!$I$2:$I$74)</f>
         <v>4</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="16" t="s">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="B42" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A42)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A42)</f>
         <v>0</v>
       </c>
       <c r="C42" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A42,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A42,事故一覧!$I$2:$I$74)</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="16" t="s">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="B43" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A43)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A43)</f>
         <v>0</v>
       </c>
       <c r="C43" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A43,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A43,事故一覧!$I$2:$I$74)</f>
         <v>0</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="16" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B44" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A44)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A44)</f>
         <v>2</v>
       </c>
       <c r="C44" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A44,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A44,事故一覧!$I$2:$I$74)</f>
         <v>2</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="16" t="s">
-        <v>411</v>
+        <v>431</v>
       </c>
       <c r="B45" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A45)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A45)</f>
         <v>0</v>
       </c>
       <c r="C45" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A45,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A45,事故一覧!$I$2:$I$74)</f>
         <v>0</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="16" t="s">
-        <v>412</v>
+        <v>432</v>
       </c>
       <c r="B46" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A46)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A46)</f>
         <v>0</v>
       </c>
       <c r="C46" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A46,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A46,事故一覧!$I$2:$I$74)</f>
         <v>0</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="16" t="s">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="B47" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A47)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A47)</f>
         <v>0</v>
       </c>
       <c r="C47" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A47,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A47,事故一覧!$I$2:$I$74)</f>
         <v>0</v>
       </c>
     </row>
@@ -12391,25 +13136,25 @@
         <v>150</v>
       </c>
       <c r="B48" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$69,A48)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A48)</f>
+        <v>3</v>
       </c>
       <c r="C48" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$69,A48,事故一覧!$I$2:$I$69)</f>
-        <v>2</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A48,事故一覧!$I$2:$I$74)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="14" t="s">
-        <v>387</v>
+        <v>407</v>
       </c>
       <c r="B49" s="14" t="n">
         <f aca="false">SUM(B2:B48)</f>
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C49" s="14" t="n">
         <f aca="false">SUM(C2:C48)</f>
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -12428,7 +13173,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -12439,16 +13184,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>414</v>
+        <v>434</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>391</v>
+        <v>411</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12459,11 +13204,11 @@
         <v>33</v>
       </c>
       <c r="C2" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$69,A2)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$74,A2)</f>
         <v>2</v>
       </c>
       <c r="D2" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$69,A2,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$74,A2,事故一覧!$I$2:$I$74)</f>
         <v>4</v>
       </c>
     </row>
@@ -12475,11 +13220,11 @@
         <v>49</v>
       </c>
       <c r="C3" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$69,A3)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$74,A3)</f>
         <v>2</v>
       </c>
       <c r="D3" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$69,A3,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$74,A3,事故一覧!$I$2:$I$74)</f>
         <v>2</v>
       </c>
     </row>
@@ -12491,11 +13236,11 @@
         <v>63</v>
       </c>
       <c r="C4" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$69,A4)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$74,A4)</f>
         <v>5</v>
       </c>
       <c r="D4" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$69,A4,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$74,A4,事故一覧!$I$2:$I$74)</f>
         <v>5</v>
       </c>
     </row>
@@ -12504,14 +13249,14 @@
         <v>46297</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C5" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$69,A5)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$74,A5)</f>
         <v>0</v>
       </c>
       <c r="D5" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$69,A5,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$74,A5,事故一覧!$I$2:$I$74)</f>
         <v>0</v>
       </c>
     </row>
@@ -12523,11 +13268,11 @@
         <v>93</v>
       </c>
       <c r="C6" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$69,A6)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$74,A6)</f>
         <v>3</v>
       </c>
       <c r="D6" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$69,A6,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$74,A6,事故一覧!$I$2:$I$74)</f>
         <v>3</v>
       </c>
     </row>
@@ -12539,11 +13284,11 @@
         <v>112</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$69,A7)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$74,A7)</f>
         <v>6</v>
       </c>
       <c r="D7" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$69,A7,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$74,A7,事故一覧!$I$2:$I$74)</f>
         <v>6</v>
       </c>
     </row>
@@ -12555,11 +13300,11 @@
         <v>146</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$69,A8)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$74,A8)</f>
         <v>2</v>
       </c>
       <c r="D8" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$69,A8,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$74,A8,事故一覧!$I$2:$I$74)</f>
         <v>2</v>
       </c>
     </row>
@@ -12571,11 +13316,11 @@
         <v>33</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$69,A9)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$74,A9)</f>
         <v>3</v>
       </c>
       <c r="D9" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$69,A9,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$74,A9,事故一覧!$I$2:$I$74)</f>
         <v>3</v>
       </c>
     </row>
@@ -12587,11 +13332,11 @@
         <v>49</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$69,A10)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$74,A10)</f>
         <v>3</v>
       </c>
       <c r="D10" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$69,A10,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$74,A10,事故一覧!$I$2:$I$74)</f>
         <v>3</v>
       </c>
     </row>
@@ -12603,12 +13348,12 @@
         <v>63</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$69,A11)</f>
-        <v>6</v>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$74,A11)</f>
+        <v>7</v>
       </c>
       <c r="D11" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$69,A11,事故一覧!$I$2:$I$69)</f>
-        <v>6</v>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$74,A11,事故一覧!$I$2:$I$74)</f>
+        <v>7</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12616,14 +13361,14 @@
         <v>46304</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$69,A12)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$74,A12)</f>
         <v>1</v>
       </c>
       <c r="D12" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$69,A12,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$74,A12,事故一覧!$I$2:$I$74)</f>
         <v>1</v>
       </c>
     </row>
@@ -12635,12 +13380,12 @@
         <v>93</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$69,A13)</f>
-        <v>7</v>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$74,A13)</f>
+        <v>8</v>
       </c>
       <c r="D13" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$69,A13,事故一覧!$I$2:$I$69)</f>
-        <v>7</v>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$74,A13,事故一覧!$I$2:$I$74)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12651,11 +13396,11 @@
         <v>112</v>
       </c>
       <c r="C14" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$69,A14)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$74,A14)</f>
         <v>6</v>
       </c>
       <c r="D14" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$69,A14,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$74,A14,事故一覧!$I$2:$I$74)</f>
         <v>6</v>
       </c>
     </row>
@@ -12667,11 +13412,11 @@
         <v>146</v>
       </c>
       <c r="C15" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$69,A15)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$74,A15)</f>
         <v>4</v>
       </c>
       <c r="D15" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$69,A15,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$74,A15,事故一覧!$I$2:$I$74)</f>
         <v>4</v>
       </c>
     </row>
@@ -12683,11 +13428,11 @@
         <v>33</v>
       </c>
       <c r="C16" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$69,A16)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$74,A16)</f>
         <v>5</v>
       </c>
       <c r="D16" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$69,A16,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$74,A16,事故一覧!$I$2:$I$74)</f>
         <v>5</v>
       </c>
     </row>
@@ -12699,11 +13444,11 @@
         <v>49</v>
       </c>
       <c r="C17" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$69,A17)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$74,A17)</f>
         <v>5</v>
       </c>
       <c r="D17" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$69,A17,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$74,A17,事故一覧!$I$2:$I$74)</f>
         <v>5</v>
       </c>
     </row>
@@ -12715,11 +13460,11 @@
         <v>63</v>
       </c>
       <c r="C18" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$69,A18)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$74,A18)</f>
         <v>4</v>
       </c>
       <c r="D18" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$69,A18,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$74,A18,事故一覧!$I$2:$I$74)</f>
         <v>4</v>
       </c>
     </row>
@@ -12728,29 +13473,45 @@
         <v>46311</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C19" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$69,A19)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$74,A19)</f>
         <v>4</v>
       </c>
       <c r="D19" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$69,A19,事故一覧!$I$2:$I$69)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$74,A19,事故一覧!$I$2:$I$74)</f>
         <v>4</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="14" t="s">
-        <v>387</v>
-      </c>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14" t="n">
-        <f aca="false">SUM(C2:C19)</f>
-        <v>68</v>
-      </c>
-      <c r="D20" s="14" t="n">
-        <f aca="false">SUM(D2:D19)</f>
-        <v>70</v>
+      <c r="A20" s="17" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" s="16" t="n">
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$74,A20)</f>
+        <v>3</v>
+      </c>
+      <c r="D20" s="16" t="n">
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$74,A20,事故一覧!$I$2:$I$74)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="14" t="s">
+        <v>407</v>
+      </c>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14" t="n">
+        <f aca="false">SUM(C2:C20)</f>
+        <v>73</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <f aca="false">SUM(D2:D20)</f>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -12793,10 +13554,10 @@
         <v>19</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>415</v>
+        <v>435</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>416</v>
+        <v>436</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>25</v>
@@ -12816,16 +13577,16 @@
         <v>56</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>417</v>
+        <v>437</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>419</v>
+        <v>439</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="G2" s="11" t="s">
         <v>61</v>
@@ -12843,16 +13604,16 @@
         <v>83</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>421</v>
+        <v>441</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>422</v>
+        <v>442</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>423</v>
+        <v>443</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>424</v>
+        <v>444</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>164</v>
@@ -12870,19 +13631,19 @@
         <v>83</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>425</v>
+        <v>445</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>426</v>
+        <v>446</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>419</v>
+        <v>439</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>427</v>
+        <v>447</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>428</v>
+        <v>448</v>
       </c>
       <c r="H4" s="9" t="str">
         <f aca="false">HYPERLINK("https://chunichi.co.jp/article/1321634","記事を開く")</f>
@@ -12897,16 +13658,16 @@
         <v>94</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>429</v>
+        <v>449</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>430</v>
+        <v>450</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>431</v>
+        <v>451</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>432</v>
+        <v>452</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>189</v>
@@ -12924,16 +13685,16 @@
         <v>94</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>433</v>
+        <v>453</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>434</v>
+        <v>454</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>435</v>
+        <v>455</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>194</v>
@@ -12951,19 +13712,19 @@
         <v>56</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>437</v>
+        <v>457</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>438</v>
+        <v>458</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>439</v>
+        <v>459</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="H7" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.nbs-tv.co.jp/news/","記事を開く")</f>
@@ -12978,19 +13739,19 @@
         <v>166</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>441</v>
+        <v>461</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>442</v>
+        <v>462</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>443</v>
+        <v>463</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>444</v>
+        <v>464</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="H8" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/06e1158a3abfa398275bfd5e1d8a4e62a117c2ab","記事を開く")</f>
@@ -13005,19 +13766,19 @@
         <v>50</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>445</v>
+        <v>465</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>446</v>
+        <v>466</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>447</v>
+        <v>467</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>448</v>
+        <v>468</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>449</v>
+        <v>469</v>
       </c>
       <c r="H9" s="9" t="str">
         <f aca="false">HYPERLINK("https://kobe-np.co.jp/news/jiken/202610/0020910097.shtml","記事を開く")</f>
@@ -13032,19 +13793,19 @@
         <v>99</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>450</v>
+        <v>470</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>451</v>
+        <v>471</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>452</v>
+        <v>472</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>453</v>
+        <v>473</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>454</v>
+        <v>474</v>
       </c>
       <c r="H10" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.jiji.com/jc/article?k=2026101000399&amp;g=soc","記事を開く")</f>
@@ -13059,16 +13820,16 @@
         <v>99</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>455</v>
+        <v>475</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>451</v>
+        <v>471</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>452</v>
+        <v>472</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>456</v>
+        <v>476</v>
       </c>
       <c r="G11" s="11" t="s">
         <v>61</v>
@@ -13086,19 +13847,19 @@
         <v>147</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>457</v>
+        <v>477</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>458</v>
+        <v>478</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>459</v>
+        <v>479</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>461</v>
+        <v>481</v>
       </c>
       <c r="H12" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/db9ea8f1740207802faad3b369c648aebc074777","記事を開く")</f>
@@ -13113,19 +13874,19 @@
         <v>50</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>462</v>
+        <v>482</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>463</v>
+        <v>483</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>464</v>
+        <v>484</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>465</v>
+        <v>485</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="H13" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/369ec569ebac16e8ff06c233e3feafceedfde989","記事を開く")</f>

--- a/全国交通事故データ.xlsx
+++ b/全国交通事故データ.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="506">
   <si>
     <t xml:space="preserve">このファイルについて</t>
   </si>
@@ -129,7 +129,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
     <r>
       <rPr>
@@ -6640,6 +6640,112 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">新城市</t>
+  </si>
+  <si>
+    <t xml:space="preserve">新東名高速道路 上り線（雁峰第一トンネル付近）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">車両相互（シカ衝突後の停車車両にトラック追突）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午後</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分ごろ、シカと衝突して停車中の乗用車に大型トラックが追突し、車外にいた</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">22</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳女性が死亡。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">46</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳のトラック運転手を現行犯逮捕</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">18</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日の報道で判明</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">福島市</t>
   </si>
   <si>
@@ -6868,6 +6974,419 @@
     <t xml:space="preserve">共同通信（東京新聞デジタル配信）</t>
   </si>
   <si>
+    <t xml:space="preserve">佐賀県</t>
+  </si>
+  <si>
+    <t xml:space="preserve">唐津市</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">七山滝川・国道</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">323</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">号（片側</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">車線のカーブ）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">車両相互（バイク同士の正面衝突）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時半ごろ、バイク同士が衝突し、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">38</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳会社員と大型バイクの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">代男性の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人が死亡</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NHK / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">共同通信 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ KBC</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">大分県</t>
+  </si>
+  <si>
+    <t xml:space="preserve">九重町</t>
+  </si>
+  <si>
+    <t xml:space="preserve">車両単独（大型バイクがガードワイヤーに衝突）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時すぎ、大型バイクがカーブを曲がり切れずガードワイヤーに衝突し、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">23</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳男性が約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時間後に死亡</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">OBS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">大分放送（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Yahoo!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ニュース経由）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">長井市</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">今泉・梨郷道路と国道</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">113</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">号の交差点</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">車両相互（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台衝突）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">正午すぎ、車</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台が衝突し、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">70</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">代とみられる女性が死亡、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人がけが</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">さくらんぼテレビ（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Yahoo!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ニュース経由）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">事故多発地点</t>
+  </si>
+  <si>
     <t xml:space="preserve">合計</t>
   </si>
   <si>
@@ -6934,13 +7453,7 @@
     <t xml:space="preserve">高知県</t>
   </si>
   <si>
-    <t xml:space="preserve">佐賀県</t>
-  </si>
-  <si>
     <t xml:space="preserve">長崎県</t>
-  </si>
-  <si>
-    <t xml:space="preserve">大分県</t>
   </si>
   <si>
     <t xml:space="preserve">宮崎県</t>
@@ -8065,8 +8578,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="事故一覧" displayName="事故一覧" ref="A1:R74" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:R74"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="事故一覧" displayName="事故一覧" ref="A1:R78" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:R78"/>
   <tableColumns count="18">
     <tableColumn id="1" name="No"/>
     <tableColumn id="2" name="発生日"/>
@@ -8376,7 +8889,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R77"/>
+  <dimension ref="A1:R81"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -12371,7 +12884,7 @@
         <v>93</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>255</v>
+        <v>75</v>
       </c>
       <c r="E73" s="8" t="s">
         <v>397</v>
@@ -12380,7 +12893,7 @@
         <v>398</v>
       </c>
       <c r="G73" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A6%8F%E5%B3%B6%E7%9C%8C%E7%A6%8F%E5%B3%B6%E5%B8%82%20%E6%9D%B1%E5%8C%97%E8%87%AA%E5%8B%95%E8%BB%8A%E9%81%93%20%E4%B8%8B%E3%82%8A%E7%B7%9A","地図")</f>
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E6%84%9B%E7%9F%A5%E7%9C%8C%E6%96%B0%E5%9F%8E%E5%B8%82%20%E6%96%B0%E6%9D%B1%E5%90%8D%E9%AB%98%E9%80%9F%E9%81%93%E8%B7%AF%20%E4%B8%8A%E3%82%8A%E7%B7%9A","地図")</f>
         <v>地図</v>
       </c>
       <c r="H73" s="8" t="s">
@@ -12389,28 +12902,28 @@
       <c r="I73" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J73" s="7" t="n">
-        <v>3</v>
-      </c>
+      <c r="J73" s="7"/>
       <c r="K73" s="8" t="s">
         <v>400</v>
       </c>
       <c r="L73" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M73" s="8" t="s">
+      <c r="M73" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="N73" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261018de61091","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O73" s="11" t="s">
         <v>401</v>
       </c>
-      <c r="N73" s="9" t="str">
-        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/b51bf42efd30e865cc3c8bfd906eca0854053bec","記事を開く")</f>
-        <v>記事を開く</v>
-      </c>
-      <c r="O73" s="8"/>
       <c r="P73" s="8" t="n">
-        <v>37.84</v>
+        <v>34.93</v>
       </c>
       <c r="Q73" s="8" t="n">
-        <v>140.46</v>
+        <v>137.55</v>
       </c>
       <c r="R73" s="8" t="s">
         <v>82</v>
@@ -12427,7 +12940,7 @@
         <v>93</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>56</v>
+        <v>255</v>
       </c>
       <c r="E74" s="8" t="s">
         <v>402</v>
@@ -12436,63 +12949,285 @@
         <v>403</v>
       </c>
       <c r="G74" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E7%A6%8F%E5%B3%B6%E7%9C%8C%E7%A6%8F%E5%B3%B6%E5%B8%82%20%E6%9D%B1%E5%8C%97%E8%87%AA%E5%8B%95%E8%BB%8A%E9%81%93%20%E4%B8%8B%E3%82%8A%E7%B7%9A","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H74" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="I74" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J74" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K74" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="L74" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M74" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="N74" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/b51bf42efd30e865cc3c8bfd906eca0854053bec","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O74" s="8"/>
+      <c r="P74" s="8" t="n">
+        <v>37.84</v>
+      </c>
+      <c r="Q74" s="8" t="n">
+        <v>140.46</v>
+      </c>
+      <c r="R74" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="7" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="6" t="n">
+        <v>46312</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>407</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="G75" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E9%95%B7%E9%87%8E%E7%9C%8C%E4%BD%90%E4%B9%85%E5%B8%82%20%E9%A6%99%E5%9D%82%20%E4%B8%8A%E4%BF%A1%E8%B6%8A%E8%87%AA%E5%8B%95%E8%BB%8A%E9%81%93%20%E4%B8%8A%E3%82%8A%E7%B7%9A%E3%81%AE%E3%83%88%E3%83%B3%E3%83%8D%E3%83%AB","地図")</f>
         <v>地図</v>
       </c>
-      <c r="H74" s="8" t="s">
-        <v>404</v>
-      </c>
-      <c r="I74" s="7" t="n">
+      <c r="H75" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="I75" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J74" s="7"/>
-      <c r="K74" s="8" t="s">
-        <v>405</v>
-      </c>
-      <c r="L74" s="10" t="s">
+      <c r="J75" s="7"/>
+      <c r="K75" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="L75" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M74" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="N74" s="9" t="str">
+      <c r="M75" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="N75" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.tokyo-np.co.jp/article/522213","記事を開く")</f>
         <v>記事を開く</v>
       </c>
-      <c r="O74" s="8"/>
-      <c r="P74" s="8" t="n">
+      <c r="O75" s="8"/>
+      <c r="P75" s="8" t="n">
         <v>36.3</v>
       </c>
-      <c r="Q74" s="8" t="n">
+      <c r="Q75" s="8" t="n">
         <v>138.55</v>
       </c>
-      <c r="R74" s="8" t="s">
+      <c r="R75" s="8" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="14" t="s">
-        <v>407</v>
-      </c>
-      <c r="B76" s="14" t="str">
-        <f aca="false">COUNTA(D2:D74)&amp;"件"</f>
-        <v>73件</v>
-      </c>
-      <c r="H76" s="14" t="s">
-        <v>408</v>
-      </c>
-      <c r="I76" s="14" t="n">
-        <f aca="false">SUM(I2:I74)</f>
+    <row r="76" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="6" t="n">
+        <v>46313</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="E76" s="8" t="s">
+        <v>413</v>
+      </c>
+      <c r="F76" s="8" t="s">
+        <v>414</v>
+      </c>
+      <c r="G76" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E4%BD%90%E8%B3%80%E7%9C%8C%E5%94%90%E6%B4%A5%E5%B8%82%20%E4%B8%83%E5%B1%B1%E6%BB%9D%E5%B7%9D%20%E5%9B%BD%E9%81%93323%E5%8F%B7","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H76" s="8" t="s">
+        <v>415</v>
+      </c>
+      <c r="I76" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J76" s="7"/>
+      <c r="K76" s="8" t="s">
+        <v>416</v>
+      </c>
+      <c r="L76" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M76" s="11" t="s">
+        <v>417</v>
+      </c>
+      <c r="N76" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.web.nhk/newsweb/na/nd-20261018de61233","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O76" s="8"/>
+      <c r="P76" s="8" t="n">
+        <v>33.46</v>
+      </c>
+      <c r="Q76" s="8" t="n">
+        <v>130</v>
+      </c>
+      <c r="R76" s="8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="7" t="n">
         <v>76</v>
       </c>
-      <c r="J76" s="14" t="n">
-        <f aca="false">SUM(J2:J74)</f>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="15" t="s">
-        <v>409</v>
+      <c r="B77" s="6" t="n">
+        <v>46313</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D77" s="8" t="s">
+        <v>418</v>
+      </c>
+      <c r="E77" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="F77" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="G77" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%A4%A7%E5%88%86%E7%9C%8C%E4%B9%9D%E9%87%8D%E7%94%BA%20%E7%9C%8C%E9%81%93","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H77" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="I77" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J77" s="7"/>
+      <c r="K77" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="L77" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M77" s="11" t="s">
+        <v>422</v>
+      </c>
+      <c r="N77" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/890185c87cc74e63bd43395dd99a95cd45cb395a","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O77" s="8"/>
+      <c r="P77" s="8" t="n">
+        <v>33.18</v>
+      </c>
+      <c r="Q77" s="8" t="n">
+        <v>131.16</v>
+      </c>
+      <c r="R77" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="7" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="6" t="n">
+        <v>46313</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D78" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>423</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="G78" s="9" t="str">
+        <f aca="false">HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query=%E5%B1%B1%E5%BD%A2%E7%9C%8C%E9%95%B7%E4%BA%95%E5%B8%82%20%E4%BB%8A%E6%B3%89%20%E6%A2%A8%E9%83%B7%E9%81%93%E8%B7%AF%E3%81%A8%E5%9B%BD%E9%81%93113%E5%8F%B7%E3%81%AE%E4%BA%A4%E5%B7%AE%E7%82%B9","地図")</f>
+        <v>地図</v>
+      </c>
+      <c r="H78" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="I78" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J78" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K78" s="8" t="s">
+        <v>426</v>
+      </c>
+      <c r="L78" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M78" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="N78" s="9" t="str">
+        <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/fc7060ed6bc1bc89db77712712267f6ea82ee59b","記事を開く")</f>
+        <v>記事を開く</v>
+      </c>
+      <c r="O78" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="P78" s="8" t="n">
+        <v>38.095</v>
+      </c>
+      <c r="Q78" s="8" t="n">
+        <v>140.05</v>
+      </c>
+      <c r="R78" s="8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="14" t="s">
+        <v>429</v>
+      </c>
+      <c r="B80" s="14" t="str">
+        <f aca="false">COUNTA(D2:D78)&amp;"件"</f>
+        <v>77件</v>
+      </c>
+      <c r="H80" s="14" t="s">
+        <v>430</v>
+      </c>
+      <c r="I80" s="14" t="n">
+        <f aca="false">SUM(I2:I78)</f>
+        <v>81</v>
+      </c>
+      <c r="J80" s="14" t="n">
+        <f aca="false">SUM(J2:J78)</f>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="15" t="s">
+        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -12527,10 +13262,10 @@
         <v>18</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>410</v>
+        <v>432</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>411</v>
+        <v>433</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12538,11 +13273,11 @@
         <v>94</v>
       </c>
       <c r="B2" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A2)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A2)</f>
         <v>5</v>
       </c>
       <c r="C2" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A2,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A2,事故一覧!$I$2:$I$78)</f>
         <v>6</v>
       </c>
     </row>
@@ -12551,50 +13286,50 @@
         <v>88</v>
       </c>
       <c r="B3" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A3)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A3)</f>
         <v>1</v>
       </c>
       <c r="C3" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A3,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A3,事故一覧!$I$2:$I$78)</f>
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>412</v>
+        <v>434</v>
       </c>
       <c r="B4" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A4)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A4)</f>
         <v>0</v>
       </c>
       <c r="C4" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A4,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A4,事故一覧!$I$2:$I$78)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>413</v>
+        <v>435</v>
       </c>
       <c r="B5" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A5)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A5)</f>
         <v>0</v>
       </c>
       <c r="C5" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A5,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A5,事故一覧!$I$2:$I$78)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="B6" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A6)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A6)</f>
         <v>0</v>
       </c>
       <c r="C6" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A6,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A6,事故一覧!$I$2:$I$78)</f>
         <v>0</v>
       </c>
     </row>
@@ -12603,12 +13338,12 @@
         <v>147</v>
       </c>
       <c r="B7" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A7)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A7)</f>
+        <v>3</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A7,事故一覧!$I$2:$I$74)</f>
-        <v>2</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A7,事故一覧!$I$2:$I$78)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12616,11 +13351,11 @@
         <v>255</v>
       </c>
       <c r="B8" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A8)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A8)</f>
         <v>3</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A8,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A8,事故一覧!$I$2:$I$78)</f>
         <v>3</v>
       </c>
     </row>
@@ -12629,24 +13364,24 @@
         <v>106</v>
       </c>
       <c r="B9" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A9)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A9)</f>
         <v>2</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A9,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A9,事故一覧!$I$2:$I$78)</f>
         <v>2</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>415</v>
+        <v>437</v>
       </c>
       <c r="B10" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A10)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A10)</f>
         <v>0</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A10,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A10,事故一覧!$I$2:$I$78)</f>
         <v>0</v>
       </c>
     </row>
@@ -12655,11 +13390,11 @@
         <v>133</v>
       </c>
       <c r="B11" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A11)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A11)</f>
         <v>2</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A11,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A11,事故一覧!$I$2:$I$78)</f>
         <v>2</v>
       </c>
     </row>
@@ -12668,11 +13403,11 @@
         <v>180</v>
       </c>
       <c r="B12" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A12)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A12)</f>
         <v>5</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A12,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A12,事故一覧!$I$2:$I$78)</f>
         <v>5</v>
       </c>
     </row>
@@ -12681,11 +13416,11 @@
         <v>34</v>
       </c>
       <c r="B13" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A13)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A13)</f>
         <v>2</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A13,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A13,事故一覧!$I$2:$I$78)</f>
         <v>4</v>
       </c>
     </row>
@@ -12694,11 +13429,11 @@
         <v>348</v>
       </c>
       <c r="B14" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A14)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A14)</f>
         <v>1</v>
       </c>
       <c r="C14" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A14,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A14,事故一覧!$I$2:$I$78)</f>
         <v>1</v>
       </c>
     </row>
@@ -12707,11 +13442,11 @@
         <v>83</v>
       </c>
       <c r="B15" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A15)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A15)</f>
         <v>5</v>
       </c>
       <c r="C15" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A15,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A15,事故一覧!$I$2:$I$78)</f>
         <v>6</v>
       </c>
     </row>
@@ -12720,63 +13455,63 @@
         <v>196</v>
       </c>
       <c r="B16" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A16)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A16)</f>
         <v>3</v>
       </c>
       <c r="C16" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A16,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A16,事故一覧!$I$2:$I$78)</f>
         <v>3</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
-        <v>416</v>
+        <v>438</v>
       </c>
       <c r="B17" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A17)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A17)</f>
         <v>0</v>
       </c>
       <c r="C17" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A17,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A17,事故一覧!$I$2:$I$78)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="16" t="s">
-        <v>417</v>
+        <v>439</v>
       </c>
       <c r="B18" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A18)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A18)</f>
         <v>0</v>
       </c>
       <c r="C18" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A18,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A18,事故一覧!$I$2:$I$78)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="16" t="s">
-        <v>418</v>
+        <v>440</v>
       </c>
       <c r="B19" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A19)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A19)</f>
         <v>0</v>
       </c>
       <c r="C19" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A19,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A19,事故一覧!$I$2:$I$78)</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>419</v>
+        <v>441</v>
       </c>
       <c r="B20" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A20)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A20)</f>
         <v>0</v>
       </c>
       <c r="C20" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A20,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A20,事故一覧!$I$2:$I$78)</f>
         <v>0</v>
       </c>
     </row>
@@ -12785,11 +13520,11 @@
         <v>56</v>
       </c>
       <c r="B21" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A21)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A21)</f>
         <v>3</v>
       </c>
       <c r="C21" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A21,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A21,事故一覧!$I$2:$I$78)</f>
         <v>3</v>
       </c>
     </row>
@@ -12798,11 +13533,11 @@
         <v>156</v>
       </c>
       <c r="B22" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A22)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A22)</f>
         <v>3</v>
       </c>
       <c r="C22" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A22,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A22,事故一覧!$I$2:$I$78)</f>
         <v>3</v>
       </c>
     </row>
@@ -12811,11 +13546,11 @@
         <v>166</v>
       </c>
       <c r="B23" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A23)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A23)</f>
         <v>2</v>
       </c>
       <c r="C23" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A23,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A23,事故一覧!$I$2:$I$78)</f>
         <v>2</v>
       </c>
     </row>
@@ -12824,24 +13559,24 @@
         <v>75</v>
       </c>
       <c r="B24" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A24)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A24)</f>
+        <v>4</v>
+      </c>
+      <c r="C24" s="16" t="n">
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A24,事故一覧!$I$2:$I$78)</f>
         <v>3</v>
-      </c>
-      <c r="C24" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A24,事故一覧!$I$2:$I$74)</f>
-        <v>2</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="16" t="s">
-        <v>420</v>
+        <v>442</v>
       </c>
       <c r="B25" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A25)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A25)</f>
         <v>0</v>
       </c>
       <c r="C25" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A25,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A25,事故一覧!$I$2:$I$78)</f>
         <v>0</v>
       </c>
     </row>
@@ -12850,24 +13585,24 @@
         <v>245</v>
       </c>
       <c r="B26" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A26)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A26)</f>
         <v>1</v>
       </c>
       <c r="C26" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A26,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A26,事故一覧!$I$2:$I$78)</f>
         <v>1</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="16" t="s">
-        <v>421</v>
+        <v>443</v>
       </c>
       <c r="B27" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A27)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A27)</f>
         <v>0</v>
       </c>
       <c r="C27" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A27,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A27,事故一覧!$I$2:$I$78)</f>
         <v>0</v>
       </c>
     </row>
@@ -12876,11 +13611,11 @@
         <v>99</v>
       </c>
       <c r="B28" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A28)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A28)</f>
         <v>3</v>
       </c>
       <c r="C28" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A28,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A28,事故一覧!$I$2:$I$78)</f>
         <v>3</v>
       </c>
     </row>
@@ -12889,37 +13624,37 @@
         <v>50</v>
       </c>
       <c r="B29" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A29)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A29)</f>
         <v>7</v>
       </c>
       <c r="C29" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A29,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A29,事故一覧!$I$2:$I$78)</f>
         <v>7</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="16" t="s">
-        <v>422</v>
+        <v>444</v>
       </c>
       <c r="B30" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A30)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A30)</f>
         <v>0</v>
       </c>
       <c r="C30" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A30,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A30,事故一覧!$I$2:$I$78)</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="16" t="s">
-        <v>423</v>
+        <v>445</v>
       </c>
       <c r="B31" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A31)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A31)</f>
         <v>0</v>
       </c>
       <c r="C31" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A31,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A31,事故一覧!$I$2:$I$78)</f>
         <v>0</v>
       </c>
     </row>
@@ -12928,37 +13663,37 @@
         <v>143</v>
       </c>
       <c r="B32" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A32)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A32)</f>
         <v>2</v>
       </c>
       <c r="C32" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A32,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A32,事故一覧!$I$2:$I$78)</f>
         <v>2</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="16" t="s">
-        <v>424</v>
+        <v>446</v>
       </c>
       <c r="B33" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A33)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A33)</f>
         <v>0</v>
       </c>
       <c r="C33" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A33,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A33,事故一覧!$I$2:$I$78)</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="16" t="s">
-        <v>425</v>
+        <v>447</v>
       </c>
       <c r="B34" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A34)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A34)</f>
         <v>0</v>
       </c>
       <c r="C34" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A34,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A34,事故一覧!$I$2:$I$78)</f>
         <v>0</v>
       </c>
     </row>
@@ -12967,11 +13702,11 @@
         <v>120</v>
       </c>
       <c r="B35" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A35)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A35)</f>
         <v>4</v>
       </c>
       <c r="C35" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A35,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A35,事故一覧!$I$2:$I$78)</f>
         <v>4</v>
       </c>
     </row>
@@ -12980,24 +13715,24 @@
         <v>113</v>
       </c>
       <c r="B36" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A36)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A36)</f>
         <v>3</v>
       </c>
       <c r="C36" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A36,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A36,事故一覧!$I$2:$I$78)</f>
         <v>3</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="16" t="s">
-        <v>426</v>
+        <v>448</v>
       </c>
       <c r="B37" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A37)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A37)</f>
         <v>0</v>
       </c>
       <c r="C37" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A37,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A37,事故一覧!$I$2:$I$78)</f>
         <v>0</v>
       </c>
     </row>
@@ -13006,37 +13741,37 @@
         <v>261</v>
       </c>
       <c r="B38" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A38)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A38)</f>
         <v>2</v>
       </c>
       <c r="C38" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A38,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A38,事故一覧!$I$2:$I$78)</f>
         <v>2</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="16" t="s">
-        <v>427</v>
+        <v>449</v>
       </c>
       <c r="B39" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A39)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A39)</f>
         <v>0</v>
       </c>
       <c r="C39" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A39,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A39,事故一覧!$I$2:$I$78)</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="16" t="s">
-        <v>428</v>
+        <v>450</v>
       </c>
       <c r="B40" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A40)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A40)</f>
         <v>0</v>
       </c>
       <c r="C40" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A40,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A40,事故一覧!$I$2:$I$78)</f>
         <v>0</v>
       </c>
     </row>
@@ -13045,37 +13780,37 @@
         <v>43</v>
       </c>
       <c r="B41" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A41)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A41)</f>
         <v>4</v>
       </c>
       <c r="C41" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A41,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A41,事故一覧!$I$2:$I$78)</f>
         <v>4</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="16" t="s">
-        <v>429</v>
+        <v>412</v>
       </c>
       <c r="B42" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A42)</f>
-        <v>0</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A42)</f>
+        <v>1</v>
       </c>
       <c r="C42" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A42,事故一覧!$I$2:$I$74)</f>
-        <v>0</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A42,事故一覧!$I$2:$I$78)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="16" t="s">
-        <v>430</v>
+        <v>451</v>
       </c>
       <c r="B43" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A43)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A43)</f>
         <v>0</v>
       </c>
       <c r="C43" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A43,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A43,事故一覧!$I$2:$I$78)</f>
         <v>0</v>
       </c>
     </row>
@@ -13084,50 +13819,50 @@
         <v>206</v>
       </c>
       <c r="B44" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A44)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A44)</f>
         <v>2</v>
       </c>
       <c r="C44" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A44,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A44,事故一覧!$I$2:$I$78)</f>
         <v>2</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="16" t="s">
-        <v>431</v>
+        <v>418</v>
       </c>
       <c r="B45" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A45)</f>
-        <v>0</v>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A45)</f>
+        <v>1</v>
       </c>
       <c r="C45" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A45,事故一覧!$I$2:$I$74)</f>
-        <v>0</v>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A45,事故一覧!$I$2:$I$78)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="16" t="s">
-        <v>432</v>
+        <v>452</v>
       </c>
       <c r="B46" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A46)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A46)</f>
         <v>0</v>
       </c>
       <c r="C46" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A46,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A46,事故一覧!$I$2:$I$78)</f>
         <v>0</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="16" t="s">
-        <v>433</v>
+        <v>453</v>
       </c>
       <c r="B47" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A47)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A47)</f>
         <v>0</v>
       </c>
       <c r="C47" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A47,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A47,事故一覧!$I$2:$I$78)</f>
         <v>0</v>
       </c>
     </row>
@@ -13136,25 +13871,25 @@
         <v>150</v>
       </c>
       <c r="B48" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$D$2:$D$74,A48)</f>
+        <f aca="false">COUNTIF(事故一覧!$D$2:$D$78,A48)</f>
         <v>3</v>
       </c>
       <c r="C48" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$D$2:$D$74,A48,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$D$2:$D$78,A48,事故一覧!$I$2:$I$78)</f>
         <v>3</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="14" t="s">
-        <v>407</v>
+        <v>429</v>
       </c>
       <c r="B49" s="14" t="n">
         <f aca="false">SUM(B2:B48)</f>
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C49" s="14" t="n">
         <f aca="false">SUM(C2:C48)</f>
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -13173,7 +13908,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -13184,16 +13919,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>434</v>
+        <v>454</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>410</v>
+        <v>432</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>411</v>
+        <v>433</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13204,11 +13939,11 @@
         <v>33</v>
       </c>
       <c r="C2" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$74,A2)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$78,A2)</f>
         <v>2</v>
       </c>
       <c r="D2" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$74,A2,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$78,A2,事故一覧!$I$2:$I$78)</f>
         <v>4</v>
       </c>
     </row>
@@ -13220,11 +13955,11 @@
         <v>49</v>
       </c>
       <c r="C3" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$74,A3)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$78,A3)</f>
         <v>2</v>
       </c>
       <c r="D3" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$74,A3,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$78,A3,事故一覧!$I$2:$I$78)</f>
         <v>2</v>
       </c>
     </row>
@@ -13236,11 +13971,11 @@
         <v>63</v>
       </c>
       <c r="C4" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$74,A4)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$78,A4)</f>
         <v>5</v>
       </c>
       <c r="D4" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$74,A4,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$78,A4,事故一覧!$I$2:$I$78)</f>
         <v>5</v>
       </c>
     </row>
@@ -13252,11 +13987,11 @@
         <v>221</v>
       </c>
       <c r="C5" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$74,A5)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$78,A5)</f>
         <v>0</v>
       </c>
       <c r="D5" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$74,A5,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$78,A5,事故一覧!$I$2:$I$78)</f>
         <v>0</v>
       </c>
     </row>
@@ -13268,11 +14003,11 @@
         <v>93</v>
       </c>
       <c r="C6" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$74,A6)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$78,A6)</f>
         <v>3</v>
       </c>
       <c r="D6" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$74,A6,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$78,A6,事故一覧!$I$2:$I$78)</f>
         <v>3</v>
       </c>
     </row>
@@ -13284,11 +14019,11 @@
         <v>112</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$74,A7)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$78,A7)</f>
         <v>6</v>
       </c>
       <c r="D7" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$74,A7,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$78,A7,事故一覧!$I$2:$I$78)</f>
         <v>6</v>
       </c>
     </row>
@@ -13300,11 +14035,11 @@
         <v>146</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$74,A8)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$78,A8)</f>
         <v>2</v>
       </c>
       <c r="D8" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$74,A8,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$78,A8,事故一覧!$I$2:$I$78)</f>
         <v>2</v>
       </c>
     </row>
@@ -13316,11 +14051,11 @@
         <v>33</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$74,A9)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$78,A9)</f>
         <v>3</v>
       </c>
       <c r="D9" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$74,A9,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$78,A9,事故一覧!$I$2:$I$78)</f>
         <v>3</v>
       </c>
     </row>
@@ -13332,11 +14067,11 @@
         <v>49</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$74,A10)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$78,A10)</f>
         <v>3</v>
       </c>
       <c r="D10" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$74,A10,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$78,A10,事故一覧!$I$2:$I$78)</f>
         <v>3</v>
       </c>
     </row>
@@ -13348,11 +14083,11 @@
         <v>63</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$74,A11)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$78,A11)</f>
         <v>7</v>
       </c>
       <c r="D11" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$74,A11,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$78,A11,事故一覧!$I$2:$I$78)</f>
         <v>7</v>
       </c>
     </row>
@@ -13364,11 +14099,11 @@
         <v>221</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$74,A12)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$78,A12)</f>
         <v>1</v>
       </c>
       <c r="D12" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$74,A12,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$78,A12,事故一覧!$I$2:$I$78)</f>
         <v>1</v>
       </c>
     </row>
@@ -13380,11 +14115,11 @@
         <v>93</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$74,A13)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$78,A13)</f>
         <v>8</v>
       </c>
       <c r="D13" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$74,A13,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$78,A13,事故一覧!$I$2:$I$78)</f>
         <v>8</v>
       </c>
     </row>
@@ -13396,11 +14131,11 @@
         <v>112</v>
       </c>
       <c r="C14" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$74,A14)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$78,A14)</f>
         <v>6</v>
       </c>
       <c r="D14" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$74,A14,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$78,A14,事故一覧!$I$2:$I$78)</f>
         <v>6</v>
       </c>
     </row>
@@ -13412,11 +14147,11 @@
         <v>146</v>
       </c>
       <c r="C15" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$74,A15)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$78,A15)</f>
         <v>4</v>
       </c>
       <c r="D15" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$74,A15,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$78,A15,事故一覧!$I$2:$I$78)</f>
         <v>4</v>
       </c>
     </row>
@@ -13428,11 +14163,11 @@
         <v>33</v>
       </c>
       <c r="C16" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$74,A16)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$78,A16)</f>
         <v>5</v>
       </c>
       <c r="D16" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$74,A16,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$78,A16,事故一覧!$I$2:$I$78)</f>
         <v>5</v>
       </c>
     </row>
@@ -13444,11 +14179,11 @@
         <v>49</v>
       </c>
       <c r="C17" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$74,A17)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$78,A17)</f>
         <v>5</v>
       </c>
       <c r="D17" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$74,A17,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$78,A17,事故一覧!$I$2:$I$78)</f>
         <v>5</v>
       </c>
     </row>
@@ -13460,11 +14195,11 @@
         <v>63</v>
       </c>
       <c r="C18" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$74,A18)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$78,A18)</f>
         <v>4</v>
       </c>
       <c r="D18" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$74,A18,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$78,A18,事故一覧!$I$2:$I$78)</f>
         <v>4</v>
       </c>
     </row>
@@ -13476,11 +14211,11 @@
         <v>221</v>
       </c>
       <c r="C19" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$74,A19)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$78,A19)</f>
         <v>4</v>
       </c>
       <c r="D19" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$74,A19,事故一覧!$I$2:$I$74)</f>
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$78,A19,事故一覧!$I$2:$I$78)</f>
         <v>4</v>
       </c>
     </row>
@@ -13492,26 +14227,42 @@
         <v>93</v>
       </c>
       <c r="C20" s="16" t="n">
-        <f aca="false">COUNTIF(事故一覧!$B$2:$B$74,A20)</f>
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$78,A20)</f>
+        <v>4</v>
+      </c>
+      <c r="D20" s="16" t="n">
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$78,A20,事故一覧!$I$2:$I$78)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="17" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="C21" s="16" t="n">
+        <f aca="false">COUNTIF(事故一覧!$B$2:$B$78,A21)</f>
         <v>3</v>
       </c>
-      <c r="D20" s="16" t="n">
-        <f aca="false">SUMIF(事故一覧!$B$2:$B$74,A20,事故一覧!$I$2:$I$74)</f>
+      <c r="D21" s="16" t="n">
+        <f aca="false">SUMIF(事故一覧!$B$2:$B$78,A21,事故一覧!$I$2:$I$78)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="14" t="s">
-        <v>407</v>
-      </c>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14" t="n">
-        <f aca="false">SUM(C2:C20)</f>
-        <v>73</v>
-      </c>
-      <c r="D21" s="14" t="n">
-        <f aca="false">SUM(D2:D20)</f>
-        <v>76</v>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="14" t="s">
+        <v>429</v>
+      </c>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14" t="n">
+        <f aca="false">SUM(C2:C21)</f>
+        <v>77</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <f aca="false">SUM(D2:D21)</f>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -13554,10 +14305,10 @@
         <v>19</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>435</v>
+        <v>455</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>25</v>
@@ -13577,16 +14328,16 @@
         <v>56</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>437</v>
+        <v>457</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>438</v>
+        <v>458</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>439</v>
+        <v>459</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="G2" s="11" t="s">
         <v>61</v>
@@ -13604,16 +14355,16 @@
         <v>83</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>441</v>
+        <v>461</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>442</v>
+        <v>462</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>443</v>
+        <v>463</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>444</v>
+        <v>464</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>164</v>
@@ -13631,19 +14382,19 @@
         <v>83</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>445</v>
+        <v>465</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>446</v>
+        <v>466</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>439</v>
+        <v>459</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>447</v>
+        <v>467</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>448</v>
+        <v>468</v>
       </c>
       <c r="H4" s="9" t="str">
         <f aca="false">HYPERLINK("https://chunichi.co.jp/article/1321634","記事を開く")</f>
@@ -13658,16 +14409,16 @@
         <v>94</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>449</v>
+        <v>469</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>450</v>
+        <v>470</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>451</v>
+        <v>471</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>452</v>
+        <v>472</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>189</v>
@@ -13685,16 +14436,16 @@
         <v>94</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>453</v>
+        <v>473</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>454</v>
+        <v>474</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>455</v>
+        <v>475</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>456</v>
+        <v>476</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>194</v>
@@ -13712,16 +14463,16 @@
         <v>56</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>457</v>
+        <v>477</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>458</v>
+        <v>478</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>459</v>
+        <v>479</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="G7" s="11" t="s">
         <v>219</v>
@@ -13739,16 +14490,16 @@
         <v>166</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>461</v>
+        <v>481</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>462</v>
+        <v>482</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>463</v>
+        <v>483</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>464</v>
+        <v>484</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>333</v>
@@ -13766,19 +14517,19 @@
         <v>50</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>465</v>
+        <v>485</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>466</v>
+        <v>486</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>467</v>
+        <v>487</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>468</v>
+        <v>488</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>469</v>
+        <v>489</v>
       </c>
       <c r="H9" s="9" t="str">
         <f aca="false">HYPERLINK("https://kobe-np.co.jp/news/jiken/202610/0020910097.shtml","記事を開く")</f>
@@ -13793,19 +14544,19 @@
         <v>99</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>470</v>
+        <v>490</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>471</v>
+        <v>491</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>472</v>
+        <v>492</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>473</v>
+        <v>493</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>474</v>
+        <v>494</v>
       </c>
       <c r="H10" s="9" t="str">
         <f aca="false">HYPERLINK("https://www.jiji.com/jc/article?k=2026101000399&amp;g=soc","記事を開く")</f>
@@ -13820,16 +14571,16 @@
         <v>99</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>475</v>
+        <v>495</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>471</v>
+        <v>491</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>472</v>
+        <v>492</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>476</v>
+        <v>496</v>
       </c>
       <c r="G11" s="11" t="s">
         <v>61</v>
@@ -13847,19 +14598,19 @@
         <v>147</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>477</v>
+        <v>497</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>478</v>
+        <v>498</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>479</v>
+        <v>499</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>481</v>
+        <v>501</v>
       </c>
       <c r="H12" s="9" t="str">
         <f aca="false">HYPERLINK("https://news.yahoo.co.jp/articles/db9ea8f1740207802faad3b369c648aebc074777","記事を開く")</f>
@@ -13874,16 +14625,16 @@
         <v>50</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>482</v>
+        <v>502</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>483</v>
+        <v>503</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>484</v>
+        <v>504</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>485</v>
+        <v>505</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>338</v>
